--- a/faculty_unique_mesh_terms.xlsx
+++ b/faculty_unique_mesh_terms.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adaptation, Physiological; Australia; Authorship; Bacteria; Biodegradation, Environmental; Biological Evolution; Biomass; California; Carbon; Carbon Cycle; Climate; Climate Change; Communication; Conservation of Natural Resources; Coral Reefs; Curriculum; Drought Resistance; Droughts; Ecological and Environmental Phenomena; Ecosystem; Education, Graduate; Environmental Justice; Environmental Microbiology; Environmental Science; Enzymes; Extreme Weather; Financial Management; Forests; Genomics; Grassland; Greenhouse Gases; Humanities; Interdisciplinary Communication; Introduced Species; Isoptera; Life History Traits; Loma; Metagenome; Metagenomics; Methane; Microbial Interactions; Microbiota; Mutation; Nitrification; Nitrogen; Phylogeny; Plant Leaves; Plants; Policy; Policy Making; Program Evaluation; Resilience, Psychological; Skin Pigmentation; Social Sciences; Soil; Soil Microbiology; Sphingomonas; Stress, Physiological; Temperature; Trees; Tropical Climate; Uncertainty; Water; Wildfires; Wood; Workforce; Writing; nan</t>
+          <t>Adaptation, Physiological; Australia; Authorship; Bacteria; Biodegradation, Environmental; Biodiversity; Biological Evolution; Biomass; California; Carbon; Carbon Cycle; Climate; Climate Change; Communication; Conservation of Natural Resources; Coral Reefs; Curriculum; Drought Resistance; Droughts; Earth, Planet; Ecological and Environmental Phenomena; Ecosystem; Education, Graduate; Environmental Justice; Environmental Microbiology; Environmental Science; Enzymes; Extreme Weather; Feasibility Studies; Financial Management; Forests; Genomics; Government; Government Agencies; Grassland; Greenhouse Gases; Hot Temperature; Humanities; Interdisciplinary Communication; Interdisciplinary Research; Introduced Species; Isoptera; Life History Traits; Loma; Metagenome; Metagenomics; Methane; Microbial Interactions; Microbiota; Mutation; Needs Assessment; Nitrification; Nitrogen; Phylogeny; Plant Leaves; Plants; Policy; Policy Making; Private Sector; Program Evaluation; Resilience, Psychological; Risk Assessment; Skin Pigmentation; Social Planning; Social Sciences; Soil; Soil Microbiology; Sphingomonas; Stress, Physiological; Temperature; Trees; Tropical Climate; Uncertainty; Water; Wildfires; Wood; Workforce; Writing; nan</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Computational Biology; Developmental Biology; Genetics; Metabolism; Signal Transduction; Transforming Growth Factor beta</t>
+          <t>Binding Sites; CDC2 Protein Kinase; Cadmium; Caenorhabditis elegans; Caenorhabditis elegans Proteins; Cdc20 Proteins; Cell Line, Tumor; Cells, Cultured; Computational Biology; Conserved Sequence; Cyclin B; Cyclin B1; Cyclin B2; DNA-Binding Proteins; Developmental Biology; Embryo, Nonmammalian; Gene Expression Regulation; Genetics; HEK293 Cells; HeLa Cells; Hedgehog Proteins; Hippo Signaling Pathway; Homeostasis; Inactivation, Metabolic; MAP Kinase Signaling System; Metabolism; Mitogen-Activated Protein Kinase 1; Mitosis; Mutation; Neoplasms; Phosphorylation; Protein Binding; Protein Serine-Threonine Kinases; Repressor Proteins; Signal Transduction; Stress, Physiological; Transcription Factor MTF-1; Transcription Factors; Transcription, Genetic; Transforming Growth Factor beta; Tumor Suppressor Proteins; Zinc; Zinc Finger Protein GLI1</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Algorithms; Allografts; Binding Sites; Bioprinting; Brain; CRISPR-Cas Systems; Carcinogenesis; Carcinoma, Basal Cell; Carcinoma, Basosquamous; Cell Communication; Cell Differentiation; Cell Line, Tumor; Cell Proliferation; Cells, Cultured; Chromatography, Liquid; Clone Cells; Clustered Regularly Interspaced Short Palindromic Repeats; Computer Simulation; Conserved Sequence; Dermis; Drug Resistance; Ecosystem; Epidermal Cells; Epidermis; Epithelial Cells; Extrude; Gene Expression Profiling; Gene Regulatory Networks; Genes, Suppressor; Genetic Techniques; Hair Follicle; Hedgehog Proteins; Hedgehogs; HhAntag691; Immune System; Immunity; Immunotherapy; Intercellular Signaling Peptides and Proteins; Keratinocytes; Lung Neoplasms; MAP Kinase Signaling System; Membrane Proteins; Microphysiological Systems; Mitogen-Activated Protein Kinase 1; Molecular Biology; Multiomics; Mutation; Neoplasms; Neutrophil Activation; Neutrophils; Nucleosides; Organoids; Phosphorylation; Phosphotransferases; Pluripotent Stem Cells; Prostate; Protein Binding; Protein Kinase C; RNA; Repressor Proteins; Sebaceous Glands; Secretome; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Skin; Skin Neoplasms; Small Cell Lung Carcinoma; Stem Cells; T-Lymphocytes; Tandem Mass Spectrometry; Tissue Engineering; Transcription Factors; Transcriptome; Tumor Microenvironment; Wnt Signaling Pathway; Zinc Finger Protein GLI1; cemiplimab</t>
+          <t>Algorithms; Allografts; Binding Sites; Bioprinting; Brain; CRISPR-Cas Systems; Carcinogenesis; Carcinoma, Basal Cell; Carcinoma, Basosquamous; Cell Communication; Cell Differentiation; Cell Line, Tumor; Cell Proliferation; Cells, Cultured; Chromatography, Liquid; Clone Cells; Clustered Regularly Interspaced Short Palindromic Repeats; Computer Simulation; Conserved Sequence; Dermis; Drug Resistance; Ecosystem; Epidermal Cells; Epidermis; Epithelial Cells; Extrude; Gene Expression Profiling; Gene Regulatory Networks; Genes, Suppressor; Genetic Techniques; Hair Follicle; Hedgehog Proteins; Hedgehogs; HhAntag691; Immune System; Immunity; Immunotherapy; Intercellular Signaling Peptides and Proteins; Keratinocytes; Lung Neoplasms; MAP Kinase Signaling System; Membrane Proteins; Microphysiological Systems; Mitogen-Activated Protein Kinase 1; Molecular Biology; Multiomics; Mutation; Neoplasms; Neutrophil Activation; Neutrophils; Nucleosides; Organoids; Phosphorylation; Phosphotransferases; Pluripotent Stem Cells; Prostate; Protein Binding; Protein Kinase C; RNA; Repressor Proteins; Sebaceous Glands; Secretome; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Skin; Skin Neoplasms; Small Cell Lung Carcinoma; Stem Cells; T-Lymphocytes; Tandem Mass Spectrometry; Tissue Engineering; Transcription Factors; Transcriptome; Tumor Microenvironment; Wnt Signaling Pathway; Zinc Finger Protein GLI1; cemiplimab; nan</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Achilles Tendon; Aging; Alligators and Crocodiles; Anura; Biocompatible Materials; Biomechanical Phenomena; Biomimetic Materials; Bufo marinus; Connective Tissue; Conservation of Energy Resources; Elasticity; Elastomers; Electromyography; Environment; Exercise; Extremities; Forelimb; Gait; Galliformes; Hindlimb; Isometric Contraction; Locomotion; Lower Extremity; Motor Activity; Movement; Muscle Contraction; Muscle Fibers, Skeletal; Muscle Spindles; Muscle, Skeletal; Physics; Poaceae; Robotic Surgical Procedures; Robotics; Running; Sand; Stress, Mechanical; Swimming; Temperature; Tendons; Torque; Trees; Virtual Reality; Viscosity; Walking</t>
+          <t>Achilles Tendon; Aging; Alligators and Crocodiles; Anura; Biocompatible Materials; Biomechanical Phenomena; Biomimetic Materials; Bufo marinus; Connective Tissue; Conservation of Energy Resources; Elasticity; Elastomers; Electromyography; Environment; Exercise; Extremities; Forelimb; Gait; Galliformes; Hindlimb; Isometric Contraction; Locomotion; Lower Extremity; Motor Activity; Movement; Muscle Contraction; Muscle Fibers, Skeletal; Muscle Spindles; Muscle, Skeletal; Nonlinear Dynamics; Physics; Poaceae; Robotic Surgical Procedures; Robotics; Running; Sand; Stress, Mechanical; Swimming; Temperature; Tendons; Torque; Trees; Virtual Reality; Viscosity; Walking</t>
         </is>
       </c>
     </row>
@@ -494,11 +494,7 @@
           <t>Baker, Nicholas</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Anemia, Diamond-Blackfan; Aneuploidy; Basic Helix-Loop-Helix Transcription Factors; Carrier Proteins; Caspases; Cell Competition; Cullin Proteins; DNA-Binding Proteins; Drosophila Proteins; Drosophila melanogaster; Erythropoiesis; Eukaryotic Initiation Factor-2; Eye; Gene Expression Regulation, Developmental; Genes, Essential; Haploinsufficiency; Hematopoietic Stem Cells; Imaginal Discs; Larva; Mutation; Oncogenes; Pancytopenia; Phosphorylation; Photoreceptor Cells, Invertebrate; Protein Binding; Protein Biosynthesis; Proto-Oncogene Proteins; Puromycin; Receptors, Notch; Repressor Proteins; Ribosomal Proteins; Ribosomes; Shelterin Complex; Signal Transduction; Telomere-Binding Proteins; Transcription Factors; Tumor Suppressor Protein p53; Ubiquitin-Protein Ligases; Wnt1 Protein</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -532,7 +528,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Acetylation; Administration, Inhalation; Aged; Aging; Alleles; Alzheimer Disease; Amino Acid Sequence; Amyloid beta-Peptides; Amyloidogenic Proteins; Amyloidosis; Antibodies; Antibodies, Monoclonal; Apolipoprotein E3; Apolipoprotein E4; Apolipoproteins E; Astrocytes; Autoimmune Diseases; Biomarkers; Blood-Brain Barrier; Brain; Brain Injuries, Traumatic; Brain Neoplasms; Breast Neoplasms; C9orf72 Protein; Calcinosis; Calcium; Calcium Signaling; Caregivers; Cell Death; Cell Movement; Cell- and Tissue-Based Therapy; Cells, Cultured; Chemokines; Chemotaxis; Chimera; Cholesterol; Chromatin; Chromatin Immunoprecipitation Sequencing; Coculture Techniques; Cognition; Cognitive Dysfunction; Complement C1q; Contusions; Cyclic AMP; Cytokines; Dementia; Diabetes Mellitus; Diet; Disease Progression; Drug Development; Endoplasmic Reticulum; Endosomal Sorting Complexes Required for Transport; Endothelial Cells; Epigenesis, Genetic; Ferroptosis; Frontal Lobe; Frontotemporal Dementia; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genome-Wide Association Study; Genomics; Gliosis; Grassland; Hippocampus; Histones; Homeostasis; Housing Quality; Immunohistochemistry; Immunotherapy; Induced Pluripotent Stem Cells; Infant; Infant, Newborn; Inflammation; Inflammation Mediators; Injections, Intraperitoneal; Interferon-gamma; Interferons; Interleukin-17; Interleukin-1beta; Intermediate Filaments; Intracranial Hemorrhages; Isothiocyanates; Leukoencephalopathies; Lipid Metabolism; Lipid Peroxidation; Lipopolysaccharides; Liver Diseases; Lysosomes; Macrophage Colony-Stimulating Factor; Macrophages; Microglia; Microscopy; Microtubules; Mitochondria; Monocytes; Multiple Sclerosis; Mutation; Mycoses; Myelin Basic Protein; Myelin Sheath; Myeloid Cells; NF-E2-Related Factor 2; Nervous System Diseases; Nervous System Malformations; Neurites; Neurodegenerative Diseases; Neurofibrillary Tangles; Neuroinflammatory Diseases; Neurons; Neutrophils; Nucleotide Motifs; Obesity; Organelles; Organic Chemicals; Organoids; Outcome Assessment, Health Care; Oxidative Stress; Parkinson Disease; Patient Advocacy; Phagocytosis; Phenotype; Phosphorylation; Physicians; Pick Disease of the Brain; Plaque, Amyloid; Pluripotent Stem Cells; Presenilin-1; Prosencephalon; Protein Isoforms; Proteomics; Quantitative Trait Loci; RNA; Rare Diseases; Receptor, Macrophage Colony-Stimulating Factor; Receptors, Chimeric Antigen; Receptors, Granulocyte-Macrophage Colony-Stimulating Factor; Research Report; Resilience, Psychological; Risk Factors; Schizophrenia; Sequence Analysis, RNA; Sex Factors; Single-Cell Gene Expression Analysis; Social Cohesion; Stem Cell Research; Stem Cells; Sulfoxides; Synaptophysin; Tauopathies; Thalamus; Tissue Distribution; Toll-Like Receptor 4; Transcription Factors; Transcriptional Activation; Transcriptome; Transplantation, Heterologous; Treatment Outcome; Twins, Monozygotic; Weaning; White Matter; Whole Genome Sequencing; Xenon; anti-synaptophysin; heparin proteoglycan; peptide A; tau Proteins</t>
+          <t>Acetylation; Administration, Inhalation; Aged; Aging; Alleles; Alzheimer Disease; Amino Acid Sequence; Amyloid beta-Peptides; Amyloidogenic Proteins; Amyloidosis; Antibodies; Antibodies, Monoclonal; Apolipoprotein E3; Apolipoprotein E4; Apolipoproteins E; Astrocytes; Autoimmune Diseases; Biomarkers; Blood-Brain Barrier; Brain; Brain Neoplasms; Breast Neoplasms; C9orf72 Protein; Calcinosis; Calcium; Calcium Signaling; Caregivers; Cell Death; Cell Movement; Cell- and Tissue-Based Therapy; Cells, Cultured; Central Nervous System; Chemokines; Chemotaxis; Chimera; Cholesterol; Chromatin; Chromatin Immunoprecipitation Sequencing; Coculture Techniques; Cognition; Cognitive Dysfunction; Complement C1q; Cyclic AMP; Cytokines; Dementia; Diabetes Mellitus; Diet; Disease Progression; Drug Development; Endoplasmic Reticulum; Endosomal Sorting Complexes Required for Transport; Endothelial Cells; Epigenesis, Genetic; Ferroptosis; Frontal Lobe; Frontotemporal Dementia; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genome-Wide Association Study; Genomics; Gliosis; Grassland; Hepatitis A Virus Cellular Receptor 2; Hippocampus; Histones; Homeostasis; Housing Quality; Immunohistochemistry; Immunotherapy; Induced Pluripotent Stem Cells; Infant; Infant, Newborn; Inflammation; Inflammation Mediators; Injections, Intraperitoneal; Interferon-gamma; Interferons; Interleukin-17; Interleukin-1beta; Intermediate Filaments; Intracranial Hemorrhages; Isothiocyanates; Leukoencephalopathies; Lipid Metabolism; Lipid Peroxidation; Lipopolysaccharides; Liver Diseases; Lysosomes; Macrophage Colony-Stimulating Factor; Macrophages; Microglia; Microscopy; Microtubules; Mitochondria; Monocytes; Multiple Sclerosis; Mutation; Mycoses; Myelin Basic Protein; Myelin Sheath; Myeloid Cells; NF-E2-Related Factor 2; Neprilysin; Nervous System Diseases; Nervous System Malformations; Neurites; Neurodegenerative Diseases; Neurofibrillary Tangles; Neuroinflammatory Diseases; Neurons; Neutrophils; Nucleotide Motifs; Obesity; Organelles; Organic Chemicals; Organoids; Outcome Assessment, Health Care; Oxidative Stress; Parkinson Disease; Patient Advocacy; Phagocytosis; Phenotype; Phosphorylation; Physicians; Pick Disease of the Brain; Plaque, Amyloid; Pluripotent Stem Cells; Presenilin-1; Prosencephalon; Protein Isoforms; Proteomics; Quantitative Trait Loci; RNA; Rare Diseases; Receptor, Macrophage Colony-Stimulating Factor; Receptor, Transforming Growth Factor-beta Type II; Receptors, Chimeric Antigen; Receptors, Granulocyte-Macrophage Colony-Stimulating Factor; Research Report; Resilience, Psychological; Risk Factors; Schizophrenia; Sequence Analysis, RNA; Sex Factors; Signal Transduction; Single-Cell Gene Expression Analysis; Smad2 Protein; Social Cohesion; Stem Cell Research; Stem Cells; Sulfoxides; Synaptophysin; Tauopathies; Thalamus; Tissue Distribution; Toll-Like Receptor 4; Transcription Factors; Transcriptional Activation; Transcriptome; Transforming Growth Factor beta; Transplantation, Heterologous; Treatment Outcome; Twins, Monozygotic; Weaning; White Matter; Whole Genome Sequencing; Xenon; anti-synaptophysin; heparin proteoglycan; peptide A; tau Proteins</t>
         </is>
       </c>
     </row>
@@ -576,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aged; Aging; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Anhedonia; Antiviral Agents; Anxiety; Apathy; Atrophy; Basal Forebrain; Biomarkers; Biomedical Research; Blood-Brain Barrier; Body Fluids; Brain; COVID-19; Cellular Senescence; Checklist; Child; Cholinergic Agents; Chromosomes, Human, Pair 21; Cognition; Cognitive Dysfunction; Defense Mechanisms; Delusions; Depression; Diagnostic Errors; Down Syndrome; Extracellular Vesicles; Fetus; Gene Expression Profiling; Guanosine Triphosphate; Hallucinations; Human Genetics; Incidence; Inflammation; Interferons; Leadership; Live Birth; Longitudinal Studies; Membrane Proteins; Memory Disorders; Microglia; Mitochondria; Models, Genetic; Molecular Biology; Mutation; Nerve Degeneration; Nerve Growth Factor; Nervous System Diseases; Neurodegenerative Diseases; Neurofibrillary Tangles; Neuroinflammatory Diseases; Neurons; New York; Oxidative Stress; Peptides; Pharmaceutical Preparations; Plaque, Amyloid; Precision Medicine; Pregnancy; Probability; Protein Precursors; Proteomics; Psychiatrists; Quality of Life; RNA, Viral; Schizophrenia; Spain; Spinal Puncture; Tetraspanin 28; Trisomy; United States Food and Drug Administration; Vulnerable Populations; tau Proteins</t>
+          <t>Aged; Aging; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Aneuploidy; Anhedonia; Antiviral Agents; Anxiety; Apathy; Atrophy; Basal Forebrain; Biomarkers; Biomedical Research; Blood-Brain Barrier; Body Fluids; Brain; COVID-19; Cells, Cultured; Cellular Senescence; Cerebral Cortex; Checklist; Child; Cholinergic Agents; Chromosomes, Human, Pair 21; Cognition; Cognitive Dysfunction; Defense Mechanisms; Delusions; Depression; Diagnostic Errors; Down Syndrome; Extracellular Vesicles; Fetus; Gene Expression Profiling; Guanosine Triphosphate; Hallucinations; Human Genetics; Incidence; Inflammation; Interferons; Leadership; Live Birth; Longitudinal Studies; Membrane Proteins; Memory Disorders; Microglia; Mitochondria; Models, Genetic; Molecular Biology; Mutation; Nerve Degeneration; Nerve Growth Factor; Nervous System Diseases; Neurodegenerative Diseases; Neurofibrillary Tangles; Neuroinflammatory Diseases; Neurons; New York; Oxidative Stress; Peptides; Pharmaceutical Preparations; Plaque, Amyloid; Precision Medicine; Pregnancy; Probability; Protein Precursors; Proteomics; Psychiatrists; Quality of Life; RNA, Viral; SARS-CoV-2; Schizophrenia; Serine Endopeptidases; Spain; Spinal Puncture; Tetraspanin 28; Trisomy; United States Food and Drug Administration; Vulnerable Populations; tau Proteins</t>
         </is>
       </c>
     </row>
@@ -600,7 +596,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Acetylation; Biological Phenomena; Blastocyst; Blastula; Cadmium; Caenorhabditis elegans; Cell Differentiation; Cell Line, Tumor; Cell Lineage; Central Nervous System; Chromatin; Computational Biology; Congenital Abnormalities; Consensus Sequence; Curriculum; DNA; DNA-Binding Proteins; Developmental Biology; Ectoderm; Embryonic Development; Embryonic Structures; Endoderm; Endodermal Sinus Tumor; Epidermis; Epigenesis, Genetic; Epigenomics; Fertilization; Fetus; Forkhead Transcription Factors; Gastrula; Gastrulation; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Developmental; Gene Regulatory Networks; Genes, Developmental; Genome; Genomics; Germ Layers; HEK293 Cells; HeLa Cells; Hippo Signaling Pathway; Histone Deacetylase 1; Histone Deacetylase 2; Histone Deacetylases; Histones; Homeostasis; Inactivation, Metabolic; Lysine; Mesoderm; Multiomics; Mutation; N-Myc Proto-Oncogene Protein; Nervous System; Neural Tube; Neurulation; Nutrients; Phenotype; Phosphorylation; Pregnancy Complications; Preimplantation Diagnosis; Protein Binding; Protein Serine-Threonine Kinases; Proteomics; RNA; Regenerative Medicine; SOXB1 Transcription Factors; Sequence Analysis, RNA; Signal Transduction; Stem Cell Research; Stress, Physiological; Thinking; Transcription Factor MTF-1; Transcription Factors; Transcription, Genetic; Tumor Suppressor Proteins; Uterus; Xenopus; Xenopus Proteins; Xenopus laevis; Zinc; Zygote; animal cap</t>
+          <t>Acetylation; Adolescent; Aged; Aged, 80 and over; Biological Phenomena; Blastocyst; Blastula; Caenorhabditis elegans; Caregivers; Case-Control Studies; Cell Differentiation; Cell Lineage; Central Nervous System; Chromatin; Computational Biology; Congenital Abnormalities; Curriculum; Depression; Developmental Biology; Ectoderm; Educational Measurement; Embryo, Nonmammalian; Embryonic Development; Embryonic Structures; Endoderm; Endodermal Sinus Tumor; Epidermis; Epigenesis, Genetic; Epigenomics; Fertilization; Fetus; Forkhead Transcription Factors; Gastrula; Gastrulation; Gene Expression; Gene Expression Profiling; Gene Expression Regulation, Developmental; Gene Regulatory Networks; Genes, Developmental; Genome; Genomics; Germ Layers; Health Services Accessibility; Healthcare Disparities; Heart Failure; Histone Deacetylase 1; Histone Deacetylase 2; Histone Deacetylases; Histones; Insurance Coverage; International Cooperation; Kidney Failure, Chronic; Kidney Transplantation; Laboratories; Learning; Logistic Models; Lysine; Medicaid; Mesoderm; Multiomics; Mutation; N-Myc Proto-Oncogene Protein; Nervous System; Neural Tube; Neurulation; Nutrients; Ovarian Neoplasms; Phenotype; Pregnancy Complications; Preimplantation Diagnosis; Prodromal Symptoms; Prospective Studies; Proteomics; Psychotic Disorders; RNA; Regenerative Medicine; Risk Assessment; Risk Factors; SOXB1 Transcription Factors; Schizophrenia; Self Care; Sequence Analysis, RNA; Signal Transduction; Socioeconomic Disparities in Health; Socioeconomic Factors; Stem Cell Research; Thinking; Transcription Factors; Transcription, Genetic; Uterus; Xenopus; Xenopus Proteins; Xenopus laevis; Young Adult; Zygote; animal cap; nan</t>
         </is>
       </c>
     </row>
@@ -612,7 +608,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Adolescent; Alzheimer Disease; Artificial Intelligence; Brain; Cerebral Cortex; Cognition; Cognitive Neuroscience; Cognitive Science; Computer Simulation; Confusion; Depression; Diffusion Magnetic Resonance Imaging; Figural Aftereffect; Functional Neuroimaging; Gray Matter; Gyrus Cinguli; Head; Hippocampus; Individuality; Interpersonal Relations; Judgment; Learning; Magnetic Resonance Imaging; Maze Learning; Memory; Memory, Episodic; Menopause; Motion; Motion Perception; Neuroimaging; Neurons; Organ Size; Parietal Lobe; Pregnancy; Spatial Learning; Spatial Memory; Spatial Navigation; Temporal Lobe; Theta Rhythm; Virtual Reality; White Matter; Young Adult</t>
+          <t>Adolescent; Alzheimer Disease; Artificial Intelligence; Brain; Cerebral Cortex; Cognition; Cognitive Neuroscience; Cognitive Science; Computer Simulation; Confusion; Depression; Diffusion Magnetic Resonance Imaging; Exploratory Behavior; Figural Aftereffect; Functional Neuroimaging; Gray Matter; Gyrus Cinguli; Head; Hippocampus; Individuality; Interpersonal Relations; Judgment; Learning; Magnetic Resonance Imaging; Maze Learning; Memory; Memory, Episodic; Menopause; Motion; Motion Perception; Neuroimaging; Neurons; Organ Size; Parietal Lobe; Pregnancy; Sex Factors; Spatial Learning; Spatial Memory; Spatial Navigation; Temporal Lobe; Theta Rhythm; Virtual Reality; White Matter; Young Adult</t>
         </is>
       </c>
     </row>
@@ -624,7 +620,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aging; Artificial Intelligence; Cell Line; Chromatin Immunoprecipitation; Computational Biology; DNA Damage; Databases, Factual; Generative Artificial Intelligence; Genomics; Language; Large Language Models; Liquid Biopsy; Medicine; Mutation; Neoplasms; Noninvasive Prenatal Testing; Programming Languages; Software; Systems Biology; nan</t>
+          <t>Aging; Artificial Intelligence; Cell Line; Chromatin Immunoprecipitation; Computational Biology; Consensus; DNA Damage; Databases, Factual; Generative Artificial Intelligence; Genomics; Language; Large Language Models; Liquid Biopsy; Medicine; Mutation; Neoplasms; Noninvasive Prenatal Testing; Peer Review; Programming Languages; Software; Systems Biology</t>
         </is>
       </c>
     </row>
@@ -636,7 +632,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amino Acids; Amino Sugars; Anemia, Sickle Cell; Arabidopsis; Bacteria; Basic Helix-Loop-Helix Transcription Factors; Biological Products; Biological Science Disciplines; Brain; Cannabidiol; Cannabinoids; Cannabis; Carcinogens; Cell Adhesion; Cell Membrane; Cellular Senescence; Cerebral Hemorrhage; Chromatography, High Pressure Liquid; DNA, Satellite; Dronabinol; Drug Development; Drug Resistance, Microbial; Employment; Epigenesis, Genetic; Erythrocytes; Ethanol; Fertilizers; Flavonoids; Furunculosis; Gas Chromatography-Mass Spectrometry; Genomics; Genotype; Heinz Bodies; Helium; Hemoglobinopathies; Hemoglobins; Herbicides; Hispanic or Latino; Hydrogen; Hydrogen-Ion Concentration; Information Sources; Isotopes; Kinetics; Ligands; Lipids; Magnetic Resonance Imaging; Magnetic Resonance Spectroscopy; Magnets; Marijuana Use; Medical Marijuana; Membrane Proteins; Metabolome; Microbiota; Molecular Dynamics Simulation; Molecular Structure; Mutation; Myoglobin; Natural Science Disciplines; Neoplasms; Oryza; Oxides; Oxygen; Pesticides; Plant Extracts; Protein Binding; Protein Interaction Maps; Proteins; Recombinant Proteins; Seasons; Seeds; Sugars; Temperature; Terpenes; Water; beta-myrcene; caryophyllene oxide; voxelotor</t>
+          <t>Amino Acids; Amino Sugars; Anemia, Sickle Cell; Arabidopsis; Bacteria; Basic Helix-Loop-Helix Transcription Factors; Biological Products; Biological Science Disciplines; Brain; Cannabidiol; Cannabinoids; Cannabis; Carcinogens; Cell Adhesion; Cell Membrane; Cellular Senescence; Cerebral Hemorrhage; Chromatography, High Pressure Liquid; DNA, Satellite; Dronabinol; Drug Development; Drug Resistance, Microbial; Employment; Epigenesis, Genetic; Erythrocytes; Ethanol; Fertilizers; Flavonoids; Furunculosis; Gas Chromatography-Mass Spectrometry; Genomics; Genotype; Heinz Bodies; Helium; Hemoglobinopathies; Hemoglobins; Herbicides; Hispanic or Latino; Hydrogen; Hydrogen-Ion Concentration; Information Sources; Isotopes; Kinetics; Ligands; Lipids; Magnetic Resonance Imaging; Magnetic Resonance Spectroscopy; Magnets; Marijuana Use; Medical Marijuana; Membrane Proteins; Metabolome; Microbiota; Molecular Dynamics Simulation; Molecular Structure; Mutation; Myoglobin; Natural Science Disciplines; Neoplasms; Oryza; Oxides; Oxygen; Pesticides; Plant Extracts; Protein Binding; Protein Interaction Maps; Proteins; Recombinant Proteins; Seasons; Seeds; Sugars; Temperature; Terpenes; Water; beta-myrcene; caryophyllene oxide; nan; voxelotor</t>
         </is>
       </c>
     </row>
@@ -684,7 +680,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Air; Aircraft; Algorithms; Artificial Limbs; Avatar; Awards and Prizes; Behavior, Animal; Bioengineering; Biomechanical Phenomena; Biomimetics; Biophysics; Biotechnology; Birds; Cognition; Communication; Computer Simulation; Connective Tissue; Conservation of Energy Resources; Dancing; Elasticity; Elastomers; Electromyography; Environment; Exoskeleton Device; Extremities; Fellowships and Scholarships; Financial Management; Flight, Animal; Gait; Galliformes; Genomics; History, 20th Century; History, 21st Century; Information Dissemination; Interdisciplinary Research; Invertebrates; Isometric Contraction; Leadership; Leg; Locomotion; Motion; Motor Activity; Movement; Muscle Contraction; Muscle Proteins; Muscle, Skeletal; Muscles; Neuromuscular Diseases; Prostheses and Implants; Rats, Sprague-Dawley; Resilience, Psychological; Robotic Surgical Procedures; Robotics; Running; Schools; Self-Help Devices; Social Cohesion; Social Media; Spinal Cord; Sports; Stress, Mechanical; Tendons; Vertebrates; Viscosity; Walking; Wearable Electronic Devices; Wings, Animal; X-Ray Diffraction</t>
+          <t>Air; Aircraft; Algorithms; Artificial Limbs; Avatar; Awards and Prizes; Behavior, Animal; Bioengineering; Biomechanical Phenomena; Biomimetics; Biophysics; Biotechnology; Birds; Cognition; Communication; Computer Simulation; Connective Tissue; Conservation of Energy Resources; Dancing; Elasticity; Elastomers; Electromyography; Environment; Exoskeleton Device; Extremities; Fellowships and Scholarships; Financial Management; Flight, Animal; Gait; Galliformes; Genomics; History, 20th Century; History, 21st Century; Information Dissemination; Interdisciplinary Research; Invertebrates; Isometric Contraction; Leadership; Leg; Locomotion; Motion; Motor Activity; Movement; Muscle Contraction; Muscle Proteins; Muscle, Skeletal; Muscles; Neuromuscular Diseases; Prostheses and Implants; Rats, Sprague-Dawley; Resilience, Psychological; Robotic Surgical Procedures; Robotics; Running; Schools; Self-Help Devices; Social Cohesion; Social Media; Spinal Cord; Sports; Stress, Mechanical; Tendons; Vertebrates; Viscosity; Walking; Wearable Electronic Devices; Wings, Animal; X-Ray Diffraction; nan</t>
         </is>
       </c>
     </row>
@@ -708,7 +704,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Acyclovir; Antiviral Agents; Blister; COVID-19; CRISPR-Cas Systems; Cell Culture Techniques; Cell Line; Cell Nucleus; Chlorocebus aethiops; Cidofovir; Clustered Regularly Interspaced Short Palindromic Repeats; Cytomegalovirus; DNA Replication; DNA, Viral; DNA-Directed DNA Polymerase; Decitabine; Drug Repositioning; Drug Resistance, Viral; Drug Synergism; Encephalitis, Herpes Simplex; Epithelial Cells; Eukaryotic Cells; Fibroblasts; Ficus; Foscarnet; Gene Expression; Gene Expression Regulation; Gene Expression Regulation, Viral; Genes, Tumor Suppressor; Genome, Viral; HEK293 Cells; Hepatitis C, Chronic; Herpes Labialis; Herpes Simplex; Herpesviridae; Herpesviridae Infections; Herpesvirus 1, Equid; Herpesvirus 1, Human; Homeodomain Proteins; Host Microbial Interactions; Host-Pathogen Interactions; Immunocompromised Host; Infant, Newborn; Interferons; Kaposi Varicelliform Eruption; Keratinocytes; Keratitis, Herpetic; Life Cycle Stages; Machine Learning; Methylation; Microfluidics; Mutation; Myelodysplastic Syndromes; National Institute of Allergy and Infectious Diseases (U.S.); Organoids; Orthomyxoviridae; Pandemics; Phenotype; Prevalence; Protein Interaction Mapping; RNA; SARS-CoV-2; Sequence Analysis, RNA; Serial Passage; Simplexvirus; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Skin Diseases, Viral; Surgery, Plastic; Systems Biology; Thymidine Kinase; Transcription, Genetic; Transferases; Ulcer; Vero Cells; Viral Proteins; Virology; Virus Diseases; Virus Replication; Viruses; Zygote</t>
+          <t>Acyclovir; Antiviral Agents; Blister; COVID-19; CRISPR-Cas Systems; Cell Culture Techniques; Cell Line; Cell Nucleus; Chlorocebus aethiops; Cidofovir; Clustered Regularly Interspaced Short Palindromic Repeats; Cytomegalovirus; DNA Replication; DNA, Viral; DNA-Directed DNA Polymerase; Decitabine; Drug Repositioning; Drug Resistance, Viral; Drug Synergism; Encephalitis, Herpes Simplex; Epithelial Cells; Eukaryotic Cells; Fibroblasts; Ficus; Foscarnet; Gene Expression; Gene Expression Regulation; Gene Expression Regulation, Viral; Genes, Tumor Suppressor; Genome, Viral; HEK293 Cells; Hepatitis C, Chronic; Herpes Labialis; Herpes Simplex; Herpesviridae; Herpesviridae Infections; Herpesvirus 1, Equid; Herpesvirus 1, Human; Homeodomain Proteins; Host Microbial Interactions; Host-Pathogen Interactions; Immunocompromised Host; Infant, Newborn; Interferons; Kaposi Varicelliform Eruption; Keratinocytes; Keratitis, Herpetic; Life Cycle Stages; Machine Learning; Methylation; Microfluidics; Mutation; Myelodysplastic Syndromes; National Institute of Allergy and Infectious Diseases (U.S.); Organoids; Orthomyxoviridae; Pandemics; Phenotype; Prevalence; Protein Interaction Mapping; RNA; SARS-CoV-2; Sequence Analysis, RNA; Serial Passage; Simplexvirus; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Skin Diseases, Viral; Surgery, Plastic; Systems Biology; Thymidine Kinase; Transcription, Genetic; Transferases; Ulcer; Vero Cells; Viral Proteins; Virology; Virus Diseases; Virus Replication; Viruses; Zygote; nan</t>
         </is>
       </c>
     </row>
@@ -720,7 +716,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alleles; Allergy and Immunology; Amiloride; Aminopyridines; Asialoglycoprotein Receptor; Autophagy; Base Pairing; Biological Transport; COVID-19; COVID-19 Vaccines; CRISPR-Cas Systems; Cell Line, Tumor; Cell Membrane; Cell Proliferation; Class III Phosphatidylinositol 3-Kinases; Codon, Nonsense; Codon, Terminator; Cultural Diversity; Cytoplasm; Cytosol; Diet, High-Fat; Drug Resistance; Endocytosis; Endosomes; ErbB Receptors; Feasibility Studies; Ficus; Genomics; HeLa Cells; Hepatocytes; Heterocyclic Compounds, 3-Ring; Hot Temperature; Intercellular Signaling Peptides and Proteins; Karyopherins; Kidney; Kidney Glomerulus; Ligands; Lipid Nanoparticles; Liver; Lung; Lung Neoplasms; Lysosomes; Metabolism; Minority Groups; Mitochondria; Morpholines; Neoplasms; Nucleotides; Nutrients; Obesity; Oligonucleotides; Oligonucleotides, Antisense; Oncogenes; PTEN Phosphohydrolase; Phosphatidylinositol 3-Kinases; Phosphatidylinositols; Pinocytosis; Plague; Podocytes; Polypharmacology; Proof of Concept Study; Prostatic Neoplasms; Protein Phosphatase 2; Proto-Oncogene Proteins B-raf; Proto-Oncogene Proteins p21(ras); RNA, Small Interfering; Ribosomes; Saccharomyces cerevisiae; Schools; Sodium-Hydrogen Exchangers; Sphingolipids; Sphingosine; Transcription Factors; Tumor Microenvironment; Vacuolar Proton-Translocating ATPases; Vacuoles; patisiran</t>
+          <t>Alleles; Allergy and Immunology; Amiloride; Aminopyridines; Asialoglycoprotein Receptor; Autophagy; Base Pairing; Biological Transport; COVID-19; COVID-19 Vaccines; CRISPR-Cas Systems; Cell Line, Tumor; Cell Membrane; Cell Proliferation; Class III Phosphatidylinositol 3-Kinases; Codon, Nonsense; Codon, Terminator; Cultural Diversity; Cytoplasm; Cytosol; Diet, High-Fat; Drug Resistance; Endocytosis; Endosomes; ErbB Receptors; Feasibility Studies; Ficus; Genomics; HeLa Cells; Hepatocytes; Heterocyclic Compounds, 3-Ring; Hot Temperature; Intercellular Signaling Peptides and Proteins; Karyopherins; Kidney; Kidney Glomerulus; Ligands; Lipid Nanoparticles; Liver; Lung; Lung Neoplasms; Lysosomes; Metabolism; Minority Groups; Mitochondria; Morpholines; Neoplasms; Nucleotides; Nutrients; Obesity; Oligonucleotides; Oligonucleotides, Antisense; Oncogenes; PTEN Phosphohydrolase; Phosphatidylinositol 3-Kinases; Phosphatidylinositols; Pinocytosis; Plague; Podocytes; Polypharmacology; Proof of Concept Study; Prostatic Neoplasms; Protein Phosphatase 2; Proto-Oncogene Proteins B-raf; Proto-Oncogene Proteins p21(ras); RNA, Small Interfering; Ribosomes; Saccharomyces cerevisiae; Schools; Sodium-Hydrogen Exchangers; Sphingolipids; Sphingosine; Transcription Factors; Tumor Microenvironment; Vacuolar Proton-Translocating ATPases; Vacuoles; nan; patisiran</t>
         </is>
       </c>
     </row>
@@ -744,7 +740,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cell Communication; Cell Surface Extensions; Connexins; Diffusion; Drosophila Proteins; Endoderm; Extracellular Vesicles; Keratinocytes; Macrophages; Matrix Metalloproteinase 9; Muscles; Pigments, Biological; Pseudopodia; Signal Transduction; Zebrafish</t>
+          <t>Cell Communication; Cell Surface Extensions; Connexins; Diffusion; Drosophila Proteins; Endoderm; Extracellular Vesicles; Keratinocytes; Macrophages; Matrix Metalloproteinase 9; Muscles; Pigments, Biological; Pseudopodia; Signal Transduction; Zebrafish; nan</t>
         </is>
       </c>
     </row>
@@ -768,7 +764,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Academia; Acoustic Stimulation; Algorithms; Auditory Perception; Behavior; Brain; CA1 Region, Hippocampal; Cognition; Computers; Decision Making; Electrodes, Implanted; Electrophysiology; Government; Hippocampus; Leadership; Machine Learning; Memory; Memory, Episodic; Nerve Net; Odorants; Olfactory Perception; Planning Techniques; Prefrontal Cortex; Stereotaxic Techniques; Substance-Related Disorders; Technology; Theta Rhythm; Time; Time Factors</t>
+          <t>Academia; Acoustic Stimulation; Algorithms; Auditory Perception; Behavior; Brain; CA1 Region, Hippocampal; Cognition; Computers; Decision Making; Electrodes, Implanted; Electrophysiology; Government; Hippocampus; Leadership; Machine Learning; Memory; Memory, Episodic; Nerve Net; Odorants; Olfactory Perception; Planning Techniques; Prefrontal Cortex; Stereotaxic Techniques; Substance-Related Disorders; Technology; Theta Rhythm; Time; Time Factors; nan</t>
         </is>
       </c>
     </row>
@@ -780,7 +776,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adenosine Triphosphate; Administration, Inhalation; Adolescent; Aerosols; Alcohol Drinking; Alcoholism; Analgesics, Opioid; Antineoplastic Agents; Apoptosis; Behavior; Biomedical Research; Brain; Brain-Derived Neurotrophic Factor; Cannabidiol; Cannabis; Cell Line, Tumor; Cell Movement; Cell Proliferation; Cerebellar Neoplasms; Child; Cholinergic Neurons; Chromatin; Clustered Regularly Interspaced Short Palindromic Repeats; Cocaine; Cognition; Consummatory Behavior; Craving; Dopamine; Dopaminergic Neurons; Dronabinol; E-Cigarette Vapor; Eating; Electronic Nicotine Delivery Systems; Electrophysiology; Epigenesis, Genetic; Ethanol; Extracellular Vesicles; Eye Diseases; Genomics; Habenula; Learning; Lynx; Marketing; Mass Spectrometry; Medulloblastoma; Memory; Menthol; Mice; Microscopy; National Eye Institute (U.S.); Nicotine; Nicotinic Agonists; Nucleus Accumbens; Pregnancy; Prenatal Exposure Delayed Effects; Proteomics; Quality of Life; Rats, Sprague-Dawley; Receptor, Cannabinoid, CB1; Receptors, Nicotinic; Receptors, Purinergic P2; Recurrence; Rodentia; Self Administration; Sex Characteristics; Signal Transduction; Smoking; Smoking Cessation; Social Behavior; Social Environment; Substance Withdrawal Syndrome; Substance-Related Disorders; Synaptic Transmission; Therapeutics; Tobacco Products; Tobacco Use; Tobacco Use Cessation Devices; Tobacco Use Disorder; Ventral Tegmental Area; Vision, Ocular; Xenograft Model Antitumor Assays</t>
+          <t>Adenosine Triphosphate; Administration, Inhalation; Adolescent; Aerosols; Alcohol Drinking; Alcoholism; Analgesics, Opioid; Antineoplastic Agents; Apoptosis; Behavior; Biomedical Research; Brain; Brain-Derived Neurotrophic Factor; Cannabidiol; Cannabis; Cell Line, Tumor; Cell Movement; Cell Proliferation; Cerebellar Neoplasms; Child; Cholinergic Neurons; Chromatin; Clustered Regularly Interspaced Short Palindromic Repeats; Cocaine; Cognition; Consummatory Behavior; Craving; Dopamine; Dopaminergic Neurons; Dronabinol; E-Cigarette Vapor; Eating; Electronic Nicotine Delivery Systems; Electrophysiology; Epigenesis, Genetic; Ethanol; Extracellular Vesicles; Eye Diseases; Genomics; Habenula; Learning; Lynx; Marketing; Mass Spectrometry; Medulloblastoma; Memory; Menthol; Mice; Microscopy; National Eye Institute (U.S.); Nicotine; Nicotinic Agonists; Nucleus Accumbens; Pregnancy; Prenatal Exposure Delayed Effects; Proteomics; Quality of Life; Rats, Sprague-Dawley; Receptor, Cannabinoid, CB1; Receptors, Nicotinic; Receptors, Purinergic P2; Recurrence; Rodentia; Self Administration; Sex Characteristics; Signal Transduction; Smoking; Smoking Cessation; Social Behavior; Social Environment; Substance Withdrawal Syndrome; Substance-Related Disorders; Synaptic Transmission; Therapeutics; Tobacco Products; Tobacco Use; Tobacco Use Cessation Devices; Tobacco Use Disorder; Ventral Tegmental Area; Vision, Ocular; Xenograft Model Antitumor Assays; nan</t>
         </is>
       </c>
     </row>
@@ -840,7 +836,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Acclimatization; Adaptation, Physiological; Alkaline Phosphatase; Aminopeptidases; Amylases; Animal Husbandry; Biological Evolution; Body Size; Carnivory; Cellulases; Chromosomes; Cold Temperature; Diet; Diet, Food, and Nutrition; Dietary Fiber; Digestion; Digestive System Physiological Phenomena; Ecological and Environmental Phenomena; Ecosystem; Enzymes; Esters; Fermentation; Fires; Fishes; Gastrointestinal Microbiome; Gastropoda; Gene Expression Profiling; Genetics; Genome; Genomics; Heat-Shock Response; Leucine; Lipase; Lizards; Marine Biology; Microbiota; Mytilus; Pancreatic alpha-Amylases; Perciformes; Phylogeny; Physiology; RNA, Ribosomal, 16S; Reproducibility of Results; Stomach; Temperature; Transcriptome; Trypsin; Zebrafish; alpha-Glucosidases; nan</t>
+          <t>Acclimatization; Adaptation, Physiological; Alkaline Phosphatase; Alzheimer Disease; Aminopeptidases; Amylases; Animal Husbandry; Bays; Biological Evolution; Biomarkers; Body Size; California; Carbohydrates; Carboxylesterase; Carnivory; Cellulases; Chromosomes; Cold Temperature; Conservation of Natural Resources; DNA Copy Number Variations; Diet; Diet, Food, and Nutrition; Dietary Fiber; Digestion; Digestive System Physiological Phenomena; Disease Progression; Down Syndrome; Ecological and Environmental Phenomena; Ecosystem; Endangered Species; Enzymes; Esters; Fatty Acids, Essential; Fermentation; Fires; Fisheries; Fishes; Gametogenesis; Gastrointestinal Microbiome; Gastrointestinal Tract; Gastropoda; Gene Dosage; Gene Expression Profiling; Genetics; Genome; Genomics; Heat-Shock Response; Herbivory; Hydrogen-Ion Concentration; Hydrolysis; Immunohistochemistry; Leucine; Life Cycle Stages; Lipase; Lipids; Lizards; Macrocystis; Marine Biology; Mexico; Microalgae; Microbiota; Mytilus; Pancreatic alpha-Amylases; Parents; Perciformes; Phylogeny; Physiology; Protein Isoforms; Proteomics; RNA, Ribosomal, 16S; Reproducibility of Results; Reproduction; Stomach; Temperature; Transcriptome; Trypsin; Zebrafish; alpha-Glucosidases; nan; tau Proteins</t>
         </is>
       </c>
     </row>
@@ -852,7 +848,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Adipogenesis; Adipose Tissue; Allografts; Antiviral Agents; Artificial Intelligence; Cell Line; Cell Nucleus; Chromatin; DNA; DNA Damage; Deep Learning; Disease Outbreaks; Escherichia coli; Fascia; Human Embryonic Stem Cells; Immunity, Innate; Mass Spectrometry; Membrane Proteins; Morphogenesis; Mpox (monkeypox); Obesity; Phosphoric Monoester Hydrolases; Poxviridae; Protein Binding; Protein C; Proteome; Proteomics; Rodentia; Signal Transduction; Smallpox; Systems Biology; Technology; Transcription Factor 7-Like 1 Protein; Triple Negative Breast Neoplasms; Tumor Microenvironment; Vaccines; Vaccinia; Vaccinia virus; Viral Replication Compartments; Virion; Virology; Wnt Signaling Pathway</t>
+          <t>Adipogenesis; Adipose Tissue; Allografts; Antiviral Agents; Artificial Intelligence; Cell Differentiation; Cell Line; Cell Nucleus; Chromatin; DNA; DNA Damage; DNA-Binding Proteins; Deep Learning; Diabetes Mellitus, Experimental; Disease Outbreaks; Escherichia coli; Fascia; Glucose; Human Embryonic Stem Cells; Immunity, Innate; Insulin Secretion; Insulin-Secreting Cells; Ion Channels; Islets of Langerhans; Mass Spectrometry; Membrane Proteins; Morphogenesis; Mpox (monkeypox); Nuclear Proteins; Obesity; Organoids; Phosphoric Monoester Hydrolases; Pluripotent Stem Cells; Poxviridae; Protein Binding; Protein C; Proteome; Proteomics; Proto-Oncogene Mas; Rodentia; Signal Transduction; Smallpox; Systems Biology; Technology; Transcription Factor 7-Like 1 Protein; Transcription Factors; Transcriptome; Triple Negative Breast Neoplasms; Tumor Microenvironment; Vaccines; Vaccinia; Vaccinia virus; Viral Replication Compartments; Virion; Virology; Wnt Signaling Pathway; nan; src-Family Kinases</t>
         </is>
       </c>
     </row>
@@ -864,7 +860,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Adaptive Immunity; Aging; Algorithms; Allergy and Immunology; Alzheimer Disease; Amino Acids; Amyloid; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Amyloidogenic Proteins; Antibodies; Antibodies, Monoclonal; Antibody Specificity; Bacteriophages; Brain; Brain-Derived Neurotrophic Factor; CA1 Region, Hippocampal; Calcium; Cognition; Communicable Diseases; Congo Red; Energy Metabolism; Epitopes; Glutathione; High-Throughput Nucleotide Sequencing; Hypertension; Immunity; Immunity, Innate; Immunotherapy; Indicators and Reagents; Infant; Microglia; Neurodegenerative Diseases; Neurofibrillary Tangles; Peptides; Phosphatidylinositol-3,4,5-Trisphosphate 5-Phosphatases; Plaque, Amyloid; Pre-Eclampsia; Pregnancy; Protein Conformation, beta-Strand; Proteinuria; Serum Amyloid A Protein; Single-Domain Antibodies; Statistics, Nonparametric; Supranuclear Palsy, Progressive; Synucleins; Vaccines; Virulence; tau Proteins</t>
+          <t>Adaptive Immunity; Aging; Algorithms; Allergy and Immunology; Alzheimer Disease; Amino Acids; Amyloid; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Amyloidogenic Proteins; Antibodies; Antibodies, Monoclonal; Antibody Specificity; Autoantibodies; Bacteriophages; Brain; Brain-Derived Neurotrophic Factor; CA1 Region, Hippocampal; Calcium; Cognition; Communicable Diseases; Congo Red; Desmoglein 1; Desmoglein 3; Energy Metabolism; Epitopes; Glutathione; High-Throughput Nucleotide Sequencing; Hypertension; Immunity; Immunity, Innate; Immunotherapy; Indicators and Reagents; Infant; Keratinocytes; Microglia; Neurodegenerative Diseases; Neurofibrillary Tangles; Pemphigus; Peptides; Phosphatidylinositol-3,4,5-Trisphosphate 5-Phosphatases; Plaque, Amyloid; Pre-Eclampsia; Pregnancy; Protein Conformation, beta-Strand; Proteinuria; Receptor, Muscarinic M3; Serum Amyloid A Protein; Single-Domain Antibodies; Statistics, Nonparametric; Supranuclear Palsy, Progressive; Synucleins; Vaccines; Virulence; nan; tau Proteins</t>
         </is>
       </c>
     </row>
@@ -876,7 +872,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Algorithms; Anti-Bacterial Agents; Bacteriophages; Biochemistry; Conotoxins; Conus Snail; Cryoelectron Microscopy; Deep Learning; Eye; Genomics; Gram-Negative Bacterial Infections; Heart; Image Processing, Computer-Assisted; Ion Channel Gating; Kinetics; Membranes; Microscopy; Models, Molecular; Molecular Structure; Multiprotein Complexes; NAV1.8 Voltage-Gated Sodium Channel; Neoplasms; Peptides; Phage Therapy; Protein Binding; Protein Conformation; Protein Folding; Proteins; Spider Venoms; Stenotrophomonas maltophilia; Voltage-Gated Sodium Channel Blockers; Wastewater</t>
+          <t>Algorithms; Anti-Bacterial Agents; Bacteriophages; Biochemistry; Brain; Conotoxins; Conus Snail; Cryoelectron Microscopy; Deep Learning; Escherichia coli; Eye; Gastrointestinal Microbiome; Genomics; Gram-Negative Bacterial Infections; Heart; Image Processing, Computer-Assisted; Ion Channel Gating; Kinetics; Membranes; Microscopy; Models, Molecular; Molecular Structure; Multiprotein Complexes; NAV1.8 Voltage-Gated Sodium Channel; Neoplasms; Peptides; Phage Therapy; Protein Conformation; Protein Folding; Proteins; Spider Venoms; Stenotrophomonas maltophilia; Virion; Voltage-Gated Sodium Channel Blockers; Wastewater; Zebrafish; nan</t>
         </is>
       </c>
     </row>
@@ -900,7 +896,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ATP-Binding Cassette Transporters; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Apolipoproteins E; Astrocytes; Biomarkers; Bone Marrow; Brain; Brain Neoplasms; Brain-Derived Neurotrophic Factor; Breast Neoplasms; COVID-19; Cell Communication; Cell Nucleus; Cell Proliferation; Central Nervous System Diseases; Cognition; Coronavirus Infections; Cystatins; Demyelinating Diseases; Dendrimers; Disease Progression; Double-Blind Method; Down Syndrome; Gastrointestinal Microbiome; Gene Expression; Gene Expression Profiling; Gene Knock-In Techniques; Gene Regulatory Networks; Genes, fms; Genetic Variation; Genotype; Homeostasis; Immunotherapy; Integrases; Macrophage Colony-Stimulating Factor; Macrophages; Membrane Glycoproteins; Metabolomics; Microbiota; Microglia; Monocytes; Murine hepatitis virus; Mutation; Mutation, Missense; Myeloid Cells; NLR Family, Pyrin Domain-Containing 3 Protein; Nerve Degeneration; Nerve Regeneration; Neurites; Neuroglia; Neuroinflammatory Diseases; Neurons; Niacinamide; Pandemics; Phagocytosis; Phosphorylation; Plaque, Amyloid; Proof of Concept Study; Receptor, trkB; Receptors, Granulocyte-Macrophage Colony-Stimulating Factor; Receptors, Immunologic; Remyelination; Resilience, Psychological; Risk Factors; SARS-CoV-2; Sex Characteristics; Single-Cell Analysis; Synapses; Tauopathies; Transcriptome; Treatment Outcome; Trimethoprim; Vitamin B Complex; White Matter; tau Proteins</t>
+          <t>ATP-Binding Cassette Transporters; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Apolipoproteins E; Astrocytes; Biomarkers; Bone Marrow; Brain; Brain Neoplasms; Brain-Derived Neurotrophic Factor; Breast Neoplasms; Cell Communication; Cell Nucleus; Cell Proliferation; Central Nervous System Diseases; Cognition; Coronavirus Infections; Cystatins; Demyelinating Diseases; Dendrimers; Disease Progression; Double-Blind Method; Down Syndrome; Gastrointestinal Microbiome; Gene Expression; Gene Expression Profiling; Gene Knock-In Techniques; Gene Regulatory Networks; Genes, fms; Genetic Variation; Genotype; Homeostasis; Immunotherapy; Integrases; Macrophage Colony-Stimulating Factor; Macrophages; Membrane Glycoproteins; Metabolomics; Microbiota; Microglia; Monocytes; Murine hepatitis virus; Mutation; Mutation, Missense; Myeloid Cells; NLR Family, Pyrin Domain-Containing 3 Protein; Nerve Degeneration; Nerve Regeneration; Neurites; Neuroglia; Neuroinflammatory Diseases; Neurons; Niacinamide; Phagocytosis; Phosphorylation; Plaque, Amyloid; Proof of Concept Study; Receptor, trkB; Receptors, Granulocyte-Macrophage Colony-Stimulating Factor; Receptors, Immunologic; Resilience, Psychological; Sex Characteristics; Single-Cell Analysis; Synapses; Tauopathies; Transcriptome; Treatment Outcome; Trimethoprim; Vitamin B Complex; tau Proteins</t>
         </is>
       </c>
     </row>
@@ -912,7 +908,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Administration, Intravenous; Adolescent; Aged, 80 and over; Alleles; Antifungal Agents; Bias; Candidemia; Candidiasis, Invasive; Catalysis; Catalytic Domain; Chemistry, Bioinorganic; Child; Child, Preschool; Chloride Peroxidase; Cohort Studies; Coordination Complexes; Crystallography, X-Ray; Cytochrome P-450 Enzyme System; Cytochromes; Electron Spin Resonance Spectroscopy; Electron Transport; Electrons; Genetic Predisposition to Disease; Genome-Wide Association Study; Genomics; Heme; Hemeproteins; Infant; Iron; Ligands; Logistic Models; Metalloproteins; Metals; Models, Molecular; Nitrogenase; Oxidation-Reduction; Oxygen; Polymorphism, Single Nucleotide; Risk Factors; Schizophrenia; Serine; Spectrum Analysis, Raman; Thermodynamics; Treatment Outcome; Triazoles; X-Ray Absorption Spectroscopy</t>
+          <t>Administration, Intravenous; Adolescent; Algorithms; Anisotropy; Antifungal Agents; Bias; Bipolar Disorder; Black or African American; Brain; Candidiasis, Invasive; Catalysis; Catalytic Domain; Chemistry, Bioinorganic; Child; Child, Preschool; Chromosome Mapping; Climate Change; Cohort Studies; Cross-Sectional Studies; Crystallography, X-Ray; Cytochrome P-450 Enzyme System; Cytochromes; Diffusion Tensor Imaging; Ecosystem; Electron Transport; Electrons; Europe; Genetic Predisposition to Disease; Genetic Variation; Genome-Wide Association Study; Genomics; Gray Matter; Head; Hemeproteins; Hippocampus; Hispanic or Latino; Infant; Iron; Ligands; Machine Learning; Magnetic Resonance Imaging; Metalloproteins; Metals; Models, Molecular; Neoplasms; Neuroimaging; Nitrogen; North America; Organ Size; Oxidation-Reduction; Oxygen; Phenotype; Plant Development; Plant Leaves; Plant Physiological Phenomena; Plants; Polymorphism, Single Nucleotide; Reproducibility of Results; Schizophrenia; Schizophrenic Psychology; Signal Transduction; Snow; Spectrum Analysis, Raman; Thermodynamics; Thinking; Treatment Outcome; Triazoles; White; White Matter; White People; X-Ray Absorption Spectroscopy</t>
         </is>
       </c>
     </row>
@@ -924,7 +920,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Adenosine Triphosphate; Administration, Oral; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloidogenic Proteins; Antibodies, Monoclonal; Antibodies, Monoclonal, Humanized; Asian; Asian American Native Hawaiian and Pacific Islander; Autopsy; Biomarkers; Brain; California; Caregivers; Centers for Medicare and Medicaid Services, U.S.; Clinical Trials Data Monitoring Committees; Clinical Trials as Topic; Clinical Trials, Phase II as Topic; Cognitive Dysfunction; Cohort Studies; Control Groups; Dementia; Disclosure; Disease Management; Disease Progression; Double-Blind Method; Ethnicity; Exercise; Feasibility Studies; Hispanic or Latino; Insurance Coverage; Intermediate Filaments; Life Style; Longitudinal Studies; Magnetic Resonance Imaging; Medicaid; Medicare; Mental Status and Dementia Tests; Motivation; Niacinamide; Patient Selection; Philippines; Phosphorylation; Positron-Emission Tomography; Prognosis; Proof of Concept Study; Racial Groups; Randomized Controlled Trials as Topic; Registries; Republic of Korea; Research Subjects; Severity of Illness Index; Suicidal Ideation; Suicide; Surveys and Questionnaires; Treatment Outcome; Vitamin B Complex; nan; tau Proteins</t>
+          <t>Adenosine Triphosphate; Administration, Oral; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloidogenic Proteins; Anhedonia; Antibodies, Monoclonal; Antibodies, Monoclonal, Humanized; Anxiety; Apathy; Apolipoprotein E4; Asian; Asian American Native Hawaiian and Pacific Islander; Autopsy; Biomarkers; Brain; California; Caregivers; Checklist; Clinical Trials Data Monitoring Committees; Clinical Trials as Topic; Clinical Trials, Phase II as Topic; Cognition; Cognitive Dysfunction; Cohort Studies; Control Groups; Delusions; Dementia; Depression; Diagnostic Errors; Disclosure; Disease Management; Disease Progression; Double-Blind Method; Ethnicity; Feasibility Studies; Hallucinations; Hispanic or Latino; Intermediate Filaments; Leadership; Life Style; Longitudinal Studies; Magnetic Resonance Imaging; Memory Disorders; Mental Status and Dementia Tests; Motivation; Neurodegenerative Diseases; Niacinamide; Patient Selection; Philippines; Phosphorylation; Positron-Emission Tomography; Prognosis; Proof of Concept Study; Psychiatrists; Randomized Controlled Trials as Topic; Registries; Republic of Korea; Research Subjects; Schizophrenia; Severity of Illness Index; Spinal Puncture; Suicidal Ideation; Suicide; Surveys and Questionnaires; Treatment Outcome; Vitamin B Complex; tau Proteins</t>
         </is>
       </c>
     </row>
@@ -936,7 +932,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Adenosine Diphosphate; Adjuvants, Immunologic; Adjuvants, Pharmaceutic; Anti-Bacterial Agents; Anti-Infective Agents; Antimicrobial Cationic Peptides; Antimicrobial Peptides; Biological Transport; Biophysics; Brain; Cell Communication; Clostridioides; Clostridioides difficile; Computational Biology; Computer Simulation; Cytoskeleton; DNA; Diffusion; Dynactin Complex; Dyneins; Glycogen Synthase Kinase 3 beta; Histones; Kinesins; Kinetics; Lipid Droplets; Metronidazole; Microbiota; Microtubule-Associated Proteins; Microtubules; Molecular Motor Proteins; Motor Neuron Disease; Muscular Atrophy, Spinal; Mutation; Neurodegenerative Diseases; Neurons; Optical Tweezers; Organelles; Parkinson Disease; Protein Binding; Protein Conformation; Protein Processing, Post-Translational; Proteins; Saccharomyces cerevisiae; Tubulin; Vancomycin</t>
+          <t>Adenosine Diphosphate; Adjuvants, Immunologic; Adjuvants, Pharmaceutic; Anti-Bacterial Agents; Anti-Infective Agents; Antimicrobial Cationic Peptides; Antimicrobial Peptides; Biological Transport; Biophysics; Brain; Cell Communication; Cell Membrane; Clostridioides; Clostridioides difficile; Computational Biology; Computer Simulation; Cytoskeleton; DNA; Diffusion; Dynactin Complex; Dyneins; Escherichia coli; Glycogen Synthase Kinase 3 beta; Histones; Immunity, Innate; Kinesins; Kinetics; Lipid Droplets; Lipopolysaccharides; Metronidazole; Microbiota; Microtubule-Associated Proteins; Microtubules; Molecular Motor Proteins; Motor Neuron Disease; Muscular Atrophy, Spinal; Mutation; Neurodegenerative Diseases; Neurons; Optical Tweezers; Organelles; Parkinson Disease; Polymyxin B; Protein Binding; Protein Conformation; Protein Processing, Post-Translational; Proteins; Saccharomyces cerevisiae; Tubulin; Vancomycin</t>
         </is>
       </c>
     </row>
@@ -960,7 +956,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Agriculture; Anthropogenic Effects; Bacteria; Bees; Biodiversity; Biological Evolution; Coral Bleaching; Crithidia; Crops, Agricultural; DNA Contamination; Data Analysis; Disease Resistance; Dysbiosis; Ecological and Environmental Phenomena; Ecology; Ecosystem; Gastrointestinal Microbiome; Genetics; Health; Host Microbial Interactions; Human Activities; Insecta; Longevity; Magnolia; Metagenomics; Microbiota; Motivation; Parasites; Pollination; Quality Indicators, Health Care; RNA, Ribosomal, 16S; Reproduction; Schools; Seasons; Social Behavior; Social Interaction; Symbiosis</t>
+          <t>Agriculture; Anthropogenic Effects; Bacteria; Bees; Biodiversity; Biological Evolution; Coral Bleaching; Crithidia; Crops, Agricultural; DNA Contamination; Data Analysis; Diet; Disease Resistance; Dysbiosis; Ecological and Environmental Phenomena; Ecology; Ecosystem; Gastrointestinal Microbiome; Genetics; Health; Host Microbial Interactions; Human Activities; Insecta; Longevity; Magnolia; Metagenomics; Microbiota; Motivation; Parasites; Pollination; Quality Indicators, Health Care; RNA, Ribosomal, 16S; Reproduction; Schools; Seasons; Serratia marcescens; Social Behavior; Social Interaction; Symbiosis; nan</t>
         </is>
       </c>
     </row>
@@ -972,7 +968,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Adenosine Triphosphate; Aldehyde Oxidoreductases; Ammonia; Anaerobiosis; Azotobacter vinelandii; Bacterial Proteins; Biocatalysis; Bioreactors; Biosynthetic Pathways; Biotechnology; Carbon Dioxide; Carbon Monoxide; Catalysis; Chemistry, Bioinorganic; Ecosystem; Electrons; Enzymes; Escherichia coli; Evolution, Molecular; Formate Dehydrogenases; Gene Expression; Hydrocarbons; Hydrogen; Hydrogenase; Iron-Sulfur Proteins; Metalloproteins; Methyltransferases; Models, Molecular; Molybdenum; Molybdoferredoxin; Multienzyme Complexes; Nitrogen; Nitrogen Cycle; Nitrogen Fixation; Nitrogenase; Oxidation-Reduction; Oxidoreductases; Oxygen; Phylogeny; Recombinant Proteins; Rotation; S-Adenosylmethionine; Sulfur; Technology</t>
+          <t>Adenosine Triphosphate; Aged; Aged, 80 and over; Ammonia; Anaerobiosis; Animals, Genetically Modified; Azotobacter vinelandii; Bacterial Proteins; Biocatalysis; Biomarkers, Tumor; Bioreactors; Biosynthetic Pathways; Breast Neoplasms; Carbon Dioxide; Carbon Monoxide; Carcinoma, Non-Small-Cell Lung; Catalysis; Cell Line, Tumor; Chemistry, Bioinorganic; Chromosomes, Human, Pair 17; Circulating Tumor DNA; Drosophila Proteins; Drosophila melanogaster; Drug Carriers; Drug Delivery Systems; Drug Liberation; Drug Resistance, Neoplasm; Ecosystem; Electrons; Enzymes; ErbB Receptors; Escherichia coli; Evolution, Molecular; Exons; Gene Expression; Gold; Hydrocarbons; Hydrogen; Hydrogen Peroxide; Immunohistochemistry; In Situ Hybridization; Iron-Sulfur Proteins; Lactic Acid; Lung Neoplasms; Metal Nanoparticles; Metalloproteins; Mixed Function Oxygenases; Models, Molecular; Molybdenum; Molybdoferredoxin; Mutagenesis, Insertional; Nanoparticles; Neoplasms; Nitrogen; Nitrogen Cycle; Nitrogen Fixation; Nitrogenase; Oxidoreductases; Oxygen; Phylogeny; Prognosis; Protein Kinase Inhibitors; Receptor, ErbB-2; Retrospective Studies; Rotation; Silicon Dioxide; Sulfur; Technology; Transcription Factors; Warburg Effect, Oncologic</t>
         </is>
       </c>
     </row>
@@ -984,7 +980,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Adipogenesis; Adipose Tissue; Allografts; Alzheimer Disease; Anemia; Angiogenesis; Anxiety; Apolipoprotein E2; Apolipoprotein E4; Arteries; Arteriovenous Malformations; Astrocytes; Basement Membrane; Bayes Theorem; Biomarkers, Tumor; Biomimetics; Blood Vessels; Blood-Brain Barrier; Brain; Breast; Capillaries; Cell Line, Tumor; Cell- and Tissue-Based Therapy; Clustered Regularly Interspaced Short Palindromic Repeats; Coculture Techniques; Colonic Neoplasms; Colorectal Neoplasms; Cytoreduction Surgical Procedures; Diabetes Mellitus; Drug Development; Drug Evaluation; Drug Interactions; Drug Repositioning; Endoglin; Endothelial Cells; Endothelium, Vascular; Epistaxis; Exosomes; Extracellular Matrix; Fascia; Fibroblasts; Fluorouracil; Gene Expression; Glucose; Heart Failure; Huntington Disease; Hyperthermia, Induced; Hyperthermic Intraperitoneal Chemotherapy; Immunotherapy; Immunotherapy, Adoptive; Incidence; Induced Pluripotent Stem Cells; Infant; Insulin; Islets of Langerhans; Islets of Langerhans Transplantation; Lab-On-A-Chip Devices; Leucovorin; Liver; Lung; Microfluidics; Microglia; Microphysiological Systems; Microvessels; Mutation; Myocytes, Smooth Muscle; Neoadjuvant Therapy; Neoplasms; Neoplastic Processes; Neovascularization, Pathologic; Neurons; Obesity; Oxaliplatin; Paclitaxel; Pancreas; Pancreatic Neoplasms; Patient Advocacy; Pazopanib; Peptides; Pericytes; Peritoneal Cavity; Peritoneal Neoplasms; Peritoneum; Phenotype; Port-Wine Stain; Prospective Studies; RNA; Rare Diseases; Rodentia; Signal Transduction; Single-Cell Gene Expression Analysis; Snail Family Transcription Factors; Splenic Neoplasms; Stomach Neoplasms; Stroke; Stromal Cells; Sturge-Weber Syndrome; Survival Rate; Telangiectasia, Hereditary Hemorrhagic; Thrombosis; Tight Junctions; Tissue Engineering; Transcription Factors; Transcriptome; Transcytosis; Triple Negative Breast Neoplasms; Tumor Microenvironment; Vascular Malformations; cdc42 GTP-Binding Protein; nan; peptide I; rho GTP-Binding Proteins</t>
+          <t>Adipogenesis; Adipose Tissue; Allografts; Alzheimer Disease; Anemia; Angiogenesis; Anxiety; Apolipoprotein E2; Apolipoprotein E4; Arteries; Arteriovenous Malformations; Astrocytes; Basement Membrane; Bayes Theorem; Biomarkers, Tumor; Biomimetics; Blood Substitutes; Blood Vessels; Blood-Borne Pathogens; Blood-Brain Barrier; Brain; Breast; Capillaries; Cell Line, Tumor; Central Nervous System Diseases; Clustered Regularly Interspaced Short Palindromic Repeats; Coculture Techniques; Colonic Neoplasms; Colorectal Neoplasms; Cytoreduction Surgical Procedures; Diabetes Mellitus; Drug Development; Drug Evaluation; Drug Interactions; Drug Repositioning; Endoglin; Endothelial Cells; Endothelium, Vascular; Epistaxis; Exosomes; Extracellular Matrix; Fascia; Fibroblasts; Fluorouracil; Gene Expression; Glucose; Heart Failure; Huntington Disease; Hyperthermia, Induced; Hyperthermic Intraperitoneal Chemotherapy; Incidence; Induced Pluripotent Stem Cells; Infant; Insulin; Islets of Langerhans; Islets of Langerhans Transplantation; Lab-On-A-Chip Devices; Leucovorin; Liver; Lung; Microfluidics; Microglia; Microphysiological Systems; Microvessels; Mutation; Myocytes, Smooth Muscle; Neoadjuvant Therapy; Neoplasms; Neoplastic Processes; Neovascularization, Pathologic; Neurons; Obesity; Oxaliplatin; Paclitaxel; Pancreas; Pancreatic Neoplasms; Patient Advocacy; Pazopanib; Peptides; Pericytes; Peritoneal Cavity; Peritoneal Neoplasms; Peritoneum; Phenotype; Port-Wine Stain; Prospective Studies; RNA; Rare Diseases; Rodentia; Signal Transduction; Single-Cell Gene Expression Analysis; Sitting Position; Snail Family Transcription Factors; Splenic Neoplasms; Stomach Neoplasms; Stroke; Stromal Cells; Sturge-Weber Syndrome; Survival Rate; Technology; Telangiectasia, Hereditary Hemorrhagic; Thrombosis; Tight Junctions; Tissue Engineering; Transcription Factors; Transcriptome; Transcytosis; Triple Negative Breast Neoplasms; Tumor Microenvironment; Vascular Malformations; cdc42 GTP-Binding Protein; nan; peptide I; rho GTP-Binding Proteins</t>
         </is>
       </c>
     </row>
@@ -996,7 +992,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Biodiversity; Biomass; Carbon; Climate Change; Desert Climate; Ecological and Environmental Phenomena; Ecology; Ecosystem; Fertilizers; Grassland; Groundwater; Health Surveys; Humidity; Hydrology; Museums; Nitrogen; Nutrients; Phosphorus; Physiology, Comparative; Plants; Rain; Remote Sensing Technology; Soil; Temperature; Volunteers; Water; Water Resources; Water Supply; Wind</t>
+          <t>Biodiversity; Biomass; California; Carbon; Climate Change; Desert Climate; Ecological and Environmental Phenomena; Ecology; Ecosystem; Fertilizers; Grassland; Groundwater; Health Surveys; Humidity; Hydrology; Introduced Species; Museums; Nitrogen; Nutrients; Phosphorus; Physiology, Comparative; Plants; Rain; Remote Sensing Technology; Soil; Temperature; Volunteers; Water; Water Resources; Water Supply; Wind</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1028,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Adrenergic beta-Antagonists; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloidosis; Amyotrophic Lateral Sclerosis; Angiotensin-Converting Enzyme Inhibitors; Aniline Compounds; Apolipoproteins E; Atrophy; Autopsy; Biomarkers; Brain; Case-Control Studies; Cataract; Cell Separation; Centenarians; Cerebral Cortex; Cerebrovascular Circulation; Cerebrovascular Disorders; Clinical Trials as Topic; Cognition; Cognitive Dysfunction; Cohort Studies; Cryopreservation; DNA-Binding Proteins; Databases, Factual; Dementia; Dementia, Vascular; Diagnosis, Differential; Disease Progression; Educational Status; Epidemiology; Ethnicity; Ethylene Glycols; Executive Function; Extracellular Vesicles; Frailty; Frontotemporal Lobar Degeneration; Geriatric Assessment; Hand Strength; Hippocampal Sclerosis; Hippocampus; Incidence; Inclusion Bodies; Lewy Bodies; Lewy Body Disease; Life Style; Limbic System; Logistic Models; Longitudinal Studies; Magnetic Resonance Imaging; Medical History Taking; Nervous System Diseases; Neurofibrillary Tangles; Neuroglia; Neuroimaging; Neurons; Neuropathology; Neuropsychological Tests; Nonagenarians; Organ Size; Physical Functional Performance; Plaque, Amyloid; Positron-Emission Tomography; Public Health; RNA-Seq; Racial Groups; Reference Values; Resilience, Psychological; Retrospective Studies; Risk Factors; Self Report; Self-Help Devices; Sex Factors; Sleep; Sleep Duration; Syncope; TDP-43 Proteinopathies; Tauopathies; Walking Speed; White Matter</t>
+          <t>Adrenergic beta-Antagonists; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloidosis; Amyotrophic Lateral Sclerosis; Angiotensin-Converting Enzyme Inhibitors; Aniline Compounds; Apolipoproteins E; Atrophy; Autopsy; Biomarkers; Brain; Case-Control Studies; Cataract; Cell Separation; Centenarians; Cerebral Cortex; Cerebrovascular Circulation; Cerebrovascular Disorders; Clinical Trials as Topic; Cognition; Cognitive Dysfunction; Cohort Studies; Cryopreservation; DNA-Binding Proteins; Databases, Factual; Dementia; Dementia, Vascular; Diagnosis, Differential; Disease Progression; Educational Status; Epidemiology; Ethnicity; Ethylene Glycols; Executive Function; Extracellular Vesicles; Frailty; Frontotemporal Lobar Degeneration; Geriatric Assessment; Hand Strength; Hippocampus; Incidence; Inclusion Bodies; Lewy Bodies; Lewy Body Disease; Life Style; Limbic System; Longitudinal Studies; Magnetic Resonance Imaging; Medical History Taking; Nervous System Diseases; Neurofibrillary Tangles; Neuroglia; Neuroimaging; Neurons; Neuropsychological Tests; Nonagenarians; Organ Size; Physical Functional Performance; Plaque, Amyloid; Positron-Emission Tomography; Public Health; RNA-Seq; Racial Groups; Reference Values; Resilience, Psychological; Retrospective Studies; Risk Factors; Self Report; Self-Help Devices; Sex Factors; Sleep; Sleep Duration; Syncope; TDP-43 Proteinopathies; Tauopathies; Walking Speed; White Matter</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1038,11 @@
           <t>Kim, Seungsoo</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Academies and Institutes; Adolescent; Aged; Animals, Domestic; Antibodies, Monoclonal, Humanized; Antineoplastic Combined Chemotherapy Protocols; Attitude of Health Personnel; B7-H1 Antigen; Biomarkers, Tumor; Blepharoptosis; California; Cancer Care Facilities; Environmental Monitoring; Fertility; Fertility Preservation; Fluorocarbons; Fluorouracil; Genomics; Genotype; Interviews as Topic; Machine Learning; National Cancer Institute (U.S.); Neoplasms; Oncologists; Ophthalmic Solutions; Ophthalmology; Phenotype; Phenylephrine; Physician-Patient Relations; Platinum; Qualitative Research; Receptor, ErbB-2; Stomach Neoplasms; Transcriptome; Trastuzumab; Waste Disposal, Fluid; Wastewater; Water Pollutants, Chemical; Young Adult</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AMP-Activated Protein Kinases; Abdominal Cavity; Adenocarcinoma; Adenocarcinoma, Mucinous; Adenomatous Polyposis Coli; Adolescent; Allografts; Antineoplastic Agents; Appendectomy; Appendiceal Neoplasms; Ascitic Fluid; Biological Products; Cachexia; Carcinogenesis; Carcinoma; Catalytic Domain; Cell Cycle; Cell Differentiation; Cell Line; Cell Line, Tumor; Cell Plasticity; Cell Proliferation; Chemistry, Pharmaceutical; Chromatin; Chromatography, Liquid; Clinical Relevance; Colonic Neoplasms; Colorectal Neoplasms; Cost of Illness; Cytokines; Cytoreduction Surgical Procedures; DNA; Diabetes Mellitus; Diabetes Mellitus, Type 2; Diet, High-Fat; Diet, Ketogenic; Dietary Supplements; Dioxygenases; Drug Resistance, Neoplasm; Early Detection of Cancer; Epigenesis, Genetic; Epigenomics; Ficus; Gastrointestinal Neoplasms; Gene Expression; Gene Expression Regulation, Neoplastic; Genes, Tumor Suppressor; Genes, p16; Genetics; Glucose; Glutamine; Heterografts; High-Throughput Screening Assays; Histone Code; Histone Demethylases; Histone Methyltransferases; Histones; Homeostasis; Hospitalization; Hyperthermic Intraperitoneal Chemotherapy; Immunity; Immunotherapy; Incidence; Intestinal Mucosa; Isotopes; Ketoglutaric Acids; Ketone Bodies; Ketones; Lactic Acid; Lipid Metabolism; Lipids; Lipogenesis; Liquid Chromatography-Mass Spectrometry; Liver Neoplasms; Lubricants; Melanoma; Metabolic Diseases; Metabolic Networks and Pathways; Metabolism; Metformin; Micronutrients; Microscopy; Military Personnel; Monocarboxylic Acid Transporters; Morbidity; Muscles; Mutation; National Center for Advancing Translational Sciences (U.S.); Neoplasms; Neoplasms, Second Primary; Neoplastic Processes; Neoplastic Stem Cells; Nutrients; Obesity; Organoids; Ovarian Neoplasms; Oxidative Phosphorylation; PPAR gamma; Peptide Hydrolases; Peritoneal Cavity; Peritoneal Neoplasms; Peritoneum; Peroxisome Proliferator-Activated Receptors; Phenotype; Phosphoprotein Phosphatases; Phosphoric Monoester Hydrolases; Phosphorylation; Pilot Projects; Pioglitazone; Prevalence; Prostatic Neoplasms; Protein Phosphatase 2; Protein Serine-Threonine Kinases; Proteolysis; Pseudomyxoma Peritonei; Pyruvic Acid; Quality of Life; RNA; RNA, Long Noncoding; Rectal Neoplasms; Risk Factors; Sequence Analysis, RNA; Sex Characteristics; Sex Chromosomes; Signal Transduction; Standard of Care; Stem Cells; Substrate Specificity; T-Lymphocytes; TWEAK Receptor; Tandem Mass Spectrometry; Thiazolidinediones; Transcription Factors; Tumor Microenvironment; Vitamin A; Vitamin B 6; Vitamins; Weight Loss; Wnt Signaling Pathway; nan</t>
+          <t>AMP-Activated Protein Kinases; Abdominal Cavity; Adenocarcinoma; Adenocarcinoma, Mucinous; Adenomatous Polyposis Coli; Adolescent; Aged; Allografts; Antineoplastic Agents; Appendectomy; Appendiceal Neoplasms; Ascitic Fluid; Autoimmune Diseases; Biological Products; Cachexia; California; Carcinogenesis; Carcinoma; Catalytic Domain; Cell Cycle; Cell Differentiation; Cell Line; Cell Line, Tumor; Cell Plasticity; Cell Proliferation; Chemistry, Pharmaceutical; Chromatin; Chromatography, Liquid; Clinical Relevance; Colonic Neoplasms; Colorectal Neoplasms; Communication Barriers; Cost of Illness; Cytokines; Cytoreduction Surgical Procedures; DNA; Diabetes Mellitus; Diabetes Mellitus, Type 2; Diet, High-Fat; Diet, Ketogenic; Dietary Supplements; Dioxygenases; Drug Resistance, Neoplasm; Early Detection of Cancer; Epigenesis, Genetic; Epigenomics; Ficus; Gastrointestinal Neoplasms; Gene Expression; Gene Expression Regulation, Neoplastic; Genes, Tumor Suppressor; Genes, p16; Genetics; Glucose; Glutamine; Heterografts; High-Throughput Screening Assays; Histone Code; Histone Demethylases; Histone Methyltransferases; Histones; Homeostasis; Hospitalization; Hyperthermic Intraperitoneal Chemotherapy; Immunity; Immunoglobulin G; Immunoglobulin G4-Related Disease; Immunotherapy; Incidence; Intestinal Mucosa; Isotopes; Ketoglutaric Acids; Ketone Bodies; Ketones; Lactic Acid; Language; Lipid Metabolism; Lipids; Lipogenesis; Liquid Chromatography-Mass Spectrometry; Liver Neoplasms; Lubricants; Melanoma; Metabolic Diseases; Metabolic Networks and Pathways; Metabolism; Metformin; Micronutrients; Microscopy; Military Personnel; Monocarboxylic Acid Transporters; Morbidity; Muscles; Mutation; National Center for Advancing Translational Sciences (U.S.); Neoplasms; Neoplasms, Second Primary; Neoplastic Processes; Neoplastic Stem Cells; Nutrients; Obesity; Organoids; Ovarian Neoplasms; Oxidative Phosphorylation; PPAR gamma; Pancreas; Patient Preference; Peptide Hydrolases; Peritoneal Cavity; Peritoneal Neoplasms; Peritoneum; Peroxisome Proliferator-Activated Receptors; Phenotype; Phosphoprotein Phosphatases; Phosphoric Monoester Hydrolases; Phosphorylation; Pilot Projects; Pioglitazone; Positron Emission Tomography Computed Tomography; Prevalence; Prostatic Neoplasms; Protein Phosphatase 2; Protein Serine-Threonine Kinases; Proteolysis; Pseudomyxoma Peritonei; Pyruvic Acid; Qualitative Research; Quality of Life; RNA; RNA, Long Noncoding; Rectal Neoplasms; Risk Factors; Sequence Analysis, RNA; Sex Characteristics; Sex Chromosomes; Signal Transduction; Standard of Care; Stem Cells; Substrate Specificity; T-Lymphocytes; TWEAK Receptor; Tandem Mass Spectrometry; Thiazolidinediones; Transcription Factors; Tumor Microenvironment; Videoconferencing; Vitamin A; Vitamin B 6; Vitamins; Weight Loss; Wnt Signaling Pathway; nan</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,11 @@
           <t>Konieczny, Piotr</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1072,7 +1076,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Africa; Alleles; Animal Fins; Australia; Autism Spectrum Disorder; Autistic Disorder; Base Sequence; Brain; Brain Neoplasms; CCCTC-Binding Factor; CRISPR-Cas Systems; Cell Culture Techniques; Cell Cycle Proteins; Chromatin; Chromosomal Proteins, Non-Histone; Chromosomes; Chromosomes, Human, Pair 8; Clinical Relevance; Cohesins; Congenital Abnormalities; Craniofacial Abnormalities; DNA Transposable Elements; DNA, Intergenic; Ectopic Gene Expression; Enhancer Elements, Genetic; Epigenome; Epigenomics; Evolution, Molecular; Extinction, Biological; Extremities; Fetal Heart; Fishes; Gain of Function Mutation; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Developmental; Gene Rearrangement; Genes, Reporter; Genetic Variation; Genome; Genome Size; Genomics; Glioma; Heart Diseases; Hedgehog Proteins; Homeodomain Proteins; Intellectual Disability; Introns; Isocitrate Dehydrogenase; Karyotype; Limb Buds; Locomotion; Marsupialia; MicroRNAs; Mutation; Organoids; Otx Transcription Factors; Phenotype; Phylogeny; Piwi-Interacting RNA; Polydactyly; Polymorphism, Single Nucleotide; Promoter Regions, Genetic; RNA, Long Noncoding; Regulatory Sequences, Nucleic Acid; Single-Cell Analysis; South America; Time Factors; Transcription Factors; Transcriptional Activation; Virulence; Zinc Fingers</t>
+          <t>Africa; Alleles; Animal Fins; Australia; Autism Spectrum Disorder; Autistic Disorder; Base Sequence; Binding Sites; Brain; Brain Neoplasms; CCCTC-Binding Factor; CRISPR-Cas Systems; Cell Culture Techniques; Cell Cycle Proteins; Chromatin; Chromosomal Proteins, Non-Histone; Chromosomes; Chromosomes, Human, Pair 8; Clinical Relevance; Cohesins; Congenital Abnormalities; Craniofacial Abnormalities; DNA; DNA Transposable Elements; DNA, Intergenic; Ectopic Gene Expression; Enhancer Elements, Genetic; Epigenome; Epigenomics; Evolution, Molecular; Extinction, Biological; Extremities; Fetal Heart; Fishes; Gain of Function Mutation; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Developmental; Gene Rearrangement; Genes, Reporter; Genetic Code; Genetic Variation; Genome; Genome Size; Genomics; Glioma; Heart Diseases; Hedgehog Proteins; Homeodomain Proteins; Intellectual Disability; Introns; Isocitrate Dehydrogenase; Karyotype; Limb Buds; Locomotion; Marsupialia; MicroRNAs; Mutation; Nucleotide Motifs; Organoids; Otx Transcription Factors; Phenotype; Phylogeny; Piwi-Interacting RNA; Polydactyly; Polymorphism, Single Nucleotide; Promoter Regions, Genetic; Protein Binding; RNA, Long Noncoding; Regulatory Sequences, Nucleic Acid; SELEX Aptamer Technique; Single-Cell Analysis; South America; Time Factors; Transcription Factors; Transcriptional Activation; Virulence; Zinc Fingers</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1088,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ATP-Binding Cassette Transporters; Aged; Aged, 80 and over; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Apolipoproteins E; Asian; Astrocytes; Biomarkers; Brain; CRISPR-Associated Proteins; CRISPR-Cas Systems; Cathepsin D; Chromatin Immunoprecipitation Sequencing; Clustered Regularly Interspaced Short Palindromic Repeats; Cognition; Cuprizone; Data Management; Demyelinating Diseases; Disease Progression; Down Syndrome; Down-Regulation; Doxycycline; Endoribonucleases; Fibroblasts; Gastrointestinal Microbiome; Gene Editing; Gene Expression Profiling; Gene Expression Regulation; Gene Knock-In Techniques; Genetic Variation; Genome-Wide Association Study; Genotype; Glial Fibrillary Acidic Protein; HEK293 Cells; Hispanic or Latino; Induced Pluripotent Stem Cells; Laboratories; Leadership; Lipidomics; Longevity; Membrane Glycoproteins; Metabolome; Metabolomics; Microbiota; Microglia; Mobile Applications; Mutation; Myeloid Differentiation Factor 88; NF-kappa B; Neurodegenerative Diseases; Neuroglia; Neuroimaging; Neurons; Phagocytosis; Phenotype; Plaque, Amyloid; Proteomics; RNA Splicing; RNA-Seq; Receptors, Immunologic; Registries; Resilience, Psychological; Response Elements; Rodentia; Sex Characteristics; Signal Transduction; Single-Cell Gene Expression Analysis; Tauopathies; Tetracycline; Transcriptome; Translational Research, Biomedical; tau Proteins</t>
+          <t>ATP-Binding Cassette Transporters; Aged; Aged, 80 and over; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Apolipoproteins E; Asian; Astrocytes; Biomarkers; Brain; CRISPR-Associated Proteins; CRISPR-Cas Systems; Case-Control Studies; Cathepsin D; Chromatin Immunoprecipitation Sequencing; Chromosomes, Human, X; Clustered Regularly Interspaced Short Palindromic Repeats; Cognition; Cuprizone; Data Management; Demyelinating Diseases; Disease Progression; Down Syndrome; Down-Regulation; Doxycycline; Endoribonucleases; Fibroblasts; Gastrointestinal Microbiome; Gene Editing; Gene Expression Profiling; Gene Expression Regulation; Gene Knock-In Techniques; Genetic Predisposition to Disease; Genetic Variation; Genome-Wide Association Study; Genotype; Glial Fibrillary Acidic Protein; HEK293 Cells; Hispanic or Latino; Induced Pluripotent Stem Cells; Laboratories; Leadership; Lipidomics; Longevity; Membrane Glycoproteins; Metabolome; Metabolomics; Microbiota; Microglia; Mobile Applications; Mutation; Myeloid Differentiation Factor 88; NF-kappa B; Neurodegenerative Diseases; Neuroglia; Neuroimaging; Neurons; Phagocytosis; Phenotype; Plaque, Amyloid; Polymorphism, Single Nucleotide; Proteomics; RNA Splicing; RNA-Seq; Receptors, Immunologic; Registries; Resilience, Psychological; Response Elements; Rodentia; Sex Characteristics; Signal Transduction; Single-Cell Gene Expression Analysis; Tauopathies; Tetracycline; Transcriptome; Translational Research, Biomedical; X Chromosome Inactivation; tau Proteins</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1124,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Activin Receptors; Adiposity; Aged; Aging; Allergy and Immunology; Alzheimer Disease; Amino Acid Sequence; Amino Acids; Amyloid beta-Peptides; Angiotensin-Converting Enzyme 2; Animals, Genetically Modified; Anosmia; Apolipoprotein E4; Astrocytes; Axons; B-Lymphocytes; Bacterial Infections; Bone Marrow Transplantation; Brain; CD4 Antigens; CD4-Positive T-Lymphocytes; COVID-19; Catalytic Domain; Central Nervous System; Chemokine CXCL1; Cognition; Cognitive Dysfunction; Coronavirus; Coronavirus 3C Proteases; Coronavirus Infections; Crystallography, X-Ray; Cystatins; Cysteine; Cytokine Release Syndrome; Dementia; Demyelinating Diseases; Disease Progression; Disulfides; Dysgeusia; Encephalitis; Encephalitis, Viral; Encephalomyelitis, Autoimmune, Experimental; Forkhead Transcription Factors; Gene Expression; Gene Expression Profiling; Hashimoto's encephalitis; Headache; Human Embryonic Stem Cells; Immune System; Immunity; Immunity, Innate; Induced Pluripotent Stem Cells; Infant; Inflammation; Inflammation Mediators; Integrases; Ischemia; Lung; Lymphocyte Activation; Lysosomal Membrane Proteins; Macrophages; Matrix Metalloproteinase 9; Memory Consolidation; Meningitis; Mental Fatigue; Microglia; Mitochondrial Diseases; Models, Molecular; Monocytes; Monomeric GTP-Binding Proteins; Multiple Sclerosis; Murine hepatitis virus; Muscle, Skeletal; Mutation; Myelin Sheath; Neural Stem Cells; Neurodegenerative Diseases; Neuroglia; Neuroinflammatory Diseases; Neurons; Neutrophils; Oxidation-Reduction; Pandemics; Parkinson Disease; Plaque, Amyloid; Protein Multimerization; RNA, Messenger; RNA, Viral; Receptor Protein-Tyrosine Kinases; Remyelination; Risk Factors; Rodentia; SARS-CoV-2; Secretome; Sequence Analysis, RNA; Signal Transduction; Single Molecule Imaging; Spinal Cord; Stem Cells; Stroke; Sweden; Synaptic Transmission; T-Lymphocytes; T-Lymphocytes, Regulatory; Tetracyclines; Virus Diseases; Virus Replication; White Matter</t>
+          <t>Activin Receptors; Adiposity; Aged; Aging; Allergy and Immunology; Alzheimer Disease; Amino Acid Sequence; Amino Acids; Amyloid beta-Peptides; Aneuploidy; Angiotensin-Converting Enzyme 2; Animals, Genetically Modified; Anosmia; Apolipoprotein E4; Astrocytes; Axons; B-Lymphocytes; Bacterial Infections; Bone Marrow Transplantation; Brain; CD4 Antigens; CD4-Positive T-Lymphocytes; COVID-19; Catalytic Domain; Cells, Cultured; Central Nervous System; Cerebral Cortex; Chemokine CXCL1; Cognition; Cognitive Dysfunction; Coronavirus; Coronavirus 3C Proteases; Coronavirus Infections; Crystallography, X-Ray; Cystatins; Cysteine; Cytokine Release Syndrome; Dementia; Demyelinating Diseases; Disease Progression; Disulfides; Down Syndrome; Dysgeusia; Encephalitis; Encephalitis, Viral; Encephalomyelitis, Autoimmune, Experimental; Forkhead Transcription Factors; Gene Expression; Gene Expression Profiling; Hashimoto's encephalitis; Headache; Human Embryonic Stem Cells; Immune System; Immunity; Immunity, Innate; Induced Pluripotent Stem Cells; Infant; Inflammation; Inflammation Mediators; Integrases; Ischemia; Lung; Lymphocyte Activation; Lysosomal Membrane Proteins; Macrophages; Matrix Metalloproteinase 9; Memory Consolidation; Meningitis; Mental Fatigue; Microglia; Mitochondrial Diseases; Models, Molecular; Monocytes; Monomeric GTP-Binding Proteins; Multiple Sclerosis; Murine hepatitis virus; Muscle, Skeletal; Mutation; Myelin Sheath; Neural Stem Cells; Neurodegenerative Diseases; Neuroglia; Neuroinflammatory Diseases; Neurons; Neutrophils; Oxidation-Reduction; Pandemics; Parkinson Disease; Plaque, Amyloid; Protein Multimerization; RNA, Messenger; RNA, Viral; Receptor Protein-Tyrosine Kinases; Remyelination; Risk Factors; Rodentia; SARS-CoV-2; Secretome; Sequence Analysis, RNA; Serine Endopeptidases; Signal Transduction; Single Molecule Imaging; Spinal Cord; Stem Cells; Stroke; Sweden; Synaptic Transmission; T-Lymphocytes; T-Lymphocytes, Regulatory; Tetracyclines; Virus Diseases; Virus Replication; White Matter</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1136,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Aging; Anaphase-Promoting Complex-Cyclosome; CDC2 Protein Kinase; Caenorhabditis elegans; Caenorhabditis elegans Proteins; Cdc20 Proteins; Cell Cycle; Cell Cycle Checkpoints; Cell Cycle Proteins; Cell Differentiation; Cell Proliferation; Centers for Disease Control and Prevention, U.S.; Clustered Regularly Interspaced Short Palindromic Repeats; Cues; Cyclin B; Cyclin B1; Cyclin B2; Cyclins; Embryo, Nonmammalian; Embryonic Development; Ependymoglial Cells; Genomics; Germ Cells; Kinetochores; M Phase Cell Cycle Checkpoints; Microscopy; Microtubule-Associated Proteins; Mitosis; Neocortex; Neoplasms; Phosphorylation; Protein Serine-Threonine Kinases; Repressor Proteins; Spindle Apparatus; Tetratricopeptide Repeat; nan</t>
+          <t>Aging; Anaphase-Promoting Complex-Cyclosome; Antineoplastic Agents; CDC2 Protein Kinase; Caenorhabditis elegans; Caenorhabditis elegans Proteins; Cdc20 Proteins; Cell Cycle; Cell Cycle Checkpoints; Cell Cycle Proteins; Cell Differentiation; Cell Proliferation; Centers for Disease Control and Prevention, U.S.; Chromosome Segregation; Clustered Regularly Interspaced Short Palindromic Repeats; Cues; Cyclin B; Cyclin B1; Cyclin B2; Cyclins; Embryo, Nonmammalian; Embryonic Development; Ependymoglial Cells; Genomics; Germ Cells; Kinetochores; M Phase Cell Cycle Checkpoints; Microscopy; Microtubule-Associated Proteins; Mitosis; Neocortex; Neoplasms; Phosphorylation; Protein Serine-Threonine Kinases; Repressor Proteins; Spindle Apparatus; Tetratricopeptide Repeat; nan</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1148,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Absorptiometry, Photon; Adipocytes; Aged; Amyotrophic Lateral Sclerosis; Asian; Base Sequence; Biological Evolution; Body Mass Index; Bone Density; Bone Diseases, Metabolic; COVID-19; COVID-19 Drug Treatment; Cell Differentiation; Chromatin; Chromosomes; Cricetinae; DNA; DNA Transposable Elements; Diet; Drug-Related Side Effects and Adverse Reactions; Early Detection of Cancer; East Asian People; Eating; Ecological and Environmental Phenomena; Epidermis; Epigenesis, Genetic; Epigenome; Epigenomics; Eukaryotic Cells; Evolution, Molecular; Fabry Disease; Fatty Acid-Binding Proteins; Fellowships and Scholarships; Femur Neck; Fertility; Frontotemporal Dementia; Gene Expression Profiling; Genetics; Genetics, Population; Genome; Genome, Human; Genomic Instability; Genomics; Health; Health Status; Heterochromatin; Keratinocytes; Lung; Multiomics; Mutation; Neoplasms; Nutrients; Obesity; Obesity, Abdominal; Organoids; Osteitis Deformans; Osteoporosis; Parasites; Pharmaceutical Preparations; RNA; Retroelements; Risk Factors; SARS-CoV-2; Sequence Homology; Skin; Sleep Apnea Syndromes; Social Responsibility; Species Specificity; Surveys and Questionnaires; Tetraodontiformes; Transcriptome; Urodela; Valosin Containing Protein; Virus Replication; Waist-Hip Ratio</t>
+          <t>Absorptiometry, Photon; Adenosine; Adipocytes; Aged; Alternative Splicing; Anti-Bacterial Agents; Antigens, CD; Base Sequence; Bile Acids and Salts; Biological Evolution; Biomarkers; Bone Density; Bone Diseases, Metabolic; Brain; Breast Neoplasms; COVID-19; COVID-19 Drug Treatment; Cadherins; Caenorhabditis elegans; Caenorhabditis elegans Proteins; Cell Death; Cell Line, Tumor; Cell Movement; Cell Proliferation; Chromatin; Chromosomes; Colonic Neoplasms; Cricetinae; DNA; DNA Transposable Elements; DNA-Binding Proteins; Diet; Disease Progression; Drug-Related Side Effects and Adverse Reactions; Dysbiosis; Early Detection of Cancer; Eating; Ecological and Environmental Phenomena; Epigenesis, Genetic; Epigenome; Epigenomics; Epithelial-Mesenchymal Transition; Eukaryotic Cells; Evolution, Molecular; Eye Neoplasms; Fabry Disease; Fatty Acid-Binding Proteins; Fatty Liver; Fellowships and Scholarships; Femur Neck; Fertility; Fructose; Gastrointestinal Microbiome; Gene Expression Profiling; Genetics; Genetics, Population; Genome; Genome, Human; Genomic Instability; Genomics; HEK293 Cells; Health; Heterochromatin; Huntingtin Protein; Huntington Disease; Lipogenesis; Lipopolysaccharides; Liver; Longevity; Lung; Mechanistic Target of Rapamycin Complex 1; Methyltransferases; Mevalonic Acid; Mice, Nude; Multiomics; Multiprotein Complexes; Necroptosis; Neoplasm Metastasis; Neoplasms; Non-alcoholic Fatty Liver Disease; Nuclear Proteins; Nutrients; Ophthalmologic Surgical Procedures; Orbital Implants; Osteoporosis; Oxidative Stress; Parasites; Pharmaceutical Preparations; Phosphoglycerate Dehydrogenase; Phosphorylation; Proteasome Endopeptidase Complex; Protein Binding; Protein Stability; Proteolysis; RNA; RNA Methylation; RNA Splicing; RNA, Messenger; Receptor-Interacting Protein Serine-Threonine Kinases; Repressor Proteins; Retroelements; Ribosomal Protein S6 Kinases, 70-kDa; SARS-CoV-2; Sequence Homology; Serine; Signal Transduction; Social Responsibility; Species Specificity; TOR Serine-Threonine Kinases; Tetraodontiformes; Transcriptome; Ubiquitin; Ubiquitin-Protein Ligases; Ubiquitination; Urodela; Virus Replication; nan</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1160,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AIDS Dementia Complex; Acquired Immunodeficiency Syndrome; Adaptive Immunity; Adaptor Proteins, Signal Transducing; Allergy and Immunology; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Anti-Infective Agents; Antigen Presentation; Astrocytes; Blood Coagulation; Blood-Brain Barrier; Brain; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Capparis; Caspase 1; Caspase 8; Caspases; Cell Death; Cell Membrane; Cell Proliferation; Central Nervous System; Central Nervous System Infections; Cerebrovascular Circulation; Chemokine CCL2; Chemokines; Clustered Regularly Interspaced Short Palindromic Repeats; Coculture Techniques; Cognition; Coinfection; Communicable Disease Control; Cytokines; Dendritic Cells; Encephalitis; Endothelial Cells; Fibrin; Gasdermins; Gene Regulatory Networks; HIV Infections; Heart Transplantation; Hemodynamics; Hippo Signaling Pathway; Host-Parasite Interactions; Host-Pathogen Interactions; Immunity; Immunity, Innate; Induced Pluripotent Stem Cells; Infections; Inflammasomes; Inflammation; Inflammation Mediators; Intercellular Adhesion Molecule-1; Interleukin-1beta; Ion Channels; Lipoproteins; Liver; Macrophages; Mechanotransduction, Cellular; Memory T Cells; Metabolic Diseases; Microglia; Microscopy; Microvessels; Monocytes; Myeloid Cells; NF-kappa B; NLR Family, Pyrin Domain-Containing 3 Protein; Necroptosis; Neoplasm Recurrence, Local; Neurodegenerative Diseases; Neuroimaging; Neuroinflammatory Diseases; Neuroprotection; Neuroprotective Agents; Parasites; Perfusion; Persistent Infection; Phagocytosis; Phenotype; Plaque, Amyloid; Platelet Aggregation; Protozoan Proteins; Receptor-Interacting Protein Serine-Threonine Kinases; Receptors, Scavenger; Signal Transduction; Syk Kinase; T-Lymphocytes; T-Lymphocytes, Regulatory; THP-1 Cells; Thromboinflammation; Toxoplasma; Toxoplasmosis; Toxoplasmosis, Cerebral; Transcription Factor RelA; Virulence; Virulence Factors; nan</t>
+          <t>AIDS Dementia Complex; Acquired Immunodeficiency Syndrome; Adaptive Immunity; Adaptor Proteins, Signal Transducing; Allergy and Immunology; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Anti-Infective Agents; Antigen Presentation; Astrocytes; Blood Coagulation; Blood-Brain Barrier; Brain; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Capparis; Caspase 1; Caspase 8; Caspases; Cell Death; Cell Membrane; Cell Proliferation; Central Nervous System; Central Nervous System Infections; Cerebrovascular Circulation; Chemokine CCL2; Chemokines; Clustered Regularly Interspaced Short Palindromic Repeats; Coculture Techniques; Cognition; Coinfection; Communicable Disease Control; Cytokines; Dendritic Cells; Encephalitis; Endothelial Cells; Fibrin; Gasdermins; Gene Regulatory Networks; HIV Infections; Heart Transplantation; Hemodynamics; Hippo Signaling Pathway; Host-Parasite Interactions; Host-Pathogen Interactions; Immunity; Immunity, Innate; Induced Pluripotent Stem Cells; Infections; Inflammasomes; Inflammation; Inflammation Mediators; Intercellular Adhesion Molecule-1; Interleukin-1beta; Ion Channels; Lipoproteins; Liver; Macrophages; Mechanotransduction, Cellular; Memory T Cells; Metabolic Diseases; Microglia; Microscopy; Microvessels; Monocytes; Myeloid Cells; NF-kappa B; NLR Family, Pyrin Domain-Containing 3 Protein; Necroptosis; Neoplasm Recurrence, Local; Neurodegenerative Diseases; Neuroimaging; Neuroinflammatory Diseases; Neuroprotection; Neuroprotective Agents; Parasites; Peptides; Perfusion; Persistent Infection; Phagocytosis; Phenotype; Plaque, Amyloid; Platelet Aggregation; Protozoan Proteins; Receptor-Interacting Protein Serine-Threonine Kinases; Receptors, Scavenger; Signal Transduction; Syk Kinase; T-Lymphocytes; T-Lymphocytes, Regulatory; THP-1 Cells; Thromboinflammation; Toxoplasma; Toxoplasmosis; Toxoplasmosis, Cerebral; Transcription Factor RelA; Virulence; Virulence Factors; nan; tdTomato</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1172,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adaptation, Biological; Aging; Alleles; Antibody Formation; Biological Evolution; Borrelia burgdorferi; Breeding; CRISPR-Cas Systems; Chromatin; Chromatin Immunoprecipitation Sequencing; Chromosome Mapping; Computers; Confidence Intervals; DNA; Data Analysis; Deer; Diptera; Drosophila melanogaster; Ecological and Environmental Phenomena; Gene Frequency; Gene Knockout Techniques; Genes, MHC Class II; Genetic Variation; Genetics; Genetics, Population; Genome, Fungal; Genome-Wide Association Study; Genomics; Genotype; Haplotypes; High-Throughput Nucleotide Sequencing; Immunization; Immunoglobulin G; Incubators; Insecticide Resistance; Insecticides; Kansas; Lyme Disease; Macrophages; Malathion; Models, Genetic; Multifactorial Inheritance; Nitric Oxide; OspA protein; Parents; Peromyscus; Persistent Infection; Phagocytes; Phenotype; Polymorphism, Single Nucleotide; Quantitative Trait Loci; Reactive Nitrogen Species; Recombination, Genetic; Reproduction, Asexual; Reverse Genetics; Saccharomyces cerevisiae; Selection, Genetic; Translational Research, Biomedical</t>
+          <t>Adaptation, Biological; Aging; Alleles; Antibody Formation; Biological Evolution; Borrelia burgdorferi; Breeding; CRISPR-Cas Systems; Chromatin; Chromatin Immunoprecipitation Sequencing; Chromosome Mapping; Computers; Confidence Intervals; CpG Islands; DNA; DNA Methylation; Data Analysis; Deer; Diptera; Drosophila melanogaster; Ecological and Environmental Phenomena; Gene Frequency; Gene Knockout Techniques; Genes, MHC Class II; Genetic Variation; Genetics; Genetics, Population; Genome, Fungal; Genome-Wide Association Study; Genomics; Genotype; Haplotypes; High-Throughput Nucleotide Sequencing; Immunization; Immunoglobulin G; Incubators; Insecticide Resistance; Insecticides; Kansas; Lyme Disease; Macrophages; Malathion; Models, Genetic; Multifactorial Inheritance; Nitric Oxide; OspA protein; Parents; Peromyscus; Persistent Infection; Phagocytes; Phenotype; Photoperiod; Polymorphism, Single Nucleotide; Quantitative Trait Loci; Reactive Nitrogen Species; Recombination, Genetic; Reproduction; Reproduction, Asexual; Reverse Genetics; Saccharomyces cerevisiae; Seasons; Selection, Genetic; Translational Research, Biomedical</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1184,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Adaptor Proteins, Signal Transducing; Adenosine Triphosphate; Allosteric Regulation; Allosteric Site; Amines; Amino Acids; Antineoplastic Agents; Artificial Cells; Binding Sites; Biocatalysis; Biomarkers; Bioreactors; Carbohydrates; Carcinoma, Hepatocellular; Cell Line; Cell Line, Tumor; Computational Biology; Dimerization; Drug Delivery Systems; Drug Discovery; Early Detection of Cancer; Entropy; Escherichia coli; Gas Chromatography-Mass Spectrometry; Glucose 1-Dehydrogenase; Head and Neck Neoplasms; Hippo Signaling Pathway; Intrinsically Disordered Proteins; Liver Cirrhosis; Liver Neoplasms; Loss of Function Mutation; Lung Neoplasms; Models, Molecular; Molecular Dynamics Simulation; Mutation; Mutation, Missense; NAD; NADP; Neoplasms; Neurofibromin 2; Nicotinamide Mononucleotide; Normal Distribution; Nucleic Acids; Oxidation-Reduction; Oxidoreductases; Peptides; Phase Separation; Polymers; Protein Binding; Protein Biosynthesis; Protein Conformation; Protein Serine-Threonine Kinases; Protein Tyrosine Phosphatase, Non-Receptor Type 11; Proteins; Proteome; Proteomics; Pyrimidines; Signal Transduction; Solutions; Solvents; Static Electricity; Volatile Organic Compounds; Water; nan</t>
+          <t>Adaptor Proteins, Signal Transducing; Adenosine Triphosphate; Allosteric Regulation; Allosteric Site; Amines; Amino Acids; Antineoplastic Agents; Artificial Cells; Binding Sites; Biocatalysis; Biomarkers; Bioreactors; Budgets; Carcinoma, Hepatocellular; Cats; Cell Line, Tumor; Computational Biology; Dendritic Cells; Dimerization; Drug Delivery Systems; Early Detection of Cancer; Entropy; Escherichia coli; Gas Chromatography-Mass Spectrometry; Glucose 1-Dehydrogenase; Green Fluorescent Proteins; Head and Neck Neoplasms; Hippo Signaling Pathway; Hydrogels; Immunity, Cellular; Intrinsically Disordered Proteins; Liver Cirrhosis; Liver Neoplasms; Loss of Function Mutation; Lung Neoplasms; Models, Molecular; Molecular Dynamics Simulation; Mutation; Mutation, Missense; NAD; NADP; Neoplasms; Neurofibromin 2; Nicotinamide Mononucleotide; Normal Distribution; Oxidation-Reduction; Oxidoreductases; Peptides; Phase Separation; Polymers; Protein Binding; Protein Biosynthesis; Protein Conformation; Protein Serine-Threonine Kinases; Protein Tyrosine Phosphatase, Non-Receptor Type 11; Proteins; RNA, Messenger; Signal Transduction; Solutions; Solvents; Static Electricity; T-Lymphocytes; Viral Vaccines; Volatile Organic Compounds; mRNA Vaccines; nan</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1196,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Action Potentials; Adenosine Triphosphate; Adolescent; Adverse Childhood Experiences; Aging; Amblyopia; Animal Care Committees; Brain; Calcium Channels; Central Nervous System; Cholinergic Neurons; Cognition; Decision Making; Electronic Nicotine Delivery Systems; Electrophysiology; Genetics; Habenula; Memory; Memory Consolidation; Memory, Short-Term; Movement; Neurons; Neurosciences; Nicotine; Nicotinic Agonists; Optogenetics; Parietal Lobe; Patch-Clamp Techniques; Postsynaptic Potential Summation; Primary Visual Cortex; Psychomotor Performance; Pyramidal Cells; Receptors, Purinergic P2; Rejuvenation; Reward; Software; Stress, Psychological; Synapses; Synaptic Transmission; Visual Acuity; Wakefulness; nan</t>
+          <t>Action Potentials; Adenosine Triphosphate; Adolescent; Adverse Childhood Experiences; Aging; Amblyopia; Animal Care Committees; Anticonvulsants; Basolateral Nuclear Complex; Brain; Calcium; Calcium Channels; Central Nervous System; Cholinergic Neurons; Cognition; Computer Simulation; Decision Making; Electroencephalography; Electronic Nicotine Delivery Systems; Electrophysiology; Epilepsy; Epilepsy, Temporal Lobe; Genetics; Habenula; Hippocampus; Magnetic Fields; Memory; Memory Consolidation; Memory, Short-Term; Mental Disorders; Movement; Nanoparticles; Neural Pathways; Neurons; Neurosciences; Nicotine; Nicotinic Agonists; Optogenetics; Parietal Lobe; Patch-Clamp Techniques; Postsynaptic Potential Summation; Primary Visual Cortex; Psychomotor Performance; Pyramidal Cells; Quality of Life; Receptors, Purinergic P2; Rejuvenation; Reward; Seizures; Software; Stress, Psychological; Synapses; Synaptic Transmission; Visual Acuity; Wakefulness</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1208,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Behavior, Animal; Body Temperature Regulation; Brain; Ecological and Environmental Phenomena; Hibernation; Hormones; Life History Traits; Neurobiology; Periodicity; Physiology, Comparative; Seasons; Stress, Physiological; Temperature</t>
+          <t>Behavior, Animal; Body Temperature Regulation; Brain; Ecological and Environmental Phenomena; Hibernation; Hormones; Life History Traits; Neurobiology; Periodicity; Physiology, Comparative; Seasons; Stress, Physiological; Temperature; nan</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1232,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adolescent; Adverse Childhood Experiences; Aerosols; Amphetamine; Analgesics, Opioid; Anhedonia; Arachidonic Acids; Basal Forebrain; Basolateral Nuclear Complex; Brain; Cannabidiol; Cannabis; Chromatography, High Pressure Liquid; Clozapine; Cognition; Conditioning, Operant; Corticotropin-Releasing Hormone; Designer Drugs; Dopamine; Dopaminergic Neurons; Dose-Response Relationship, Drug; Dronabinol; Endocannabinoids; Genetics; Growth and Development; Learning; Mass Spectrometry; Microsomes; Morphine; Motivation; Neural Pathways; Neurobiology; Nucleus Accumbens; Ovarian Follicle; Ovarian Reserve; Polyunsaturated Alkamides; Prefrontal Cortex; Rats, Long-Evans; Rats, Sprague-Dawley; Reward; Substance-Related Disorders; Tandem Mass Spectrometry; Vaping; Ventral Tegmental Area; gamma-Aminobutyric Acid</t>
+          <t>Adolescent; Adolescent Development; Adverse Childhood Experiences; Aerosols; Amphetamine; Analgesics, Opioid; Anhedonia; Arachidonic Acids; Basal Forebrain; Basolateral Nuclear Complex; Brain; Cannabidiol; Cannabis; Chromatography, High Pressure Liquid; Clozapine; Cognition; Conditioning, Operant; Corticotropin-Releasing Hormone; Designer Drugs; Dopamine; Dopaminergic Neurons; Dose-Response Relationship, Drug; Dronabinol; Endocannabinoids; Genetics; Growth and Development; Learning; Mass Spectrometry; Microglia; Microsomes; Morphine; Motivation; Neural Pathways; Neurobiology; Neuronal Plasticity; Nucleus Accumbens; Ovarian Follicle; Ovarian Reserve; Polyunsaturated Alkamides; Prefrontal Cortex; Rats, Long-Evans; Rats, Sprague-Dawley; Reward; Substance-Related Disorders; Tandem Mass Spectrometry; Vaping; Ventral Tegmental Area; gamma-Aminobutyric Acid</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1244,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Biological Evolution; Biomechanical Phenomena; Carbon; Coral Reefs; Ecological and Environmental Phenomena; Ecosystem; Evolution, Molecular; Extinction, Biological; Feeding Behavior; Fishes; Genetic Speciation; Jaw; Mandible; Motion; Movement; Natural History; Perciformes; Phylogeny; Predatory Behavior; Somatotypes; Swimming; Water; nan</t>
+          <t>Aquatic Organisms; Biological Evolution; Biomechanical Phenomena; Carbon; Characidae; Coral Reefs; Ecological and Environmental Phenomena; Ecosystem; Evolution, Molecular; Extinction, Biological; Feeding Behavior; Fishes; Genetic Speciation; Information Services; Jaw; Mandible; Motion; Movement; Natural History; Perciformes; Phylogeny; Predatory Behavior; Schools; Social Behavior; Social Factors; Somatotypes; Swimming; Water; nan</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Anti-Bacterial Agents; Bacteria; Bayes Theorem; Biodiversity; Biomass; California; Carbon; Carbon Cycle; Climate Change; Drug Resistance, Bacterial; Drug Resistance, Multiple, Bacterial; Ecological and Environmental Phenomena; Ecosystem; Ecotype; El Nino-Southern Oscillation; Escherichia coli; Escherichia coli Infections; Food Chain; Genetic Variation; Genetics; Genomics; Indian Ocean; Life History Traits; Metagenome; Metagenomics; Microbial Sensitivity Tests; Microbiology; Microbiota; Nitrates; Nitrogen; Nitrogen Fixation; Nutrients; Oceanography; Oceans and Seas; Phosphates; Phylogeny; Phylogeography; Phytoplankton; Plankton; Prochlorococcus; Proteome; Seasons; Seawater; Soil; Soil Microbiology; Synechococcus; Temperature; Uncertainty</t>
+          <t>Anti-Bacterial Agents; Bacteria; Bayes Theorem; Biodiversity; Biomass; California; Carbon; Carbon Cycle; Climate Change; Drug Resistance, Bacterial; Drug Resistance, Multiple, Bacterial; Earth, Planet; Ecological and Environmental Phenomena; Ecosystem; Ecotype; El Nino-Southern Oscillation; Escherichia coli; Escherichia coli Infections; Food Chain; Genetic Variation; Genetics; Genomics; Indian Ocean; Life History Traits; Metagenome; Metagenomics; Microbial Sensitivity Tests; Microbiology; Microbiota; Nitrates; Nitrogen; Nitrogen Fixation; Nutrients; Oceanography; Oceans and Seas; Phosphates; Phylogeny; Phylogeography; Phytoplankton; Plankton; Prochlorococcus; Proteome; Seasons; Seawater; Soil; Soil Microbiology; Synechococcus; Temperature; Uncertainty</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1268,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Actinomycetales; Ambulatory Care Facilities; American Indian or Alaska Native; Anti-Bacterial Agents; Bacteria; Bays; Bifidobacterium; Biodiversity; Biological Evolution; Biotechnology; Carbohydrates; Carbon; Carbon Sequestration; Cardiovascular Diseases; Climate Change; Computational Biology; Curriculum; Cyanobacteria; DNA Methylation; Desert Climate; Diabetes Mellitus; Diet; Dietary Fiber; Drought Resistance; Droughts; Ecological and Environmental Phenomena; Ecology; Ecosystem; Electrons; Feces; Fermentation; Gastrointestinal Microbiome; Gene Transfer, Horizontal; Genetic Engineering; Genetic Variation; Genomics; Greenhouse Gases; Human Body; Internship and Residency; Interspersed Repetitive Sequences; Leadership; Life History Traits; Masks; Metadata; Metagenome; Metagenomics; Microbiology; Microbiota; Mutation; Mycobiome; Neoplasms; New Mexico; Nitrogen; Nitrogen Fixation; Noncommunicable Diseases; Ohio; Oregon; Pacific Island People; Phylogeny; Plant Leaves; Plasmids; Prebiotics; Probiotics; RNA, Ribosomal, 16S; Reproducibility of Results; Resilience, Psychological; Schools; Soil; Soil Microbiology; Stress, Physiological; Time Factors; Uncertainty; Water Purification; Wildfires; Workflow</t>
+          <t>Actinomycetales; Ambulatory Care Facilities; American Indian or Alaska Native; Anti-Bacterial Agents; Bacteria; Bays; Bifidobacterium; Biodiversity; Biological Evolution; Biotechnology; Carbohydrates; Carbon; Carbon Sequestration; Cardiovascular Diseases; Climate Change; Computational Biology; Curriculum; Cyanobacteria; DNA Damage; DNA Methylation; DNA Repair; Desert Climate; Desiccation; Diabetes Mellitus; Diet; Dietary Fiber; Drought Resistance; Droughts; Earth, Planet; Ecological and Environmental Phenomena; Ecology; Ecosystem; Electrons; Feces; Fermentation; Gastrointestinal Microbiome; Gene Transfer, Horizontal; Genetic Engineering; Genetic Variation; Genomics; Greenhouse Gases; Human Body; Internship and Residency; Interspersed Repetitive Sequences; Leadership; Life History Traits; Masks; Metadata; Metagenome; Metagenomics; Microbiology; Microbiota; Mutation; Mycobiome; Neoplasms; New Mexico; Nitrogen; Nitrogen Fixation; Noncommunicable Diseases; Ohio; Oregon; Pacific Island People; Phylogeny; Plant Leaves; Plasmids; Prebiotics; Probiotics; RNA, Ribosomal, 16S; Reproducibility of Results; Resilience, Psychological; Schools; Soil; Soil Microbiology; Stress, Physiological; Time Factors; Uncertainty; Water Purification; Wildfires; Workflow</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Animal Communication; Animals, Wild; Behavior, Animal; Biomechanical Phenomena; Communication; Cues; Cypriniformes; Ecological and Environmental Phenomena; Environment; Escape Reaction; Fishes; Fresh Water; Gait; Genomics; Hydrodynamics; Larva; Lateral Line System; Light; Locomotion; Movement; Oligochaeta; Organizations; Perciformes; Phototaxis; Predatory Behavior; Robotics; Schools; Scyphozoa; Sense Organs; Skeleton; Smegmamorpha; Social Behavior; Starfish; Swimming; Technology; Water Movements; Zebrafish</t>
+          <t>Animal Communication; Animals, Wild; Behavior, Animal; Biomechanical Phenomena; Communication; Cues; Cypriniformes; Ecological and Environmental Phenomena; Environment; Escape Reaction; Fishes; Fresh Water; Gait; Genomics; Hydrodynamics; Larva; Lateral Line System; Light; Locomotion; Movement; Oligochaeta; Organizations; Perciformes; Phototaxis; Predatory Behavior; Robotics; Schools; Scyphozoa; Sense Organs; Skeleton; Smegmamorpha; Social Behavior; Starfish; Swimming; Technology; Water Movements; Zebrafish; nan</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1304,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Allergy and Immunology; Apoptosis; Bacteria; Bacterial Infections; Bacteriophage P22; Binding Sites; CRISPR-Cas Systems; Capsid; Carcinoma, Hepatocellular; Caspase 1; Cell Culture Techniques; Cell Survival; Clostridium acetobutylicum; Cryoelectron Microscopy; Cryopyrin-Associated Periodic Syndromes; Cytokines; DNA; DNA Glycosylases; DNA, Mitochondrial; DNA, Viral; Drug Discovery; Endodeoxyribonucleases; Epithelium; Fluorocarbons; Galium; Gasdermins; Gene Editing; Heat-Shock Response; Host Microbial Interactions; Imaging, Three-Dimensional; Immune System; Inflammasomes; Inflammation; Interleukin-1; Interleukin-18; Interleukin-1beta; Ligands; Liver Neoplasms; Macromolecular Substances; Mass Spectrometry; Membrane Fluidity; Microscopy, Electron, Transmission; Mitochondria; Mitochondrial Diseases; Molecular Structure; Mutagenesis; NLR Family, Pyrin Domain-Containing 3 Protein; Neoplasms; Non-alcoholic Fatty Liver Disease; Nucleic Acids; Oxidative Stress; Oxides; Pathogen-Associated Molecular Pattern Molecules; Protein Binding; Protein Processing, Post-Translational; Protein Subunits; Proteins; Pyrin; Pyrin Domain; RNA; Signal Transduction; Signal-To-Noise Ratio; Virus Assembly; nan</t>
+          <t>Allergy and Immunology; Amino Acids; Anti-Inflammatory Agents; Apoptosis; Bacteria; Bacterial Infections; Bacteriophage P22; Binding Sites; COVID-19; COVID-19 Drug Treatment; CRISPR-Cas Systems; Capsid; Carcinoma, Hepatocellular; Caspase 1; Cell Culture Techniques; Cell Survival; Clostridium acetobutylicum; Cryoelectron Microscopy; Cryopyrin-Associated Periodic Syndromes; Cytokines; DNA; DNA Glycosylases; DNA, Mitochondrial; DNA, Viral; Drug Discovery; Endodeoxyribonucleases; Epithelium; Fluorocarbons; Galium; Gasdermins; Gene Editing; Heat-Shock Response; Host Microbial Interactions; Imaging, Three-Dimensional; Immune System; Immunity, Innate; Inflammasomes; Inflammation; Inflammation Mediators; Interleukin-1; Interleukin-18; Interleukin-1beta; Ligands; Liver Neoplasms; Macromolecular Substances; Macrophages; Mass Spectrometry; Membrane Fluidity; Microscopy, Electron, Transmission; Mitochondria; Mitochondrial Diseases; Molecular Structure; Mutagenesis; Mutation; NLR Family, Pyrin Domain-Containing 3 Protein; Neoplasms; Non-alcoholic Fatty Liver Disease; Nucleic Acids; Oxidative Stress; Oxides; Pathogen-Associated Molecular Pattern Molecules; Protein Binding; Protein Processing, Post-Translational; Protein Subunits; Proteins; Pyrin; Pyrin Domain; RNA; Signal Transduction; Signal-To-Noise Ratio; Virus Assembly; nan</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1316,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Acetylcholine; Acoustic Stimulation; Alzheimer Disease; Auditory Cortex; Auditory Perception; Auditory Perceptual Disorders; Cognition; Cognitive Dysfunction; Entorhinal Cortex; Hearing; Hippocampus; Interneurons; Neurons; Nicotine; Nicotinic Agonists; Nootropic Agents; Pharmaceutical Preparations; Physiology; Receptors, Nicotinic</t>
+          <t>Acetylcholine; Acoustic Stimulation; Alzheimer Disease; Auditory Cortex; Auditory Perception; Auditory Perceptual Disorders; Cognition; Cognitive Dysfunction; Entorhinal Cortex; Hearing; Hippocampus; Interneurons; Neurons; Nicotine; Nicotinic Agonists; Nootropic Agents; Pharmaceutical Preparations; Physiology; Receptors, Nicotinic; nan</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1352,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Amino Acid Substitution; Amino Acids; Antiparasitic Agents; Apicoplasts; Biolistics; Cells, Cultured; Chemistry, Pharmaceutical; Chlamydomonas; Clemastine; Colchicine; Communicable Diseases; Cryptosporidiosis; Cryptosporidium; Cryptosporidium parvum; Cytoskeleton; Drug Resistance; Embryophyta; Eukaryota; Fibroblasts; Genes, Essential; Germ Cells; Haploidy; Helminths; Herbicides; Histamine Antagonists; Household Work; Ligands; Macronucleus; Malaria; Meiosis; Micronucleus, Germline; Microtubules; Mitosis; Morbidity; Mutation; Mutation, Missense; Neoplasms; Paclitaxel; Parasites; Paromomycin; Pharmaceutical Preparations; Plasmids; Protozoan Proteins; Recombination, Genetic; Solubility; Tetrahymena; Toxoplasma; Transfection; Treatment Outcome; Tropism; Tubulin; Vertebrates; nan; oryzalin; pendimethalin; pironetin; pronamide</t>
+          <t>Amino Acid Substitution; Amino Acids; Antiparasitic Agents; Apicoplasts; Binding Sites; Biolistics; Cell Shape; Cells, Cultured; Chemistry, Pharmaceutical; Chlamydomonas; Clemastine; Colchicine; Communicable Diseases; Cryptosporidiosis; Cryptosporidium; Cryptosporidium parvum; Cytokinesis; Cytoskeleton; Drug Resistance; Embryophyta; Eukaryota; Fibroblasts; Genes, Essential; Germ Cells; Haploidy; Helminths; Herbicides; Histamine Antagonists; Household Work; Ligands; Macronucleus; Malaria; Meiosis; Micronucleus, Germline; Microtubules; Mitosis; Morbidity; Mutation; Mutation, Missense; Neoplasms; Paclitaxel; Parasites; Paromomycin; Pharmaceutical Preparations; Plasmids; Protozoan Proteins; Recombination, Genetic; Solubility; Tetrahymena; Toxoplasma; Transfection; Treatment Outcome; Tropism; Tubulin; Vertebrates; nan; oryzalin; pendimethalin; pironetin; pronamide</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1364,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5-Methylcytosine; 6-methyladenine; ATP-Binding Cassette Transporters; Aging; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Astrocytes; Brain; Cell Differentiation; Cerebellum; Chromatin; DNA Methylation; Gene Expression Profiling; Gene Regulatory Networks; Genetic Variation; Genomics; Hair; Hair Follicle; High-Throughput Nucleotide Sequencing; Hippocampus; Homeodomain Proteins; Hyaluronan Receptors; In Situ Hybridization, Fluorescence; Machine Learning; Melanocytes; Microglia; Molecular Sequence Annotation; Muscle Fibers, Skeletal; Muscular Dystrophy, Facioscapulohumeral; Myoblasts; Neuroglia; Neurons; Nevus; Nucleotides; Osteopontin; Phagocytosis; Plaque, Amyloid; Pseudouridine; RNA Editing; RNA, Long Noncoding; RNA-Seq; Receptor, Anaphylatoxin C5a; Resilience, Psychological; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Stem Cells; Transcriptome</t>
+          <t>5-Methylcytosine; 6-methyladenine; ATP-Binding Cassette Transporters; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Antineoplastic Combined Chemotherapy Protocols; Astrocytes; Brain; Carcinoma, Transitional Cell; Cell Differentiation; Cerebellum; Chromatin; DNA Methylation; Gene Expression Profiling; Gene Regulatory Networks; Genetic Variation; Genomics; Hair; Hair Follicle; High-Throughput Nucleotide Sequencing; Hippocampus; Homeodomain Proteins; Hyaluronan Receptors; In Situ Hybridization, Fluorescence; Machine Learning; Melanocytes; Microglia; Molecular Sequence Annotation; Muscle Fibers, Skeletal; Muscular Dystrophy, Facioscapulohumeral; Myoblasts; Neoplasm Metastasis; Neuroglia; Neurons; Nevus; Nivolumab; Nucleotides; Osteopontin; Phagocytosis; Plaque, Amyloid; Pseudouridine; RNA Editing; RNA, Long Noncoding; RNA-Seq; Receptor, Anaphylatoxin C5a; Resilience, Psychological; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Stem Cells; Transcriptome; Urinary Bladder Neoplasms; Urologic Neoplasms</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1376,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Adaptive Immunity; Adipose Tissue; Adiposity; Aged; Aging; Allergy and Immunology; Anabolic Androgenic Steroids; Androgens; Anti-Inflammatory Agents; Antibodies; Antibodies, Neutralizing; Antibody Formation; Antigen Presentation; Antigens, CD1; Autoantibodies; Autoantigens; Autoimmune Diseases; B-Lymphocyte Subsets; Biocompatible Materials; Blood Glucose; CD8-Positive T-Lymphocytes; COVID-19; Cardiac Output; Cardiovascular Diseases; Carrier Proteins; Cell Differentiation; Cell Fractionation; Cell Line; Cell Line, Tumor; Cell Membrane; Cell Plasticity; Cell Proliferation; Cell Survival; Cellular Senescence; Coculture Techniques; Computer Simulation; Cross-Sectional Studies; Culture Media, Conditioned; Cytokines; Diabetes Mellitus; Diabetes Mellitus, Type 2; Diet; Diet, High-Fat; Disease Progression; Drug Evaluation, Preclinical; Endocrinology; Ethnic and Racial Minorities; Fertility; Flow Cytometry; Follicle Stimulating Hormone; Gene Expression Profiling; Gene Expression Regulation, Neoplastic; Glucose; Glucose Transporter Type 1; Glycated Hemoglobin; Glycolysis; Gonadal Steroid Hormones; Gonadotropins; Gonadotropins, Pituitary; H3B-8800; Homeostasis; Immunophenotyping; Immunotherapy; Industrial Development; Infertility; Inflammation; Inflammation Mediators; Influenza Vaccines; Insulin; Insulin Resistance; Interleukin-17; Laboratories; Lipid Metabolism; Lipids; Lipopolysaccharides; Losartan; Luteinizing Hormone; Lymphocytic Choriomeningitis; Lymphocytic choriomeningitis virus; Lymphoid Tissue; Memory B Cells; Metabolic Networks and Pathways; Metabolism; Methanol; Mexican Americans; Mice, Obese; Neoplastic Stem Cells; Obesity; Organoids; Ovarian Neoplasms; Palatine Tonsil; Pandemics; Persistent Infection; Phenotype; Pituitary Diseases; Pituitary Gland; Polycystic Ovary Syndrome; Preceptorship; Prevalence; Printing, Three-Dimensional; Professional Competence; Proprotein Convertase 9; Protein Array Analysis; Protein Transport; Proteins; Proto-Oncogene Proteins c-akt; Quality of Life; RNA, Long Noncoding; Reproduction; Research Personnel; Risk Factors; Sedentary Behavior; Sequence Analysis, RNA; Signal Transduction; Single-Cell Gene Expression Analysis; Solvents; T-Lymphocytes; Technology; Testosterone; Th17 Cells; Transcriptome; Up-Regulation; Weight Loss; Workflow; lobeglitazone; polyvinylidene fluoride</t>
+          <t>Adaptive Immunity; Adipose Tissue; Adiposity; Aged; Aging; Allergy and Immunology; Anabolic Androgenic Steroids; Androgens; Anti-Inflammatory Agents; Antibodies; Antibodies, Neutralizing; Antibody Formation; Antigen Presentation; Antigens, CD1; Autoantibodies; Autoantigens; Autoimmune Diseases; B-Lymphocyte Subsets; Bacteriophages; Biocompatible Materials; Blood Glucose; Brain; CD8-Positive T-Lymphocytes; COVID-19; Cardiac Output; Cardiovascular Diseases; Carrier Proteins; Cell Differentiation; Cell Fractionation; Cell Line; Cell Line, Tumor; Cell Membrane; Cell Plasticity; Cell Proliferation; Cell Survival; Cellular Senescence; Coculture Techniques; Computer Simulation; Cross-Sectional Studies; Culture Media, Conditioned; Cytokines; Diabetes Mellitus; Diabetes Mellitus, Type 2; Diet; Diet, High-Fat; Disease Progression; Drug Evaluation, Preclinical; Endocrinology; Escherichia coli; Ethnic and Racial Minorities; Fertility; Flow Cytometry; Follicle Stimulating Hormone; Gastrointestinal Microbiome; Gene Expression Profiling; Gene Expression Regulation, Neoplastic; Glucose; Glucose Transporter Type 1; Glycated Hemoglobin; Glycolysis; Gonadal Steroid Hormones; Gonadotropins; Gonadotropins, Pituitary; H3B-8800; Homeostasis; Immunophenotyping; Immunotherapy; Industrial Development; Infertility; Inflammation; Inflammation Mediators; Influenza Vaccines; Insulin; Insulin Resistance; Interleukin-17; Laboratories; Lipid Metabolism; Lipids; Lipopolysaccharides; Losartan; Luteinizing Hormone; Lymphocytic Choriomeningitis; Lymphocytic choriomeningitis virus; Lymphoid Tissue; Memory B Cells; Metabolic Networks and Pathways; Metabolism; Methanol; Mexican Americans; Mice, Obese; Neoplastic Stem Cells; Obesity; Organoids; Ovarian Neoplasms; Palatine Tonsil; Pandemics; Persistent Infection; Phenotype; Pituitary Diseases; Pituitary Gland; Polycystic Ovary Syndrome; Preceptorship; Prevalence; Printing, Three-Dimensional; Professional Competence; Proprotein Convertase 9; Protein Array Analysis; Protein Transport; Proteins; Proto-Oncogene Proteins c-akt; Quality of Life; RNA, Long Noncoding; Reproduction; Research Personnel; Risk Factors; Sedentary Behavior; Sequence Analysis, RNA; Signal Transduction; Single-Cell Gene Expression Analysis; Solvents; T-Lymphocytes; Technology; Testosterone; Th17 Cells; Transcriptome; Up-Regulation; Virion; Weight Loss; Workflow; Zebrafish; lobeglitazone; nan; polyvinylidene fluoride</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1388,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Adenosine; Adipocytes; Adjuvants, Immunologic; Algorithms; Alpha-Ketoglutarate-Dependent Dioxygenase FTO; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Antibodies, Neutralizing; Antibodies, Viral; Benchmarking; Big Data; Biocompatible Materials; Biological Phenomena; Biomechanical Phenomena; CD8-Positive T-Lymphocytes; COVID-19; Cardiomyopathy, Dilated; Cartilage; Cell Body; Cell Communication; Cell Differentiation; Cell Line, Tumor; Cell Lineage; Cicatrix; Cluster Analysis; Computational Biology; Computer Simulation; Connectome; Cross-Linking Reagents; Data Analysis; Deep Learning; Developmental Biology; Down-Regulation; Drug Repositioning; Embryo, Mammalian; Embryonic Development; Endocrine System Diseases; Extracellular Fluid; Extracellular Matrix; Extracellular Space; Fibroblasts; Gelatin; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genomics; Haploinsufficiency; Hemagglutinin Glycoproteins, Influenza Virus; Homeostasis; Hydrogels; Immune Checkpoint Inhibitors; Immunotherapy; Induced Pluripotent Stem Cells; Inducible T-Cell Co-Stimulator Protein; Inflammation; Influenza A Virus, H5N1 Subtype; Influenza Vaccines; Interleukin-2; Islets of Langerhans; Keratinocytes; Kidney Diseases; Lamin Type A; Ligands; Lipid A; Lipid Droplets; Lipid Metabolism; Lipogenesis; Lymphocytes; Macrophages; Melanoma; Melanoma, Experimental; Methylation; Methyltransferases; Mice, Inbred BALB C; Motor Neurons; Multiomics; Mutation; Myocytes, Cardiac; Nervous System Diseases; Neurons; Neurotransmitter Agents; Obesity; Oligodeoxyribonucleotides; Orthomyxoviridae Infections; Pericardium; Polysorbates; Programmed Cell Death 1 Receptor; Proteins; RANK Ligand; RNA; RNA-Seq; Rosacea; SARS-CoV-2; Saponins; Schwann Cells; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Skin; Software; Squalene; Systems Biology; T-Lymphocytes; T-Lymphocytes, Regulatory; Transcriptome; Vacuoles; Wound Healing; Young Adult; nan</t>
+          <t>Adenosine; Adipocytes; Adjuvants, Immunologic; Algorithms; Alpha-Ketoglutarate-Dependent Dioxygenase FTO; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Antibodies, Neutralizing; Antibodies, Viral; Benchmarking; Big Data; Biocompatible Materials; Biological Phenomena; Biomechanical Phenomena; CD8-Positive T-Lymphocytes; COVID-19; Cardiomyopathy, Dilated; Cartilage; Cell Body; Cell Communication; Cell Cycle Checkpoints; Cell Differentiation; Cell Line, Tumor; Cell Lineage; Cellular Senescence; Chemokines; Choroid Plexus; Cicatrix; Clinical Relevance; Cluster Analysis; Computational Biology; Computer Simulation; Connectome; Cross-Linking Reagents; Cues; Cytokines; Data Analysis; Deep Learning; Developmental Biology; Down-Regulation; Drug Repositioning; Embryo, Mammalian; Embryonic Development; Endocrine System Diseases; Endopeptidases; Epithelial Cells; Extracellular Fluid; Extracellular Matrix; Extracellular Space; Feedback, Physiological; Fibroblasts; Gelatin; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genomics; Haploinsufficiency; Hemagglutinin Glycoproteins, Influenza Virus; Homeostasis; Hydrogels; Immune Checkpoint Inhibitors; Immunotherapy; Induced Pluripotent Stem Cells; Inducible T-Cell Co-Stimulator Protein; Inflammation; Influenza A Virus, H5N1 Subtype; Influenza Vaccines; Interleukin-2; Islets of Langerhans; Keratinocytes; Kidney Diseases; Lamin Type A; Ligands; Lipid A; Lipid Droplets; Lipid Metabolism; Lipogenesis; Lymphocytes; Machine Learning; Macrophages; Melanoma; Melanoma, Experimental; Methylation; Methyltransferases; Mice, Inbred BALB C; Motor Neurons; Multiomics; Mutation; Myocytes, Cardiac; Nervous System Diseases; Neural Networks, Computer; Neurons; Neurotransmitter Agents; Obesity; Oligodeoxyribonucleotides; Organoids; Orthomyxoviridae Infections; Peptide Hydrolases; Pericardium; Pluripotent Stem Cells; Polysorbates; Programmed Cell Death 1 Receptor; Proteins; RANK Ligand; RNA; RNA-Seq; Rosacea; SARS-CoV-2; Saponins; Schwann Cells; Secretome; Senescence-Associated Secretory Phenotype; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Skin; Software; Squalene; Systems Biology; T-Lymphocytes; T-Lymphocytes, Regulatory; Transcriptome; Vacuoles; Wound Healing; Young Adult</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1400,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Academic Performance; Acinar Cells; Adenocarcinoma; Alleles; Animals, Genetically Modified; Animals, Laboratory; Antigen Presentation; BRCA1 Protein; BRCA2 Protein; Bayes Theorem; Bicarbonates; Breast Neoplasms; Carcinogens; Carcinoma, Ovarian Epithelial; Case-Control Studies; Cell Differentiation; Child; Demography; Developmental Biology; Diabetes Mellitus; Diabetes Mellitus, Type 1; Diabetes Mellitus, Type 2; Disease Progression; Endocrine Cells; Epithelium; Financial Support; Gastrointestinal Microbiome; Gene Knockout Techniques; Genetic Phenomena; Genetic Predisposition to Disease; Genetic Testing; Genetic Variation; Growth and Development; Hispanic or Latino; Homeostasis; Homozygote; Hyperglycemia; Inflammation; Insulin-Secreting Cells; Insulins; Integrases; Islets of Langerhans; Language; Larva; Leadership; Likelihood Functions; Liver; Metaplasia; Metronidazole; Neoplasms; Nitroreductases; Optimism; Ovarian Neoplasms; Pancreas; Pancreas, Exocrine; Pancreatic Neoplasms; Pancreatitis; Penetrance; Polymorphism, Single Nucleotide; Prospective Studies; Regeneration; Risk Factors; Sequence Analysis, RNA; Signal Transduction; Stem Cells; Technology; Thinking; Transcriptome; Volunteers; Water; Workforce; Zebrafish</t>
+          <t>Academic Performance; Acinar Cells; Adenocarcinoma; Alleles; Animals, Genetically Modified; Animals, Laboratory; Antigen Presentation; BRCA1 Protein; BRCA2 Protein; Bayes Theorem; Bicarbonates; Breast Neoplasms; Carcinogens; Carcinoma, Ovarian Epithelial; Case-Control Studies; Cell Differentiation; Child; Demography; Developed Countries; Developmental Biology; Diabetes Mellitus; Diabetes Mellitus, Type 1; Diabetes Mellitus, Type 2; Disease Progression; Endocrine Cells; Epithelium; Financial Support; Gastrointestinal Microbiome; Gene Knockout Techniques; Genetic Phenomena; Genetic Predisposition to Disease; Genetic Testing; Genetic Variation; Growth and Development; Hispanic or Latino; Homeostasis; Homozygote; Hyperglycemia; Incidence; Indigenous Peoples; Inflammation; Insulin-Secreting Cells; Insulins; Integrases; Islets of Langerhans; Language; Larva; Leadership; Likelihood Functions; Liver; Metaplasia; Metronidazole; Neoplasms; Nitroreductases; Optimism; Ovarian Neoplasms; Pancreas; Pancreas, Exocrine; Pancreatic Neoplasms; Pancreatitis; Penetrance; Polymorphism, Single Nucleotide; Prospective Studies; Regeneration; Risk Factors; Sequence Analysis, RNA; Signal Transduction; Stem Cells; Stroke; Technology; Thinking; Transcriptome; Volunteers; Water; Workforce; Zebrafish; nan</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1420,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Adaptor Proteins, Signal Transducing; Adipocytes; Aged; Aging; Ambystoma mexicanum; Amputation, Surgical; Biocompatible Materials; Biological Evolution; Biomechanical Phenomena; Birds; Black or African American; Body Patterning; Brazil; Calcitonin Gene-Related Peptide; Cartilage; Casein Kinase 1 epsilon; Cell Communication; Cell Line, Tumor; Cell Proliferation; Cellular Senescence; China; Chromatin; Cicatrix; Circadian Clocks; Circadian Rhythm; Collagen; Colorectal Neoplasms; Computational Biology; Computer Simulation; Cross-Linking Reagents; Culicidae; Cytokines; Cytosol; DNA, Ancient; DNA-Binding Proteins; Dengue; Dermis; Disease Progression; Disease Susceptibility; Elephants; Embryonic Development; Epidermis; Epigenesis, Genetic; Epigenomics; Epithelial Cells; Ethnicity; Evidence Gaps; Evolution, Molecular; Extracellular Matrix; Fibroblasts; Fibrosis; Flavivirus; Fossils; Gelatin; Gene Expression; Gene Expression Profiling; Gene Expression Regulation, Developmental; Gene Expression Regulation, Neoplastic; Gene Regulatory Networks; Genome; Genomics; Glycolysis; HCT116 Cells; Hair; Hair Follicle; Hispanic or Latino; Homeodomain Proteins; Homeostasis; Hydrogels; Inflammation; Inflammatory Bowel Diseases; Internship and Residency; Intestinal Mucosa; Keloid; Keratinocytes; Latin America; Lipid Droplets; Lipid Metabolism; Lipogenesis; Locomotion; Macrophages; Mammoths; Marsupialia; Mechanistic Target of Rapamycin Complex 2; Melanocytes; Mesenchymal Stem Cells; Mitochondria; Mitochondrial Proteins; Mosquito Vectors; Multifactorial Inheritance; Multiomics; Myofibroblasts; NAD; Necroptosis; Neoplasms; Nevus; Nociceptors; Obesity; Organoids; Osteopontin; Ovosiston; Pain; Pandemic Preparedness; Pandemics; Phenotype; Phosphofructokinase-2; Phosphoprotein Phosphatases; Phosphorylation; Phylogeny; Pigmentation Disorders; Protein Serine-Threonine Kinases; Proto-Oncogene Proteins c-akt; Pruritus; Public Health; R-Loop Structures; RANK Ligand; RNA; RNA, Small Interfering; Reactive Oxygen Species; Referral and Consultation; Regeneration; Regulatory Sequences, Nucleic Acid; Reptiles; Saliva; Scalp; Schools; Secretome; Senescence-Associated Secretory Phenotype; Senotherapeutics; Sequence Analysis, RNA; Serine-Threonine Kinase 3; Signal Transduction; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Sirolimus; Skin; Skin Aging; Skin Diseases; Skin Physiological Phenomena; Skin Pigmentation; Software; Stem Cells; TOR Serine-Threonine Kinases; TRPV Cation Channels; Transcription Factors; Transcriptome; Tumor Suppressor Proteins; Urodela; Vaccines; Vaccinology; Vacuoles; West Nile virus; Wnt Signaling Pathway; World Health Organization; Wound Healing; X Chromosome; YAP-Signaling Proteins; Yellow Fever; Young Adult; Zebrafish; Zika Virus; Zika Virus Infection; nan</t>
+          <t>Adaptor Proteins, Signal Transducing; Adipocytes; Aged; Aging; Ambystoma mexicanum; Amputation, Surgical; Anti-Infective Agents; Autopsy; Biocompatible Materials; Biological Evolution; Biomechanical Phenomena; Birds; Black or African American; Body Patterning; Brazil; Cadaver; Calcitonin Gene-Related Peptide; Cartilage; Casein Kinase 1 epsilon; Cell Communication; Cell Line, Tumor; Cell Proliferation; Cellular Senescence; China; Chromatin; Cicatrix; Circadian Clocks; Circadian Rhythm; Collagen; Colorectal Neoplasms; Computational Biology; Computer Simulation; Cross-Linking Reagents; Culicidae; Cytokines; Cytosol; DNA, Ancient; DNA-Binding Proteins; Dengue; Dermis; Disease Progression; Disease Susceptibility; Elephants; Embryonic Development; Epidermis; Epigenesis, Genetic; Epigenomics; Epithelial Cells; Ethnicity; Evidence Gaps; Evolution, Molecular; Extracellular Matrix; Eyebrows; Eyelids; Fibroblasts; Fibrosis; Flavivirus; Fossils; Gelatin; Gene Expression; Gene Expression Profiling; Gene Expression Regulation, Developmental; Gene Expression Regulation, Neoplastic; Gene Ontology; Gene Regulatory Networks; Genome; Genome, Human; Genomics; Glycolysis; HCT116 Cells; Hair; Hair Follicle; Heterografts; Hispanic or Latino; Homeodomain Proteins; Homeostasis; Hydrogels; Inflammation; Inflammatory Bowel Diseases; Internship and Residency; Intestinal Mucosa; Keloid; Keratinocytes; Latin America; Lipid Droplets; Lipid Metabolism; Lipogenesis; Locomotion; Macrophages; Mammoths; Marsupialia; Mechanistic Target of Rapamycin Complex 2; Melanocytes; Mesenchymal Stem Cells; Mitochondria; Mitochondrial Proteins; Mosquito Vectors; Multifactorial Inheritance; Multiomics; Myofibroblasts; NAD; Necroptosis; Neoplasms; Nevus; Nociceptors; Obesity; Organoids; Osteopontin; Ovosiston; Pain; Pandemic Preparedness; Pandemics; Phenotype; Phosphofructokinase-2; Phosphoprotein Phosphatases; Phosphorylation; Phylogeny; Pigmentation Disorders; Protein Serine-Threonine Kinases; Proto-Oncogene Proteins c-akt; Pruritus; Public Health; Quality Control; R-Loop Structures; RANK Ligand; RNA; RNA, Small Interfering; RNA-Seq; Reactive Oxygen Species; Referral and Consultation; Regeneration; Regulatory Sequences, Nucleic Acid; Reptiles; Saliva; Scalp; Schools; Secretome; Senescence-Associated Secretory Phenotype; Senotherapeutics; Sequence Analysis, RNA; Serine-Threonine Kinase 3; Signal Transduction; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Sirolimus; Skin; Skin Aging; Skin Diseases; Skin Physiological Phenomena; Skin Pigmentation; Software; Stem Cells; TOR Serine-Threonine Kinases; TRPV Cation Channels; Transcription Factors; Transcriptome; Tumor Suppressor Proteins; Urodela; Vaccines; Vaccinology; Vacuoles; West Nile virus; Wnt Signaling Pathway; World Health Organization; Wound Healing; X Chromosome; YAP-Signaling Proteins; Yellow Fever; Young Adult; Zebrafish; Zika Virus; Zika Virus Infection; nan</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1444,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Adenosine Triphosphate; Apoptosis; Basic Helix-Loop-Helix Transcription Factors; Binding Sites; Biomarkers; Breast Neoplasms; CRISPR-Cas Systems; Cancer Survivors; Carcinogens; Carcinoma, Renal Cell; Cell Line, Tumor; Cell Lineage; Cell Movement; Cell Plasticity; Cell Transformation, Neoplastic; Cyclic N-Oxides; Cyclin-Dependent Kinase 9; Cyclin-Dependent Kinase Inhibitor Proteins; Cyclin-Dependent Kinases; Dimerization; Down-Regulation; Drug Resistance, Neoplasm; Electron Transport; Epithelial Cell Adhesion Molecule; ErbB Receptors; Fatty Acids; Gene Expression Regulation, Neoplastic; Genes, Suppressor; Heterografts; Hypoxia; Immune Checkpoint Inhibitors; Immunogenic Cell Death; Indolizines; Integrin alpha6; Integrins; Kidney Neoplasms; Lipid Droplets; Lipid Metabolism; Lipids; Metabolism; Microscopy; Mitochondria; Motivation; Myeloid Cell Leukemia Sequence 1 Protein; Neoplasm Metastasis; Neoplasms; Neoplastic Processes; Neoplastic Stem Cells; Ovarian Neoplasms; Oxidative Phosphorylation; Oxygen; Pedigree; Peptides; Phenotype; Phosphoproteins; Protein Kinase Inhibitors; Pyridinium Compounds; RNA Polymerase II; RNA, Long Noncoding; Signal Transduction; Survival Rate; Synthetic Lethal Mutations; Tetracyclines; Transcriptome; Triple Negative Breast Neoplasms; Tumor Microenvironment; Tyrosine; Tyrosine Kinase Inhibitors; Up-Regulation; Von Hippel-Lindau Tumor Suppressor Protein; belzutifan; dinaciclib; endothelial PAS domain-containing protein 1; saracatinib; src-Family Kinases; von Hippel-Lindau Disease</t>
+          <t>Adenosine Triphosphate; Apoptosis; Basic Helix-Loop-Helix Transcription Factors; Binding Sites; Biomarkers; Breast Neoplasms; CRISPR-Cas Systems; Cancer Survivors; Carcinogens; Carcinoma, Renal Cell; Cell Line, Tumor; Cell Lineage; Cell Movement; Cell Plasticity; Cell Transformation, Neoplastic; Cyclic N-Oxides; Cyclin-Dependent Kinase 9; Cyclin-Dependent Kinase Inhibitor Proteins; Cyclin-Dependent Kinases; Dimerization; Down-Regulation; Drug Resistance, Neoplasm; Electron Transport; Epithelial Cell Adhesion Molecule; ErbB Receptors; Fatty Acids; Gene Expression Regulation, Neoplastic; Genes, Suppressor; Heterografts; Hypoxia; Immune Checkpoint Inhibitors; Immunogenic Cell Death; Indolizines; Integrin alpha6; Integrins; Kidney Neoplasms; Lipid Droplets; Lipid Metabolism; Lipids; Metabolism; Microscopy; Mitochondria; Motivation; Myeloid Cell Leukemia Sequence 1 Protein; Neoplasm Metastasis; Neoplasms; Neoplastic Processes; Neoplastic Stem Cells; Ovarian Neoplasms; Oxidative Phosphorylation; Oxygen; Pedigree; Peptides; Phenotype; Phosphoproteins; Protein Kinase Inhibitors; Pyridinium Compounds; RNA Polymerase II; RNA, Long Noncoding; Signal Transduction; Survival Rate; Synthetic Lethal Mutations; Tetracyclines; Transcriptome; Triple Negative Breast Neoplasms; Tumor Microenvironment; Tyrosine; Tyrosine Kinase Inhibitors; Up-Regulation; Von Hippel-Lindau Tumor Suppressor Protein; belzutifan; dinaciclib; endothelial PAS domain-containing protein 1; nan; saracatinib; src-Family Kinases; von Hippel-Lindau Disease</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1456,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Algorithms; Ammonia; Arabidopsis; Awards and Prizes; Bacteria; Biological Evolution; Bioprinting; Cell Survival; Communicable Diseases; Denitrification; Droughts; Drug Resistance, Microbial; Ecological and Environmental Phenomena; Ecosystem; Evolution, Molecular; Farmers; Gases; Genetics, Population; Metabolism; Mexico; Microbiota; Natural Science Disciplines; Nitrogen; Nitrogen Cycle; Pandemics; Plants; Plasmids; Printing, Three-Dimensional; Soil; Switzerland; Synthetic Biology; Technology; United Kingdom; Water; nan</t>
+          <t>Agave; Agriculture; Algorithms; Ammonia; Arabidopsis; Awards and Prizes; Bacteria; Biological Evolution; Bioprinting; Carbon; Cell Survival; Communicable Diseases; Crops, Agricultural; Denitrification; Droughts; Drug Resistance, Microbial; Ecological and Environmental Phenomena; Ecosystem; Edible Grain; Evolution, Molecular; Farmers; Feedback
+ DNA, Single-Stranded
+ Learning
+ Ecology
+ Empirical Research; Gases; Genetics, Population; Metabolism; Mexico; Microbiota; Natural Science Disciplines; Nitrogen; Nitrogen Cycle; Pandemics; Plants; Plasmids; Printing, Three-Dimensional; Soil; Sorghum; Switzerland; Synthetic Biology; Technology; United Kingdom; Water; nan</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1496,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Academia; Algorithms; Arousal; Behavior Control; Brain; Cognition; Cognitive Dysfunction; Cognitive Neuroscience; Consciousness; Cues; Decision Making; Depression; Electroencephalography; Electrophysiology; Healthy Volunteers; Latent Infection; Leadership; Learning; Machine Learning; Magnetic Resonance Imaging; Memory; Memory Consolidation; Memory, Episodic; Mental Health; Mood Disorders; Neurobiology; Neuroimaging; Odorants; Pilot Projects; Probability; Rodentia; Sleep; Spatial Memory; Spatial Navigation; Stress Disorders, Post-Traumatic; Vacuum; Wakefulness</t>
+          <t>Academia; Algorithms; Arousal; Bacteriophage T7; Bacteriophages; Behavior Control; Brain; Cognition; Cognitive Dysfunction; Cognitive Neuroscience; Computational Biology; Consciousness; Cues; DNA; DNA-Directed RNA Polymerases; Data Collection; Decision Making; Depression; Diffusion; Electroencephalography; Electrophysiology; Healthy Volunteers; Latent Infection; Leadership; Learning; Machine Learning; Magnetic Resonance Imaging; Memory; Memory Consolidation; Memory, Episodic; Mental Health; Molecular Dynamics Simulation; Mood Disorders; Neurobiology; Neuroimaging; Odorants; Pilot Projects; Probability; Promoter Regions, Genetic; RNA, Viral; Research Personnel; Rodentia; Sexual and Gender Minorities; Sleep; Spatial Memory; Spatial Navigation; Stress Disorders, Post-Traumatic; Transcription Factors; Transcription, Genetic; Vacuum; Wakefulness</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1508,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Adipocytes; Animals, Genetically Modified; Aquaporins; Biological Evolution; Biomechanical Phenomena; Bone and Bones; Branchial Region; Calcium; Cartilage; Cell Cycle Proteins; Cell Lineage; Cell Polarity; Cell Proliferation; Chondrocytes; Chromosomal Proteins, Non-Histone; Cichlids; Clinical Relevance; Cohesins; Congenital Abnormalities; Craniofacial Abnormalities; Embryo, Nonmammalian; Embryology; Embryonic Development; Embryonic Induction; Extracellular Matrix; Eye Proteins; Fibroblasts; Gene Dosage; Gene Expression Profiling; Gene Expression Regulation, Developmental; Germ Cells; Gonads; Growth Plate; Hand-Foot Syndrome; Jaw; Laboratories; Lakes; Larva; Lens, Crystalline; Ligaments; Lipid Droplets; Lipid Metabolism; Lipogenesis; Malawi; Mechanotransduction, Cellular; Mesoderm; Morphogenesis; Muscle Contraction; Mutation; Obesity; Permeability; Phenotype; Quantitative Trait Loci; Receptor Tyrosine Kinase-like Orphan Receptors; Receptors, Retinoic Acid; Receptors, Wnt; Regulatory Sequences, Nucleic Acid; Sex Determination Processes; Signal Transduction; Skeleton; Skull; Species Specificity; Systems Biology; Tendons; Tenocytes; Transcription Factors; Transcriptome; Tretinoin; Vacuoles; Van Maldergem Wetzburger Verloes syndrome; Vertebrates; Water; Wnt Proteins; Wnt Signaling Pathway; Zebrafish; Zebrafish Proteins; nan</t>
+          <t>Adipocytes; Animals, Genetically Modified; Aquaporins; Biological Evolution; Biomechanical Phenomena; Bone and Bones; Branchial Region; Calcium; Cartilage; Cell Adhesion; Cell Cycle Proteins; Cell Lineage; Cell Movement; Cell Polarity; Cell Proliferation; Chondrocytes; Chromosomal Proteins, Non-Histone; Cichlids; Clinical Relevance; Cohesins; Computer Simulation; Congenital Abnormalities; Craniofacial Abnormalities; Embryo, Nonmammalian; Embryology; Embryonic Development; Embryonic Induction; Extracellular Matrix; Eye Proteins; Fibroblasts; Gene Dosage; Gene Expression; Gene Expression Profiling; Gene Expression Regulation, Developmental; Germ Cells; Gonads; Growth Plate; Hand-Foot Syndrome; Jaw; Laboratories; Lakes; Larva; Lens, Crystalline; Ligaments; Lipid Droplets; Lipid Metabolism; Lipogenesis; Malawi; Mechanotransduction, Cellular; Mesoderm; Morphogenesis; Muscle Contraction; Mutation; Neural Crest; Obesity; Permeability; Phenotype; Quantitative Trait Loci; Receptor Tyrosine Kinase-like Orphan Receptors; Receptors, Retinoic Acid; Receptors, Wnt; Regulatory Sequences, Nucleic Acid; Sex Determination Processes; Signal Transduction; Skeleton; Skull; Species Specificity; Systems Biology; Tendons; Tenocytes; Transcription Factors; Transcriptome; Tretinoin; Vacuoles; Van Maldergem Wetzburger Verloes syndrome; Vertebrates; Water; Wnt Proteins; Wnt Signaling Pathway; Zebrafish; Zebrafish Proteins; nan</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1520,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Acyltransferases; Aging; Alzheimer Disease; Amyloid beta-Peptides; Antibodies; Astrocytes; Axons; Benchmarking; Bioengineering; Biomarkers; Biophysics; Biotechnology; Brain; Brain Injuries; Carcinogenesis; Cell Biology; Cell Nucleus; Cell Proliferation; Cell Transformation, Neoplastic; Chromatin; Coloring Agents; Dendrites; Early Diagnosis; Endocytosis; Estrogens; Gene Expression Profiling; Gene Expression Regulation; HEK293 Cells; HeLa Cells; Health Personnel; Heterochromatin; High-Throughput Nucleotide Sequencing; Hippocampus; Human Body; Hydrogels; Intrinsically Disordered Proteins; Lamins; Long-Term Potentiation; Mass Spectrometry; Memory; Memory Disorders; Microscopy; Microscopy, Fluorescence; Molecular Structure; Multiomics; Nerve Degeneration; Neurodegenerative Diseases; Neurons; Nuclear Lamina; Nucleic Acids; Organelles; Peptides; Phenotype; Pinocytosis; Plaque, Amyloid; Prefrontal Cortex; Protein Binding; Protein Biosynthesis; Protein Interaction Mapping; Protein Kinase C; Protein Processing, Post-Translational; Proteins; Proteome; Proteomics; RNA 3' End Processing; RNA Polymerase II; RNA Precursors; RNA Processing, Post-Transcriptional; RNA Splicing; RNA, Messenger; RNA-Binding Proteins; Receptors, AMPA; Receptors, Progesterone; Ribosomes; Sequence Analysis, RNA; Sex Factors; Single Molecule Imaging; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Staining and Labeling; Synapses; Tissues; Transcriptome; Triple Negative Breast Neoplasms</t>
+          <t>Academia; Acyltransferases; Adaptor Proteins, Signal Transducing; Aging; Alzheimer Disease; Amyloid beta-Peptides; Amyloidogenic Proteins; Astrocytes; Axons; Benchmarking; Bioengineering; Biomarkers; Biophysics; Biotechnology; Brain; Brain Injuries; Capacity Building; Carcinogenesis; Cell Biology; Cell Line, Tumor; Cell Nucleus; Cell Proliferation; Cell Transformation, Neoplastic; Chromatin; Chromosomes, Plant; Colorectal Neoplasms; Crops, Agricultural; Cytosol; Dendrites; Diploidy; Disease Progression; Early Diagnosis; Endocytosis; Epigenesis, Genetic; Epigenomics; Estrogens; Fibrinolytic Agents; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Plant; Genes, Plant; Genetic Variation; Genetics, Population; Genome, Plant; Genomics; HCT116 Cells; HEK293 Cells; HeLa Cells; Heterochromatin; Heterozygote; High-Throughput Nucleotide Sequencing; Hippocampus; Homozygote; Human Body; Hydrogels; Intrinsically Disordered Proteins; Lamins; Latin America; Long-Term Potentiation; Mass Spectrometry; Memory; Memory Disorders; Microscopy; Microscopy, Fluorescence; Mitochondria; Mitochondrial Proteins; Molecular Structure; Multiomics; Nerve Degeneration; Neurodegenerative Diseases; Neurons; Nuclear Lamina; Nucleic Acids; Organelles; Outsourced Services; Peptides; Phenotype; Phosphoprotein Phosphatases; Phosphorylation; Pinocytosis; Plague; Plant Breeding; Plaque, Amyloid; Pollination; Prefrontal Cortex; Protein Binding; Protein Biosynthesis; Protein Interaction Mapping; Protein Kinase C; Protein Processing, Post-Translational; Protein Serine-Threonine Kinases; Proteins; Proteome; Proteomics; RNA 3' End Processing; RNA Polymerase II; RNA Precursors; RNA Processing, Post-Transcriptional; RNA Splicing; RNA, Messenger; RNA-Binding Proteins; Reactive Oxygen Species; Receptors, AMPA; Receptors, Progesterone; Reproduction; Ribosomes; Sequence Analysis, RNA; Serine-Threonine Kinase 3; Sex Factors; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Staining and Labeling; Synapses; Tissues; Transcription Factors; Transcriptome; Triple Negative Breast Neoplasms; Tumor Suppressor Proteins; Vitis; YAP-Signaling Proteins; nan</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1544,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Aged; Aged, 80 and over; Aging; Algorithms; Alzheimer Disease; Amyloid beta-Peptides; Atlases as Topic; Atrophy; Behavior, Animal; Benchmarking; Biomarkers; Brain; Brain Mapping; Calcineurin; Calcineurin Inhibitors; Cerebral Cortex; Cognition; Cognitive Dysfunction; Disease Progression; Dogs; Entorhinal Cortex; Gray Matter; Hippocampus; Image Processing, Computer-Assisted; Learning; Magnetic Resonance Imaging; Magnetic Resonance Spectroscopy; Memory; Mental Status and Dementia Tests; NFATC Transcription Factors; Neuroimaging; Neuropsychological Tests; Oxygen; Pattern Recognition, Physiological; Pattern Recognition, Visual; Positron-Emission Tomography; Protons; Quality Control; Reading; Reference Standards; Repression, Psychology; Reproducibility of Results; Software; Spatial Learning; Tacrolimus; Temporal Lobe; Verbal Learning; Young Adult; tau Proteins</t>
+          <t>Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid beta-Peptides; Atlases as Topic; Atrophy; Behavior, Animal; Benchmarking; Biomarkers; Brain; Brain Mapping; Calcineurin; Calcineurin Inhibitors; Cerebral Cortex; Cognition; Cognitive Dysfunction; Disease Progression; Dogs; Entorhinal Cortex; Foot; Foot Deformities; Hallux Valgus; Hippocampus; Image Processing, Computer-Assisted; Learning; Magnetic Resonance Imaging; Memory; Mental Status and Dementia Tests; NFATC Transcription Factors; Neuroimaging; Neuropsychological Tests; Oxygen; Pattern Recognition, Physiological; Pattern Recognition, Visual; Positron-Emission Tomography; Quality Control; Radiography; Reading; Repression, Psychology; Reproducibility of Results; Spatial Learning; Tacrolimus; Temporal Lobe; Verbal Learning; Young Adult; nan; tau Proteins</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1568,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AMP-Activated Protein Kinases; Asymptomatic Infections; Bacteria; Bacterial Proteins; Causality; Cell Biology; Cell Culture Techniques; Cell Cycle; Centers for Disease Control and Prevention, U.S.; Centrosome; Chlamydia; Chlamydia Infections; Chlamydia trachomatis; Cilia; Epithelial Cells; Epithelium; Escherichia coli; Fallopian Tubes; Gene Expression Regulation, Bacterial; Gene Knockdown Techniques; Golgi Apparatus; HeLa Cells; Infertility; Lipids; Membrane Proteins; Membranes; Microbiology; Microbiota; Microscopy; Oocytes; Organelles; Ovary; Pregnancy; Pregnancy, Ectopic; Proto-Oncogene Proteins c-akt; RNA; RNA, Messenger; RNA, Small Untranslated; Reverse Genetics; Sorting Nexins; Staining and Labeling; Stem Cells; Vacuoles</t>
+          <t>AMP-Activated Protein Kinases; Asymptomatic Infections; Bacteria; Bacterial Proteins; Causality; Cell Biology; Cell Culture Techniques; Cell Cycle; Centers for Disease Control and Prevention, U.S.; Centrosome; Chlamydia; Chlamydia Infections; Chlamydia trachomatis; Cilia; Epithelial Cells; Epithelium; Escherichia coli; Fallopian Tubes; Gene Expression Regulation, Bacterial; Gene Knockdown Techniques; Golgi Apparatus; HeLa Cells; Infertility; Lipids; Membrane Proteins; Membranes; Microbiology; Microbiota; Microscopy; Oocytes; Organelles; Ovary; Pregnancy; Pregnancy, Ectopic; Proto-Oncogene Proteins c-akt; RNA; RNA, Messenger; RNA, Small Untranslated; Reverse Genetics; Sorting Nexins; Staining and Labeling; Stem Cells; Vacuoles; nan</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1580,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Acetylation; Adolescent; Allosteric Regulation; Animals, Genetically Modified; Brain; CA1 Region, Hippocampal; Cause of Death; Cognition; Cognitive Dysfunction; Epigenesis, Genetic; Hippocampus; Histones; Interneurons; Long-Term Potentiation; Longevity; Mortality, Premature; Mutation; N-Methylaspartate; Neuregulin-1; Nicotiana; Nicotine; Nicotinic Agonists; Phosphorylation; Prefrontal Cortex; Pregnancy; Pyramidal Cells; Quinolines; Rats, Sprague-Dawley; Receptor, Muscarinic M1; Receptors, N-Methyl-D-Aspartate; Receptors, Nicotinic; Reward; Schizophrenia; Signal Transduction; Smoking; Smoking Cessation; Tobacco Smoking; Tobacco Use; Tobacco Use Disorder; Transcription, Genetic; Tyrosine; Up-Regulation; nan; src-Family Kinases</t>
+          <t>Acetylation; Adolescent; Allosteric Regulation; Alzheimer Disease; Animals, Genetically Modified; Behavior Rating Scale; Brain; CA1 Region, Hippocampal; Cause of Death; Chemokines; Child; Cholinergic Neurons; Cognition; Cognitive Dysfunction; Cytokines; Down-Regulation; Electrophysiology; Epigenesis, Genetic; Fluorescent Antibody Technique; Hippocampus; Histone Deacetylase Inhibitors; Histone Deacetylases; Histones; Homeostasis; Interneurons; Ligands; Long-Term Potentiation; Longevity; Memory Disorders; Microglia; Mortality, Premature; Mutation; N-Methylaspartate; Neocortex; Neuregulin-1; Nicotiana; Nicotine; Nicotinic Agonists; Phosphorylation; Plaque, Amyloid; Prefrontal Cortex; Pregnancy; Pyramidal Cells; Quinolines; RNA, Messenger; Rats, Sprague-Dawley; Receptor, Muscarinic M1; Receptors, N-Methyl-D-Aspartate; Receptors, Nicotinic; Reward; Schizophrenia; Signal Transduction; Smoking; Smoking Cessation; Somatostatin; Substance-Related Disorders; Tobacco Smoking; Tobacco Use; Tobacco Use Disorder; Transcription, Genetic; Tyrosine; Up-Regulation; src-Family Kinases</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1592,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Algorithms; Alleles; Biological Evolution; Biomarkers; Brain; Breast Neoplasms; Carcinogenesis; Carcinoma, Hepatocellular; Cell Differentiation; Cell Line, Tumor; Cell Plasticity; Cell Proliferation; Cell Survival; Chromosomes, Human, X; Clustered Regularly Interspaced Short Palindromic Repeats; Colonic Neoplasms; Computational Biology; Down-Regulation; Drosophila Proteins; Drosophila melanogaster; Dysbiosis; Embryonic Development; Epigenesis, Genetic; Epigenomics; Eutheria; Evolution, Molecular; Fetal Stem Cells; Gastrointestinal Microbiome; Gene Editing; Gene Expression Profiling; Gene Expression Regulation, Neoplastic; Gene Frequency; Genes, X-Linked; Genetic Fitness; Genetic Linkage; Genetics; Genital Neoplasms, Female; Glomerulonephritis; Glutamine; Health; Homeodomain Proteins; Incidence; Kidney; Lactobacillus; Life Style; Liver Neoplasms; Lupus Nephritis; Lymphadenopathy; Marsupialia; Metabolic Reprogramming; Mice, Inbred MRL lpr; MicroRNAs; Microscopy, Fluorescence; Models, Genetic; Molecular Biology; Multigene Family; Mutation; Neoplasms; Neoplastic Processes; Neoplastic Stem Cells; Optical Imaging; Organoids; Ovarian Neoplasms; Oxidative Phosphorylation; Precision Medicine; Prognosis; Proteinuria; RNA; RNA, Guide, CRISPR-Cas Systems; RNA, Long Noncoding; RNA, Ribosomal, 16S; RNA, Untranslated; Selection, Genetic; Sex Characteristics; Sex Chromosomes; Spleen; Splenomegaly; Stem Cells; Stress, Physiological; Toll-Like Receptor 5; Trans-Activators; Tumor Microenvironment; X Chromosome; X Chromosome Inactivation; Y Chromosome</t>
+          <t>Aged; Algorithms; Biological Evolution; Biomarkers; Biomarkers, Tumor; Brain; Breast Neoplasms; Carcinogenesis; Carcinoma, Hepatocellular; Carcinoma, Non-Small-Cell Lung; Cell Differentiation; Cell Line, Tumor; Cell Plasticity; Cell Proliferation; Cell Survival; Chromosomes, Human, X; Circulating Tumor DNA; Clustered Regularly Interspaced Short Palindromic Repeats; Colonic Neoplasms; Computational Biology; Diagnosis, Differential; Down-Regulation; Drug Resistance, Neoplasm; Educational Measurement; Embryonic Development; Epigenesis, Genetic; Epigenomics; ErbB Receptors; Eutheria; Evolution, Molecular; Exons; Fetal Stem Cells; Gene Editing; Gene Expression Profiling; Gene Expression Regulation, Neoplastic; Genes, X-Linked; Genetics; Genital Neoplasms, Female; Glutamine; Health; Incidence; Large Language Models; Life Style; Liver Neoplasms; Lung Neoplasms; Marsupialia; Metabolic Reprogramming; Microscopy, Fluorescence; Molecular Biology; Multigene Family; Mutagenesis, Insertional; Mutation; Neoplastic Processes; Neoplastic Stem Cells; Optical Imaging; Organoids; Ovarian Neoplasms; Oxidative Phosphorylation; Precision Medicine; Prognosis; Protein Kinase Inhibitors; RNA; RNA, Guide, CRISPR-Cas Systems; RNA, Long Noncoding; RNA, Untranslated; Radiology; Reproducibility of Results; Retrospective Studies; Sex Characteristics; Sex Chromosomes; Specialty Boards; Stem Cells; Stress, Physiological; Trans-Activators; Tumor Microenvironment; X Chromosome; X Chromosome Inactivation; Y Chromosome; nan</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1604,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid beta-Peptides; Apolipoproteins E; Astrocytes; Autism Spectrum Disorder; Axons; Brain; CD8-Positive T-Lymphocytes; Cell Communication; Cell Line; Cell Nucleus; Cell Proliferation; Cellular Reprogramming; Central Nervous System; Chromatin Immunoprecipitation Sequencing; Cocaine; Demyelinating Diseases; Disease Progression; Down Syndrome; Encephalitis Virus, Japanese; Encephalitis, Japanese; Epigenesis, Genetic; Epigenomics; Fatty Acids, Volatile; Ganglia, Spinal; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genetic Variation; Genetics; Genomics; Habenula; Immunity, Innate; Inflammation; Integrases; Integrins; Killer Cells, Natural; Memory; MicroRNAs; Microglia; Multiomics; Multiple Sclerosis; Myelin Sheath; Myeloid Cells; NF-KappaB Inhibitor alpha; NF-kappa B; Natural Killer T-Cells; Nerve Regeneration; Nervous System Malformations; Neurodegenerative Diseases; Neuroglia; Neuroinflammatory Diseases; Neurons; Occipital Lobe; Oligodendrocyte Precursor Cells; Oligodendroglia; Parkinson Disease; Parkinsonian Disorders; Plaque, Amyloid; Postmortem Changes; Proteomics; Pseudogenes; RNA; RNA, Small Nuclear; RNA-Seq; Rats, Sprague-Dawley; Recurrence; Remyelination; Resilience, Psychological; Sensory Receptor Cells; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Spatial Memory; Spinal Cord; Spinal Cord Injuries; Sterol Regulatory Element Binding Protein 1; Stroke; Substance-Related Disorders; Systems Biology; Tauopathies; Time Factors; Transcription Factors; Transcriptome; White Matter; Wound Healing; nan; tau Proteins</t>
+          <t>Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid beta-Peptides; Apolipoproteins E; Astrocytes; Brain; CD8-Positive T-Lymphocytes; Cell Communication; Cell Line; Cell Nucleus; Cell Proliferation; Cellular Reprogramming; Central Nervous System; Chromatin Immunoprecipitation Sequencing; Cocaine; Cognition; Critical Pathways; Demyelinating Diseases; Disease Progression; Down Syndrome; Encephalitis Virus, Japanese; Encephalitis, Japanese; Epigenesis, Genetic; Epigenomics; Fatty Acids, Volatile; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genes; Genetic Variation; Genetics; Genomics; Habenula; Healthy Aging; Immunity, Innate; Inflammation; Integrases; Killer Cells, Natural; Longevity; Memory; MicroRNAs; Microglia; Multiomics; Multiple Sclerosis; Myelin Sheath; Myeloid Cells; NF-KappaB Inhibitor alpha; NF-kappa B; Natural Killer T-Cells; Nervous System Malformations; Neurodegenerative Diseases; Neuroglia; Neuroinflammatory Diseases; Neurons; Occipital Lobe; Oligodendrocyte Precursor Cells; Oligodendroglia; Parkinson Disease; Parkinsonian Disorders; Plaque, Amyloid; Postmortem Changes; Prefrontal Cortex; Proteomics; Pseudogenes; Quality Control; RNA; RNA, Small Nuclear; RNA-Seq; Recurrence; Regulator; Remyelination; Reproducibility of Results; Resilience, Psychological; Risk Factors; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Spatial Memory; Spinal Cord; Spinal Cord Injuries; Sterol Regulatory Element Binding Protein 1; Stroke; Substance-Related Disorders; Systems Biology; Tauopathies; Time Factors; Transcription Factors; Transcriptome; White Matter; Wound Healing; nan; tau Proteins</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1640,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Actin Cytoskeleton; Actins; Adenosine Triphosphate; Alleles; Axons; Blood-Brain Barrier; Calcium; Cell Death; Cytoskeleton; Dendrites; Drosophila melanogaster; Endothelial Cells; Energy Metabolism; Extracellular Matrix; Gene Expression Profiling; Glutamine; Huntington Disease; Integrins; Microtubules; Mitochondria; Mitochondrial Dynamics; Nerve Regeneration; Neurites; Neurodegenerative Diseases; Neurogenesis; Neuroglia; Neurons; Neuroprotection; Neuroprotective Agents; Peptides; Peripheral Nervous System; Potassium Channels, Inwardly Rectifying; Proteolysis; Regeneration; Sensory Receptor Cells; Signal Transduction; Spinocerebellar Ataxias; Time-Lapse Imaging; Transgenes; polyglutamine</t>
+          <t>Actin Cytoskeleton; Actins; Adenosine Triphosphate; Alleles; Axons; Blood-Brain Barrier; Calcium; Cell Death; Cytoskeleton; Dendrites; Drosophila melanogaster; Endothelial Cells; Energy Metabolism; Extracellular Matrix; Gene Expression Profiling; Glutamine; Huntington Disease; Integrins; Microtubules; Mitochondria; Mitochondrial Dynamics; Nerve Regeneration; Neurites; Neurodegenerative Diseases; Neurogenesis; Neuroglia; Neurons; Neuroprotection; Neuroprotective Agents; Peptides; Peripheral Nervous System; Potassium Channels, Inwardly Rectifying; Proteolysis; Regeneration; Sensory Receptor Cells; Signal Transduction; Spinocerebellar Ataxias; Time-Lapse Imaging; Transgenes; nan; polyglutamine</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1652,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>6-methyladenine; Academia; Adenosine; Aged; Algorithms; Alternative Splicing; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Animals, Genetically Modified; Artificial Intelligence; Astrocytes; Ataxin-1; Atrophy; Autophagy; Biological Phenomena; Biomarkers; Biomedical Research; Biotin; Brain; Brain-Derived Neurotrophic Factor; C9orf72 Protein; Calcium Signaling; Caregivers; Case-Control Studies; Cell Death; Cell Differentiation; Cell Line; Cell- and Tissue-Based Therapy; Cells, Cultured; Cerebellum; Cerebral Cortex; Child; Child, Preschool; Chorea; Chromatin; Chromatin Immunoprecipitation Sequencing; Chromatography, Liquid; Clinical Trials, Phase I as Topic; Clustered Regularly Interspaced Short Palindromic Repeats; Cognition; Cognitive Dysfunction; Communication; Corpus Striatum; DNA Breaks, Double-Stranded; DNA Damage; DNA Repair; DNA-Binding Proteins; Deep Learning; Delayed Diagnosis; Dementia; Demography; Depression; Dihydroxyphenylalanine; Disease Progression; Dopaminergic Neurons; Drug Development; Dystonia 3, Torsion, X-Linked; Edema; Electrophysiology; Embryonic Stem Cells; Epigenesis, Genetic; Epigenomics; Epilepsies, Partial; Exons; Feasibility Studies; Fibroblasts; Frontotemporal Dementia; Frontotemporal Lobar Degeneration; Gene Editing; Gene Expression Profiling; Gene Expression Regulation; Genetic Association Studies; Genetic Diseases, X-Linked; Genetic Therapy; Genetic Variation; Graft Rejection; HeLa Cells; Hematopoietic Stem Cell Transplantation; Histones; Hospitalization; Huntingtin Protein; Huntington Disease; Immunosuppression Therapy; Induced Pluripotent Stem Cells; Inflammation; Inosine; Intermediate Filaments; Intranuclear Inclusion Bodies; Isomerism; Lewy Bodies; Ligases; Liquid Chromatography-Mass Spectrometry; Lysosomes; Medium Spiny Neurons; Methylation; Methyltransferases; Microglia; Microscopy; Microscopy, Electron; Mitochondria; Mitochondrial Proteins; Motor Neurons; Multiomics; Muscle, Skeletal; Mutation; Negotiating; Nervous System Diseases; Neural Stem Cells; Neurites; Neurobiology; Neurodegenerative Diseases; Neurons; Neurons, Efferent; Oligonucleotides, Antisense; Optogenetics; Organelles; Outcome Assessment, Health Care; Parkinson Disease; Peptides; Pharmaceutical Preparations; Phenotype; Pluripotent Stem Cells; Poly Adenosine Diphosphate Ribose; Prevalence; Primates; Prisoners; Promoter Regions, Genetic; Protein Binding; Protein Biosynthesis; Protein Isoforms; Proteins; Proteome; Proteomics; Proteostasis; Quantitative Trait Loci; RNA; RNA Methylation; RNA Splicing; RNA Stability; RNA, Messenger; RNA, Small Interfering; RNA-Binding Proteins; Receptors, Antigen, T-Cell; Receptors, Metabotropic Glutamate; Regenerative Medicine; Registries; Research Report; Retroelements; Robotic Surgical Procedures; SUMO-1 Protein; Salts; Seizures; Seizures, Febrile; Sequence Analysis, RNA; Signal Transduction; Sodium Chloride; Spinocerebellar Ataxias; Stem Cell Transplantation; Stem Cells; Sumoylation; Superoxide Dismutase-1; Synapses; Synapsins; Synaptosomes; Synucleins; Systems Biology; Tandem Mass Spectrometry; Tandem Repeat Sequences; Terminology as Topic; Tissue Distribution; Transcription, Genetic; Transcriptome; Translational Science, Biomedical; Treatment Outcome; Trinucleotide Repeat Expansion; Trinucleotide Repeats; Ubiquitin; Ubiquitin-Protein Ligases; Whole Genome Sequencing; gamma-Aminobutyric Acid</t>
+          <t>6-methyladenine; Academia; Adenosine; Aged; Algorithms; Alternative Splicing; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Animals, Genetically Modified; Artificial Intelligence; Astrocytes; Ataxin-1; Atrophy; Autophagy; Biological Phenomena; Biomarkers; Biomedical Research; Biotin; Brain; Brain-Derived Neurotrophic Factor; C9orf72 Protein; Calcium Signaling; Caregivers; Case-Control Studies; Cell Death; Cell Differentiation; Cell Line; Cell- and Tissue-Based Therapy; Cells, Cultured; Cerebellum; Cerebral Cortex; Child; Child, Preschool; Chorea; Chromatin; Chromatin Immunoprecipitation Sequencing; Chromatography, Liquid; Clinical Trials, Phase I as Topic; Clustered Regularly Interspaced Short Palindromic Repeats; Cognition; Cognitive Dysfunction; Colon; Communication; Corpus Striatum; DNA Breaks, Double-Stranded; DNA Damage; DNA Repair; DNA-Binding Proteins; Deep Learning; Delayed Diagnosis; Dementia; Demography; Depression; Dihydroxyphenylalanine; Disease Progression; Dopaminergic Neurons; Drug Development; Dystonia 3, Torsion, X-Linked; Edema; Electrophysiology; Embryonic Stem Cells; Epigenesis, Genetic; Epigenomics; Epilepsies, Partial; Exons; Feasibility Studies; Fibroblasts; Frontotemporal Dementia; Frontotemporal Lobar Degeneration; Gene Editing; Gene Expression Profiling; Gene Expression Regulation; Gene Knockout Techniques; Genetic Diseases, X-Linked; Genetic Therapy; Genetic Variation; Graft Rejection; HeLa Cells; Hematopoietic Stem Cell Transplantation; Histones; Hospital Mortality; Hospitalization; Huntingtin Protein; Huntington Disease; Immunosuppression Therapy; Induced Pluripotent Stem Cells; Inflammation; Inosine; Intermediate Filaments; Intranuclear Inclusion Bodies; Isomerism; Length of Stay; Lewy Bodies; Ligases; Liquid Chromatography-Mass Spectrometry; Lysosomes; Medium Spiny Neurons; Methylation; Methyltransferases; Microglia; Microscopy; Microscopy, Electron; Mitochondria; Mitochondrial Proteins; Motor Neurons; Multiomics; Muscle, Skeletal; Mutation; Negotiating; Nervous System Diseases; Neural Stem Cells; Neurites; Neurobiology; Neurodegenerative Diseases; Neurons; Neurons, Efferent; Oligonucleotides, Antisense; Optogenetics; Organelles; Outcome Assessment, Health Care; Parkinson Disease; Peptides; Pharmaceutical Preparations; Phenotype; Poly Adenosine Diphosphate Ribose; Prevalence; Primates; Prisoners; Promoter Regions, Genetic; Prospective Studies; Protein Binding; Protein Biosynthesis; Protein Isoforms; Proteomics; Proteostasis; Quantitative Trait Loci; RNA; RNA Methylation; RNA Splicing; RNA Stability; RNA, Messenger; RNA, Small Interfering; RNA-Binding Proteins; Receptors, Antigen, T-Cell; Receptors, Metabotropic Glutamate; Rectum; Regenerative Medicine; Registries; Research Report; Retroelements; Robotic Surgical Procedures; SUMO-1 Protein; Salts; Seizures; Seizures, Febrile; Sequence Analysis, RNA; Signal Transduction; Sodium Chloride; Spinocerebellar Ataxias; Stem Cell Transplantation; Stem Cells; Sumoylation; Superoxide Dismutase-1; Surgical Wound Infection; Synapses; Synapsins; Synaptosomes; Synucleins; Systems Biology; Tandem Mass Spectrometry; Tandem Repeat Sequences; Terminology as Topic; Tissue Distribution; Transcription, Genetic; Transcriptome; Translational Science, Biomedical; Treatment Outcome; Trinucleotide Repeat Expansion; Ubiquitin; Ubiquitin-Protein Ligases; Whole Genome Sequencing; Wound Closure Techniques; gamma-Aminobutyric Acid; nan</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1676,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ADP-ribosyl Cyclase; AMP-Activated Protein Kinases; Adaptive Immunity; Aged; Aging; Allergy and Immunology; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Antibodies, Blocking; Antigens; Antiviral Agents; Arm; Autoimmunity; B7-H1 Antigen; Brain; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Calcium Signaling; Caregivers; Cell Differentiation; Cell Line, Tumor; Cell Movement; Cell Proliferation; Cell Survival; Chromatin; Chronic Disease; Cognition; Cognitive Dysfunction; Coloring Agents; Delivery of Health Care; Dendritic Cells; Dengue; Diet; Disease-Free Survival; Epigenesis, Genetic; Feasibility Studies; Ficus; Financing, Organized; Flow Cytometry; Gene Expression Profiling; Genetic Predisposition to Disease; HIV Infections; HMGB2 Protein; Hemorrhagic Fever, Ebola; Hepatitis A Virus Cellular Receptor 2; Hepatitis B; Hepatitis C; Homeostasis; Immune Checkpoint Inhibitors; Immune Checkpoint Proteins; Immune System; Immunity; Immunoglobulin G; Immunologic Memory; Immunologic Techniques; Immunosuppression Therapy; Immunotherapy; Incidence; Influenza A Virus, H1N1 Subtype; Influenza A Virus, H7N9 Subtype; Intravital Microscopy; Ligands; Longevity; Lymph Nodes; Lymphocyte Activation; Lymphocytic Choriomeningitis; Lymphocytic choriomeningitis virus; Macrophages; Melanoma; Membrane Glycoproteins; Memory T Cells; Metabolic Networks and Pathways; Microbiota; Microscopy; Military Personnel; Molecular Biology; Morbidity; Mutation; Myeloid Cells; Natural Killer T-Cells; Neoadjuvant Therapy; Neoplasms; Neoplasms, Second Primary; P-Selectin; P-selectin ligand protein; Persistent Infection; Phosphoprotein Phosphatases; PrPC Proteins; Prion Proteins; Programmed Cell Death 1 Receptor; Receptors, Antigen, T-Cell; Research; Risk Factors; SARS-CoV-2; Sequence Analysis, RNA; Signal Transduction; Skin Neoplasms; Spleen; Survival Rate; T-Cell Exhaustion; T-Lymphocytes; Transcription Factors; Treatment Outcome; Tumor Microenvironment; Up-Regulation; Vaccines; Virus Diseases; protein phosphatase 6</t>
+          <t>ADP-ribosyl Cyclase; AMP-Activated Protein Kinases; Adaptive Immunity; Aged; Aging; Allergy and Immunology; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Antibodies, Blocking; Antigens; Antiviral Agents; Arm; Autoimmunity; B7-H1 Antigen; Brain; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Calcium Signaling; Caregivers; Cell Differentiation; Cell Line, Tumor; Cell Movement; Cell Proliferation; Cell Survival; Chromatin; Chronic Disease; Cognition; Cognitive Dysfunction; Coloring Agents; Delivery of Health Care; Dendritic Cells; Dengue; Diet; Disease-Free Survival; Epigenesis, Genetic; Feasibility Studies; Ficus; Financing, Organized; Flow Cytometry; Gene Expression Profiling; Genetic Predisposition to Disease; HIV Infections; HMGB2 Protein; Hemorrhagic Fever, Ebola; Hepatitis A Virus Cellular Receptor 2; Hepatitis B; Hepatitis C; Homeostasis; Immune Checkpoint Inhibitors; Immune Checkpoint Proteins; Immune System; Immunity; Immunoglobulin G; Immunologic Memory; Immunologic Techniques; Immunosuppression Therapy; Immunotherapy; Incidence; Influenza A Virus, H1N1 Subtype; Influenza A Virus, H7N9 Subtype; Intravital Microscopy; Ligands; Longevity; Lymph Nodes; Lymphocyte Activation; Lymphocytic Choriomeningitis; Lymphocytic choriomeningitis virus; Macrophages; Melanoma; Membrane Glycoproteins; Memory T Cells; Metabolic Networks and Pathways; Microbiota; Microscopy; Military Personnel; Molecular Biology; Morbidity; Mutation; Myeloid Cells; Natural Killer T-Cells; Neoadjuvant Therapy; Neoplasms; Neoplasms, Second Primary; P-Selectin; P-selectin ligand protein; Persistent Infection; Phosphoprotein Phosphatases; PrPC Proteins; Prion Proteins; Programmed Cell Death 1 Receptor; Receptors, Antigen, T-Cell; Research; Risk Factors; SARS-CoV-2; Sequence Analysis, RNA; Signal Transduction; Skin Neoplasms; Spleen; Survival Rate; T-Cell Exhaustion; T-Lymphocytes; Transcription Factors; Treatment Outcome; Tumor Microenvironment; Up-Regulation; Vaccines; Virus Diseases; nan; protein phosphatase 6</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1688,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Actinomycetales; Alaska; Alternaria; Anti-Bacterial Agents; Ants; Arthropods; Bacteria; Biomass; Canada; Carbon; Carbon Dioxide; Climate Change; Climate Models; Cold Temperature; Computers; Crop Production; Dermabrasion; Droughts; Drug Resistance, Bacterial; Ecological and Environmental Phenomena; Ecology; Ecosystem; Extracellular Polymeric Substance Matrix; Farmers; Forests; Fungi; Gene Expression Profiling; Genes, Bacterial; Genome, Bacterial; Genotype; Global Warming; Grassland; Hawaii; Hot Temperature; Incidence; Information Dissemination; Lepidoptera; Life History Traits; Longevity; Metagenome; Metagenomics; Microbiota; Mycorrhizae; Neon; Nitrogen; Plant Development; Plants; Poaceae; Resilience, Psychological; Seedlings; Seeds; Soil; Soil Microbiology; Songbirds; Survivorship; Temperature; Thermotolerance; Transcription, Genetic; Transcriptome; Uncertainty; Water; West Nile Fever; West Nile virus; Wildfires</t>
+          <t>Actinomycetales; Alaska; Alternaria; Anti-Bacterial Agents; Ants; Arthropods; Bacteria; Biomass; Canada; Carbon; Carbon Dioxide; Climate Change; Climate Models; Cold Temperature; Computers; Crop Production; Dermabrasion; Droughts; Drug Resistance, Bacterial; Ecological and Environmental Phenomena; Ecology; Ecosystem; Extracellular Polymeric Substance Matrix; Farmers; Forests; Fungi; Gene Expression Profiling; Genes, Bacterial; Genome, Bacterial; Genotype; Global Warming; Grassland; Hawaii; Hot Temperature; Incidence; Information Dissemination; Lepidoptera; Life History Traits; Longevity; Metagenome; Metagenomics; Microbiota; Mycorrhizae; Neon; Nitrogen; Plant Development; Plants; Poaceae; Policy; Resilience, Psychological; Seedlings; Seeds; Soil; Soil Microbiology; Songbirds; Survivorship; Technology; Temperature; Thermotolerance; Transcription, Genetic; Transcriptome; Uncertainty; Water; West Nile Fever; West Nile virus; Wildfires</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1700,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Antineoplastic Agents; Big Data; Biological Products; COVID-19; Catalytic Domain; Crystallography; Daunorubicin; Drug Design; Machine Learning; Mutagenesis; Polyketide Synthases; Polyketides; Post-Acute COVID-19 Syndrome</t>
+          <t>Aged; Aged, 80 and over; Algorithms; Analgesics, Opioid; Androgens; Antineoplastic Agents; Atrial Fibrillation; Big Data; Biological Products; Bipolar Disorder; Black or African American; Brain; COVID-19; COVID-19 Drug Treatment; COVID-19 Serotherapy; Catalytic Domain; Cell Differentiation; Child; Chromosome Mapping; Cohort Studies; Comorbidity; Cross-Sectional Studies; Crystallography; Daunorubicin; Drug Design; Electrocardiography, Ambulatory; Epithelial Cells; Europe; Genetic Predisposition to Disease; Genome-Wide Association Study; Genomics; Gray Matter; HIV Infections; Hair Follicle; Heart; Hippocampus; Hispanic or Latino; Hospitalization; Hypertension; Immunization, Passive; Machine Learning; Magnetic Resonance Imaging; Medical Oncology; Mutagenesis; Neoplasms; Neuroimaging; North America; Oncology Nursing; Opioid-Related Disorders; Oxygen; Patient Safety; Pediatrics; Phenotype; Polyketide Synthases; Polyketides; Post-Acute COVID-19 Syndrome; Reproducibility of Results; SARS-CoV-2; Schizophrenia; Sebaceous Glands; Single-Cell Analysis; Skin; Societies, Nursing; Treatment Outcome; White; White People</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1712,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Adjuvants, Immunologic; Allergy and Immunology; Alzheimer Disease; Antibodies, Monoclonal, Humanized; Antibody Formation; Astrocytes; Autoimmunity; Bioengineering; Bioprinting; Biotechnology; Bone Marrow; CD4 Antigens; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Cell Adhesion Molecules; Cell Death; Clinical Trials, Phase II as Topic; Clustered Regularly Interspaced Short Palindromic Repeats; Coronavirus Infections; Demyelinating Diseases; Embryonic Stem Cells; Encephalomyelitis, Autoimmune, Experimental; Epitopes; Epstein-Barr Virus Infections; Esophageal Neoplasms; Flow Cytometry; Fluticasone; Forkhead Transcription Factors; Fucose; Fucosyltransferases; Gene Expression Profiling; Graft vs Host Disease; Hematologic Neoplasms; Hematopoietic Stem Cell Transplantation; Hematopoietic Stem Cells; Herpesvirus 4, Human; Image Cytometry; Immune Tolerance; Immunity, Cellular; Immunity, Innate; Immunization; Immunosuppressive Agents; Immunotherapy; Incubators; Induced Pluripotent Stem Cells; Inflammation; Ischemia; Killer Cells, Natural; Laboratories; Lymphocyte Activation; Macrophages; Magnetic Phenomena; Meningitis, Aseptic; Microglia; Microscopy; Multiomics; Multiple Sclerosis; Multiple Sclerosis, Relapsing-Remitting; Murine hepatitis virus; Neural Stem Cells; Neuroinflammatory Diseases; Organoids; Persistent Infection; Receptors, Antigen, T-Cell; Regenerative Medicine; Remyelination; S Phase; Single-Cell Gene Expression Analysis; Stem Cell Research; Stem Cells; T-Lymphocytes; T-Lymphocytes, Regulatory; Transplantation, Homologous; Tumor Escape; Vaccination; Vaccine Efficacy; Vaccines; White Matter; aducanumab</t>
+          <t>Adjuvants, Immunologic; Alcoholism; Allergy and Immunology; Alzheimer Disease; Anti-HIV Agents; Antibodies, Monoclonal, Humanized; Antibody Formation; Assessment of Medication Adherence; Astrocytes; Autoimmunity; Bioengineering; Bioprinting; Biotechnology; Bone Marrow; CD4 Antigens; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Cell Adhesion Molecules; Cell Death; Clinical Trials, Phase II as Topic; Clustered Regularly Interspaced Short Palindromic Repeats; Coronavirus Infections; Demyelinating Diseases; Embryonic Stem Cells; Encephalomyelitis, Autoimmune, Experimental; Epitopes; Epstein-Barr Virus Infections; Esophageal Neoplasms; Flow Cytometry; Fluticasone; Forkhead Transcription Factors; Fucose; Fucosyltransferases; Gene Expression Profiling; Graft vs Host Disease; HIV Infections; Hematologic Neoplasms; Hematopoietic Stem Cell Transplantation; Hematopoietic Stem Cells; Herpesvirus 4, Human; Image Cytometry; Immune Tolerance; Immunity, Cellular; Immunity, Innate; Immunization; Immunosuppressive Agents; Immunotherapy; Incubators; Induced Pluripotent Stem Cells; Inflammation; Ischemia; Killer Cells, Natural; Laboratories; Lymphocyte Activation; Macrophages; Magnetic Phenomena; Medication Adherence; Meningitis, Aseptic; Microglia; Microscopy; Motivational Interviewing; Multiomics; Multiple Sclerosis; Multiple Sclerosis, Relapsing-Remitting; Murine hepatitis virus; Neural Stem Cells; Neuroinflammatory Diseases; Organoids; Persistent Infection; Receptors, Antigen, T-Cell; Regenerative Medicine; Remyelination; S Phase; Single-Cell Gene Expression Analysis; Smartphone; Stem Cell Research; Stem Cells; T-Lymphocytes; T-Lymphocytes, Regulatory; Transplantation, Homologous; Treatment Outcome; Tumor Escape; Vaccination; Vaccine Efficacy; Vaccines; White Matter; aducanumab; nan</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1724,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AMP-Activated Protein Kinases; Acetylation; Adaptor Proteins, Signal Transducing; Adenocarcinoma of Lung; Adolescent; Antineoplastic Agents; Apoptosis; Autophagy; Autophagy-Related Protein 8 Family; B7-H1 Antigen; Blastocyst; Body Patterning; Brain; Breast Neoplasms; Calmodulin-Binding Proteins; Carcinogenesis; Cell Differentiation; Cell Line, Tumor; Cell Proliferation; Cell Survival; Cell Transformation, Neoplastic; Child; Chromatin; Cues; DNA-Binding Proteins; Drosophila Proteins; Drug Resistance, Neoplasm; Dynactin Complex; Dyneins; Embryonic Development; Endoderm; Ependymoma; Fertilization; Florida; Gene Expression Regulation, Developmental; Gene Expression Regulation, Neoplastic; Gene Regulatory Networks; Genes, Neurofibromatosis 2; Genes, Regulator; Genetic Background; Glucose; Glycogen Synthase Kinase 3 beta; Glycosylation; Head and Neck Neoplasms; Hippo Signaling Pathway; Histone Deacetylase 1; Histone Deacetylase 2; Histone Deacetylases; Histones; Homeostasis; Immunity, Innate; Immunotherapy; Inflammation; Intercellular Signaling Peptides and Proteins; Interdisciplinary Research; Intracellular Signaling Peptides and Proteins; Kinesins; Lipids; Loss of Function Mutation; Lung Neoplasms; MAP Kinase Signaling System; Mass Spectrometry; Meningeal Neoplasms; Meningioma; Metabolic Networks and Pathways; Metals, Heavy; Microtubule-Associated Proteins; Microtubules; Morbidity; Mutation; Mutation, Missense; N-Myc Proto-Oncogene Protein; Neoplasms; Neurilemmoma; Neurofibromatosis 2; Neurofibromin 2; Organ Size; Organelles; Phosphoric Monoester Hydrolases; Phosphorylation; Physiological Phenomena; Platinum Compounds; Protein Interaction Mapping; Protein Interaction Maps; Protein Serine-Threonine Kinases; Proteins; Proteomics; Publishing; Pyridines; RNA, Long Noncoding; Receptor, Notch1; Regeneration; Sequence Deletion; Serine; Serine-Threonine Kinase 3; Signal Transduction; Stem Cells; TEA Domain Transcription Factors; Transcription Factor MTF-1; Transcription Factors; Tumor Escape; Tumor Suppressor Proteins; Ubiquitin-Protein Ligases; Ubiquitination; Writing; Xenograft Model Antitumor Assays; nan</t>
+          <t>AMP-Activated Protein Kinases; Adaptor Proteins, Signal Transducing; Adenocarcinoma of Lung; Adolescent; Air Pollutants; Air Pollution; Animals, Domestic; Antineoplastic Agents; Apoptosis; Benzothiazoles; Biological Phenomena; Body Patterning; Brain; Carcinogenesis; Catalysis; Cell Line, Tumor; Cell Proliferation; Cell Survival; Cell Transformation, Neoplastic; Child; China; Cities; Cues; DNA-Binding Proteins; Drug Resistance, Neoplasm; Environmental Exposure; Environmental Monitoring; Ependymoma; Fertilization; Florida; Fluorescence; Gene Expression; Gene Expression Regulation, Neoplastic; Genes, Neurofibromatosis 2; Genetic Background; Genomics; Genotype; Glucose; Head and Neck Neoplasms; High-Throughput Screening Assays; Hippo Signaling Pathway; Homeostasis; Hydroxyl Radical; Intercellular Signaling Peptides and Proteins; Interdisciplinary Research; Kinetics; Lipids; Loss of Function Mutation; Lung Neoplasms; MAP Kinase Signaling System; Meningeal Neoplasms; Meningioma; Metabolic Networks and Pathways; Metals, Heavy; Models, Chemical; Morbidity; Mortality; Mutation; Mutation, Missense; Neoplasms; Neurilemmoma; Neurofibromatosis 2; Neurofibromin 2; Organ Size; Ovarian Neoplasms; Oxidation-Reduction; Oxygen; Particulate Matter; Phenotype; Phosphorylation; Physiological Phenomena; Plasmodium falciparum; Platinum; Polyamines; Protein Interaction Maps; Protein Serine-Threonine Kinases; Publishing; Putrescine; Regeneration; Saccharomyces cerevisiae; Saccharomyces cerevisiae Proteins; Sequence Deletion; Signal Transduction; Spermidine; Stem Cells; TEA Domain Transcription Factors; Transcription Factors; Transcriptome; Writing; Xenograft Model Antitumor Assays; nan</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1748,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Adjuvants, Immunologic; Adjuvants, Pharmaceutic; Aged; Aging; Alzheimer Disease; Ampicillin; Amyloid beta-Peptides; Angiotensin Receptor Antagonists; Angiotensin-Converting Enzyme Inhibitors; Anti-Bacterial Agents; Anti-Infective Agents; Antineoplastic Agents, Hormonal; Antioxidants; Appendectomy; Appendicitis; Autistic Disorder; Autoimmune Diseases; Bacteremia; Bacteria; Bacteria, Anaerobic; Bacterial Infections; Bacterial Physiological Phenomena; Bacteriophages; Benchmarking; Biodiversity; Biofilms; Biological Evolution; Biomarkers; Brain; Brain-Gut Axis; Breast Neoplasms; Bronchoalveolar Lavage Fluid; COVID-19; Caregivers; Case-Control Studies; Child; Chromatography, Gas; Clostridioides difficile; Clostridium Infections; Cohort Studies; Coliphages; Colon; Colonic Neoplasms; Colonoscopy; Communicable Diseases; Compassionate Use Trials; Complement C1q; Computational Biology; Critical Illness; Cross Infection; Cryopreservation; Culture Media; Cystic Fibrosis; DNA; Data Management; Dementia; Demography; Dendritic Cells; Diabetes Mellitus, Type 1; Diabetes Mellitus, Type 2; Diagnosis; Diet; Diet Therapy; Diet, Mediterranean; Dietary Fiber; Digestion; Drug Resistance, Bacterial; Drug Resistance, Microbial; Drug Resistance, Multiple, Bacterial; Dysbiosis; Ecology; Ecosystem; Ecuador; Endometriosis; Enterococcus; Enterococcus faecalis; Enterococcus faecium; Epithelium; Escherichia coli; Estonia; Ethics Committees, Research; Fatty Acids, Volatile; Feasibility Studies; Fecal Microbiota Transplantation; Fellowships and Scholarships; Fermentation; Freezing; Gas Chromatography-Mass Spectrometry; Gastroenterology; Gastrointestinal Microbiome; Gene Expression Profiling; Gene Knock-In Techniques; Genome Size; Genomics; Genotype; Germ-Free Life; Global Health; Glycoside Hydrolases; Gram-Negative Bacteria; Gram-Negative Bacterial Infections; Gram-Positive Bacterial Infections; Health; Healthy Volunteers; High-Throughput Nucleotide Sequencing; Hospitalization; Host Microbial Interactions; Host Specificity; Human Body; Hunting; Hydrogen-Ion Concentration; Hypersensitivity; Immunity; Immunocompromised Host; Immunosenescence; Immunotherapy; Incidence; Individuality; Inflammation; Inflammatory Bowel Diseases; Informed Consent; Inpatients; Interdisciplinary Research; Internship and Residency; Intestine, Small; Kinetics; Laboratories; Leadership; Life Cycle Stages; Linezolid; Longitudinal Studies; Lung; Macrophages; Mass Spectrometry; Melanoma; Metabolome; Metabolomics; Metagenome; Metagenomics; Methicillin-Resistant Staphylococcus aureus; Microbial Sensitivity Tests; Microbiology; Microbiota; Microscopy; Microscopy, Fluorescence; Molecular Biology; Molecular Sequence Annotation; Morocco; Mutation; Myeloproliferative Disorders; Neoplasms; Neurodegenerative Diseases; Neuroinflammatory Diseases; Nutrients; Obesity; Optical Imaging; Outcome Assessment, Health Care; Pandemics; Patient Discharge; Phage Therapy; Pilot Projects; Planets; Pneumonia; Precision Medicine; Premature Birth; Prevalence; Probiotics; Pseudomonas; Pseudomonas aeruginosa; Public Health; Pyocyanine; RNA; RNA, Ribosomal, 16S; Random Forest; Receptors, Complement; Recommended Dietary Allowances; Reproducibility of Results; Research Personnel; Resilience, Psychological; Respiration; Respiration Disorders; Respiratory Mucosa; Respiratory System; Respiratory Tract Infections; Sequence Analysis, DNA; Sequence Analysis, RNA; Sewage; Sex Characteristics; Societies, Scientific; Sputum; Staphylococcal Infections; Staphylococcus; Staphylococcus aureus; Stenotrophomonas; Stenotrophomonas maltophilia; Stomach; Streptococcus; Surface-Active Agents; Tamoxifen; Tetracycline; Tobacco Smoke Pollution; Transcriptome; Translational Research, Biomedical; Translational Science, Biomedical; Vaccine Efficacy; Vancomycin; Virome; Viruses; Volatile Organic Compounds; Volunteers; Wastewater; Wastewater-Based Epidemiological Monitoring; Western World; Young Adult</t>
+          <t>Adjuvants, Immunologic; Adjuvants, Pharmaceutic; Aged; Aging; Alzheimer Disease; Ampicillin; Amyloid beta-Peptides; Angiotensin Receptor Antagonists; Angiotensin-Converting Enzyme Inhibitors; Anti-Bacterial Agents; Anti-Infective Agents; Antineoplastic Agents, Hormonal; Antioxidants; Appendectomy; Appendicitis; Autistic Disorder; Autoimmune Diseases; Bacteremia; Bacteria; Bacteria, Anaerobic; Bacterial Infections; Bacterial Physiological Phenomena; Bacteriophages; Benchmarking; Biodiversity; Biofilms; Biological Evolution; Biomarkers; Brain; Brain-Gut Axis; Breast Neoplasms; Bronchoalveolar Lavage Fluid; COVID-19; Caregivers; Case-Control Studies; Child; Chromatography, Gas; Clostridioides difficile; Clostridium Infections; Cohort Studies; Coliphages; Colon; Colonic Neoplasms; Colonoscopy; Communicable Diseases; Compassionate Use Trials; Complement C1q; Computational Biology; Critical Illness; Cross Infection; Cryopreservation; Culture Media; Cystic Fibrosis; DNA; Data Management; Dementia; Demography; Dendritic Cells; Diabetes Mellitus, Type 1; Diabetes Mellitus, Type 2; Diagnosis; Diet; Diet Therapy; Diet, Mediterranean; Dietary Fiber; Digestion; Drug Resistance, Bacterial; Drug Resistance, Microbial; Drug Resistance, Multiple, Bacterial; Dysbiosis; Ecology; Ecosystem; Ecuador; Endometriosis; Enterococcus; Enterococcus faecalis; Enterococcus faecium; Epithelium; Escherichia coli; Estonia; Ethics Committees, Research; Fatty Acids, Volatile; Feasibility Studies; Fecal Microbiota Transplantation; Fellowships and Scholarships; Fermentation; Freezing; Gas Chromatography-Mass Spectrometry; Gastroenterology; Gastrointestinal Microbiome; Gene Expression Profiling; Gene Knock-In Techniques; Genome Size; Genomics; Genotype; Germ-Free Life; Global Health; Glycoside Hydrolases; Gram-Negative Bacteria; Gram-Negative Bacterial Infections; Gram-Positive Bacterial Infections; Health; Healthy Volunteers; High-Throughput Nucleotide Sequencing; Hospitalization; Host Microbial Interactions; Host Specificity; Human Body; Hunting; Hydrogen-Ion Concentration; Hypersensitivity; Immunity; Immunocompromised Host; Immunosenescence; Immunotherapy; Incidence; Individuality; Inflammation; Inflammatory Bowel Diseases; Informed Consent; Inpatients; Interdisciplinary Research; Internship and Residency; Intestine, Small; Kinetics; Laboratories; Leadership; Life Cycle Stages; Linezolid; Longitudinal Studies; Lung; Macrophages; Mass Spectrometry; Melanoma; Metabolome; Metabolomics; Metagenome; Metagenomics; Methicillin-Resistant Staphylococcus aureus; Microbial Sensitivity Tests; Microbiology; Microbiota; Microscopy; Microscopy, Fluorescence; Molecular Biology; Molecular Sequence Annotation; Morocco; Mutation; Myeloproliferative Disorders; Neoplasms; Neurodegenerative Diseases; Neuroinflammatory Diseases; Nutrients; Obesity; Optical Imaging; Outcome Assessment, Health Care; Pandemics; Patient Discharge; Phage Therapy; Pilot Projects; Planets; Pneumonia; Precision Medicine; Premature Birth; Prevalence; Probiotics; Pseudomonas; Pseudomonas aeruginosa; Public Health; Pyocyanine; RNA; RNA, Ribosomal, 16S; Random Forest; Receptors, Complement; Recommended Dietary Allowances; Reproducibility of Results; Research Personnel; Resilience, Psychological; Respiration; Respiration Disorders; Respiratory Mucosa; Respiratory System; Respiratory Tract Infections; Sequence Analysis, DNA; Sequence Analysis, RNA; Sewage; Sex Characteristics; Societies, Scientific; Sputum; Staphylococcal Infections; Staphylococcus; Staphylococcus aureus; Stenotrophomonas; Stenotrophomonas maltophilia; Stomach; Streptococcus; Surface-Active Agents; Tamoxifen; Tetracycline; Tobacco Smoke Pollution; Transcriptome; Translational Research, Biomedical; Translational Science, Biomedical; Vaccine Efficacy; Vancomycin; Virome; Viruses; Volatile Organic Compounds; Volunteers; Wastewater; Wastewater-Based Epidemiological Monitoring; Western World; Young Adult; nan</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1760,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Animals, Genetically Modified; Animals, Wild; Anti-Bacterial Agents; Anti-Inflammatory Agents; Antioxidants; Bacteria; Bacterial Physiological Phenomena; Bacterial Proteins; Bacteriophages; Biological Evolution; Chromosomes; Climate Change; DNA Damage; Diabetes Mellitus; Disease Transmission, Infectious; Drug Resistance, Microbial; Ecology; Ecosystem; Escherichia coli; Evolution, Molecular; Feasibility Studies; Food Supply; Gastrointestinal Microbiome; Gastrointestinal Motility; Gene Flow; Gene Transfer, Horizontal; Genetic Engineering; Genetics; Homeostasis; Host Microbial Interactions; Hyperglycemia; Imaging, Three-Dimensional; Immune System; Inflammation; Intestines; Macrophages; Metronidazole; Microbial Consortia; Microbiology; Microbiota; Motivation; Nitroreductases; Oxidation-Reduction; Peptides; Planets; Predatory Behavior; Public Health; Reactive Oxygen Species; SOS Response, Genetics; Soil; Symbiosis; Synthetic Biology; Systems Biology; Type VI Secretion Systems; Vibrio cholerae; Zebrafish; nan</t>
+          <t>Animals, Genetically Modified; Animals, Wild; Anti-Bacterial Agents; Anti-Inflammatory Agents; Antioxidants; Bacteria; Bacterial Physiological Phenomena; Bacterial Proteins; Bacteriophages; Biological Evolution; Brain; Chromosomes; Climate Change; DNA Damage; Diabetes Mellitus; Disease Transmission, Infectious; Drug Resistance, Microbial; Ecology; Ecosystem; Escherichia coli; Evolution, Molecular; Feasibility Studies; Food Supply; Gastrointestinal Microbiome; Gastrointestinal Motility; Gene Flow; Gene Transfer, Horizontal; Genetic Engineering; Genetics; Homeostasis; Host Microbial Interactions; Hyperglycemia; Imaging, Three-Dimensional; Immune System; Inflammation; Intestines; Macrophages; Metronidazole; Microbial Consortia; Microbiology; Microbiota; Motivation; Nitroreductases; Oxidation-Reduction; Peptides; Planets; Predatory Behavior; Public Health; Reactive Oxygen Species; SOS Response, Genetics; Soil; Symbiosis; Synthetic Biology; Systems Biology; Type VI Secretion Systems; Vibrio cholerae; Virion; Zebrafish; nan</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1772,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Acetate-CoA Ligase; Acetyl Coenzyme A; Acetylation; Activin Receptors, Type I; Adverse Childhood Experiences; Aging; Alzheimer Disease; Amyloid beta-Peptides; Antibodies; Anxiety; Autism Spectrum Disorder; Blotting, Western; Brain; Brain Neoplasms; Brain-Derived Neurotrophic Factor; Calcium; Censuses; Child; Chin; Cholinergic Agents; Cholinergic Neurons; Chromatin; Chromatin Immunoprecipitation; Circadian Rhythm; Cocaine; Cognition; Color Vision Defects; Conditioning, Classical; Cues; Cuprizone; DNA; DNA Methylation; DNA-Binding Proteins; Demyelinating Diseases; Dopaminergic Neurons; Drug-Seeking Behavior; Entropy; Epigenesis, Genetic; Epigenetic Memory; Epigenomics; Fear; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genes, X-Linked; Genetic Variation; Genetics; Genomics; Habenula; High-Throughput Nucleotide Sequencing; Hippocampus; Histone Code; Histones; Immunohistochemistry; Intellectual Disability; Interneurons; Jumonji Domain-Containing Histone Demethylases; Leucine Zippers; Life Change Events; Long-Term Potentiation; Longevity; Mass Spectrometry; Medium Spiny Neurons; Membrane Glycoproteins; Memory; Memory Consolidation; Memory, Long-Term; Mental Disorders; Mental Health; Microglia; Mutation; N-nitrosoiminodiacetic acid; Neurodegenerative Diseases; Neurogenesis; Neuroglia; Neuroinflammatory Diseases; Neuronal Plasticity; Neurons; Neurosciences; Nicotine; Nucleosomes; Nucleus Accumbens; Occupations; Pharmaceutical Preparations; Physical Conditioning, Animal; Plaque, Amyloid; Polyadenylation; Polymerase Chain Reaction; Promoter Regions, Genetic; Proteomics; RNA Splicing; RNA, Catalytic; RNA, Messenger; RNA-Binding Proteins; Radiation Dose Hypofractionation; Radiation Exposure; Radiotherapy; Radiotherapy Dosage; Receptors, Immunologic; Recurrence; Reproducibility of Results; Resilience, Psychological; Reward; Sequence Analysis, RNA; Sleep; Spatial Memory; Substance-Related Disorders; Synapses; Synaptic Transmission; Trans-Activators; Transcription Factors; Transcriptome; Wood; X Chromosome; histone deacetylase 3; nan</t>
+          <t>Abortion, Induced; Acetyl Coenzyme A; Acetylation; Activin Receptors, Type I; Adverse Childhood Experiences; Aged; Aging; Alzheimer Disease; Amyloid beta-Peptides; Antibodies; Anxiety; Autism Spectrum Disorder; Blotting, Western; Brain; Brain-Derived Neurotrophic Factor; Calcium; Cannabinoids; Cannabis; Cardiovascular System; Censuses; Chin; Cholinergic Agents; Cholinergic Neurons; Chromatin; Chromatin Immunoprecipitation; Cocaine; Cocaine-Related Disorders; Cognition; Color Vision Defects; Conditioning, Operant; Cues; Cuprizone; DNA; DNA Methylation; DNA-Binding Proteins; Delivery of Health Care; Demyelinating Diseases; Depression; Dopamine Uptake Inhibitors; Dopaminergic Neurons; Drug-Seeking Behavior; Epigenesis, Genetic; Epigenetic Memory; Epigenomics; Gastrin-Secreting Cells; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genes, X-Linked; Genetic Variation; Genetics; Genomics; Habenula; High-Throughput Nucleotide Sequencing; Hippocampus; Histone Code; Histone Deacetylases; Histones; Immunohistochemistry; Intellectual Disability; Interneurons; Jumonji Domain-Containing Histone Demethylases; Leucine Zippers; Life Change Events; Long-Term Potentiation; Longevity; Mass Spectrometry; Maternal Health; Medium Spiny Neurons; Membrane Glycoproteins; Memory; Memory Consolidation; Memory, Long-Term; Mental Health; Microglia; Multivariate Analysis; Mutation; N-nitrosoiminodiacetic acid; Neoplasms; Neurodegenerative Diseases; Neurogenesis; Neuroglia; Neuroinflammatory Diseases; Neuronal Plasticity; Neurons; Neurosciences; Nicotine; Nucleosomes; Nucleus Accumbens; Occupations; Pharmaceutical Preparations; Physical Conditioning, Animal; Plaque, Amyloid; Point Mutation; Polyadenylation; Polymerase Chain Reaction; Pregnancy; Promoter Regions, Genetic; Proteomics; Psychiatry; Public Health; RNA Splicing; RNA, Catalytic; RNA, Messenger; RNA-Binding Proteins; Radiation Dose Hypofractionation; Radiotherapy Dosage; Receptors, Immunologic; Recurrence; Reproducibility of Results; Resilience, Psychological; Reward; Schools; Self Administration; Self Report; Sequence Analysis, RNA; Spatial Memory; Speech; Substance-Related Disorders; Synapses; Synaptic Transmission; Trans-Activators; Transcription Factors; Transcriptome; Wood; X Chromosome; histone deacetylase 3; hydrogen sulfite</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1784,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Bacteria; Coculture Techniques; Gastrointestinal Microbiome; Microbiota; Phylogeny</t>
+          <t>Bacteria; Coculture Techniques; Ecosystem; Gastrointestinal Microbiome; Microbiota; Phylogeny; Population Density; Ruminants</t>
         </is>
       </c>
     </row>
@@ -1788,319 +1796,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Adolescent; Adverse Childhood Experiences; Age Factors; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amygdala; Amyloid; Amyloid beta-Peptides; Anhedonia; Aniline Compounds; Anniversaries and Special Events; Anxiety; Artificial Intelligence; Biological Specimen Banks; Biomarkers; Brain; Cerebrovascular Disorders; Child; Clinical Trials as Topic; Cognition; Cognitive Dysfunction; Cohort Studies; Community-Institutional Relations; Compulsive Behavior; Computational Biology; Computer Simulation; Consensus; Data Aggregation; Data Collection; Data Management; Data Science; Dementia; Depression; Discrimination, Psychological; Documentation; Down Syndrome; Drug Discovery; Ecosystem; Electrophysiological Phenomena; Emotions; Entorhinal Cortex; Exercise; Financial Management; Frontal Lobe; Gamma Rhythm; Head; Hippocampus; Infant, Newborn; Interdisciplinary Research; Interneurons; Learning; Longitudinal Studies; Machine Learning; Magnetic Resonance Imaging; Memory; Memory Consolidation; Memory Disorders; Memory, Episodic; Mental Disorders; Mental Recall; Metadata; Midline Thalamic Nuclei; Motivation; Neocortex; Nervous System Diseases; Neural Pathways; Neuroimaging; Neurophysiology; Neuropsychological Tests; Neuropsychology; Nucleus Accumbens; Oceans and Seas; Pattern Recognition, Physiological; Peptide Fragments; Phenotype; Physicians; Policy; Polyethylene Terephthalates; Polysomnography; Positron-Emission Tomography; Prefrontal Cortex; Premature Birth; Primates; Prospective Studies; Proteostasis Deficiencies; Psychiatry; Publishing; Quality of Life; Reward; Risk Factors; Saliva; Sleep; Software; Spectrum Analysis; Stress Disorders, Post-Traumatic; Surveys and Questionnaires; Temporal Lobe; Theta Rhythm; UK Biobank; Wakefulness; White Matter; Writing; Young Adult; tau Proteins</t>
+          <t>Adolescent; Adverse Childhood Experiences; Age Factors; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amygdala; Amyloid; Amyloid beta-Peptides; Anhedonia; Aniline Compounds; Anniversaries and Special Events; Anxiety; Artificial Intelligence; Biological Specimen Banks; Biomarkers; Brain; Cerebral Small Vessel Diseases; Cerebrovascular Disorders; Child; Clinical Trials as Topic; Cognition; Cognitive Dysfunction; Cohort Studies; Community-Institutional Relations; Compulsive Behavior; Computational Biology; Computer Simulation; Consensus; Data Aggregation; Data Collection; Data Management; Data Science; Dementia; Depression; Discrimination, Psychological; Documentation; Down Syndrome; Drug Discovery; Ecosystem; Electrophysiological Phenomena; Emotions; Entorhinal Cortex; Exercise; Financial Management; Frontal Lobe; Gamma Rhythm; Head; Hippocampus; Hypoxia; Infant, Newborn; Interdisciplinary Research; Interneurons; Learning; Longitudinal Studies; Machine Learning; Magnetic Resonance Imaging; Memory; Memory Consolidation; Memory Disorders; Memory, Episodic; Mental Disorders; Mental Recall; Metadata; Midline Thalamic Nuclei; Motivation; Neocortex; Nervous System Diseases; Neural Pathways; Neuroimaging; Neurophysiology; Neuropsychological Tests; Neuropsychology; Nucleus Accumbens; Oceans and Seas; Pattern Recognition, Physiological; Peptide Fragments; Phenotype; Physicians; Policy; Polyethylene Terephthalates; Polysomnography; Positron-Emission Tomography; Prefrontal Cortex; Premature Birth; Primates; Prospective Studies; Proteostasis Deficiencies; Psychiatry; Publishing; Quality of Life; Reward; Risk Factors; Saliva; Sleep; Sleep Apnea, Obstructive; Software; Spectrum Analysis; Stress Disorders, Post-Traumatic; Surveys and Questionnaires; Temporal Lobe; Theta Rhythm; UK Biobank; Wakefulness; White Matter; Writing; Young Adult; tau Proteins</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002B87155CDAEBE54E8A991CDFF09FE870" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07d22f826efb92a1b7f7a52cdc9ab0c0">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ccd2e96c-ba06-41a4-9d14-ee5d4767a409" xmlns:ns3="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f50f4dd1661db9c8120150ec829b0b2" ns2:_="" ns3:_="">
-    <xsd:import namespace="ccd2e96c-ba06-41a4-9d14-ee5d4767a409"/>
-    <xsd:import namespace="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns3:ProjectRole" minOccurs="0"/>
-                <xsd:element ref="ns3:Notes" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ccd2e96c-ba06-41a4-9d14-ee5d4767a409" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{5edd41bb-06d5-49d8-8697-11a388b6c936}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="ccd2e96c-ba06-41a4-9d14-ee5d4767a409">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="733ad1a4-bcb6-4664-8873-2816a39d1396" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="ProjectRole" ma:index="26" nillable="true" ma:displayName="Project Role" ma:format="Dropdown" ma:internalName="ProjectRole">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="Senior/Key Person"/>
-          <xsd:enumeration value="Other Personnel"/>
-          <xsd:enumeration value="Advisory Board"/>
-          <xsd:enumeration value="Evaluator"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Notes" ma:index="27" nillable="true" ma:displayName="Notes" ma:format="Dropdown" ma:internalName="Notes">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <ProjectRole xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" xsi:nil="true"/>
-    <Notes xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ccd2e96c-ba06-41a4-9d14-ee5d4767a409" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34E84BF1-5F9B-4096-B936-0D48D7C5F545}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17A7E850-9D4D-44B4-8B9C-953269D84094}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1332A14B-ECB0-424C-8FEF-A4568240472F}"/>
 </file>
--- a/faculty_unique_mesh_terms.xlsx
+++ b/faculty_unique_mesh_terms.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B115"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,1364 +443,1092 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Allison, Steven</t>
+          <t>Acharya, Munjal Mahendra</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adaptation, Physiological; Australia; Authorship; Bacteria; Biodegradation, Environmental; Biodiversity; Biological Evolution; Biomass; California; Carbon; Carbon Cycle; Climate; Climate Change; Communication; Conservation of Natural Resources; Coral Reefs; Curriculum; Drought Resistance; Droughts; Earth, Planet; Ecological and Environmental Phenomena; Ecosystem; Education, Graduate; Environmental Justice; Environmental Microbiology; Environmental Science; Enzymes; Extreme Weather; Feasibility Studies; Financial Management; Forests; Genomics; Government; Government Agencies; Grassland; Greenhouse Gases; Hot Temperature; Humanities; Interdisciplinary Communication; Interdisciplinary Research; Introduced Species; Isoptera; Life History Traits; Loma; Metagenome; Metagenomics; Methane; Microbial Interactions; Microbiota; Mutation; Needs Assessment; Nitrification; Nitrogen; Phylogeny; Plant Leaves; Plants; Policy; Policy Making; Private Sector; Program Evaluation; Resilience, Psychological; Risk Assessment; Skin Pigmentation; Social Planning; Social Sciences; Soil; Soil Microbiology; Sphingomonas; Stress, Physiological; Temperature; Trees; Tropical Climate; Uncertainty; Water; Wildfires; Wood; Workforce; Writing; nan</t>
+          <t>Adolescent; Aged; Aged, 80 and over; Alzheimer Disease; Amyloid beta-Peptides; Antineoplastic Agents; Behavior, Animal; Brain; Brain Neoplasms; Brain-Derived Neurotrophic Factor; Breast Neoplasms; CA1 Region, Hippocampal; Cell Communication; Cognition; Cognitive Dysfunction; Cranial Irradiation; Cytokines; Dendrites; Dose-Response Relationship, Radiation; Doxorubicin; Dynamin I; Dynamins; Ethnicity; Extinction, Psychological; Extracellular Vesicles; Fear; GABAergic Neurons; Glial Cell Line-Derived Neurotrophic Factor; Glioblastoma; Glutamic Acid; Hippocampus; Immune Checkpoint Inhibitors; Incidence; Inflammation; Interleukin-21; Interleukins; Long-Term Potentiation; Longitudinal Studies; Microglia; Neoplasms; Neurodegenerative Diseases; Neurogenesis; Neuroinflammatory Diseases; Neuronal Plasticity; Neurons; Neuroprotective Agents; Neurosciences; Patient Reported Outcome Measures; Plaque, Amyloid; Prefrontal Cortex; Prospective Studies; Pyramidal Cells; Quality of Life; RNA, Long Noncoding; Radiation Exposure; Receptors, Interleukin-21; Riluzole; Risk Factors; Self Report; Synapses; Translational Research, Biomedical; Tumor Microenvironment; Young Adult</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Arora, Kavita</t>
+          <t>Calof, Anne L</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Binding Sites; CDC2 Protein Kinase; Cadmium; Caenorhabditis elegans; Caenorhabditis elegans Proteins; Cdc20 Proteins; Cell Line, Tumor; Cells, Cultured; Computational Biology; Conserved Sequence; Cyclin B; Cyclin B1; Cyclin B2; DNA-Binding Proteins; Developmental Biology; Embryo, Nonmammalian; Gene Expression Regulation; Genetics; HEK293 Cells; HeLa Cells; Hedgehog Proteins; Hippo Signaling Pathway; Homeostasis; Inactivation, Metabolic; MAP Kinase Signaling System; Metabolism; Mitogen-Activated Protein Kinase 1; Mitosis; Mutation; Neoplasms; Phosphorylation; Protein Binding; Protein Serine-Threonine Kinases; Repressor Proteins; Signal Transduction; Stress, Physiological; Transcription Factor MTF-1; Transcription Factors; Transcription, Genetic; Transforming Growth Factor beta; Tumor Suppressor Proteins; Zinc; Zinc Finger Protein GLI1</t>
+          <t>Animals, Genetically Modified; Brain; CHO Cells; Cell Cycle Proteins; Cricetulus; Databases, Factual; De Lange Syndrome; Gastrulation; Gene Expression; Green Fluorescent Proteins; HEK293 Cells; Heterozygote; Metronidazole; Mutation; Nitroreductases; Phenotype; Pregnancy; Prodrugs; Protein Engineering; Proteins; Recombinant Proteins; Retina; Transcriptome; Vibrio; X-Ray Microtomography; Zebrafish</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Atwood, Scott</t>
+          <t>Chen, Lulu Y</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Algorithms; Allografts; Binding Sites; Bioprinting; Brain; CRISPR-Cas Systems; Carcinogenesis; Carcinoma, Basal Cell; Carcinoma, Basosquamous; Cell Communication; Cell Differentiation; Cell Line, Tumor; Cell Proliferation; Cells, Cultured; Chromatography, Liquid; Clone Cells; Clustered Regularly Interspaced Short Palindromic Repeats; Computer Simulation; Conserved Sequence; Dermis; Drug Resistance; Ecosystem; Epidermal Cells; Epidermis; Epithelial Cells; Extrude; Gene Expression Profiling; Gene Regulatory Networks; Genes, Suppressor; Genetic Techniques; Hair Follicle; Hedgehog Proteins; Hedgehogs; HhAntag691; Immune System; Immunity; Immunotherapy; Intercellular Signaling Peptides and Proteins; Keratinocytes; Lung Neoplasms; MAP Kinase Signaling System; Membrane Proteins; Microphysiological Systems; Mitogen-Activated Protein Kinase 1; Molecular Biology; Multiomics; Mutation; Neoplasms; Neutrophil Activation; Neutrophils; Nucleosides; Organoids; Phosphorylation; Phosphotransferases; Pluripotent Stem Cells; Prostate; Protein Binding; Protein Kinase C; RNA; Repressor Proteins; Sebaceous Glands; Secretome; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Skin; Skin Neoplasms; Small Cell Lung Carcinoma; Stem Cells; T-Lymphocytes; Tandem Mass Spectrometry; Tissue Engineering; Transcription Factors; Transcriptome; Tumor Microenvironment; Wnt Signaling Pathway; Zinc Finger Protein GLI1; cemiplimab; nan</t>
+          <t>Adipocytes; Basolateral Nuclear Complex; Behavior, Animal; Boron Compounds; Cell Adhesion Molecules, Neuronal; Central Nervous System Stimulants; Conditioning, Operant; Corticotropin-Releasing Hormone; Dopaminergic Neurons; Fat Necrosis; Gene Deletion; Hippocampus; Homeodomain Proteins; Homing Behavior; Lipolysis; Maze Learning; Nerve Net; Nerve Tissue Proteins; Neural Cell Adhesion Molecules; Nucleus Accumbens; Pilot Projects; Presynaptic Terminals; Reversal Learning; Reward; Seizures; Sex Characteristics; Swine; Synaptic Transmission; Transcription Factors; gamma-Aminobutyric Acid</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azizi, Emanuel</t>
+          <t>Diaz Alonso, Javier</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Achilles Tendon; Aging; Alligators and Crocodiles; Anura; Biocompatible Materials; Biomechanical Phenomena; Biomimetic Materials; Bufo marinus; Connective Tissue; Conservation of Energy Resources; Elasticity; Elastomers; Electromyography; Environment; Exercise; Extremities; Forelimb; Gait; Galliformes; Hindlimb; Isometric Contraction; Locomotion; Lower Extremity; Motor Activity; Movement; Muscle Contraction; Muscle Fibers, Skeletal; Muscle Spindles; Muscle, Skeletal; Nonlinear Dynamics; Physics; Poaceae; Robotic Surgical Procedures; Robotics; Running; Sand; Stress, Mechanical; Swimming; Temperature; Tendons; Torque; Trees; Virtual Reality; Viscosity; Walking</t>
+          <t>Disks Large Homolog 4 Protein; Long-Term Potentiation; Nuclear Proteins; Receptors, AMPA; Synapses; Synaptic Transmission</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Baker, Nicholas</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>Ewell, Laura Ann</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Acetamides; Action Potentials; Brain Injuries; Cerebellum; Dendrites; Dentate Gyrus; Dystonia; Epilepsy; GTP-Binding Proteins; Hippocampus; Neurons; Purkinje Cells; Pyramidal Cells; Reproducibility of Results; Seizures; Software; User-Computer Interface</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bardwell, Lee</t>
+          <t>Gall, Christine M</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alleles; Binding Sites; CDC2 Protein Kinase; Cadmium; Caenorhabditis elegans; Caenorhabditis elegans Proteins; Cdc20 Proteins; Cell Line, Tumor; Cells, Cultured; Child; Clinical Relevance; Comprehension; Congenital Hypothyroidism; Conserved Sequence; Cyclin B; Cyclin B1; Cyclin B2; DNA; DNA-Binding Proteins; Developmental Disabilities; Diabetes Mellitus; Embryo, Nonmammalian; Evidence Gaps; Extracellular Signal-Regulated MAP Kinases; Gene Expression Regulation; Greig cephalopolysyndactyly syndrome; HEK293 Cells; HeLa Cells; Hedgehog Proteins; Hippo Signaling Pathway; Homeostasis; Inactivation, Metabolic; Infant, Newborn; Ligands; MAP Kinase Signaling System; Mitogen-Activated Protein Kinase 1; Mitogen-Activated Protein Kinases; Mitosis; Mutation; Neoplasms; Nuclear Matrix-Associated Proteins; Phosphatidylinositol 3-Kinases; Phosphorylation; Protein Binding; Protein Kinases; Protein Serine-Threonine Kinases; Repressor Proteins; Saccharomyces cerevisiae; Schizophrenia; Signal Transduction; Stress, Physiological; Transcription Factor MTF-1; Transcription Factors; Transcription, Genetic; Transcriptional Activation; Tumor Suppressor Proteins; Zinc; Zinc Finger Protein GLI1; ras GTPase-Activating Proteins</t>
+          <t>Arachidonic Acids; CA1 Region, Hippocampal; CA3 Region, Hippocampal; Calcium; Dentate Gyrus; Dizocilpine Maleate; Electric Stimulation; Endocannabinoids; Entorhinal Cortex; Estrogen Receptor alpha; Excitatory Postsynaptic Potentials; Glycerides; Hippocampus; Long-Term Potentiation; Memory; Memory, Episodic; Microglia; Nerve Net; Neural Pathways; Neuronal Plasticity; Perforant Pathway; Phenols; Piperidines; Rats, Sprague-Dawley; Receptors, N-Methyl-D-Aspartate; Rodentia; Sex Characteristics; Sex Factors; Signal Transduction; Spatial Memory; Synapses; Theta Rhythm; gamma-Aminobutyric Acid</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Blumberg, Bruce</t>
+          <t>Hunt, Robert Francis</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3T3-L1 Cells; Adipocytes; Adipogenesis; Adipose Tissue; Adolescent; Autism Spectrum Disorder; Autistic Disorder; Benzamides; Caenorhabditis elegans; Cannabidiol; Cell Differentiation; Cell Line, Transformed; Child; Child, Preschool; Chromatin; Consensus; DNA; DNA Methylation; Diabetes Mellitus; Diabetes Mellitus, Type 2; Diet, Fat-Restricted; Diet, High-Fat; Diet, Western; Dietary Fats; Drinking Water; Endocrine Disruptors; Energy Metabolism; Environmental Exposure; Epidemiologic Studies; Epigenesis, Genetic; Epigenomics; Fasting; Flutamide; Genetic Predisposition to Disease; Genetics; Germ Cells; Histones; Inheritance Patterns; Insulin Resistance; Insulysin; Leptin; Lipids; Lipogenesis; Lipolysis; Liver; Mesenchymal Stem Cells; Metabolic Diseases; Methylation; MicroRNAs; Multiomics; Mutation; Noncommunicable Diseases; Obesity; Oxazoles; PPAR gamma; Pandemics; Pesticides; Phenotype; Pregnancy; Pregnane X Receptor; Prenatal Exposure Delayed Effects; Pyridines; Receptors, Cytoplasmic and Nuclear; Receptors, Steroid; Retinoid X Receptors; Rosiglitazone; Spermatozoa; Trialkyltin Compounds; Weight Gain; Xenobiotics; Zebrafish; vinclozolin</t>
+          <t>Acyltransferases; Brain; Brain Injuries; Brain Injuries, Traumatic; Brain Mapping; Endocytosis; Glycosylation; Hippocampus; Homing Behavior; Interneurons; Long-Term Potentiation; Membrane Proteins; Memory; Memory Disorders; Nerve Net; Neurogenesis; Neurons; Peptides; Pinocytosis; Protein Kinase C; Receptors, AMPA; Seizures; Sex Characteristics; Synapses; Synaptic Transmission</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Blurton-Jones, Mathew</t>
+          <t>Igarashi, Kei</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Acetylation; Administration, Inhalation; Aged; Aging; Alleles; Alzheimer Disease; Amino Acid Sequence; Amyloid beta-Peptides; Amyloidogenic Proteins; Amyloidosis; Antibodies; Antibodies, Monoclonal; Apolipoprotein E3; Apolipoprotein E4; Apolipoproteins E; Astrocytes; Autoimmune Diseases; Biomarkers; Blood-Brain Barrier; Brain; Brain Neoplasms; Breast Neoplasms; C9orf72 Protein; Calcinosis; Calcium; Calcium Signaling; Caregivers; Cell Death; Cell Movement; Cell- and Tissue-Based Therapy; Cells, Cultured; Central Nervous System; Chemokines; Chemotaxis; Chimera; Cholesterol; Chromatin; Chromatin Immunoprecipitation Sequencing; Coculture Techniques; Cognition; Cognitive Dysfunction; Complement C1q; Cyclic AMP; Cytokines; Dementia; Diabetes Mellitus; Diet; Disease Progression; Drug Development; Endoplasmic Reticulum; Endosomal Sorting Complexes Required for Transport; Endothelial Cells; Epigenesis, Genetic; Ferroptosis; Frontal Lobe; Frontotemporal Dementia; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genome-Wide Association Study; Genomics; Gliosis; Grassland; Hepatitis A Virus Cellular Receptor 2; Hippocampus; Histones; Homeostasis; Housing Quality; Immunohistochemistry; Immunotherapy; Induced Pluripotent Stem Cells; Infant; Infant, Newborn; Inflammation; Inflammation Mediators; Injections, Intraperitoneal; Interferon-gamma; Interferons; Interleukin-17; Interleukin-1beta; Intermediate Filaments; Intracranial Hemorrhages; Isothiocyanates; Leukoencephalopathies; Lipid Metabolism; Lipid Peroxidation; Lipopolysaccharides; Liver Diseases; Lysosomes; Macrophage Colony-Stimulating Factor; Macrophages; Microglia; Microscopy; Microtubules; Mitochondria; Monocytes; Multiple Sclerosis; Mutation; Mycoses; Myelin Basic Protein; Myelin Sheath; Myeloid Cells; NF-E2-Related Factor 2; Neprilysin; Nervous System Diseases; Nervous System Malformations; Neurites; Neurodegenerative Diseases; Neurofibrillary Tangles; Neuroinflammatory Diseases; Neurons; Neutrophils; Nucleotide Motifs; Obesity; Organelles; Organic Chemicals; Organoids; Outcome Assessment, Health Care; Oxidative Stress; Parkinson Disease; Patient Advocacy; Phagocytosis; Phenotype; Phosphorylation; Physicians; Pick Disease of the Brain; Plaque, Amyloid; Pluripotent Stem Cells; Presenilin-1; Prosencephalon; Protein Isoforms; Proteomics; Quantitative Trait Loci; RNA; Rare Diseases; Receptor, Macrophage Colony-Stimulating Factor; Receptor, Transforming Growth Factor-beta Type II; Receptors, Chimeric Antigen; Receptors, Granulocyte-Macrophage Colony-Stimulating Factor; Research Report; Resilience, Psychological; Risk Factors; Schizophrenia; Sequence Analysis, RNA; Sex Factors; Signal Transduction; Single-Cell Gene Expression Analysis; Smad2 Protein; Social Cohesion; Stem Cell Research; Stem Cells; Sulfoxides; Synaptophysin; Tauopathies; Thalamus; Tissue Distribution; Toll-Like Receptor 4; Transcription Factors; Transcriptional Activation; Transcriptome; Transforming Growth Factor beta; Transplantation, Heterologous; Treatment Outcome; Twins, Monozygotic; Weaning; White Matter; Whole Genome Sequencing; Xenon; anti-synaptophysin; heparin proteoglycan; peptide A; tau Proteins</t>
+          <t>Alzheimer Disease; Brain; Cognition; Entorhinal Cortex; Hippocampus; Learning; Memory; Neurofibrillary Tangles; Neurons; Olfactory Bulb; Olfactory Cortex; Olfactory Pathways; Olfactory Perception; Optogenetics; Prefrontal Cortex; Punishment; Reward; Smell</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bracken, Matthew</t>
+          <t>Lyon, David Christian</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alaska; Ammonium Compounds; Biodiversity; Biomass; California; Carbon Dioxide; Climate Change; Conservation of Natural Resources; Curriculum; Ecological and Environmental Phenomena; Ecosystem; Extinction, Biological; Food Chain; Hydrogen-Ion Concentration; Kelp; Macrocystis; Marine Biology; Mollusca; Nitrates; Nitrogen; Oceans and Seas; Oxygen; Physiological Phenomena; Portugal; Seawater; Seaweed; Urea</t>
+          <t>Aging; Brain; Brain Injuries, Traumatic; Brain Mapping; CRISPR-Cas Systems; Cell-Penetrating Peptides; Ceramidases; Chromatin; DNA; DNA Mutational Analysis; Electrophysiological Phenomena; Evoked Potentials, Visual; Eye Proteins; Gene Editing; Glaucoma; HEK293 Cells; Interneurons; Intraocular Pressure; Leber Congenital Amaurosis; Lipids; Liposomes; Mice, Mutant Strains; Mutation; Nanoparticles; Neurons; Receptors, Adiponectin; Retinal Cone Photoreceptor Cells; Retinal Degeneration; Retinal Diseases; Retinal Ganglion Cells; Retinitis Pigmentosa; Rhodopsin; Ribonucleoproteins; cis-trans-Isomerases</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Briscoe, Adriana</t>
+          <t>Piomelli, Daniele</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Indian or Alaska Native; Antibody Specificity; Bees; Binding Sites; Biological Mimicry; Blotting, Western; Butterflies; Carrier Proteins; Central Nervous System; Chromosomes; Clustered Regularly Interspaced Short Palindromic Repeats; Colombia; Color; Color Vision; Communication; Costa Rica; Crystallization; Drosophila melanogaster; Ecology; Ecosystem; Electrophysiology; Evolution, Molecular; Eye; Farms; Forests; Gardening; Gene Duplication; Gene Editing; Gene Expression Profiling; Genomics; Guyana; Heating; Heredity; Immunohistochemistry; In Situ Hybridization; Insecta; Iridescence; Mating Preference, Animal; Mexican Americans; Microscopy, Confocal; Opsins; Perception; Photoreceptor Cells; Phylogeny; Pigmentation; Pupa; RNA, Messenger; RNA-Seq; Reproduction; Retina; Retinal Pigments; Rhodopsin; Rod Opsins; Sex Characteristics; Sexual Behavior, Animal; Sexual Selection; Technology; Transcriptome; Translocation, Genetic; Trees; Ultraviolet Rays; Wings, Animal; Writing; long-wavelength opsin; ommochrome; short-wavelength opsin</t>
+          <t>Abdominal Pain; Adipocytes; Adiposity; Administration, Inhalation; Adolescent; Age Factors; Aged; Amides; Amidohydrolases; Analgesics; Anemia, Sickle Cell; Anti-Inflammatory Agents; Anxiety; Arachidonic Acids; Avoidance Learning; Azetidines; Behavior, Animal; Benzamides; Biomarkers; Brain; Cannabidiol; Cannabinoid Receptor Agonists; Cannabinoids; Cannabis; Carbamates; Carrier Proteins; Case-Control Studies; Child; Corticosterone; Dentate Gyrus; Dose-Response Relationship, Drug; Dronabinol; Endocannabinoids; Energy Intake; Enzyme Inhibitors; Ethanolamines; Extracellular Vesicles; Fatty Liver; Fructose; Ganglia, Spinal; Gelatin; Glycerides; Hallucinogens; Hippocampus; Homeostasis; Hyperalgesia; Hypothermia; Inflammation; Ligands; Lipids; Lipogenesis; Liver; Long-Term Potentiation; Memory, Episodic; Microglia; Monoacylglycerol Lipases; Monocytes; Monoglycerides; Neurons; Neuroprotective Agents; Non-alcoholic Fatty Liver Disease; Obesity; Oleic Acids; PPAR alpha; Pain; Palmitic Acids; Pancreatitis; Pancreatitis, Chronic; Perforant Pathway; Persian Gulf Syndrome; Polyunsaturated Alkamides; Prefrontal Cortex; Prospective Studies; Proteomics; Rats, Sprague-Dawley; Receptor, Cannabinoid, CB1; Receptors, Cannabinoid; Reflex, Startle; Signal Transduction; Social Behavior; Social Defeat; Stress, Psychological; Synaptic Transmission; Virus Diseases; Zika Virus; Zika Virus Infection; p38 Mitogen-Activated Protein Kinases</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Burley, Nancy</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>Reinkensmeyer, David J</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Aged; Algorithms; Arm; Biomechanical Phenomena; Brain-Computer Interfaces; Chronic Disease; Cross-Over Studies; Delivery of Health Care; Electric Stimulation Therapy; Entropy; Feasibility Studies; Forearm; Gait; Gait Disorders, Neurologic; Hand; Information Dissemination; Learning; Movement; Muscle Spasticity; Persons with Disabilities; Posture; Proprioception; Recovery of Function; Rehabilitation Research; Robotics; Shoulder; Single-Blind Method; Spinal Cord Injuries; Stroke; Stroke Rehabilitation; Translational Research, Biomedical; Treatment Outcome; Upper Extremity; Wearable Electronic Devices; Wheelchairs; Wrist</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Busciglio, Jorge</t>
+          <t>Steward, Oswald</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aged; Aging; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Aneuploidy; Anhedonia; Antiviral Agents; Anxiety; Apathy; Atrophy; Basal Forebrain; Biomarkers; Biomedical Research; Blood-Brain Barrier; Body Fluids; Brain; COVID-19; Cells, Cultured; Cellular Senescence; Cerebral Cortex; Checklist; Child; Cholinergic Agents; Chromosomes, Human, Pair 21; Cognition; Cognitive Dysfunction; Defense Mechanisms; Delusions; Depression; Diagnostic Errors; Down Syndrome; Extracellular Vesicles; Fetus; Gene Expression Profiling; Guanosine Triphosphate; Hallucinations; Human Genetics; Incidence; Inflammation; Interferons; Leadership; Live Birth; Longitudinal Studies; Membrane Proteins; Memory Disorders; Microglia; Mitochondria; Models, Genetic; Molecular Biology; Mutation; Nerve Degeneration; Nerve Growth Factor; Nervous System Diseases; Neurodegenerative Diseases; Neurofibrillary Tangles; Neuroinflammatory Diseases; Neurons; New York; Oxidative Stress; Peptides; Pharmaceutical Preparations; Plaque, Amyloid; Precision Medicine; Pregnancy; Probability; Protein Precursors; Proteomics; Psychiatrists; Quality of Life; RNA, Viral; SARS-CoV-2; Schizophrenia; Serine Endopeptidases; Spain; Spinal Puncture; Tetraspanin 28; Trisomy; United States Food and Drug Administration; Vulnerable Populations; tau Proteins</t>
+          <t>Axons; Biopsy; Cell Body; Cervical Cord; Dendrites; Dentate Gyrus; Electroencephalography; Epilepsy; Exercise; Forelimb; Gene Deletion; Genetic Therapy; Genetic Vectors; Hippocampus; Luciferases; Luminescent Measurements; Mossy Fibers, Hippocampal; Motor Endplate; Motor Neurons; Muscles; Nerve Regeneration; Nerve Transfer; Neural Pathways; Neurons; PTEN Phosphohydrolase; Pyramidal Tracts; RNA; RNA, Small Interfering; Rats, Sprague-Dawley; Recovery of Function; Sex Characteristics; Shoulder; Spinal Cord; Spinal Cord Injuries</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cahill, Larry</t>
+          <t>Watanabe Kuwata, Momoko</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Administration, Intranasal; Double-Blind Method; Emotions; Estradiol; Magnetic Resonance Imaging; Memory, Episodic; Oxytocin; Sex Characteristics</t>
+          <t>Administration, Oral; Anticoagulants; Atrial Fibrillation; Austria; COVID-19; Cell Communication; Choroid Plexus; Cross-Sectional Studies; Embryonic Development; Gene Expression Profiling; Islets of Langerhans; Migraine Disorders; Multiple Sclerosis; Neuromyelitis Optica; Registries; Retrospective Studies; Risk Factors; SARS-CoV-2; Sequence Analysis, RNA; Single-Cell Analysis; Stroke; Switzerland; Transcriptome</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cho, Ken</t>
+          <t>Xu, Xiangmin</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Acetylation; Adolescent; Aged; Aged, 80 and over; Biological Phenomena; Blastocyst; Blastula; Caenorhabditis elegans; Caregivers; Case-Control Studies; Cell Differentiation; Cell Lineage; Central Nervous System; Chromatin; Computational Biology; Congenital Abnormalities; Curriculum; Depression; Developmental Biology; Ectoderm; Educational Measurement; Embryo, Nonmammalian; Embryonic Development; Embryonic Structures; Endoderm; Endodermal Sinus Tumor; Epidermis; Epigenesis, Genetic; Epigenomics; Fertilization; Fetus; Forkhead Transcription Factors; Gastrula; Gastrulation; Gene Expression; Gene Expression Profiling; Gene Expression Regulation, Developmental; Gene Regulatory Networks; Genes, Developmental; Genome; Genomics; Germ Layers; Health Services Accessibility; Healthcare Disparities; Heart Failure; Histone Deacetylase 1; Histone Deacetylase 2; Histone Deacetylases; Histones; Insurance Coverage; International Cooperation; Kidney Failure, Chronic; Kidney Transplantation; Laboratories; Learning; Logistic Models; Lysine; Medicaid; Mesoderm; Multiomics; Mutation; N-Myc Proto-Oncogene Protein; Nervous System; Neural Tube; Neurulation; Nutrients; Ovarian Neoplasms; Phenotype; Pregnancy Complications; Preimplantation Diagnosis; Prodromal Symptoms; Prospective Studies; Proteomics; Psychotic Disorders; RNA; Regenerative Medicine; Risk Assessment; Risk Factors; SOXB1 Transcription Factors; Schizophrenia; Self Care; Sequence Analysis, RNA; Signal Transduction; Socioeconomic Disparities in Health; Socioeconomic Factors; Stem Cell Research; Thinking; Transcription Factors; Transcription, Genetic; Uterus; Xenopus; Xenopus Proteins; Xenopus laevis; Young Adult; Zygote; animal cap; nan</t>
+          <t>Adenosine; Aged; Aged, 80 and over; Algorithms; Alzheimer Disease; Blood-Brain Barrier; Brain; Brain Mapping; Capsid; Carbon; Chromosomes, Plant; Cognitive Dysfunction; Cohort Studies; Crops, Agricultural; Deep Learning; Dependovirus; Diploidy; Disease Progression; Electrical Equipment and Supplies; Endothelial Cells; Enhancer Elements, Genetic; Epigenesis, Genetic; Epigenomics; Feasibility Studies; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Plant; Genes, Plant; Genetic Variation; Genetic Vectors; Genetics, Population; Genome, Plant; Genomics; Geologic Sediments; Groundwater; Heterozygote; Hippocampus; Homozygote; Image Processing, Computer-Assisted; Imaging, Three-Dimensional; Induced Pluripotent Stem Cells; Longitudinal Studies; Magnetic Resonance Imaging; Microbiota; Microglia; Monte Carlo Method; Neural Networks, Computer; Neuroimaging; Neurons; Neuropsychological Tests; Plant Breeding; Pollination; Primary Visual Cortex; Prognosis; Promoter Regions, Genetic; Prosencephalon; RNA, Antisense; RNA, Messenger; Radiation Dosage; Radiotherapy Dosage; Radiotherapy Planning, Computer-Assisted; Reproduction; Transcriptome; Transduction, Genetic; Vision, Ocular; Visual Cortex; Vitis; Water Microbiology; tau Proteins</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chrastil, Elizabeth</t>
+          <t>Buisson, Remi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Adolescent; Alzheimer Disease; Artificial Intelligence; Brain; Cerebral Cortex; Cognition; Cognitive Neuroscience; Cognitive Science; Computer Simulation; Confusion; Depression; Diffusion Magnetic Resonance Imaging; Exploratory Behavior; Figural Aftereffect; Functional Neuroimaging; Gray Matter; Gyrus Cinguli; Head; Hippocampus; Individuality; Interpersonal Relations; Judgment; Learning; Magnetic Resonance Imaging; Maze Learning; Memory; Memory, Episodic; Menopause; Motion; Motion Perception; Neuroimaging; Neurons; Organ Size; Parietal Lobe; Pregnancy; Sex Factors; Spatial Learning; Spatial Memory; Spatial Navigation; Temporal Lobe; Theta Rhythm; Virtual Reality; White Matter; Young Adult</t>
+          <t>2',5'-Oligoadenylate Synthetase; Adenosine Deaminase; Antineoplastic Agents; Ataxia Telangiectasia Mutated Proteins; CD8-Positive T-Lymphocytes; CRISPR-Cas Systems; Carcinoma, Squamous Cell; Cell Differentiation; Cell Line, Tumor; Cell Nucleus; Cell Proliferation; Chromatin; Cyclin D1; Cytidine Deaminase; Cytoplasmic Granules; Cytosine; DNA; DNA Breaks, Double-Stranded; DNA Damage; DNA Helicases; DNA Replication; DNA, Single-Stranded; DNA-(Apurinic or Apyrimidinic Site) Lyase; DNA-Binding Proteins; Deamination; Desmoplastic Small Round Cell Tumor; Drug Resistance, Neoplasm; Endoribonucleases; Enzyme Activation; Enzyme Assays; Gene Editing; Gene Expression Regulation; Gene Expression Regulation, Neoplastic; Gene Knockout Techniques; Gene Regulatory Networks; Genomic Instability; HEK293 Cells; HMGB2 Protein; HeLa Cells; High-Throughput Nucleotide Sequencing; Immunity, Innate; Interferon Regulatory Factor-2; Interleukin-1 Receptor-Associated Kinases; Intrinsically Disordered Proteins; Keratinocytes; Lung Neoplasms; Minor Histocompatibility Antigens; Molecular Targeted Therapy; Mutation; NF-kappa B; Neoplasms; Nucleotide Motifs; Oncogene Proteins, Fusion; Persistent Infection; Piperazines; Poly (ADP-Ribose) Polymerase-1; Poly-ADP-Ribose Binding Proteins; Protein Binding; Protein Isoforms; Protein Kinases; Proteins; Pyridines; Pyrimidines; RNA 3' End Processing; RNA Helicases; RNA Polymerase II; RNA Precursors; RNA Processing, Post-Transcriptional; RNA Recognition Motif Proteins; RNA Splicing; RNA Stability; RNA, Double-Stranded; RNA, Messenger; RNA, Mitochondrial; RNA, Viral; RNA-Binding Protein EWS; RNA-Binding Proteins; STAT2 Transcription Factor; Sequence Analysis, DNA; Signal Transduction; Stress Granules; Transcription Factors; Tumor Suppressor Protein p53; Virus Diseases; Virus Replication; WT1 Proteins; Xenograft Model Antitumor Assays; eIF-2 Kinase</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cinquin, Olivier</t>
+          <t>Dai, Xing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aging; Artificial Intelligence; Cell Line; Chromatin Immunoprecipitation; Computational Biology; Consensus; DNA Damage; Databases, Factual; Generative Artificial Intelligence; Genomics; Language; Large Language Models; Liquid Biopsy; Medicine; Mutation; Neoplasms; Noninvasive Prenatal Testing; Peer Review; Programming Languages; Software; Systems Biology</t>
+          <t>3T3 Cells; Age Distribution; Aged; Aged, 80 and over; Amphiregulin; Antibodies, Monoclonal, Humanized; Axin Protein; Basic Helix-Loop-Helix Transcription Factors; Biomarkers; Blindness; Brain; Breast; CD8-Positive T-Lymphocytes; Cardiovascular Diseases; Cataract; Cell Communication; Cell Differentiation; Cell Lineage; Cell Proliferation; Chromatin; Cognition; Cognitive Dysfunction; Cognitive Training; DNA-Binding Proteins; Dermatitis, Atopic; Endothelial Cells; Environmental Exposure; Epidermal Cells; Epidermis; Epithelial Cells; Epithelial-Mesenchymal Transition; Fatty Liver; Fibroblasts; Fibrosis; Fructose; Gene Expression Regulation; Global Burden of Disease; Global Health; HEK293 Cells; HaCaT Cells; Homeostasis; Imiquimod; Immunotherapy; Inflammation; Interleukin-17; Intracellular Signaling Peptides and Proteins; Keratinocytes; Lipogenesis; Liver; Macrophages; Macular Degeneration; Mammary Glands, Animal; Myocardial Ischemia; Non-alcoholic Fatty Liver Disease; Occupations; Persons with Visual Disabilities; Pharmaceutical Preparations; Prevalence; Prostatic Neoplasms; Psoriasis; Quality-Adjusted Life Years; RNA; Receptors, Aryl Hydrocarbon; Risk Assessment; Risk Factors; Sex Distribution; Signal Transduction; Single-Cell Analysis; Skin; Smoking; Stem Cells; T-Lymphocytes, Cytotoxic; Transcription Factors; Tumor Microenvironment; Universal Health Insurance; Vision, Low; Visual Acuity; White Matter; Wnt Signaling Pathway; Workforce; Wound Healing; Zinc Finger E-box-Binding Homeobox 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cocco, Melanie</t>
+          <t>Donovan, Peter J</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Amino Acids; Amino Sugars; Anemia, Sickle Cell; Arabidopsis; Bacteria; Basic Helix-Loop-Helix Transcription Factors; Biological Products; Biological Science Disciplines; Brain; Cannabidiol; Cannabinoids; Cannabis; Carcinogens; Cell Adhesion; Cell Membrane; Cellular Senescence; Cerebral Hemorrhage; Chromatography, High Pressure Liquid; DNA, Satellite; Dronabinol; Drug Development; Drug Resistance, Microbial; Employment; Epigenesis, Genetic; Erythrocytes; Ethanol; Fertilizers; Flavonoids; Furunculosis; Gas Chromatography-Mass Spectrometry; Genomics; Genotype; Heinz Bodies; Helium; Hemoglobinopathies; Hemoglobins; Herbicides; Hispanic or Latino; Hydrogen; Hydrogen-Ion Concentration; Information Sources; Isotopes; Kinetics; Ligands; Lipids; Magnetic Resonance Imaging; Magnetic Resonance Spectroscopy; Magnets; Marijuana Use; Medical Marijuana; Membrane Proteins; Metabolome; Microbiota; Molecular Dynamics Simulation; Molecular Structure; Mutation; Myoglobin; Natural Science Disciplines; Neoplasms; Oryza; Oxides; Oxygen; Pesticides; Plant Extracts; Protein Binding; Protein Interaction Maps; Proteins; Recombinant Proteins; Seasons; Seeds; Sugars; Temperature; Terpenes; Water; beta-myrcene; caryophyllene oxide; nan; voxelotor</t>
+          <t>Cell Line; Chromatin; Human Embryonic Stem Cells; Protein Binding; Transcription Factor 7-Like 1 Protein; Wnt Signaling Pathway</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cohen-Cory, Susana</t>
+          <t>Jang, Cholsoon</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amphibians; Axons; Cell Adhesion Molecules; Cell Tracking; Dendrites; Neurogenesis; Retina; Superior Colliculi; Synapses; Visual Pathways; Xenopus Proteins; Xenopus laevis</t>
+          <t>ADP-ribosyl Cyclase 1; ATP Citrate (pro-S)-Lyase; Acetate-CoA Ligase; Acetates; Acetic Acid; Acetylation; Adenosine; Adipocytes; Adipose Tissue, Brown; Adolescent; Aging; Allosteric Regulation; Alternative Splicing; Amino Acids, Branched-Chain; Anti-Bacterial Agents; Antigens, CD; Antineoplastic Agents, Hormonal; Bacteria; Biomarkers; Biomedical Research; Body Mass Index; Body Weight; Brain; Brain Stem; Breast Neoplasms; CD8-Positive T-Lymphocytes; Cadherins; Calcium; Calcium Channels; Calcium Signaling; Cardiovascular Diseases; Carrier Proteins; Cell Differentiation; Cell Line, Tumor; Cell Movement; Cell Proliferation; Cellular Senescence; Child; Citric Acid; Citric Acid Cycle; DNA-Binding Proteins; Disease Progression; Down-Regulation; Eating; Elasticity Imaging Techniques; Energy Metabolism; Epigenesis, Genetic; Epithelial-Mesenchymal Transition; Exercise; Fatty Acids; Fatty Liver; Fructokinases; Fructose; Gastrointestinal Microbiome; Gene Knockdown Techniques; Germ-Free Life; Glucose; Glycolysis; Hematopoietic Stem Cells; Hepatocytes; Hispanic or Latino; Histone Acetyltransferases; Histone Code; Histones; Homeostasis; Huntingtin Protein; Huntington Disease; Hydrolases; Hydrolysis; Insulin; Kidney; Kynurenine; Lactic Acid; Lipidomics; Lipogenesis; Lipolysis; Liver; Liver Cirrhosis; Membrane Glycoproteins; Metabolomics; Methyltransferases; Mice, Nude; Mitochondria; NAD; Neoplasm Metastasis; Non-alcoholic Fatty Liver Disease; Nutrients; Obesity; Oxidation-Reduction; Oxidative Stress; Pediatric Obesity; Phosphoglycerate Dehydrogenase; Predictive Value of Tests; Protein Kinases; Proteomics; RNA Methylation; RNA Splicing; RNA, Ribosomal, 16S; RNA, Small Interfering; Receptors, G-Protein-Coupled; Secondary Metabolism; Serine; Signal Transduction; Stress, Physiological; Tamoxifen; Taurine; Thermogenesis; Tryptophan; Weight Loss</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Connor, Kwasi</t>
+          <t>Kaiser, Peter</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Academies and Institutes; Acclimatization; Amylases; Anaerobiosis; Cellulase; Cold Temperature; Diet; Ecosystem; Gene Expression; Heat-Shock Response; Homeostasis; Hot Temperature; Metabolome; Metabolomics; Mytilus; Oxygen; Respiration; Temperature</t>
+          <t>Adaptor Proteins, Signal Transducing; Alternative Splicing; Antineoplastic Agents; Autoantigens; Autophagy; Bevacizumab; Biosimilar Pharmaceuticals; CRISPR-Cas Systems; Cadmium; Cell Cycle Proteins; Cell Line; Cell Line, Tumor; Cell Proliferation; Centromere; Centromere Protein A; Chromatin; Chromosomal Instability; Chromosomal Proteins, Non-Histone; Circadian Clocks; Circadian Rhythm; Consensus; Cullin Proteins; DNA; DNA Damage; DNA Modification Methylases; DNA Repair; DNA Repair Enzymes; DNA-Binding Proteins; Europe; F-Box Proteins; Geographic Atrophy; Glycogen Synthase Kinase 3; Histones; Homocysteine; Huntingtin Protein; Huntington Disease; Ligands; Liver; Lysosomes; Methionine; Methylation; Mitochondria; Mitochondrial Proteins; Mutation; Neoplasms; Nucleocytoplasmic Transport Proteins; Nutrients; Optometrists; Peptides; Phosphorylation; Precision Medicine; Protein Binding; Protein Domains; Protein-Arginine N-Methyltransferases; Proteolysis; Proto-Oncogene Proteins c-mdm2; Pyrimidines; RNA Splicing; RNA-Binding Proteins; Retina; Retinal Diseases; S-Phase Kinase-Associated Proteins; SKP Cullin F-Box Protein Ligases; Saccharomyces cerevisiae; Saccharomyces cerevisiae Proteins; Stress, Physiological; Sumoylation; Suprachiasmatic Nucleus; Surveys and Questionnaires; Tryptophan; Tumor Suppressor Protein p53; Tumor Suppressor Proteins; Ubiquitin; Ubiquitin-Protein Ligase Complexes; Ubiquitin-Protein Ligases; Ubiquitination; Valosin Containing Protein; Vesicular Transport Proteins; beta-Transducin Repeat-Containing Proteins</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cramer, Karina</t>
+          <t>Kessenbrock, Kai</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Acoustics; Apoptosis; Astrocytes; Auditory Pathways; Axon Guidance; Axons; Biological Evolution; Brain; Brain Stem; Caspase 3; Caspases; Cell Death; Cochlear Nerve; Cysteine; Deafness; Dendrites; Embryonic Development; Endopeptidases; Evoked Potentials, Auditory, Brain Stem; Exosomes; Gene Expression Regulation; Gene Ontology; Hearing; Microglia; Myelin Sheath; Nervous System; Neurodevelopmental Disorders; Neuroglia; Neuronal Plasticity; Neurons; Oligodendroglia; Peptide Hydrolases; Phylogeny; Presynaptic Terminals; Proteomics; RNA, Long Noncoding; Synapses; Synaptic Transmission; Tandem Mass Spectrometry; Transcriptome; Trapezoid Body; nan</t>
+          <t>3T3 Cells; Aging; Axin Protein; B7-H1 Antigen; BRCA1 Protein; BRCA2 Protein; Breast; Breast Neoplasms; CD4 Antigens; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Carcinogenesis; Cell Communication; Cell Differentiation; Cell Line, Tumor; Cell Lineage; Cell Proliferation; Cell Transformation, Neoplastic; Cellular Reprogramming; Choroid Plexus; Chromatin; Circadian Clocks; Circadian Rhythm; Colorectal Neoplasms; Cryptochromes; Cytokines; Endogenous Retroviruses; Endothelial Cells; Epigenesis, Genetic; Epigenomics; Epithelial Cells; Epithelial-Mesenchymal Transition; Fibroblasts; Fibrosis; Forkhead Transcription Factors; Galectin 3; Gene Expression; Gene Expression Profiling; Genome-Wide Association Study; Genomics; Germ-Line Mutation; HEK293 Cells; Heterochromatin; Immune Checkpoint Inhibitors; Immune Tolerance; Immunity; Immunosuppression Therapy; Lymphocyte Activation; Macrophages; Mammary Glands, Human; Multiple Sclerosis; Muscle, Skeletal; Mutation; Myeloid-Derived Suppressor Cells; Neural Stem Cells; Organoids; Paclitaxel; Pluripotent Stem Cells; RNA, Nuclear; Signal Transduction; Single-Cell Analysis; Skin; Stem Cells; Stromal Cells; Supervised Machine Learning; T-Lymphocytes, Regulatory; Transcription Factors; Transcriptome; Triple Negative Breast Neoplasms; Tumor Microenvironment; Wnt Signaling Pathway; Wound Healing; Zinc Finger E-box-Binding Homeobox 1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daley, Monica</t>
+          <t>Li, Wei</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Air; Aircraft; Algorithms; Artificial Limbs; Avatar; Awards and Prizes; Behavior, Animal; Bioengineering; Biomechanical Phenomena; Biomimetics; Biophysics; Biotechnology; Birds; Cognition; Communication; Computer Simulation; Connective Tissue; Conservation of Energy Resources; Dancing; Elasticity; Elastomers; Electromyography; Environment; Exoskeleton Device; Extremities; Fellowships and Scholarships; Financial Management; Flight, Animal; Gait; Galliformes; Genomics; History, 20th Century; History, 21st Century; Information Dissemination; Interdisciplinary Research; Invertebrates; Isometric Contraction; Leadership; Leg; Locomotion; Motion; Motor Activity; Movement; Muscle Contraction; Muscle Proteins; Muscle, Skeletal; Muscles; Neuromuscular Diseases; Prostheses and Implants; Rats, Sprague-Dawley; Resilience, Psychological; Robotic Surgical Procedures; Robotics; Running; Schools; Self-Help Devices; Social Cohesion; Social Media; Spinal Cord; Sports; Stress, Mechanical; Tendons; Vertebrates; Viscosity; Walking; Wearable Electronic Devices; Wings, Animal; X-Ray Diffraction; nan</t>
+          <t>3' Untranslated Regions; Acute-Phase Proteins; Adolescent; Age of Onset; Aged; Aged, 80 and over; Algorithms; Alternative Splicing; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Anilides; Animals, Domestic; Bacteria; Bayes Theorem; Biomarkers, Tumor; Black or African American; Body Mass Index; Brain; Brain Neoplasms; C9orf72 Protein; Carbon; Carbon Cycle; Carcinoma, Non-Small-Cell Lung; Carrier Proteins; Cell Nucleus; Cell-Free Nucleic Acids; Child; Child, Preschool; Cohort Studies; Colorectal Neoplasms; Computational Biology; CpG Islands; DEAD-box RNA Helicases; DNA Copy Number Variations; DNA Methylation; DNA Repeat Expansion; DNA-Binding Proteins; Databases, Genetic; Disease; Ecosystem; Epigenesis, Genetic; Exome; Exome Sequencing; Exosome Multienzyme Ribonuclease Complex; False Positive Reactions; Frontotemporal Dementia; Gene Conversion; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Neoplastic; Genetic Predisposition to Disease; Genetic Testing; Genetic Variation; Genome, Human; Genome-Wide Association Study; Genomic Structural Variation; Genomics; Genotype; Germ Cells; Germ-Line Mutation; HEK293 Cells; Haplotypes; HeLa Cells; Hispanic or Latino; Imidazoles; Inflammation; Introns; Liver; Liver Cirrhosis; Lung Neoplasms; Membrane Glycoproteins; Multiomics; MutS Homolog 2 Protein; Neoplasms; Organ Specificity; Phenotype; Poly A; Polyadenylation; Polymorphism, Single Nucleotide; Progression-Free Survival; Protein Kinase Inhibitors; Protein-Tyrosine Kinases; Proto-Oncogene Proteins; Pyrazoles; Pyridazines; Quantitative Trait Loci; Quinolines; RNA Splice Sites; RNA Stability; RNA, Messenger; RNA, Nuclear; RNA-Seq; Ribonucleoprotein, U1 Small Nuclear; Segmental Duplications, Genomic; Sequence Analysis, DNA; Sequence Analysis, RNA; Soil; Soil Microbiology; Tandem Repeat Sequences; Transcriptome; Whole Genome Sequencing; tau Proteins</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Donovan, Peter</t>
+          <t>Liu, Haoping</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Academia; Cell Line; Chromatin; Communication; DNA Transposable Elements; Developmental Biology; Dystonia; Embryology; Human Embryonic Stem Cells; Leadership; Mutation; Neurobiology; Neurodegenerative Diseases; Neurons; Parkinsonian Disorders; Personnel Selection; Protein Binding; Retroelements; Stem Cells; Transcription Factor 7-Like 1 Protein; Wnt Signaling Pathway</t>
+          <t>Aedes; Agammaglobulinaemia Tyrosine Kinase; Aged; Aged, 80 and over; Amino Acids, Diamino; Aminopyridines; Angiotensin II; Angiotensin II Type 1 Receptor Blockers; Animals, Domestic; Antibodies, Viral; Apoptosis; Atrial Fibrillation; Australasia; Bed Occupancy; Benzimidazoles; Benzoates; Breast; Breast Neoplasms; CARD Signaling Adaptor Proteins; COVID-19; Calcium-Binding Proteins; Candida albicans; Cartilage, Articular; Caspase 8; Cell Line; Cerebral Hemorrhage; Chondrocytes; Claudin-5; Clinical Competence; Cohort Studies; Colitis; Conjunctiva; Critical Care; Diffusion Magnetic Resonance Imaging; Dry Eye Syndromes; Enzyme-Linked Immunosorbent Assay; Epithelium, Corneal; Fas-Associated Death Domain Protein; Fungal Proteins; Gene Expression Regulation; Genomics; Genotype; Goblet Cells; Health Personnel; Hypertension; Hypertrophy; Inflammasomes; Insect Proteins; Intensive Care Units; Interferon-gamma; Interleukin-1; Interleukin-13; Interleukin-1beta; Jurkat Cells; Lectins, C-Type; Leukemia, Lymphocytic, Chronic, B-Cell; Lymphoma, Large B-Cell, Diffuse; Macrophages; Magnetic Resonance Imaging; Mannose Receptor; Mannose-Binding Lectins; Membrane Potential, Mitochondrial; Microfilament Proteins; Microglia; Mosquito Vectors; Mucins; Myocytes, Cardiac; Observer Variation; Osteoarthritis; Osteoarthritis, Knee; Oviposition; Personal Protective Equipment; Phenotype; Pneumonia; Postoperative Care; Postoperative Complications; Protein Kinase Inhibitors; Proteomics; Pyrimidines; Pyrroles; RNA, Messenger; Real-Time Polymerase Chain Reaction; Receptors, Cell Surface; Receptors, Odorant; Receptors, Somatotropin; Respiration, Artificial; Respiratory Distress Syndrome; Retrospective Studies; Risk Factors; SARS-CoV-2; Sensitivity and Specificity; Seroepidemiologic Studies; Signal Transduction; Surveys and Questionnaires; Tears; Telmisartan; Tight Junctions; Transcriptome; Treatment Outcome; United Kingdom; Vision, Ocular; X-Ray Microtomography; Young Adult</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Drayman, Nir</t>
+          <t>Marazzi, Ivan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Acyclovir; Antiviral Agents; Blister; COVID-19; CRISPR-Cas Systems; Cell Culture Techniques; Cell Line; Cell Nucleus; Chlorocebus aethiops; Cidofovir; Clustered Regularly Interspaced Short Palindromic Repeats; Cytomegalovirus; DNA Replication; DNA, Viral; DNA-Directed DNA Polymerase; Decitabine; Drug Repositioning; Drug Resistance, Viral; Drug Synergism; Encephalitis, Herpes Simplex; Epithelial Cells; Eukaryotic Cells; Fibroblasts; Ficus; Foscarnet; Gene Expression; Gene Expression Regulation; Gene Expression Regulation, Viral; Genes, Tumor Suppressor; Genome, Viral; HEK293 Cells; Hepatitis C, Chronic; Herpes Labialis; Herpes Simplex; Herpesviridae; Herpesviridae Infections; Herpesvirus 1, Equid; Herpesvirus 1, Human; Homeodomain Proteins; Host Microbial Interactions; Host-Pathogen Interactions; Immunocompromised Host; Infant, Newborn; Interferons; Kaposi Varicelliform Eruption; Keratinocytes; Keratitis, Herpetic; Life Cycle Stages; Machine Learning; Methylation; Microfluidics; Mutation; Myelodysplastic Syndromes; National Institute of Allergy and Infectious Diseases (U.S.); Organoids; Orthomyxoviridae; Pandemics; Phenotype; Prevalence; Protein Interaction Mapping; RNA; SARS-CoV-2; Sequence Analysis, RNA; Serial Passage; Simplexvirus; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Skin Diseases, Viral; Surgery, Plastic; Systems Biology; Thymidine Kinase; Transcription, Genetic; Transferases; Ulcer; Vero Cells; Viral Proteins; Virology; Virus Diseases; Virus Replication; Viruses; Zygote; nan</t>
+          <t>Adiposity; Alternative Splicing; Amyotrophic Lateral Sclerosis; Antineoplastic Agents; Antiviral Agents; Arginine; Ataxia Telangiectasia Mutated Proteins; B7-H1 Antigen; Blastocyst; CD8-Positive T-Lymphocytes; Carcinoma, Hepatocellular; Carrier Proteins; Cell Line; Cell Line, Tumor; Circadian Clocks; Circadian Rhythm; Clone Cells; Colorectal Neoplasms; Cytokines; DNA Damage; DNA Helicases; DNA Replication; DNA-Binding Proteins; Embryonic Development; Endogenous Retroviruses; Epigenesis, Genetic; Gene Expression; Gene Expression Profiling; Gene Knock-In Techniques; Heterochromatin; Homeostasis; Immune Checkpoint Inhibitors; Immune Tolerance; Immunity, Innate; Immunosuppression Therapy; Interleukin-1 Receptor-Associated Kinases; Ligands; Liver Neoplasms; Motor Neurons; Multifunctional Enzymes; Mutation; Myeloid-Derived Suppressor Cells; NF-kappa B; Proprotein Convertase 9; Protein Isoforms; Protein Kinase Inhibitors; Protein-Arginine N-Methyltransferases; Proteolysis; RNA Helicases; RNA Precursors; RNA Processing, Post-Transcriptional; RNA, Messenger; RNA, Nuclear; RNA, Viral; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Stress, Physiological; Transcription Factors; Transcriptome; Tumor Microenvironment; Ubiquitin-Protein Ligases; Viral Proteins; Viruses; Zygote; beta Catenin</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Edinger, Aimee</t>
+          <t>Masri, Selma</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alleles; Allergy and Immunology; Amiloride; Aminopyridines; Asialoglycoprotein Receptor; Autophagy; Base Pairing; Biological Transport; COVID-19; COVID-19 Vaccines; CRISPR-Cas Systems; Cell Line, Tumor; Cell Membrane; Cell Proliferation; Class III Phosphatidylinositol 3-Kinases; Codon, Nonsense; Codon, Terminator; Cultural Diversity; Cytoplasm; Cytosol; Diet, High-Fat; Drug Resistance; Endocytosis; Endosomes; ErbB Receptors; Feasibility Studies; Ficus; Genomics; HeLa Cells; Hepatocytes; Heterocyclic Compounds, 3-Ring; Hot Temperature; Intercellular Signaling Peptides and Proteins; Karyopherins; Kidney; Kidney Glomerulus; Ligands; Lipid Nanoparticles; Liver; Lung; Lung Neoplasms; Lysosomes; Metabolism; Minority Groups; Mitochondria; Morpholines; Neoplasms; Nucleotides; Nutrients; Obesity; Oligonucleotides; Oligonucleotides, Antisense; Oncogenes; PTEN Phosphohydrolase; Phosphatidylinositol 3-Kinases; Phosphatidylinositols; Pinocytosis; Plague; Podocytes; Polypharmacology; Proof of Concept Study; Prostatic Neoplasms; Protein Phosphatase 2; Proto-Oncogene Proteins B-raf; Proto-Oncogene Proteins p21(ras); RNA, Small Interfering; Ribosomes; Saccharomyces cerevisiae; Schools; Sodium-Hydrogen Exchangers; Sphingolipids; Sphingosine; Transcription Factors; Tumor Microenvironment; Vacuolar Proton-Translocating ATPases; Vacuoles; nan; patisiran</t>
+          <t>AICDA (Activation-Induced Cytidine Deaminase); ARNTL Transcription Factors; Adipocytes; Adipose Tissue; Adiposity; Ataxia Telangiectasia Mutated Proteins; B-Lymphocytes; B7-H1 Antigen; Biodiversity; CD8-Positive T-Lymphocytes; California; Cell Line, Tumor; Child; Chromatin; Circadian Clocks; Circadian Rhythm; Colorectal Neoplasms; Cross-Sectional Studies; Crowdsourcing; Cytidine Deaminase; Cytokines; DNA Breaks, Double-Stranded; DNA Damage; DNA Repair; DNA-Binding Proteins; Dopamine; Dysbiosis; Epidermal Cells; Epidermis; Fatty Acids, Nonesterified; Gastrointestinal Microbiome; Gene Expression Regulation; Genetic Loci; Glucose; Health Status Disparities; Hispanic or Latino; Homeostasis; Immune Checkpoint Inhibitors; Immune Tolerance; Immunity, Innate; Immunosuppression Therapy; Interleukin-1 Receptor-Associated Kinases; Intestinal Mucosa; Latin America; Levodopa; Lipidomics; Lipolysis; Liver; Motor Activity; Movement Disorders; Muscle, Skeletal; Mutation; Myeloid-Derived Suppressor Cells; NF-kappa B; Neoplasms; Oligopeptides; Perception; Permeability; Plants; Polycomb Repressive Complex 2; Precursor Cell Lymphoblastic Leukemia-Lymphoma; Proprotein Convertase 9; RNA Polymerase II; Receptors, Calcium-Sensing; Receptors, Cytokine; Signal Transduction; Single-Cell Analysis; Skin; Smoke; Socioeconomic Disparities in Health; Spatial Analysis; Tracheophyta; Transcription Factors; Transcription, Genetic; Translocation, Genetic; Triglycerides; Tumor Microenvironment; Wildfires</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Emerson, J.J.</t>
+          <t>Ng, Stanley Wai Kwong</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alleles; Butterflies; Chromatin; Chromatin Assembly and Disassembly; Color Vision; Cost-Benefit Analysis; Drosophila Proteins; Drosophila melanogaster; Enhancer Elements, Genetic; Evolution, Molecular; Eye; Gene Duplication; Gene Frequency; Gene Regulatory Networks; Genes, Duplicate; Genome; Genome, Insect; Genome-Wide Association Study; Genomics; Genotype; Heterochromatin; High-Throughput Nucleotide Sequencing; Molecular Conformation; Mutation; Opsins; Pesticides; Phenotype; Plants; Repetitive Sequences, Nucleic Acid; Reverse Genetics; Rhodopsin; Selection, Genetic; Software; Telomere; Uncertainty; Whole Genome Sequencing</t>
+          <t>Acyltransferases; Bone Marrow Cells; Hepatic Stellate Cells; Hepatitis, Alcoholic; Leukemia, Myeloid, Acute; Ligands; Liver; Liver Cirrhosis; Recurrence</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Eom, Dae Seok</t>
+          <t>Qiao, Feng</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cell Communication; Cell Surface Extensions; Connexins; Diffusion; Drosophila Proteins; Endoderm; Extracellular Vesicles; Keratinocytes; Macrophages; Matrix Metalloproteinase 9; Muscles; Pigments, Biological; Pseudopodia; Signal Transduction; Zebrafish; nan</t>
+          <t>Cell Cycle Proteins; Cell Line; Cell Line, Tumor; Chromatin; DNA; DNA Polymerase I; DNA Replication; Epigenesis, Genetic; Heterochromatin; Histone Chaperones; Histones; Mutation; Neoplasms; Protein Binding; Protein Domains; RNA Precursors; RNA Processing, Post-Transcriptional; RNA, Messenger; Schizosaccharomyces; Schizosaccharomyces pombe Proteins; Tumor Suppressor Protein p53</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Faiola, Celia</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Acer; Acyclic Monoterpenes; Aerosols; Air Pollutants; Air Pollution; Alabama; Artemisia; Atmosphere; Bicyclic Monoterpenes; Carbon; Carbon Dioxide; Cities; Citizen Science; Climate Change; Colorado; Computer Simulation; Crops, Agricultural; Curriculum; Dehydration; Demography; Drought Resistance; Droughts; Ecological and Environmental Phenomena; Ecosystem; Endophytes; Environmental Justice; Environmental Monitoring; Environmental Pollutants; Forests; Fossil Fuels; Greenhouse Gases; Hot Temperature; Humans; Internship and Residency; Isomerism; Liquidambar; Literacy; Los Angeles; Metabolomics; Models, Chemical; Monoterpenes; Mortality, Premature; Mycorrhizae; Oxidation-Reduction; Oxygen; Ozone; Pacific Ocean; Photochemical Processes; Photosynthesis; Pilot Projects; Plant Leaves; Plant Physiological Phenomena; Plants; Poaceae; Prognosis; Quercus; Radiation Injuries; Remote Sensing Technology; Resilience, Psychological; Rhizosphere; Schools; Seasons; Sesquiterpenes; Social Conditions; Soil; Temperature; Terpenes; Trees; Volatile Organic Compounds; Wettability</t>
-        </is>
-      </c>
+          <t>Sandmeyer, Suzanne B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Fortin, Norbert</t>
+          <t>Seldin, Marcus Michael</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Academia; Acoustic Stimulation; Algorithms; Auditory Perception; Behavior; Brain; CA1 Region, Hippocampal; Cognition; Computers; Decision Making; Electrodes, Implanted; Electrophysiology; Government; Hippocampus; Leadership; Machine Learning; Memory; Memory, Episodic; Nerve Net; Odorants; Olfactory Perception; Planning Techniques; Prefrontal Cortex; Stereotaxic Techniques; Substance-Related Disorders; Technology; Theta Rhythm; Time; Time Factors; nan</t>
+          <t>3T3-L1 Cells; Adaptation, Physiological; Adipocytes; Adipogenesis; Adipokines; Adiponectin; Adipose Tissue; Adipose Tissue, White; Adiposity; Aged; Aged, 80 and over; Aging; Antibodies, Neutralizing; Antibodies, Viral; Biomarkers; Biomedical Research; Biopsy; Blood Glucose; Blood Proteins; CRISPR-Cas Systems; Cardiovascular Diseases; Cell Differentiation; Circadian Clocks; Colorectal Neoplasms; DNA; DNA, Mitochondrial; Diabetes Mellitus, Type 2; Diet, High-Fat; Dimethylallyltranstransferase; Dysbiosis; Estrogen Receptor alpha; Exercise; Gastrointestinal Microbiome; Gene Editing; Gene Expression Regulation; Glucose; Heart Failure; High-Throughput Nucleotide Sequencing; Homeostasis; Immunoinformatics; Influenza Vaccines; Influenza, Human; Insulin; Insulin Resistance; Insulin Secretion; Intestinal Mucosa; Islets of Langerhans; Leptin; Lipid Metabolism; Liver; Macrophages; Magnetic Resonance Imaging; Metabolomics; Mitochondria; Mitochondria, Muscle; Muscle, Skeletal; Myocardium; Nucleotide Motifs; Obesity; Organoids; Overweight; Pancreas; Paracrine Communication; Permeability; Physical Conditioning, Animal; Promoter Regions, Genetic; Proteomics; RNA-Seq; Sequence Analysis, DNA; Sequence Analysis, RNA; Serpin E2; Sex Factors; Signal Transduction; Stroke Volume; Subcutaneous Fat; Subcutaneous Fat, Abdominal; Systems Biology; Th1 Cells; Transcription Factors; Transcription, Genetic; Vaccination; Vasodilation; Weight Loss</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fowler, Christie</t>
+          <t>Steele, Robert E</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adenosine Triphosphate; Administration, Inhalation; Adolescent; Aerosols; Alcohol Drinking; Alcoholism; Analgesics, Opioid; Antineoplastic Agents; Apoptosis; Behavior; Biomedical Research; Brain; Brain-Derived Neurotrophic Factor; Cannabidiol; Cannabis; Cell Line, Tumor; Cell Movement; Cell Proliferation; Cerebellar Neoplasms; Child; Cholinergic Neurons; Chromatin; Clustered Regularly Interspaced Short Palindromic Repeats; Cocaine; Cognition; Consummatory Behavior; Craving; Dopamine; Dopaminergic Neurons; Dronabinol; E-Cigarette Vapor; Eating; Electronic Nicotine Delivery Systems; Electrophysiology; Epigenesis, Genetic; Ethanol; Extracellular Vesicles; Eye Diseases; Genomics; Habenula; Learning; Lynx; Marketing; Mass Spectrometry; Medulloblastoma; Memory; Menthol; Mice; Microscopy; National Eye Institute (U.S.); Nicotine; Nicotinic Agonists; Nucleus Accumbens; Pregnancy; Prenatal Exposure Delayed Effects; Proteomics; Quality of Life; Rats, Sprague-Dawley; Receptor, Cannabinoid, CB1; Receptors, Nicotinic; Receptors, Purinergic P2; Recurrence; Rodentia; Self Administration; Sex Characteristics; Signal Transduction; Smoking; Smoking Cessation; Social Behavior; Social Environment; Substance Withdrawal Syndrome; Substance-Related Disorders; Synaptic Transmission; Therapeutics; Tobacco Products; Tobacco Use; Tobacco Use Cessation Devices; Tobacco Use Disorder; Ventral Tegmental Area; Vision, Ocular; Xenograft Model Antitumor Assays; nan</t>
+          <t>Animals, Genetically Modified; Biological Evolution; Biological Transport; Body Patterning; Cell Differentiation; Cell Lineage; Cnidaria; Ectoderm; Epithelial Cells; Genes, Homeobox; Hippo Signaling Pathway; Hydra; Morphogenesis; Nerve Net; Neurites; Neurons; Nutrients; Sea Anemones; Transcription, Genetic; Transcriptional Activation; Vitellogenesis; YAP-Signaling Proteins</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Frank, Steven</t>
+          <t>Yokomori, Kyoko</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Access to Information; Artificial Intelligence; Bacteria; Biological Evolution; Cell Biology; Communicable Diseases; Computational Biology; Computer Simulation; Disease; Ecological and Environmental Phenomena; Epigenesis, Genetic; Ergonomics; Evolution, Molecular; Gene Expression; Genetic Drift; Genetics; Genetics, Population; Genotype; Host-Parasite Interactions; Inheritance Patterns; Life History Traits; Logic; Microbiota; Models, Genetic; Molecular Epidemiology; Mutation; Neoplasms; Neurobiology; Phenotype; Public Health; Selection, Genetic; Social Evolution; Software; Systems Biology</t>
+          <t>Adolescent; Cell Differentiation; Gene Expression Profiling; Homeodomain Proteins; In Situ Hybridization, Fluorescence; Muscle Fibers, Skeletal; Muscle, Skeletal; Muscular Atrophy; Muscular Dystrophy, Facioscapulohumeral; Myoblasts; Single-Cell Analysis; Transcriptome</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Frostig, Ron</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Action Potentials; Anesthetics; Astrocytes; Behavior, Animal; Biosensing Techniques; Brain; Brain Diseases, Metabolic; Brain Ischemia; Cerebral Cortex; Cerebrovascular Circulation; Diagnostic Imaging; Electric Stimulation; Electrophysiology; Glutamic Acid; Head; Histology; Infarction, Middle Cerebral Artery; Ischemic Attack, Transient; Ischemic Stroke; Lactic Acid; Magnetic Resonance Imaging; Metabolism; Microelectrodes; Middle Cerebral Artery; Neural Conduction; Neuroimaging; Neuronal Plasticity; Neurons; Neuroprotection; Neurotransmitter Agents; Pharmacology; Rodentia; Sense Organs; Social Isolation; Stroke; Wakefulness; gamma-Aminobutyric Acid</t>
-        </is>
-      </c>
+          <t>Baker, Nicholas Edward</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Fruman, David</t>
+          <t>Barbour, Alan G</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AMP-Activated Protein Kinases; Adolescent; Antineoplastic Agents; Apoptosis; Apoptosis Regulatory Proteins; Biological Transport; Biomarkers; Biosynthetic Pathways; Catalysis; Cell Cycle Checkpoints; Cell Death; Cell Line; Cell Line, Tumor; Cell Membrane; Cell Proliferation; Cell Survival; Child; Cholesterol; Clustered Regularly Interspaced Short Palindromic Repeats; Cobalt; Cytokines; DNA Adducts; Dasatinib; Diet; Doxorubicin; Drug Delivery Systems; Drug Repositioning; Drug Synergism; Endocytosis; Endosomes; Fasting; Fusion Proteins, bcr-abl; GTP Phosphohydrolases; Gene Expression; Guanosine Triphosphate; Health Inequities; Heart Diseases; Hematologic Neoplasms; Heterografts; Hispanic or Latino; Hydroxymethylglutaryl-CoA Reductase Inhibitors; Immunosuppressive Agents; Janus Kinases; Leukemia; Leukemia, Lymphocytic, Chronic, B-Cell; Leukemia, Myeloid, Acute; Lipids; Lymphocytes; Lymphoma; MTOR Inhibitors; Mechanistic Target of Rapamycin Complex 1; Mechanistic Target of Rapamycin Complex 2; Mevalonic Acid; Mitochondria; Molecular Targeted Therapy; Multiple Myeloma; Multiprotein Complexes; Myeloid Cell Leukemia Sequence 1 Protein; Neoplasms; Neoplastic Processes; Nutrients; Oligonucleotides; Oligonucleotides, Antisense; Organelles; Philadelphia Chromosome; Phosphatidylinositol 3-Kinases; Phosphoinositide-3 Kinase Inhibitors; Phosphorylation; Precursor Cell Lymphoblastic Leukemia-Lymphoma; Prognosis; Prospective Studies; Proteasome Endopeptidase Complex; Protein Isoforms; Protein Prenylation; Protein-Tyrosine Kinases; Proteolysis; Proto-Oncogene Proteins c-akt; Proto-Oncogene Proteins c-bcl-2; Quinolines; RNA, Small Interfering; Receptors, Cytokine; Recurrence; Reperfusion Injury; Retrospective Studies; Signal Transduction; Sirolimus; Standard of Care; Sterol Regulatory Element Binding Protein 2; Sterols; Survival Rate; TOR Serine-Threonine Kinases; Terpenes; Therapeutic Index; Transcription Factors; Transcriptome; Triple Negative Breast Neoplasms; Tumor Suppressor Protein p53; Tyrosine Kinase Inhibitors; Ubiquitin; Ubiquitin-Protein Ligases; Up-Regulation; Xenograft Model Antitumor Assays; Young Adult; pitavastatin; ruxolitinib; venetoclax</t>
+          <t>Arthritis; Autoimmunity; Borrelia burgdorferi; Breeding; Deer; Endotoxins; Epitopes, T-Lymphocyte; Extracellular Matrix Proteins; Genome-Wide Association Study; HLA-DRB1 Chains; Interferon Type I; Interferon-gamma; Lipopolysaccharides; Lyme Disease; Multifactorial Inheritance; Peptides; Peromyscus; Phenotype; Polymorphism, Single Nucleotide; Zoonoses</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gaut, Brandon</t>
+          <t>Borrelli, Emilia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adaptation, Physiological; Agriculture; Alleles; Altitude; Archaeology; Base Sequence; Biological Evolution; Biological Variation, Population; California; China; Chromatin; Chromosome Mapping; Chromosomes, Plant; Clergy; Climate Change; Climate Models; Crops, Agricultural; DNA; DNA Methylation; DNA Transposable Elements; DNA-Directed RNA Polymerases; Demography; Diploidy; Disease Vectors; Domestication; Drought Resistance; Droughts; Ecological and Environmental Phenomena; Ecology; Ecosystem; Epigenesis, Genetic; Epigenome; Epigenomics; Epistasis, Genetic; Escherichia coli; Escherichia coli Proteins; Europe; Evolution, Molecular; Extreme Weather; Fruit; Gene Expression; Gene Expression Regulation, Plant; Gene Flow; Genes, Plant; Genetic Background; Genetic Drift; Genetic Fitness; Genetic Variation; Genetics; Genetics, Population; Genome Size; Genome, Plant; Genome-Wide Association Study; Genomic Instability; Genomics; Genotype; Grassland; Heterozygote; Hispanic or Latino; History, Ancient; Homozygote; Honduras; Hot Temperature; Hyperspectral Imaging; Metagenomics; MicroRNAs; Microbiota; Microscopy, Electron, Scanning Transmission; Molecular Biology; Mutation; North America; Nucleic Acid Conformation; Oryza; Parasites; Periodicals as Topic; Persea; Phenomics; Phenotype; Phylogeny; Plant Breeding; Plant Physiological Phenomena; Plants; Pollination; Polymorphism, Single Nucleotide; Protoplasts; Quantitative Trait Loci; RNA, Plant; RNA, Small Interfering; Reproduction; Rho Factor; Salt Tolerance; Seeds; Sequence Analysis, DNA; Setaria Plant; Social Mobility; Software; Soil Microbiology; Sorghum; Sphingomonas; Stress, Physiological; Temperature; Tibet; Vitis; Xylella; Zea mays</t>
+          <t>Aged; Aged, 80 and over; Angiogenesis Inhibitors; Atrophy; Bruch Membrane; Circadian Clocks; Cocaine; Corpus Striatum; Cross-Sectional Studies; Diabetic Retinopathy; Dopamine; Fluorescein Angiography; Fovea Centralis; Fundus Oculi; Liver; Macula Lutea; Metabolomics; Neurons; Reading; Receptors, Dopamine D1; Receptors, Dopamine D2; Reproducibility of Results; Retinal Neovascularization; Retinal Pigment Epithelium; Retrospective Studies; Tomography, Optical Coherence; Vascular Endothelial Growth Factor A; Visual Acuity; Wet Macular Degeneration</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>German, Donovan</t>
+          <t>Burke, Thomas P</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Acclimatization; Adaptation, Physiological; Alkaline Phosphatase; Alzheimer Disease; Aminopeptidases; Amylases; Animal Husbandry; Bays; Biological Evolution; Biomarkers; Body Size; California; Carbohydrates; Carboxylesterase; Carnivory; Cellulases; Chromosomes; Cold Temperature; Conservation of Natural Resources; DNA Copy Number Variations; Diet; Diet, Food, and Nutrition; Dietary Fiber; Digestion; Digestive System Physiological Phenomena; Disease Progression; Down Syndrome; Ecological and Environmental Phenomena; Ecosystem; Endangered Species; Enzymes; Esters; Fatty Acids, Essential; Fermentation; Fires; Fisheries; Fishes; Gametogenesis; Gastrointestinal Microbiome; Gastrointestinal Tract; Gastropoda; Gene Dosage; Gene Expression Profiling; Genetics; Genome; Genomics; Heat-Shock Response; Herbivory; Hydrogen-Ion Concentration; Hydrolysis; Immunohistochemistry; Leucine; Life Cycle Stages; Lipase; Lipids; Lizards; Macrocystis; Marine Biology; Mexico; Microalgae; Microbiota; Mytilus; Pancreatic alpha-Amylases; Parents; Perciformes; Phylogeny; Physiology; Protein Isoforms; Proteomics; RNA, Ribosomal, 16S; Reproducibility of Results; Reproduction; Stomach; Temperature; Transcriptome; Trypsin; Zebrafish; alpha-Glucosidases; nan; tau Proteins</t>
+          <t>Amino Acid Transport Systems; Cytosol; Phospholipases; Rickettsia; Rickettsia Infections; Symporters</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gershon, Paul</t>
+          <t>Byun, Minji</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Adipogenesis; Adipose Tissue; Allografts; Antiviral Agents; Artificial Intelligence; Cell Differentiation; Cell Line; Cell Nucleus; Chromatin; DNA; DNA Damage; DNA-Binding Proteins; Deep Learning; Diabetes Mellitus, Experimental; Disease Outbreaks; Escherichia coli; Fascia; Glucose; Human Embryonic Stem Cells; Immunity, Innate; Insulin Secretion; Insulin-Secreting Cells; Ion Channels; Islets of Langerhans; Mass Spectrometry; Membrane Proteins; Morphogenesis; Mpox (monkeypox); Nuclear Proteins; Obesity; Organoids; Phosphoric Monoester Hydrolases; Pluripotent Stem Cells; Poxviridae; Protein Binding; Protein C; Proteome; Proteomics; Proto-Oncogene Mas; Rodentia; Signal Transduction; Smallpox; Systems Biology; Technology; Transcription Factor 7-Like 1 Protein; Transcription Factors; Transcriptome; Triple Negative Breast Neoplasms; Tumor Microenvironment; Vaccines; Vaccinia; Vaccinia virus; Viral Replication Compartments; Virion; Virology; Wnt Signaling Pathway; nan; src-Family Kinases</t>
+          <t>Amyotrophic Lateral Sclerosis; CD8-Positive T-Lymphocytes; Clone Cells; DNA Helicases; Endogenous Retroviruses; Epigenesis, Genetic; Gene Expression; Gene Knock-In Techniques; Heterochromatin; Motor Neurons; Multifunctional Enzymes; Mutation; RNA Helicases; RNA, Nuclear</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Glabe, Charles</t>
+          <t>Goldin, Alan L</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Adaptive Immunity; Aging; Algorithms; Allergy and Immunology; Alzheimer Disease; Amino Acids; Amyloid; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Amyloidogenic Proteins; Antibodies; Antibodies, Monoclonal; Antibody Specificity; Autoantibodies; Bacteriophages; Brain; Brain-Derived Neurotrophic Factor; CA1 Region, Hippocampal; Calcium; Cognition; Communicable Diseases; Congo Red; Desmoglein 1; Desmoglein 3; Energy Metabolism; Epitopes; Glutathione; High-Throughput Nucleotide Sequencing; Hypertension; Immunity; Immunity, Innate; Immunotherapy; Indicators and Reagents; Infant; Keratinocytes; Microglia; Neurodegenerative Diseases; Neurofibrillary Tangles; Pemphigus; Peptides; Phosphatidylinositol-3,4,5-Trisphosphate 5-Phosphatases; Plaque, Amyloid; Pre-Eclampsia; Pregnancy; Protein Conformation, beta-Strand; Proteinuria; Receptor, Muscarinic M3; Serum Amyloid A Protein; Single-Domain Antibodies; Statistics, Nonparametric; Supranuclear Palsy, Progressive; Synucleins; Vaccines; Virulence; nan; tau Proteins</t>
+          <t>Action Potentials; Arrhythmias, Cardiac; Heart Conduction System; Myocytes, Cardiac; NAV1.5 Voltage-Gated Sodium Channel; Sodium Channel Blockers; Voltage-Gated Sodium Channel Blockers</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Gonen, Shane</t>
+          <t>Hertel, Klemens J</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Algorithms; Anti-Bacterial Agents; Bacteriophages; Biochemistry; Brain; Conotoxins; Conus Snail; Cryoelectron Microscopy; Deep Learning; Escherichia coli; Eye; Gastrointestinal Microbiome; Genomics; Gram-Negative Bacterial Infections; Heart; Image Processing, Computer-Assisted; Ion Channel Gating; Kinetics; Membranes; Microscopy; Models, Molecular; Molecular Structure; Multiprotein Complexes; NAV1.8 Voltage-Gated Sodium Channel; Neoplasms; Peptides; Phage Therapy; Protein Conformation; Protein Folding; Proteins; Spider Venoms; Stenotrophomonas maltophilia; Virion; Voltage-Gated Sodium Channel Blockers; Wastewater; Zebrafish; nan</t>
+          <t>Alternative Splicing; Cell Line, Tumor; Cell Proliferation; Exons; Homocysteine; Introns; Methionine; Methylation; Nutrients; Protein-Arginine N-Methyltransferases; RNA Splice Sites; RNA Splicing; RNA-Binding Proteins</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Goulding, Celia</t>
+          <t>James, Anthony A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Alanine Dehydrogenase; Anti-Bacterial Agents; Arginine; Bacteria; Bacterial Proteins; Biliverdine; Biochemistry; Bordetella pertussis; Carrier Proteins; Communicable Diseases; Cryoelectron Microscopy; Disulfides; Drug Discovery; Electrons; Enterobacter cloacae; Enzyme Inhibitors; Escherichia coli; Escherichia coli Proteins; Eukaryotic Cells; Glycation End Products, Advanced; Hemagglutinins; Heme; Heme Oxygenase (Decyclizing); Hemoglobins; Histidine Kinase; Infant; Infant, Newborn; Iron; Latent Tuberculosis; Ligands; Lysine; Mass Spectrometry; Membrane Proteins; Molecular Biology; Molecular Structure; Mycobacteriaceae; Mycobacterium tuberculosis; Nucleosides; Nutrients; Pandemics; Pertussis Vaccine; Protein Interaction Mapping; Protein Processing, Post-Translational; Protein Sorting Signals; Proteins; Proteolysis; Pyruvaldehyde; Siderophores; Tomography, X-Ray Computed; Toxins, Biological; Tuberculosis; Vaccination; Virulence; Virulence Factors; Whooping Cough; nan</t>
+          <t>Adaptive Clinical Trials as Topic; Aedes; Animals, Genetically Modified; Anopheles; Betalains; Bombyx; CRISPR-Cas Systems; Cell Death; Circadian Rhythm; Color; Culex; Culicidae; DNA Transposable Elements; Dengue; Dengue Virus; Disease Vectors; Family; Filariasis; Gene Drive Technology; Gene Expression; Gene Expression Regulation, Enzymologic; Gene Transfer Techniques; Genetic Engineering; Genetic Introgression; Hedgehog Proteins; Insect Proteins; Insecticides; Introduced Species; Malaria; Malaria, Falciparum; MicroRNAs; Mosquito Control; Mosquito Vectors; Mutagenesis, Insertional; Oviposition; Peptide Hydrolases; Pigments, Biological; Plasmodium; Plasmodium falciparum; Promoter Regions, Genetic; Protein Isoforms; RNA; RNA, Guide, CRISPR-Cas Systems; Rabbits; Receptors, Odorant; Reproduction; Sex Differentiation; Sporozoites; Transcriptional Activation; Transgenes; Tubulin; Vector Borne Diseases; Vision, Ocular; Zika Virus; Zika Virus Infection</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Green, Kim</t>
+          <t>Koyuncu, Orkide</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ATP-Binding Cassette Transporters; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Apolipoproteins E; Astrocytes; Biomarkers; Bone Marrow; Brain; Brain Neoplasms; Brain-Derived Neurotrophic Factor; Breast Neoplasms; Cell Communication; Cell Nucleus; Cell Proliferation; Central Nervous System Diseases; Cognition; Coronavirus Infections; Cystatins; Demyelinating Diseases; Dendrimers; Disease Progression; Double-Blind Method; Down Syndrome; Gastrointestinal Microbiome; Gene Expression; Gene Expression Profiling; Gene Knock-In Techniques; Gene Regulatory Networks; Genes, fms; Genetic Variation; Genotype; Homeostasis; Immunotherapy; Integrases; Macrophage Colony-Stimulating Factor; Macrophages; Membrane Glycoproteins; Metabolomics; Microbiota; Microglia; Monocytes; Murine hepatitis virus; Mutation; Mutation, Missense; Myeloid Cells; NLR Family, Pyrin Domain-Containing 3 Protein; Nerve Degeneration; Nerve Regeneration; Neurites; Neuroglia; Neuroinflammatory Diseases; Neurons; Niacinamide; Phagocytosis; Phosphorylation; Plaque, Amyloid; Proof of Concept Study; Receptor, trkB; Receptors, Granulocyte-Macrophage Colony-Stimulating Factor; Receptors, Immunologic; Resilience, Psychological; Sex Characteristics; Single-Cell Analysis; Synapses; Tauopathies; Transcriptome; Treatment Outcome; Trimethoprim; Vitamin B Complex; tau Proteins</t>
+          <t>Alphaherpesvirinae; Alzheimer Disease; Axons; Brain; Brain Mapping; Cells, Cultured; Connectome; Dependovirus; Gene Silencing; Genetic Vectors; Green Fluorescent Proteins; Herpes Simplex; Herpes Simplex Virus Protein Vmw65; Herpesvirus 1, Human; Herpesvirus 1, Suid; Microscopy, Fluorescence; Nerve Net; Neurons; Pseudorabies; Rabies; Rabies virus; Viral Proteins; Virus Activation; Virus Latency; Virus Replication</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Green, Michael</t>
+          <t>Marsden, Matthew D</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Administration, Intravenous; Adolescent; Algorithms; Anisotropy; Antifungal Agents; Bias; Bipolar Disorder; Black or African American; Brain; Candidiasis, Invasive; Catalysis; Catalytic Domain; Chemistry, Bioinorganic; Child; Child, Preschool; Chromosome Mapping; Climate Change; Cohort Studies; Cross-Sectional Studies; Crystallography, X-Ray; Cytochrome P-450 Enzyme System; Cytochromes; Diffusion Tensor Imaging; Ecosystem; Electron Transport; Electrons; Europe; Genetic Predisposition to Disease; Genetic Variation; Genome-Wide Association Study; Genomics; Gray Matter; Head; Hemeproteins; Hippocampus; Hispanic or Latino; Infant; Iron; Ligands; Machine Learning; Magnetic Resonance Imaging; Metalloproteins; Metals; Models, Molecular; Neoplasms; Neuroimaging; Nitrogen; North America; Organ Size; Oxidation-Reduction; Oxygen; Phenotype; Plant Development; Plant Leaves; Plant Physiological Phenomena; Plants; Polymorphism, Single Nucleotide; Reproducibility of Results; Schizophrenia; Schizophrenic Psychology; Signal Transduction; Snow; Spectrum Analysis, Raman; Thermodynamics; Thinking; Treatment Outcome; Triazoles; White; White Matter; White People; X-Ray Absorption Spectroscopy</t>
+          <t>Anti-HIV Agents; Anti-Retroviral Agents; Bone Marrow; Bryostatins; CD4-Positive T-Lymphocytes; Coculture Techniques; Cytokines; HIV Infections; HIV-1; Host-Pathogen Interactions; Immunotherapy, Adoptive; Jurkat Cells; Killer Cells, Natural; Leukocytes, Mononuclear; NF-kappa B; Protein Kinase C; Protein Kinase Inhibitors; Receptors, Chimeric Antigen; Sex Characteristics; Sirolimus; Spleen; Viral Load; Viremia; Virus Activation; Virus Latency; Virus Replication</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Grill, Joshua</t>
+          <t>Mcclelland, Michael</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Adenosine Triphosphate; Administration, Oral; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloidogenic Proteins; Anhedonia; Antibodies, Monoclonal; Antibodies, Monoclonal, Humanized; Anxiety; Apathy; Apolipoprotein E4; Asian; Asian American Native Hawaiian and Pacific Islander; Autopsy; Biomarkers; Brain; California; Caregivers; Checklist; Clinical Trials Data Monitoring Committees; Clinical Trials as Topic; Clinical Trials, Phase II as Topic; Cognition; Cognitive Dysfunction; Cohort Studies; Control Groups; Delusions; Dementia; Depression; Diagnostic Errors; Disclosure; Disease Management; Disease Progression; Double-Blind Method; Ethnicity; Feasibility Studies; Hallucinations; Hispanic or Latino; Intermediate Filaments; Leadership; Life Style; Longitudinal Studies; Magnetic Resonance Imaging; Memory Disorders; Mental Status and Dementia Tests; Motivation; Neurodegenerative Diseases; Niacinamide; Patient Selection; Philippines; Phosphorylation; Positron-Emission Tomography; Prognosis; Proof of Concept Study; Psychiatrists; Randomized Controlled Trials as Topic; Registries; Republic of Korea; Research Subjects; Schizophrenia; Severity of Illness Index; Spinal Puncture; Suicidal Ideation; Suicide; Surveys and Questionnaires; Treatment Outcome; Vitamin B Complex; tau Proteins</t>
+          <t>Amino Acids; Anaerobiosis; Anti-Bacterial Agents; Bacteria; Bacterial Proteins; Caco-2 Cells; Cardiolipins; Cattle; Cecum; Colitis; Dietary Proteins; Endodeoxyribonucleases; Enterobacteriaceae Infections; Formates; Gastrointestinal Microbiome; Gene Deletion; HT29 Cells; Host-Pathogen Interactions; Hydrogen Peroxide; Inflammasomes; Inflammation; Lipopolysaccharides; Lyases; Macrophages; Methionine; Mucus; NADPH Oxidases; Operon; Oxidative Stress; Peptide Hydrolases; Phagocytes; Phylogeny; Prophages; Providencia; Pyruvates; RNA; RNA, Transfer; Reactive Oxygen Species; Respiration; SOS Response, Genetics; Salmonella; Salmonella Infections; Salmonella Infections, Animal; Salmonella Phages; Salmonella enterica; Salmonella typhimurium; Serogroup; Tetracycline; Toll-Like Receptor 4; Transcription Factors; Type III Secretion Systems; Viral Proteins; Virulence Factors</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Gross, Steven</t>
+          <t>Semler, Bert L</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Adenosine Diphosphate; Adjuvants, Immunologic; Adjuvants, Pharmaceutic; Anti-Bacterial Agents; Anti-Infective Agents; Antimicrobial Cationic Peptides; Antimicrobial Peptides; Biological Transport; Biophysics; Brain; Cell Communication; Cell Membrane; Clostridioides; Clostridioides difficile; Computational Biology; Computer Simulation; Cytoskeleton; DNA; Diffusion; Dynactin Complex; Dyneins; Escherichia coli; Glycogen Synthase Kinase 3 beta; Histones; Immunity, Innate; Kinesins; Kinetics; Lipid Droplets; Lipopolysaccharides; Metronidazole; Microbiota; Microtubule-Associated Proteins; Microtubules; Molecular Motor Proteins; Motor Neuron Disease; Muscular Atrophy, Spinal; Mutation; Neurodegenerative Diseases; Neurons; Optical Tweezers; Organelles; Parkinson Disease; Polymyxin B; Protein Binding; Protein Conformation; Protein Processing, Post-Translational; Proteins; Saccharomyces cerevisiae; Tubulin; Vancomycin</t>
+          <t>2',5'-Oligoadenylate Synthetase; Adenosine Deaminase; Alzheimer Disease; Antigens, Viral; Brain; Brain Mapping; COVID-19 Nucleic Acid Testing; CRISPR-Cas Systems; Cardiomyopathy, Dilated; Connectome; Coxsackievirus Infections; Cytidine Deaminase; Cytoplasmic Granules; DNA Helicases; Endoribonucleases; Enterovirus B, Human; Enzyme Activation; Gene Knockout Techniques; Genetic Vectors; Genomics; Green Fluorescent Proteins; HEK293 Cells; Interferon Regulatory Factor-2; Microscopy, Fluorescence; Minor Histocompatibility Antigens; Molecular Diagnostic Techniques; Myocytes, Cardiac; Nerve Net; Neurons; Nucleic Acid Amplification Techniques; Peptide Hydrolases; Persistent Infection; Poly-ADP-Ribose Binding Proteins; Protein Kinases; RNA Helicases; RNA Recognition Motif Proteins; RNA Stability; RNA, Double-Stranded; RNA, Viral; RNA-Binding Proteins; Rabies; Rabies virus; Real-Time Polymerase Chain Reaction; SARS-CoV-2; STAT2 Transcription Factor; Saliva; Specimen Handling; Stress Granules; Viral Proteins; Virus Diseases; Virus Replication; eIF-2 Kinase</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Halbrook, Christopher</t>
+          <t>Shi, Yongsheng</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3-hydroxy-3-methylglutaryl-coenzyme A; Acute Disease; Adenocarcinoma; Allografts; Amiloride; Anti-Inflammatory Agents; Arginase; Arginine; Asparagine; Autophagy; CD8-Positive T-Lymphocytes; CRISPR-Cas Systems; Cancer-Associated Fibroblasts; Carcinogenesis; Carcinoma, Pancreatic Ductal; Catalytic Domain; Cell Line, Tumor; Cell Lineage; Cell Proliferation; Cell Transformation, Neoplastic; Chromatography, Liquid; Clone Cells; Communication; Critical Pathways; Cues; Cytotoxins; Deoxycytidine; Drug Resistance, Neoplasm; Early Diagnosis; Energy Metabolism; Epigenesis, Genetic; Epithelial Cells; Fibroblasts; Fibrosis; Flow Cytometry; Gemcitabine; Gene Expression Profiling; Glutathione; Granulocyte-Macrophage Colony-Stimulating Factor; Hepatocyte Growth Factor; Histones; Hospitalization; Immunotherapy; Indicators and Reagents; Liver Neoplasms; Macrophages; Metabolic Networks and Pathways; Metabolic Reprogramming; Metabolomics; Methylation; Mevalonic Acid; Myeloid Cells; Neoplasms; Organoids; Oxidation-Reduction; Oxidoreductases; Pain Management; Pancreas; Pancreatic Diseases; Pancreatic Hormones; Pancreatic Neoplasms; Pancreatitis; Pancreatitis, Chronic; Pinocytosis; Prognosis; Proteomics; Pyrimidines; RNA; Regeneration; Sequence Analysis, RNA; Signal Transduction; Sodium-Hydrogen Exchangers; Staining and Labeling; Standard of Care; Stromal Cells; Survival Rate; Symbiosis; Tandem Mass Spectrometry; Transcription Factors; Transcriptome; Tumor Microenvironment; Tumor-Associated Macrophages; Uracil; geranylgeranyl pyrophosphate</t>
+          <t>3' Untranslated Regions; Adenine; Adenosine; Agammaglobulinaemia Tyrosine Kinase; Aged; Aged, 80 and over; Air Pollutants; Air Pollution; Alternative Splicing; Alzheimer Disease; American Indian or Alaska Native; Amyloid beta-Peptides; Asian; Astrocytes; Ataxin-7; Basic Helix-Loop-Helix Transcription Factors; Blindness; Blood Pressure; Brain; Carcinoma, Pancreatic Ductal; Cell Differentiation; Cell Line, Tumor; Cell Nucleus; Cell Survival; Coculture Techniques; Comorbidity; Cross-Sectional Studies; DNA-Binding Proteins; Dementia; Dermatitis, Atopic; Diaphragm; Disease Progression; Disorders of Excessive Somnolence; Drug Resistance, Neoplasm; Emigrants and Immigrants; Endoplasmic Reticulum; Environmental Exposure; Epidermis; Exosome Multienzyme Ribonuclease Complex; Ferroptosis; Gene Expression Regulation; Gene Expression Regulation, Neoplastic; Genes, Reporter; HEK293 Cells; HeLa Cells; High-Throughput Nucleotide Sequencing; Homeostasis; Hypertension; Hypoglossal Nerve; Immunoglobulin M; Induced Pluripotent Stem Cells; Inflammation; Interferon Regulatory Factors; Intrinsically Disordered Proteins; Keratinocytes; Leukemia, Lymphocytic, Chronic, B-Cell; Lipid Peroxidation; Machine Learning; Magnetic Resonance Imaging; Medulla Oblongata; Microglia; Multimorbidity; Mutation; Neuromuscular Junction; Neurons; Nitrogen Dioxide; Organoids; Pancreatic Neoplasms; Particulate Matter; Peptides; Phagocytosis; Phrenic Nerve; Piperidines; Plasma Cells; Poly A; Polyadenylation; Polymorphism, Single Nucleotide; Polysomnography; Positive Regulatory Domain I-Binding Factor 1; Presenilin-1; Promoter Regions, Genetic; Protein Binding; Protein Kinase Inhibitors; Pyrazoles; Pyrimidines; RNA 3' End Processing; RNA Polymerase II; RNA Precursors; RNA Processing, Post-Transcriptional; RNA Splice Sites; RNA Splicing; RNA Stability; RNA, Antisense; RNA, Messenger; RNA, Nuclear; RNA, Small Nuclear; RNA-Binding Proteins; Receptors, Aryl Hydrocarbon; Retrospective Studies; Ribonucleoprotein, U1 Small Nuclear; Ribonucleoproteins, Small Nuclear; Signal Transduction; Sleep Apnea Syndromes; Sleep Apnea, Obstructive; Snoring; Spinal Cord; Spinocerebellar Ataxias; Spliceosomes; Tongue; Transcription Factors; Transcriptome; Visual Cortex; Visual Prosthesis; tau Proteins</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hammer, Tobin</t>
+          <t>Tan, Ming</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Agriculture; Anthropogenic Effects; Bacteria; Bees; Biodiversity; Biological Evolution; Coral Bleaching; Crithidia; Crops, Agricultural; DNA Contamination; Data Analysis; Diet; Disease Resistance; Dysbiosis; Ecological and Environmental Phenomena; Ecology; Ecosystem; Gastrointestinal Microbiome; Genetics; Health; Host Microbial Interactions; Human Activities; Insecta; Longevity; Magnolia; Metagenomics; Microbiota; Motivation; Parasites; Pollination; Quality Indicators, Health Care; RNA, Ribosomal, 16S; Reproduction; Schools; Seasons; Serratia marcescens; Social Behavior; Social Interaction; Symbiosis; nan</t>
+          <t>Acrylamides; Aftercare; Aged; Aged, 80 and over; Anilides; Aniline Compounds; Antineoplastic Combined Chemotherapy Protocols; Asia, Southeastern; Bacterial Proteins; Cambodia; Carbazoles; Carcinoma, Non-Small-Cell Lung; Chlamydia Infections; Chlamydia trachomatis; Cilia; DNA; Delirium; Disease Susceptibility; Drosophila Proteins; Enhancer Elements, Genetic; Epithelial Cells; ErbB Receptors; Exons; Fever; Gene Expression Regulation; Gene Expression Regulation, Bacterial; Gene Knockdown Techniques; HeLa Cells; Health Resources; High-Throughput Nucleotide Sequencing; Incidence; Indoles; Intensive Care Units; Length of Stay; Lung Neoplasms; Membrane Proteins; Metagenome; Metagenomics; Mutagenesis, Insertional; Mutation; Patient Discharge; Pilot Projects; Prognosis; Promoter Regions, Genetic; Prospective Studies; Protein Kinase Inhibitors; Public Health Surveillance; Pyrimidines; Quinolines; Retrospective Studies; Seroepidemiologic Studies; Sorting Nexins; Transcription Factors; Treatment Outcome</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Hu, Yilin</t>
+          <t>Abbott, Geoffrey Winston</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Adenosine Triphosphate; Aged; Aged, 80 and over; Ammonia; Anaerobiosis; Animals, Genetically Modified; Azotobacter vinelandii; Bacterial Proteins; Biocatalysis; Biomarkers, Tumor; Bioreactors; Biosynthetic Pathways; Breast Neoplasms; Carbon Dioxide; Carbon Monoxide; Carcinoma, Non-Small-Cell Lung; Catalysis; Cell Line, Tumor; Chemistry, Bioinorganic; Chromosomes, Human, Pair 17; Circulating Tumor DNA; Drosophila Proteins; Drosophila melanogaster; Drug Carriers; Drug Delivery Systems; Drug Liberation; Drug Resistance, Neoplasm; Ecosystem; Electrons; Enzymes; ErbB Receptors; Escherichia coli; Evolution, Molecular; Exons; Gene Expression; Gold; Hydrocarbons; Hydrogen; Hydrogen Peroxide; Immunohistochemistry; In Situ Hybridization; Iron-Sulfur Proteins; Lactic Acid; Lung Neoplasms; Metal Nanoparticles; Metalloproteins; Mixed Function Oxygenases; Models, Molecular; Molybdenum; Molybdoferredoxin; Mutagenesis, Insertional; Nanoparticles; Neoplasms; Nitrogen; Nitrogen Cycle; Nitrogen Fixation; Nitrogenase; Oxidoreductases; Oxygen; Phylogeny; Prognosis; Protein Kinase Inhibitors; Receptor, ErbB-2; Retrospective Studies; Rotation; Silicon Dioxide; Sulfur; Technology; Transcription Factors; Warburg Effect, Oncologic</t>
+          <t>Alkaloids; Analgesics; Anti-Arrhythmia Agents; Anti-Inflammatory Agents; Arrhythmias, Cardiac; Ataxia; Behavior, Animal; Benzhydryl Compounds; Calcitonin Gene-Related Peptide; Canagliflozin; Cardiomyopathies; Cardiopulmonary Resuscitation; Cocaine; Coriandrum; Death, Sudden, Cardiac; Diabetes Mellitus, Type 2; Diterpenes; Dopamine; Dopamine Uptake Inhibitors; Dopaminergic Neurons; Globus Pallidus; Glucosides; Guanidines; HEK293 Cells; Heart Arrest; Indigenous Canadians; Ion Channel Gating; Ischemic Postconditioning; KCNQ Potassium Channels; KCNQ2 Potassium Channel; KCNQ3 Potassium Channel; Kv1.1 Potassium Channel; Levodopa; Ligands; Medicine, Traditional; Memantine; Mesenteric Arteries; Molecular Docking Simulation; Molecular Dynamics Simulation; Motor Activity; Movement Disorders; Muscle, Smooth, Vascular; Mutation; Myocardial Reperfusion Injury; Myocytes, Cardiac; Myokymia; Neuronal Plasticity; Oligopeptides; Parvalbumins; Piperidines; Plant Extracts; Plants, Medicinal; Potassium Channel Blockers; Protein Isoforms; Rats, Sprague-Dawley; Rats, Wistar; Receptors, Calcium-Sensing; Receptors, N-Methyl-D-Aspartate; Renal Artery; Reperfusion Injury; Rosmarinus; Sensory Receptor Cells; Sodium-Glucose Transporter 1; Sodium-Glucose Transporter 2; Sodium-Glucose Transporter 2 Inhibitors; Sodium-Hydrogen Exchanger 1; Spermatic Cord Torsion; Stroke Volume; Sulfones; TRPV Cation Channels; Tannins; Testis; Vasodilation; Vasodilator Agents; Ventral Tegmental Area; Ventricular Function, Left</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Hughes, Christopher</t>
+          <t>Beier, Kevin T</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Adipogenesis; Adipose Tissue; Allografts; Alzheimer Disease; Anemia; Angiogenesis; Anxiety; Apolipoprotein E2; Apolipoprotein E4; Arteries; Arteriovenous Malformations; Astrocytes; Basement Membrane; Bayes Theorem; Biomarkers, Tumor; Biomimetics; Blood Substitutes; Blood Vessels; Blood-Borne Pathogens; Blood-Brain Barrier; Brain; Breast; Capillaries; Cell Line, Tumor; Central Nervous System Diseases; Clustered Regularly Interspaced Short Palindromic Repeats; Coculture Techniques; Colonic Neoplasms; Colorectal Neoplasms; Cytoreduction Surgical Procedures; Diabetes Mellitus; Drug Development; Drug Evaluation; Drug Interactions; Drug Repositioning; Endoglin; Endothelial Cells; Endothelium, Vascular; Epistaxis; Exosomes; Extracellular Matrix; Fascia; Fibroblasts; Fluorouracil; Gene Expression; Glucose; Heart Failure; Huntington Disease; Hyperthermia, Induced; Hyperthermic Intraperitoneal Chemotherapy; Incidence; Induced Pluripotent Stem Cells; Infant; Insulin; Islets of Langerhans; Islets of Langerhans Transplantation; Lab-On-A-Chip Devices; Leucovorin; Liver; Lung; Microfluidics; Microglia; Microphysiological Systems; Microvessels; Mutation; Myocytes, Smooth Muscle; Neoadjuvant Therapy; Neoplasms; Neoplastic Processes; Neovascularization, Pathologic; Neurons; Obesity; Oxaliplatin; Paclitaxel; Pancreas; Pancreatic Neoplasms; Patient Advocacy; Pazopanib; Peptides; Pericytes; Peritoneal Cavity; Peritoneal Neoplasms; Peritoneum; Phenotype; Port-Wine Stain; Prospective Studies; RNA; Rare Diseases; Rodentia; Signal Transduction; Single-Cell Gene Expression Analysis; Sitting Position; Snail Family Transcription Factors; Splenic Neoplasms; Stomach Neoplasms; Stroke; Stromal Cells; Sturge-Weber Syndrome; Survival Rate; Technology; Telangiectasia, Hereditary Hemorrhagic; Thrombosis; Tight Junctions; Tissue Engineering; Transcription Factors; Transcriptome; Transcytosis; Triple Negative Breast Neoplasms; Tumor Microenvironment; Vascular Malformations; cdc42 GTP-Binding Protein; nan; peptide I; rho GTP-Binding Proteins</t>
+          <t>Acyltransferases; Amygdala; Analgesics, Opioid; Anxiety; Behavior, Animal; Brain; Brain Injuries; Cocaine; Cocaine-Related Disorders; Dopamine; Dopamine Uptake Inhibitors; Dopaminergic Neurons; Dronabinol; Endocytosis; Globus Pallidus; Hippocampus; Hypothalamic Area, Lateral; Hypothalamus; KCNQ Potassium Channels; KCNQ3 Potassium Channel; Logic; Long-Term Potentiation; Memory; Memory Disorders; Morphine; Neural Pathways; Neuronal Plasticity; Neurons; Nicotine; Parvalbumins; Peptides; Pinocytosis; Prefrontal Cortex; Preoptic Area; Protein Kinase C; Receptors, AMPA; Receptors, Nicotinic; Receptors, Opioid, mu; Sleep; Sleep Deprivation; Sleep, REM; Social Behavior; Substance Withdrawal Syndrome; Substantia Nigra; Synapses; Tegmentum Mesencephali; Ventral Tegmental Area; Wakefulness; alpha7 Nicotinic Acetylcholine Receptor; gamma-Aminobutyric Acid</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Huxman, Travis</t>
+          <t>Cahalan, Michael</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Biodiversity; Biomass; California; Carbon; Climate Change; Desert Climate; Ecological and Environmental Phenomena; Ecology; Ecosystem; Fertilizers; Grassland; Groundwater; Health Surveys; Humidity; Hydrology; Introduced Species; Museums; Nitrogen; Nutrients; Phosphorus; Physiology, Comparative; Plants; Rain; Remote Sensing Technology; Soil; Temperature; Volunteers; Water; Water Resources; Water Supply; Wind</t>
+          <t>Adenosine Diphosphate; Alzheimer Disease; Amyloid beta-Peptides; Analgesics; Anti-Inflammatory Agents; Antigen Presentation; CD8-Positive T-Lymphocytes; Calcium; Calcium Signaling; Chemokines; Coriandrum; Corticotropin-Releasing Hormone; Fluorescent Dyes; Heart Rate; Induced Pluripotent Stem Cells; Ion Channels; Ionophores; Lighting; Membrane Glycoproteins; Membrane Potentials; Microglia; Molecular Docking Simulation; Neural Stem Cells; Neurons; Plant Extracts; Plants, Medicinal; Potassium Channel Blockers; Receptors, Immunologic; Receptors, Purinergic; Signal Transduction; Synapses; T-Lymphocytes; Tannins</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Inlay, Matthew</t>
+          <t>Davies, David Huw</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Allografts; Anemia, Aplastic; Apoptosis; Blood Component Removal; Bone Marrow; Bone Marrow Transplantation; Brain; CD4-Positive T-Lymphocytes; COVID-19 Nucleic Acid Testing; Coronavirus Infections; Cyclophosphamide; Cytokines; Drug Combinations; Fetal Blood; Flow Cytometry; Fluticasone; Glucocorticoids; Graft vs Host Disease; HLA Antigens; Hematologic Neoplasms; Hematopoietic Stem Cell Transplantation; Hematopoietic Stem Cells; Heterografts; Immunity; Immunophenotyping; Immunosuppression Therapy; Immunosuppressive Agents; Incidence; Infertility; Interleukin-2; Leptospiraceae; Leukocytes, Mononuclear; Macrophages; Magnetic Phenomena; Major Histocompatibility Complex; Microglia; Molecular Diagnostic Techniques; Neoplasms; Nucleic Acid Amplification Techniques; Parents; Patient Care; Pharmaceutical Preparations; Prednisolone; Proto-Oncogene Proteins c-bcl-2; Real-Time Polymerase Chain Reaction; Regenerative Medicine; SARS-CoV-2; Saliva; Siblings; Specimen Handling; Stem Cells; Survival Rate; Systemic Inflammatory Response Syndrome; T-Lymphocytes; T-Lymphocytes, Regulatory; Tissue Donors; Transplantation Conditioning; Transplantation, Haploidentical; Transplantation, Heterologous; Transplantation, Homologous; venetoclax</t>
+          <t>Adjuvants, Immunologic; Adjuvants, Pharmaceutic; Adjuvants, Vaccine; Adolescent; Aerosols; Antibodies, Neutralizing; Antibodies, Viral; Antibody Formation; Antigens; Antigens, Bacterial; B-Lymphocytes; Bacterial Vaccines; CD4-Positive T-Lymphocytes; Child; Child, Preschool; Coxiella burnetii; Cytokines; Delayed-Action Preparations; Down-Regulation; Ebola Vaccines; Ebolavirus; Flagellin; Glycoproteins; Green Fluorescent Proteins; Guinea Pigs; Hemagglutinin Glycoproteins, Influenza Virus; Hemagglutinins; Hemorrhagic Fever, Ebola; Homeostasis; Hydrogels; Immunization; Immunogenicity, Vaccine; Immunoglobulin Class Switching; Immunoglobulin G; Immunoglobulin Isotypes; Immunoinformatics; Immunologic Memory; Influenza A Virus, H5N1 Subtype; Influenza Vaccines; Influenza, Human; Ligands; Lipid A; Lipopolysaccharides; Lymphocytes; Malaria; Malaria Vaccines; Malaria, Falciparum; Malaria, Vivax; Memory B Cells; Mice, Inbred BALB C; Nanoparticles; Oligodeoxyribonucleotides; Organ Specificity; Organoids; Orthomyxoviridae Infections; Palatine Tonsil; Particle Size; Phylogeny; Plasmodium falciparum; Plasmodium vivax; Polylactic Acid-Polyglycolic Acid Copolymer; Polymers; Polysorbates; Q Fever; Saponins; Sex Characteristics; Sex Factors; Sporozoites; Squalene; Streptavidin; Sudan; T-Lymphocytes; Th1 Cells; Toll-Like Receptor 4; Toll-Like Receptor Agonists; Toll-Like Receptors; Vaccination; Vaccines; Vaccines, Combined; Vaccines, Synthetic; Young Adult</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>James, Anthony</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Adaptive Clinical Trials as Topic; Aedes; Animals, Genetically Modified; Anopheles; Betalains; Blood Vessels; Bombyx; Brain; CRISPR-Cas Systems; Case-Control Studies; Cell Death; Cerebral Cortex; Circadian Rhythm; Color; Culex; Culicidae; DNA Transposable Elements; Dengue; Dengue Virus; Disease Vectors; Family; Filariasis; Functional Laterality; Gene Drive Technology; Gene Expression; Gene Expression Regulation, Enzymologic; Gene Transfer Techniques; Genetic Engineering; Genetic Introgression; Genetics; Global Health; Hedgehog Proteins; Insecticides; Magnetic Resonance Imaging; Malaria; Malaria, Falciparum; MicroRNAs; Mosquito Control; Mosquito Vectors; Mutagenesis, Insertional; Oviposition; Peptide Hydrolases; Pigments, Biological; Plasmodium; Plasmodium falciparum; Promoter Regions, Genetic; RNA; RNA, Guide, CRISPR-Cas Systems; Rabbits; Reproduction; Schizophrenia; Sex Differentiation; Sporozoites; Transcriptional Activation; Transgenes; Tubulin; Vector Borne Diseases; Vision, Ocular; Zika Virus; Zika Virus Infection</t>
-        </is>
-      </c>
+          <t>Eguchi, Asuka</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kawas, Claudia</t>
+          <t>Felgner, Philip</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Adrenergic beta-Antagonists; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloidosis; Amyotrophic Lateral Sclerosis; Angiotensin-Converting Enzyme Inhibitors; Aniline Compounds; Apolipoproteins E; Atrophy; Autopsy; Biomarkers; Brain; Case-Control Studies; Cataract; Cell Separation; Centenarians; Cerebral Cortex; Cerebrovascular Circulation; Cerebrovascular Disorders; Clinical Trials as Topic; Cognition; Cognitive Dysfunction; Cohort Studies; Cryopreservation; DNA-Binding Proteins; Databases, Factual; Dementia; Dementia, Vascular; Diagnosis, Differential; Disease Progression; Educational Status; Epidemiology; Ethnicity; Ethylene Glycols; Executive Function; Extracellular Vesicles; Frailty; Frontotemporal Lobar Degeneration; Geriatric Assessment; Hand Strength; Hippocampus; Incidence; Inclusion Bodies; Lewy Bodies; Lewy Body Disease; Life Style; Limbic System; Longitudinal Studies; Magnetic Resonance Imaging; Medical History Taking; Nervous System Diseases; Neurofibrillary Tangles; Neuroglia; Neuroimaging; Neurons; Neuropsychological Tests; Nonagenarians; Organ Size; Physical Functional Performance; Plaque, Amyloid; Positron-Emission Tomography; Public Health; RNA-Seq; Racial Groups; Reference Values; Resilience, Psychological; Retrospective Studies; Risk Factors; Self Report; Self-Help Devices; Sex Factors; Sleep; Sleep Duration; Syncope; TDP-43 Proteinopathies; Tauopathies; Walking Speed; White Matter</t>
+          <t>Adjuvants, Immunologic; Adjuvants, Vaccine; Aerosols; Aged; Antibodies, Neutralizing; Antibodies, Protozoan; Antibodies, Viral; Antibody Formation; Antigens; Antigens, Bacterial; Antigens, Protozoan; Bacterial Vaccines; COVID-19; COVID-19 Serotherapy; COVID-19 Vaccines; CRISPR-Cas Systems; Case-Control Studies; Cell-Penetrating Peptides; Child; Child, Preschool; Clone Cells; Computational Biology; Coxiella burnetii; Cross Reactions; Cross-Sectional Studies; Delayed-Action Preparations; Endothelial Protein C Receptor; Epitopes; Flavivirus; Furocoumarins; Gene Editing; Gene Transfer Techniques; Genetic Therapy; Guinea Pigs; HEK293 Cells; HIV Infections; Health Personnel; Hydrogels; Immunity, Humoral; Immunization; Immunization, Passive; Immunoglobulin G; Immunoglobulin M; Lipids; Lipopolysaccharides; Liposomes; Machine Learning; Malaria; Malaria Vaccines; Malaria, Falciparum; Malaria, Vivax; Mice, Inbred BALB C; Nanoparticles; Nucleic Acids; Pandemics; Peptides; Plasmodium falciparum; Plasmodium vivax; Polylactic Acid-Polyglycolic Acid Copolymer; Protozoan Proteins; Q Fever; RNA, Small Interfering; RNA, Viral; Ribonucleoproteins; SARS-CoV-2; Seroepidemiologic Studies; Sporozoites; Support Vector Machine; Tanzania; Th1 Cells; Vaccination; Vaccine Efficacy; Vaccines, Combined; mRNA Vaccines</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kim, Seungsoo</t>
+          <t>Hicks, Michael Ryan</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Academies and Institutes; Adolescent; Aged; Animals, Domestic; Antibodies, Monoclonal, Humanized; Antineoplastic Combined Chemotherapy Protocols; Attitude of Health Personnel; B7-H1 Antigen; Biomarkers, Tumor; Blepharoptosis; California; Cancer Care Facilities; Environmental Monitoring; Fertility; Fertility Preservation; Fluorocarbons; Fluorouracil; Genomics; Genotype; Interviews as Topic; Machine Learning; National Cancer Institute (U.S.); Neoplasms; Oncologists; Ophthalmic Solutions; Ophthalmology; Phenotype; Phenylephrine; Physician-Patient Relations; Platinum; Qualitative Research; Receptor, ErbB-2; Stomach Neoplasms; Transcriptome; Trastuzumab; Waste Disposal, Fluid; Wastewater; Water Pollutants, Chemical; Young Adult</t>
+          <t>Cell Differentiation; Dystrophin; Homeodomain Proteins; Mice, Inbred mdx; Muscle Development; Muscle, Skeletal; PAX3 Transcription Factor; PAX7 Transcription Factor; Pluripotent Stem Cells; Regeneration; Satellite Cells, Skeletal Muscle; Stem Cell Niche; Tissue Distribution</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kong, Mei</t>
+          <t>Holmes, Todd C</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AMP-Activated Protein Kinases; Abdominal Cavity; Adenocarcinoma; Adenocarcinoma, Mucinous; Adenomatous Polyposis Coli; Adolescent; Aged; Allografts; Antineoplastic Agents; Appendectomy; Appendiceal Neoplasms; Ascitic Fluid; Autoimmune Diseases; Biological Products; Cachexia; California; Carcinogenesis; Carcinoma; Catalytic Domain; Cell Cycle; Cell Differentiation; Cell Line; Cell Line, Tumor; Cell Plasticity; Cell Proliferation; Chemistry, Pharmaceutical; Chromatin; Chromatography, Liquid; Clinical Relevance; Colonic Neoplasms; Colorectal Neoplasms; Communication Barriers; Cost of Illness; Cytokines; Cytoreduction Surgical Procedures; DNA; Diabetes Mellitus; Diabetes Mellitus, Type 2; Diet, High-Fat; Diet, Ketogenic; Dietary Supplements; Dioxygenases; Drug Resistance, Neoplasm; Early Detection of Cancer; Epigenesis, Genetic; Epigenomics; Ficus; Gastrointestinal Neoplasms; Gene Expression; Gene Expression Regulation, Neoplastic; Genes, Tumor Suppressor; Genes, p16; Genetics; Glucose; Glutamine; Heterografts; High-Throughput Screening Assays; Histone Code; Histone Demethylases; Histone Methyltransferases; Histones; Homeostasis; Hospitalization; Hyperthermic Intraperitoneal Chemotherapy; Immunity; Immunoglobulin G; Immunoglobulin G4-Related Disease; Immunotherapy; Incidence; Intestinal Mucosa; Isotopes; Ketoglutaric Acids; Ketone Bodies; Ketones; Lactic Acid; Language; Lipid Metabolism; Lipids; Lipogenesis; Liquid Chromatography-Mass Spectrometry; Liver Neoplasms; Lubricants; Melanoma; Metabolic Diseases; Metabolic Networks and Pathways; Metabolism; Metformin; Micronutrients; Microscopy; Military Personnel; Monocarboxylic Acid Transporters; Morbidity; Muscles; Mutation; National Center for Advancing Translational Sciences (U.S.); Neoplasms; Neoplasms, Second Primary; Neoplastic Processes; Neoplastic Stem Cells; Nutrients; Obesity; Organoids; Ovarian Neoplasms; Oxidative Phosphorylation; PPAR gamma; Pancreas; Patient Preference; Peptide Hydrolases; Peritoneal Cavity; Peritoneal Neoplasms; Peritoneum; Peroxisome Proliferator-Activated Receptors; Phenotype; Phosphoprotein Phosphatases; Phosphoric Monoester Hydrolases; Phosphorylation; Pilot Projects; Pioglitazone; Positron Emission Tomography Computed Tomography; Prevalence; Prostatic Neoplasms; Protein Phosphatase 2; Protein Serine-Threonine Kinases; Proteolysis; Pseudomyxoma Peritonei; Pyruvic Acid; Qualitative Research; Quality of Life; RNA; RNA, Long Noncoding; Rectal Neoplasms; Risk Factors; Sequence Analysis, RNA; Sex Characteristics; Sex Chromosomes; Signal Transduction; Standard of Care; Stem Cells; Substrate Specificity; T-Lymphocytes; TWEAK Receptor; Tandem Mass Spectrometry; Thiazolidinediones; Transcription Factors; Tumor Microenvironment; Videoconferencing; Vitamin A; Vitamin B 6; Vitamins; Weight Loss; Wnt Signaling Pathway; nan</t>
+          <t>Alzheimer Disease; Amyloid beta-Peptides; Animals, Genetically Modified; Arthropod Antennae; Autism Spectrum Disorder; Blood-Brain Barrier; Brain; Brain Diseases; Brain Mapping; CA1 Region, Hippocampal; Calcium; Capsid; Cell Differentiation; Cells, Cultured; Cerebral Hemorrhage; Cholecystokinin; Cognition; Cognition Disorders; Congresses as Topic; Connectome; Connexins; Dependovirus; Drosophila Proteins; Drosophila melanogaster; Endothelial Cells; Endothelium; Enhancer Elements, Genetic; Entorhinal Cortex; Erythrocytes; GABAergic Neurons; Gap Junctions; Gene Expression; Gene Expression Profiling; Genetic Vectors; Green Fluorescent Proteins; Hippocampus; Homeodomain Proteins; Immunohistochemistry; In Situ Hybridization, Fluorescence; Interneurons; Ketamine; Learning; Macaca fascicularis; Microglia; Microscopy, Fluorescence; Muscle Fibers, Skeletal; Muscular Dystrophy, Facioscapulohumeral; Myoblasts; Nerve Net; Neural Pathways; Neuroimaging; Neuronal Plasticity; Neurons; Olfactory Bulb; Olfactory Pathways; Oxidative Phosphorylation; Parvalbumins; Prosencephalon; Pyramidal Cells; Rabies; Rabies virus; Schizophrenia; Single-Cell Analysis; Smell; Transcriptome; Transduction, Genetic</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Konieczny, Piotr</t>
+          <t>Huang, Lan</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Air Pollutants; Air Pollution; Autophagy; Breast Neoplasms; Cadmium; Catalysis; Catalytic Domain; Cell Cycle Proteins; Cell Nucleus; Child Development; China; Congresses as Topic; Endopeptidases; Endoplasmic Reticulum; Endoplasmic Reticulum-Associated Degradation; Environmental Monitoring; F-Box Proteins; Gene Expression Regulation; Golgi Apparatus; HEK293 Cells; HeLa Cells; Huntingtin Protein; Huntington Disease; Immunotherapy, Adoptive; Infant; Infant, Extremely Premature; Infant, Newborn; Integrins; Intrinsically Disordered Proteins; Leukemia, Myeloid, Acute; Lipidomics; Lipids; Lysosomes; Mass Spectrometry; Membrane Proteins; Mental Health; Mice, Nude; Microscopy; Mitochondria; Mitochondrial Proteins; Models, Molecular; Multicenter Studies as Topic; Neurodevelopmental Disorders; Ozone; Parents; Peptides; Pharmaceutical Preparations; Proteasome Endopeptidase Complex; Protein Binding; Protein Biosynthesis; Protein Domains; Protein Interaction Mapping; Protein Interaction Maps; Protein Transport; Proteins; Proteolysis; Proteome; Proteomics; Proteostasis; Quality of Life; RNA 3' End Processing; RNA Polymerase II; RNA Precursors; RNA Processing, Post-Transcriptional; RNA Splicing; RNA, Messenger; RNA-Binding Proteins; Randomized Controlled Trials as Topic; Receptors, Chimeric Antigen; Ribosomes; S-Phase Kinase-Associated Proteins; SKP Cullin F-Box Protein Ligases; Saccharomyces cerevisiae; Saccharomyces cerevisiae Proteins; Seasons; Staining and Labeling; Stress, Physiological; T-Lymphocytes; Telemedicine; Ubiquitin; Ubiquitination; Valosin Containing Protein; Victoria; Volatile Organic Compounds; alpha-Synuclein</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kvon, Evgeny</t>
+          <t>Jin, Rongsheng</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Africa; Alleles; Animal Fins; Australia; Autism Spectrum Disorder; Autistic Disorder; Base Sequence; Binding Sites; Brain; Brain Neoplasms; CCCTC-Binding Factor; CRISPR-Cas Systems; Cell Culture Techniques; Cell Cycle Proteins; Chromatin; Chromosomal Proteins, Non-Histone; Chromosomes; Chromosomes, Human, Pair 8; Clinical Relevance; Cohesins; Congenital Abnormalities; Craniofacial Abnormalities; DNA; DNA Transposable Elements; DNA, Intergenic; Ectopic Gene Expression; Enhancer Elements, Genetic; Epigenome; Epigenomics; Evolution, Molecular; Extinction, Biological; Extremities; Fetal Heart; Fishes; Gain of Function Mutation; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Developmental; Gene Rearrangement; Genes, Reporter; Genetic Code; Genetic Variation; Genome; Genome Size; Genomics; Glioma; Heart Diseases; Hedgehog Proteins; Homeodomain Proteins; Intellectual Disability; Introns; Isocitrate Dehydrogenase; Karyotype; Limb Buds; Locomotion; Marsupialia; MicroRNAs; Mutation; Nucleotide Motifs; Organoids; Otx Transcription Factors; Phenotype; Phylogeny; Piwi-Interacting RNA; Polydactyly; Polymorphism, Single Nucleotide; Promoter Regions, Genetic; Protein Binding; RNA, Long Noncoding; Regulatory Sequences, Nucleic Acid; SELEX Aptamer Technique; Single-Cell Analysis; South America; Time Factors; Transcription Factors; Transcriptional Activation; Virulence; Zinc Fingers</t>
+          <t>Administration, Oral; Amino Acids; Bacterial Proteins; Bacterial Toxins; Biological Transport; Botulinum Toxins; Botulinum Toxins, Type A; Breast Neoplasms; CRISPR-Associated Protein 9; CRISPR-Cas Systems; Calcitonin Gene-Related Peptide; Cattle; Cecum; Cisplatin; Clostridioides difficile; Clostridium Infections; Clostridium botulinum; Clustered Regularly Interspaced Short Palindromic Repeats; Cryoelectron Microscopy; Dogs; Endothelial Cells; Enterotoxins; Epitopes; Gene Editing; Genetic Code; Genotype; Glucosyltransferases; Inflammation Mediators; Mammary Neoplasms, Animal; Membrane Glycoproteins; Molecular Conformation; Monomeric GTP-Binding Proteins; Multigene Family; Neoplasms; Neovascularization, Pathologic; Nerve Tissue Proteins; Neurogenic Inflammation; Neurons, Afferent; Neurotoxins; Peptide Hydrolases; Pericytes; Phenotype; Point Mutation; Protease Inhibitors; Protein Binding; Protein Domains; Proteins; Proteolysis; Receptors, Neurokinin-1; Recombination, Genetic; Saccharomyces cerevisiae; Signal Transduction; Single-Domain Antibodies; Structure-Activity Relationship; Substance P; Synaptic Vesicles; Tumor Microenvironment; Wnt Signaling Pathway; cdc42 GTP-Binding Protein; rho GTP-Binding Proteins; rhoA GTP-Binding Protein</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LaFerla, Frank</t>
+          <t>Jusiak, Barbara</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ATP-Binding Cassette Transporters; Aged; Aged, 80 and over; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Apolipoproteins E; Asian; Astrocytes; Biomarkers; Brain; CRISPR-Associated Proteins; CRISPR-Cas Systems; Case-Control Studies; Cathepsin D; Chromatin Immunoprecipitation Sequencing; Chromosomes, Human, X; Clustered Regularly Interspaced Short Palindromic Repeats; Cognition; Cuprizone; Data Management; Demyelinating Diseases; Disease Progression; Down Syndrome; Down-Regulation; Doxycycline; Endoribonucleases; Fibroblasts; Gastrointestinal Microbiome; Gene Editing; Gene Expression Profiling; Gene Expression Regulation; Gene Knock-In Techniques; Genetic Predisposition to Disease; Genetic Variation; Genome-Wide Association Study; Genotype; Glial Fibrillary Acidic Protein; HEK293 Cells; Hispanic or Latino; Induced Pluripotent Stem Cells; Laboratories; Leadership; Lipidomics; Longevity; Membrane Glycoproteins; Metabolome; Metabolomics; Microbiota; Microglia; Mobile Applications; Mutation; Myeloid Differentiation Factor 88; NF-kappa B; Neurodegenerative Diseases; Neuroglia; Neuroimaging; Neurons; Phagocytosis; Phenotype; Plaque, Amyloid; Polymorphism, Single Nucleotide; Proteomics; RNA Splicing; RNA-Seq; Receptors, Immunologic; Registries; Resilience, Psychological; Response Elements; Rodentia; Sex Characteristics; Signal Transduction; Single-Cell Gene Expression Analysis; Tauopathies; Tetracycline; Transcriptome; Translational Research, Biomedical; X Chromosome Inactivation; tau Proteins</t>
+          <t>Animals, Genetically Modified; Drosophila Proteins; Drosophila melanogaster; Gene Expression; Transcription Factors</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Lamb, Joleah</t>
+          <t>Kiser, Philip</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Acclimatization; Aquaculture; Behavioral Sciences; Biodiversity; Cities; Conservation of Natural Resources; Disease Outbreaks; Ecological and Environmental Phenomena; Ecosystem; Environmental Microbiology; Environmental Science; Germ Cells, Plant; Hot Temperature; Housing; Indonesia; Kelp; Macrocystis; Marine Biology; Microbiota; Motivation; Mutation; Oceans and Seas; One Health; Policy; Refugees; Remote Sensing Technology; Reproduction; Seaweed; Temperature; Water</t>
+          <t>Ambystoma; Amphibian Proteins; Arrestin; Arrestins; Biocatalysis; Bromocriptine; CRISPR-Cas Systems; Calcium; Camelids, New World; Carotenoids; Carrier Proteins; Catalysis; Catalytic Domain; Cattle; Cell-Penetrating Peptides; Ceramides; Cone Opsins; Crystallography, X-Ray; Cyclic AMP; Cyclic Nucleotide Phosphodiesterases, Type 6; Diabetic Retinopathy; Dioxygenases; Dogs; Drug Repositioning; Drug Therapy, Combination; Ear Auricle; Ependymoglial Cells; Evolution, Molecular; Eye Proteins; Fatty Acids, Unsaturated; Fungal Proteins; Gene Editing; Gene Library; HEK293 Cells; Hydrolysis; Iron; Isomerases; Isomerism; Leber Congenital Amaurosis; Lipids; Liposomes; Macular Degeneration; Models, Molecular; Mutation; NADP; Nanoparticles; Neuroglia; Nitric Oxide; Opsins; Oxygen; Oxygenases; Phenyl Ethers; Phosphorylation; Photoreceptor Cells, Vertebrate; Propanolamines; Protein Conformation; Protein Multimerization; Receptors, Adiponectin; Receptors, G-Protein-Coupled; Retina; Retinal Cone Photoreceptor Cells; Retinal Degeneration; Retinal Pigment Epithelium; Retinal Pigments; Retinal Rod Photoreceptor Cells; Retinaldehyde; Retinitis Pigmentosa; Retinoids; Rhodopsin; Ribonucleoproteins; Single-Domain Antibodies; Vision, Ocular; Vitamin A; Xenopus Proteins; Xenopus laevis; cis-trans-Isomerases</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Lander, Arthur</t>
+          <t>Lawson, Devon A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Aging; Algorithms; Animals, Genetically Modified; Body Patterning; Brain; CHO Cells; Cartilage; Cell Competition; Cell Cycle Proteins; Cell Differentiation; Cell Lineage; Cell Plasticity; Cell Proliferation; Chondrocytes; Chromatin; Chromosomal Proteins, Non-Histone; Cluster Analysis; Cohesins; Communication; Computational Biology; Congenital Abnormalities; Cricetulus; Data Analysis; Databases, Factual; De Lange Syndrome; Drosophila Proteins; Drosophila melanogaster; Drug Resistance, Neoplasm; Embryo, Mammalian; Embryonic Development; Entropy; Epithelial Cells; Face; Fracture Healing; Fusion Proteins, bcr-abl; Gastrulation; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Developmental; Gene Regulatory Networks; Green Fluorescent Proteins; Growth and Development; HEK293 Cells; Hedgehog Proteins; Heterozygote; Homeostasis; Imaging, Three-Dimensional; Immunity, Innate; Leukemia, Myelogenous, Chronic, BCR-ABL Positive; Machine Learning; Mass Behavior; Metronidazole; Morphogenesis; Mutation; Myelopoiesis; Neoplasms; Nitroreductases; Organoids; Osteoblasts; Osteogenesis; Periosteum; Phenotype; Pregnancy; Prodrugs; Promoter Regions, Genetic; Protein Engineering; Protein Kinase Inhibitors; Proteins; RNA; Recombinant Proteins; Retina; Saccharomyces cerevisiae; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Stem Cells; Systems Biology; TOR Serine-Threonine Kinases; Transcriptome; Tyrosine Kinase Inhibitors; Vibrio; Wings, Animal; X-Ray Microtomography; Zebrafish</t>
+          <t>B7-H1 Antigen; Blood-Brain Barrier; Brain; Brain Neoplasms; Breast; Breast Neoplasms; CD8-Positive T-Lymphocytes; Cell Line, Tumor; Cholesterol; Circadian Clocks; Circadian Rhythm; Colorectal Neoplasms; Cytokines; Endothelial Cells; Epithelial Cells; Gene Expression Profiling; Genomics; Hair; Hair Follicle; Hyaluronan Receptors; Immune Checkpoint Inhibitors; Immune Tolerance; Immunity; Immunosuppression Therapy; Melanocytes; Microglia; Myeloid-Derived Suppressor Cells; Nevus; Organic Chemicals; Osteopontin; Receptors, Granulocyte-Macrophage Colony-Stimulating Factor; Signal Transduction; Single-Cell Analysis; Stem Cells; Treatment Outcome; Tumor Microenvironment</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lane, Thomas</t>
+          <t>Marangoni, Francesco</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Activin Receptors; Adiposity; Aged; Aging; Allergy and Immunology; Alzheimer Disease; Amino Acid Sequence; Amino Acids; Amyloid beta-Peptides; Aneuploidy; Angiotensin-Converting Enzyme 2; Animals, Genetically Modified; Anosmia; Apolipoprotein E4; Astrocytes; Axons; B-Lymphocytes; Bacterial Infections; Bone Marrow Transplantation; Brain; CD4 Antigens; CD4-Positive T-Lymphocytes; COVID-19; Catalytic Domain; Cells, Cultured; Central Nervous System; Cerebral Cortex; Chemokine CXCL1; Cognition; Cognitive Dysfunction; Coronavirus; Coronavirus 3C Proteases; Coronavirus Infections; Crystallography, X-Ray; Cystatins; Cysteine; Cytokine Release Syndrome; Dementia; Demyelinating Diseases; Disease Progression; Disulfides; Down Syndrome; Dysgeusia; Encephalitis; Encephalitis, Viral; Encephalomyelitis, Autoimmune, Experimental; Forkhead Transcription Factors; Gene Expression; Gene Expression Profiling; Hashimoto's encephalitis; Headache; Human Embryonic Stem Cells; Immune System; Immunity; Immunity, Innate; Induced Pluripotent Stem Cells; Infant; Inflammation; Inflammation Mediators; Integrases; Ischemia; Lung; Lymphocyte Activation; Lysosomal Membrane Proteins; Macrophages; Matrix Metalloproteinase 9; Memory Consolidation; Meningitis; Mental Fatigue; Microglia; Mitochondrial Diseases; Models, Molecular; Monocytes; Monomeric GTP-Binding Proteins; Multiple Sclerosis; Murine hepatitis virus; Muscle, Skeletal; Mutation; Myelin Sheath; Neural Stem Cells; Neurodegenerative Diseases; Neuroglia; Neuroinflammatory Diseases; Neurons; Neutrophils; Oxidation-Reduction; Pandemics; Parkinson Disease; Plaque, Amyloid; Protein Multimerization; RNA, Messenger; RNA, Viral; Receptor Protein-Tyrosine Kinases; Remyelination; Risk Factors; Rodentia; SARS-CoV-2; Secretome; Sequence Analysis, RNA; Serine Endopeptidases; Signal Transduction; Single Molecule Imaging; Spinal Cord; Stem Cells; Stroke; Sweden; Synaptic Transmission; T-Lymphocytes; T-Lymphocytes, Regulatory; Tetracyclines; Virus Diseases; Virus Replication; White Matter</t>
+          <t>B7-H1 Antigen; CD8-Positive T-Lymphocytes; Cell Line, Tumor; Circadian Clocks; Circadian Rhythm; Colorectal Neoplasms; Cyclodextrins; Cytokines; Immune Checkpoint Inhibitors; Immune Tolerance; Immunosuppression Therapy; Immunotherapy; Inducible T-Cell Co-Stimulator Protein; Interleukin-2; Intravital Microscopy; Lymphocyte Activation; Melanoma; Melanoma, Experimental; Metal-Organic Frameworks; Metals; Myeloid-Derived Suppressor Cells; Neoplasms; Programmed Cell Death 1 Receptor; Proteins; Signal Transduction; Single-Cell Analysis; Solubility; T-Lymphocytes; T-Lymphocytes, Regulatory; Tumor Microenvironment</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Lara-Gonzalez, Pablo</t>
+          <t>Othy, Shivashankar</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Aging; Anaphase-Promoting Complex-Cyclosome; Antineoplastic Agents; CDC2 Protein Kinase; Caenorhabditis elegans; Caenorhabditis elegans Proteins; Cdc20 Proteins; Cell Cycle; Cell Cycle Checkpoints; Cell Cycle Proteins; Cell Differentiation; Cell Proliferation; Centers for Disease Control and Prevention, U.S.; Chromosome Segregation; Clustered Regularly Interspaced Short Palindromic Repeats; Cues; Cyclin B; Cyclin B1; Cyclin B2; Cyclins; Embryo, Nonmammalian; Embryonic Development; Ependymoglial Cells; Genomics; Germ Cells; Kinetochores; M Phase Cell Cycle Checkpoints; Microscopy; Microtubule-Associated Proteins; Mitosis; Neocortex; Neoplasms; Phosphorylation; Protein Serine-Threonine Kinases; Repressor Proteins; Spindle Apparatus; Tetratricopeptide Repeat; nan</t>
+          <t>Adenosine Diphosphate; Adjuvants, Immunologic; Aged; Aged, 80 and over; Alzheimer Disease; Analgesics; Anti-Inflammatory Agents; Antibodies, Neutralizing; Antibodies, Viral; CD8-Positive T-Lymphocytes; Calcium; Calcium Signaling; Cell Line, Tumor; Cognitive Dysfunction; Coriandrum; Corticotropin-Releasing Hormone; Down-Regulation; Ethnicity; Fibrosis; Galectin 3; Hemagglutinin Glycoproteins, Influenza Virus; Homeostasis; Immune Checkpoint Inhibitors; Immunotherapy; Incidence; Induced Pluripotent Stem Cells; Inducible T-Cell Co-Stimulator Protein; Influenza A Virus, H5N1 Subtype; Influenza Vaccines; Interleukin-2; Intravital Microscopy; Lipid A; Longitudinal Studies; Lymphocyte Activation; Lymphocytes; Macrophages; Melanoma; Melanoma, Experimental; Membrane Glycoproteins; Mice, Inbred BALB C; Microglia; Molecular Docking Simulation; Muscle, Skeletal; Neoplasms; Neural Stem Cells; Neurons; Oligodeoxyribonucleotides; Orthomyxoviridae Infections; Patient Reported Outcome Measures; Plant Extracts; Plants, Medicinal; Polysorbates; Potassium Channel Blockers; Programmed Cell Death 1 Receptor; Prospective Studies; Receptors, Immunologic; Receptors, Purinergic; Risk Factors; Saponins; Self Report; Signal Transduction; Squalene; Synapses; T-Lymphocytes; T-Lymphocytes, Regulatory; Tannins; Transcriptome</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Lee, Grace</t>
+          <t>Pathak, Medha</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Absorptiometry, Photon; Adenosine; Adipocytes; Aged; Alternative Splicing; Anti-Bacterial Agents; Antigens, CD; Base Sequence; Bile Acids and Salts; Biological Evolution; Biomarkers; Bone Density; Bone Diseases, Metabolic; Brain; Breast Neoplasms; COVID-19; COVID-19 Drug Treatment; Cadherins; Caenorhabditis elegans; Caenorhabditis elegans Proteins; Cell Death; Cell Line, Tumor; Cell Movement; Cell Proliferation; Chromatin; Chromosomes; Colonic Neoplasms; Cricetinae; DNA; DNA Transposable Elements; DNA-Binding Proteins; Diet; Disease Progression; Drug-Related Side Effects and Adverse Reactions; Dysbiosis; Early Detection of Cancer; Eating; Ecological and Environmental Phenomena; Epigenesis, Genetic; Epigenome; Epigenomics; Epithelial-Mesenchymal Transition; Eukaryotic Cells; Evolution, Molecular; Eye Neoplasms; Fabry Disease; Fatty Acid-Binding Proteins; Fatty Liver; Fellowships and Scholarships; Femur Neck; Fertility; Fructose; Gastrointestinal Microbiome; Gene Expression Profiling; Genetics; Genetics, Population; Genome; Genome, Human; Genomic Instability; Genomics; HEK293 Cells; Health; Heterochromatin; Huntingtin Protein; Huntington Disease; Lipogenesis; Lipopolysaccharides; Liver; Longevity; Lung; Mechanistic Target of Rapamycin Complex 1; Methyltransferases; Mevalonic Acid; Mice, Nude; Multiomics; Multiprotein Complexes; Necroptosis; Neoplasm Metastasis; Neoplasms; Non-alcoholic Fatty Liver Disease; Nuclear Proteins; Nutrients; Ophthalmologic Surgical Procedures; Orbital Implants; Osteoporosis; Oxidative Stress; Parasites; Pharmaceutical Preparations; Phosphoglycerate Dehydrogenase; Phosphorylation; Proteasome Endopeptidase Complex; Protein Binding; Protein Stability; Proteolysis; RNA; RNA Methylation; RNA Splicing; RNA, Messenger; Receptor-Interacting Protein Serine-Threonine Kinases; Repressor Proteins; Retroelements; Ribosomal Protein S6 Kinases, 70-kDa; SARS-CoV-2; Sequence Homology; Serine; Signal Transduction; Social Responsibility; Species Specificity; TOR Serine-Threonine Kinases; Tetraodontiformes; Transcriptome; Ubiquitin; Ubiquitin-Protein Ligases; Ubiquitination; Urodela; Virus Replication; nan</t>
+          <t>Brain; Calcium; Cell Membrane; Cell Movement; Cholesterol; Cytokinesis; Ion Channels; Keratinocytes; Mechanotransduction, Cellular; Neural Stem Cells; Pseudopodia</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lodoen, Melissa</t>
+          <t>Skowronska-Krawczyk, Dorota</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AIDS Dementia Complex; Acquired Immunodeficiency Syndrome; Adaptive Immunity; Adaptor Proteins, Signal Transducing; Allergy and Immunology; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Anti-Infective Agents; Antigen Presentation; Astrocytes; Blood Coagulation; Blood-Brain Barrier; Brain; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Capparis; Caspase 1; Caspase 8; Caspases; Cell Death; Cell Membrane; Cell Proliferation; Central Nervous System; Central Nervous System Infections; Cerebrovascular Circulation; Chemokine CCL2; Chemokines; Clustered Regularly Interspaced Short Palindromic Repeats; Coculture Techniques; Cognition; Coinfection; Communicable Disease Control; Cytokines; Dendritic Cells; Encephalitis; Endothelial Cells; Fibrin; Gasdermins; Gene Regulatory Networks; HIV Infections; Heart Transplantation; Hemodynamics; Hippo Signaling Pathway; Host-Parasite Interactions; Host-Pathogen Interactions; Immunity; Immunity, Innate; Induced Pluripotent Stem Cells; Infections; Inflammasomes; Inflammation; Inflammation Mediators; Intercellular Adhesion Molecule-1; Interleukin-1beta; Ion Channels; Lipoproteins; Liver; Macrophages; Mechanotransduction, Cellular; Memory T Cells; Metabolic Diseases; Microglia; Microscopy; Microvessels; Monocytes; Myeloid Cells; NF-kappa B; NLR Family, Pyrin Domain-Containing 3 Protein; Necroptosis; Neoplasm Recurrence, Local; Neurodegenerative Diseases; Neuroimaging; Neuroinflammatory Diseases; Neuroprotection; Neuroprotective Agents; Parasites; Peptides; Perfusion; Persistent Infection; Phagocytosis; Phenotype; Plaque, Amyloid; Platelet Aggregation; Protozoan Proteins; Receptor-Interacting Protein Serine-Threonine Kinases; Receptors, Scavenger; Signal Transduction; Syk Kinase; T-Lymphocytes; T-Lymphocytes, Regulatory; THP-1 Cells; Thromboinflammation; Toxoplasma; Toxoplasmosis; Toxoplasmosis, Cerebral; Transcription Factor RelA; Virulence; Virulence Factors; nan; tdTomato</t>
+          <t>Aged; Aging; Axonal Transport; Cell Differentiation; Cell Membrane; Cellular Senescence; Ceramides; Chromatin; Cyclic Nucleotide Phosphodiesterases, Type 6; Cytoskeletal Proteins; DNA Damage; DNA-Binding Proteins; Docosahexaenoic Acids; Endonucleases; Eye Proteins; Fatty Acids, Unsaturated; Glaucoma; Glaucoma, Open-Angle; Glycoproteins; Glycosylation; Integrases; Intraocular Pressure; Leber Congenital Amaurosis; Lipid Metabolism; Lipids; Macular Degeneration; Membrane Proteins; Microscopy; Nonlinear Optical Microscopy; Organoids; Pluripotent Stem Cells; Progeria; Proteins; Proteome; Proteomics; Receptors, Adiponectin; Retina; Retinal Degeneration; Retinal Ganglion Cells; Retinal Pigment Epithelium; Retinitis Pigmentosa; Spectrum Analysis, Raman; Trabecular Meshwork; cis-trans-Isomerases</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Long, Anthony</t>
+          <t>Tombola, Francesco</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adaptation, Biological; Aging; Alleles; Antibody Formation; Biological Evolution; Borrelia burgdorferi; Breeding; CRISPR-Cas Systems; Chromatin; Chromatin Immunoprecipitation Sequencing; Chromosome Mapping; Computers; Confidence Intervals; CpG Islands; DNA; DNA Methylation; Data Analysis; Deer; Diptera; Drosophila melanogaster; Ecological and Environmental Phenomena; Gene Frequency; Gene Knockout Techniques; Genes, MHC Class II; Genetic Variation; Genetics; Genetics, Population; Genome, Fungal; Genome-Wide Association Study; Genomics; Genotype; Haplotypes; High-Throughput Nucleotide Sequencing; Immunization; Immunoglobulin G; Incubators; Insecticide Resistance; Insecticides; Kansas; Lyme Disease; Macrophages; Malathion; Models, Genetic; Multifactorial Inheritance; Nitric Oxide; OspA protein; Parents; Peromyscus; Persistent Infection; Phagocytes; Phenotype; Photoperiod; Polymorphism, Single Nucleotide; Quantitative Trait Loci; Reactive Nitrogen Species; Recombination, Genetic; Reproduction; Reproduction, Asexual; Reverse Genetics; Saccharomyces cerevisiae; Seasons; Selection, Genetic; Translational Research, Biomedical</t>
+          <t>Biosensing Techniques; Electronic Nose; Ion Channels; Ligands; Lipid Bilayers; Magnoliopsida; Nanowires; Protons; Receptors, Odorant; Tracheophyta</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Luo, Ray</t>
+          <t>Villalta, Sergio Armando</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Adaptor Proteins, Signal Transducing; Adenosine Triphosphate; Allosteric Regulation; Allosteric Site; Amines; Amino Acids; Antineoplastic Agents; Artificial Cells; Binding Sites; Biocatalysis; Biomarkers; Bioreactors; Budgets; Carcinoma, Hepatocellular; Cats; Cell Line, Tumor; Computational Biology; Dendritic Cells; Dimerization; Drug Delivery Systems; Early Detection of Cancer; Entropy; Escherichia coli; Gas Chromatography-Mass Spectrometry; Glucose 1-Dehydrogenase; Green Fluorescent Proteins; Head and Neck Neoplasms; Hippo Signaling Pathway; Hydrogels; Immunity, Cellular; Intrinsically Disordered Proteins; Liver Cirrhosis; Liver Neoplasms; Loss of Function Mutation; Lung Neoplasms; Models, Molecular; Molecular Dynamics Simulation; Mutation; Mutation, Missense; NAD; NADP; Neoplasms; Neurofibromin 2; Nicotinamide Mononucleotide; Normal Distribution; Oxidation-Reduction; Oxidoreductases; Peptides; Phase Separation; Polymers; Protein Binding; Protein Biosynthesis; Protein Conformation; Protein Serine-Threonine Kinases; Protein Tyrosine Phosphatase, Non-Receptor Type 11; Proteins; RNA, Messenger; Signal Transduction; Solutions; Solvents; Static Electricity; T-Lymphocytes; Viral Vaccines; Volatile Organic Compounds; mRNA Vaccines; nan</t>
+          <t>Amidohydrolases; Brain; Brain Neoplasms; Breast Neoplasms; CD8-Positive T-Lymphocytes; Cross-Sectional Studies; DNA-Binding Proteins; Disease Progression; Endogenous Retroviruses; Enzyme Inhibitors; Epigenesis, Genetic; Fibrosis; Galectin 3; Gene Expression; Hand Strength; Heterochromatin; Heterografts; Hyperalgesia; Immunologic Memory; Immunophenotyping; Killer Cells, Natural; Leukocytes, Mononuclear; Lipids; Macrophages; Mice, Inbred mdx; Microglia; Monocytes; Muscle, Skeletal; Muscular Dystrophy, Duchenne; Myositis; Myositis, Inclusion Body; Outcome Assessment, Health Care; PPAR alpha; Pain; RNA, Nuclear; Severity of Illness Index; Transcriptome; Treatment Outcome; Vacuoles</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lur, Gyorgy</t>
+          <t>Wagar, Lisa</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Action Potentials; Adenosine Triphosphate; Adolescent; Adverse Childhood Experiences; Aging; Amblyopia; Animal Care Committees; Anticonvulsants; Basolateral Nuclear Complex; Brain; Calcium; Calcium Channels; Central Nervous System; Cholinergic Neurons; Cognition; Computer Simulation; Decision Making; Electroencephalography; Electronic Nicotine Delivery Systems; Electrophysiology; Epilepsy; Epilepsy, Temporal Lobe; Genetics; Habenula; Hippocampus; Magnetic Fields; Memory; Memory Consolidation; Memory, Short-Term; Mental Disorders; Movement; Nanoparticles; Neural Pathways; Neurons; Neurosciences; Nicotine; Nicotinic Agonists; Optogenetics; Parietal Lobe; Patch-Clamp Techniques; Postsynaptic Potential Summation; Primary Visual Cortex; Psychomotor Performance; Pyramidal Cells; Quality of Life; Receptors, Purinergic P2; Rejuvenation; Reward; Seizures; Software; Stress, Psychological; Synapses; Synaptic Transmission; Visual Acuity; Wakefulness</t>
+          <t>Adaptive Immunity; Adjuvants, Immunologic; Adolescent; Antibodies, Neutralizing; Antibodies, Viral; Antibody Formation; Antigens; Antigens, Viral; B-Lymphocytes; Bangladesh; CD4-Positive T-Lymphocytes; CD40 Ligand; COVID-19; Cell Culture Techniques; Cells, Cultured; Child; Child, Preschool; Environmental Exposure; Hemagglutinin Glycoproteins, Influenza Virus; Immunity; Immunoinformatics; Immunologic Memory; Infant; Influenza A Virus, H1N1 Subtype; Influenza A virus; Influenza Vaccines; Influenza, Human; Lymphoma, Follicular; Memory B Cells; Nanoparticles; Organ Specificity; Organoids; Palatine Tonsil; Receptors, Antigen, T-Cell; SARS-CoV-2; Sex Characteristics; Sex Factors; T Follicular Helper Cells; T-Lymphocytes; T-Lymphocytes, Helper-Inducer; Th1 Cells; Toll-Like Receptor 7; Tumor Microenvironment; Vaccination; Vaccines; Vaccines, Subunit; Young Adult</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Lutterschmidt, Deborah</t>
+          <t>Yu, Alvin</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Behavior, Animal; Body Temperature Regulation; Brain; Ecological and Environmental Phenomena; Hibernation; Hormones; Life History Traits; Neurobiology; Periodicity; Physiology, Comparative; Seasons; Stress, Physiological; Temperature; nan</t>
+          <t>3' Untranslated Regions; Acoustics; Acrylic Resins; Aged; Alanine; Antiviral Agents; Asian People; Ataxia; Blepharoplasty; Bone Density; Bone and Bones; Brain; British Columbia; Butadienes; COVID-19; COVID-19 Vaccines; California; Canada; Cell Line; Cell Nucleus; Cohort Studies; DNA Breaks, Double-Stranded; DNA Repair; Diterpenes; Dose-Response Relationship, Radiation; Electrons; Exosome Multienzyme Ribonuclease Complex; Eyelids; Feasibility Studies; HEK293 Cells; Hand Disinfection; HeLa Cells; Health Knowledge, Attitudes, Practice; Hepatitis C; Hippocampus; Incidence; Infection Control; Interrupted Time Series Analysis; Kv1.1 Potassium Channel; Ligands; Long-Term Potentiation; Lung; Masks; Molecular Conformation; Molecular Dynamics Simulation; Myokymia; Neoplasms; Neurogenesis; Osteoporosis; Pandemics; Parents; Particle Accelerators; Patient Acceptance of Health Care; Phantoms, Imaging; Phosphorylation; Physical Distancing; Pilot Projects; Plant Extracts; Poly A; Polyadenylation; Polyesters; Polymorphism, Single Nucleotide; Polystyrenes; Printing, Three-Dimensional; Protein Conformation; RNA Precursors; RNA Processing, Post-Transcriptional; RNA Splice Sites; RNA Stability; RNA, Messenger; RNA, Nuclear; Radiometry; Radiotherapy Dosage; Radiotherapy Planning, Computer-Assisted; Reproducibility of Results; Retrospective Studies; Ribonucleoprotein, U1 Small Nuclear; SARS-CoV-2; Substance Abuse, Intravenous; Suture Techniques; Telemedicine; Tomography, X-Ray Computed; Transcriptome; Translocation, Genetic; Treatment Outcome; Ubiquitin; Ubiquitin-Protein Ligases; Vaccination; Vaccination Hesitancy; Vaccines; Wastewater; Wastewater-Based Epidemiological Monitoring; Water; X-Ray Microtomography; Young Adult</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MacGregor, Grant</t>
+          <t>Monuki, Edwin</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ATP-Binding Cassette Transporters; Adenosine Triphosphate; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Apolipoproteins E; Astrocytes; Brain; Brain-Derived Neurotrophic Factor; Coronavirus Infections; Cuprizone; Cystatins; DNA, Mitochondrial; Demyelinating Diseases; Diabetes Mellitus; Diabetic Cardiomyopathies; Disease Progression; Energy Metabolism; Gastrointestinal Microbiome; Gene Expression Profiling; Gene Knock-In Techniques; Genetic Variation; Genotype; Heart Transplantation; Insulin; Integrases; Membrane Glycoproteins; Metabolomics; Microbiota; Microglia; Mitochondria; Mitochondria, Heart; Murine hepatitis virus; Mutation; Mutation, Missense; Myocardium; Neuroglia; Neuroinflammatory Diseases; Neurons; Oxidative Phosphorylation; Phagocytosis; Phosphatidylinositol 3-Kinases; Plaque, Amyloid; Proto-Oncogene Proteins c-akt; RNA Splicing; Reactive Oxygen Species; Receptor, trkB; Receptors, Immunologic; Resilience, Psychological; Sex Characteristics; Signal Transduction; Single-Cell Analysis; T-Lymphocytes, Regulatory; Tauopathies; Transcriptome; tau Proteins</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Mahler, Stephen</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Adolescent; Adolescent Development; Adverse Childhood Experiences; Aerosols; Amphetamine; Analgesics, Opioid; Anhedonia; Arachidonic Acids; Basal Forebrain; Basolateral Nuclear Complex; Brain; Cannabidiol; Cannabis; Chromatography, High Pressure Liquid; Clozapine; Cognition; Conditioning, Operant; Corticotropin-Releasing Hormone; Designer Drugs; Dopamine; Dopaminergic Neurons; Dose-Response Relationship, Drug; Dronabinol; Endocannabinoids; Genetics; Growth and Development; Learning; Mass Spectrometry; Microglia; Microsomes; Morphine; Motivation; Neural Pathways; Neurobiology; Neuronal Plasticity; Nucleus Accumbens; Ovarian Follicle; Ovarian Reserve; Polyunsaturated Alkamides; Prefrontal Cortex; Rats, Long-Evans; Rats, Sprague-Dawley; Reward; Substance-Related Disorders; Tandem Mass Spectrometry; Vaping; Ventral Tegmental Area; gamma-Aminobutyric Acid</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Martinez, Christopher</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Aquatic Organisms; Biological Evolution; Biomechanical Phenomena; Carbon; Characidae; Coral Reefs; Ecological and Environmental Phenomena; Ecosystem; Evolution, Molecular; Extinction, Biological; Feeding Behavior; Fishes; Genetic Speciation; Information Services; Jaw; Mandible; Motion; Movement; Natural History; Perciformes; Phylogeny; Predatory Behavior; Schools; Social Behavior; Social Factors; Somatotypes; Swimming; Water; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Martiny, Adam</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Anti-Bacterial Agents; Bacteria; Bayes Theorem; Biodiversity; Biomass; California; Carbon; Carbon Cycle; Climate Change; Drug Resistance, Bacterial; Drug Resistance, Multiple, Bacterial; Earth, Planet; Ecological and Environmental Phenomena; Ecosystem; Ecotype; El Nino-Southern Oscillation; Escherichia coli; Escherichia coli Infections; Food Chain; Genetic Variation; Genetics; Genomics; Indian Ocean; Life History Traits; Metagenome; Metagenomics; Microbial Sensitivity Tests; Microbiology; Microbiota; Nitrates; Nitrogen; Nitrogen Fixation; Nutrients; Oceanography; Oceans and Seas; Phosphates; Phylogeny; Phylogeography; Phytoplankton; Plankton; Prochlorococcus; Proteome; Seasons; Seawater; Soil; Soil Microbiology; Synechococcus; Temperature; Uncertainty</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Martiny, Jennifer</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Actinomycetales; Ambulatory Care Facilities; American Indian or Alaska Native; Anti-Bacterial Agents; Bacteria; Bays; Bifidobacterium; Biodiversity; Biological Evolution; Biotechnology; Carbohydrates; Carbon; Carbon Sequestration; Cardiovascular Diseases; Climate Change; Computational Biology; Curriculum; Cyanobacteria; DNA Damage; DNA Methylation; DNA Repair; Desert Climate; Desiccation; Diabetes Mellitus; Diet; Dietary Fiber; Drought Resistance; Droughts; Earth, Planet; Ecological and Environmental Phenomena; Ecology; Ecosystem; Electrons; Feces; Fermentation; Gastrointestinal Microbiome; Gene Transfer, Horizontal; Genetic Engineering; Genetic Variation; Genomics; Greenhouse Gases; Human Body; Internship and Residency; Interspersed Repetitive Sequences; Leadership; Life History Traits; Masks; Metadata; Metagenome; Metagenomics; Microbiology; Microbiota; Mutation; Mycobiome; Neoplasms; New Mexico; Nitrogen; Nitrogen Fixation; Noncommunicable Diseases; Ohio; Oregon; Pacific Island People; Phylogeny; Plant Leaves; Plasmids; Prebiotics; Probiotics; RNA, Ribosomal, 16S; Reproducibility of Results; Resilience, Psychological; Schools; Soil; Soil Microbiology; Stress, Physiological; Time Factors; Uncertainty; Water Purification; Wildfires; Workflow</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>McHenry, Matthew</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Animal Communication; Animals, Wild; Behavior, Animal; Biomechanical Phenomena; Communication; Cues; Cypriniformes; Ecological and Environmental Phenomena; Environment; Escape Reaction; Fishes; Fresh Water; Gait; Genomics; Hydrodynamics; Larva; Lateral Line System; Light; Locomotion; Movement; Oligochaeta; Organizations; Perciformes; Phototaxis; Predatory Behavior; Robotics; Schools; Scyphozoa; Sense Organs; Skeleton; Smegmamorpha; Social Behavior; Starfish; Swimming; Technology; Water Movements; Zebrafish; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>McNaughton, Bruce</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Action Potentials; Adverse Childhood Experiences; Auditory Cortex; Autistic Disorder; Behavior Therapy; Brain; Brain Diseases; Brain Stem; Cognition; Cognitive Reserve; Computer Simulation; Control Groups; Cues; Deep Learning; Default Mode Network; ET protocol; Electroencephalography; Electronic Mail; Electrophysiological Phenomena; Electrophysiology; Feasibility Studies; GABAergic Neurons; Grid Cells; Gyrus Cinguli; Hallucinogens; Hippocampal Sclerosis; Hippocampus; History, 20th Century; History, 21st Century; Imaging, Three-Dimensional; Ketanserin; Learning; Maze Learning; Memory; Memory Consolidation; Memory Disorders; Memory, Episodic; Memory, Short-Term; Models, Neurological; Neocortex; Nesting Behavior; Neural Networks, Computer; Neuroanatomy; Neuronal Plasticity; Neurons; Neurosciences; Optogenetics; Pilot Projects; Place Cells; Psilocybin; Reward; Schizophrenia; Serotonin 5-HT2 Receptor Antagonists; Silicon; Sleep; Sleep Deprivation; Sleep, REM; Sleep, Slow-Wave; Software; Space Perception; Spatial Navigation; Stroke; Synapses; Systems Theory; Wakefulness</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>McNulty, Reginald</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Allergy and Immunology; Amino Acids; Anti-Inflammatory Agents; Apoptosis; Bacteria; Bacterial Infections; Bacteriophage P22; Binding Sites; COVID-19; COVID-19 Drug Treatment; CRISPR-Cas Systems; Capsid; Carcinoma, Hepatocellular; Caspase 1; Cell Culture Techniques; Cell Survival; Clostridium acetobutylicum; Cryoelectron Microscopy; Cryopyrin-Associated Periodic Syndromes; Cytokines; DNA; DNA Glycosylases; DNA, Mitochondrial; DNA, Viral; Drug Discovery; Endodeoxyribonucleases; Epithelium; Fluorocarbons; Galium; Gasdermins; Gene Editing; Heat-Shock Response; Host Microbial Interactions; Imaging, Three-Dimensional; Immune System; Immunity, Innate; Inflammasomes; Inflammation; Inflammation Mediators; Interleukin-1; Interleukin-18; Interleukin-1beta; Ligands; Liver Neoplasms; Macromolecular Substances; Macrophages; Mass Spectrometry; Membrane Fluidity; Microscopy, Electron, Transmission; Mitochondria; Mitochondrial Diseases; Molecular Structure; Mutagenesis; Mutation; NLR Family, Pyrin Domain-Containing 3 Protein; Neoplasms; Non-alcoholic Fatty Liver Disease; Nucleic Acids; Oxidative Stress; Oxides; Pathogen-Associated Molecular Pattern Molecules; Protein Binding; Protein Processing, Post-Translational; Protein Subunits; Proteins; Pyrin; Pyrin Domain; RNA; Signal Transduction; Signal-To-Noise Ratio; Virus Assembly; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Metherate, Raju</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Acetylcholine; Acoustic Stimulation; Alzheimer Disease; Auditory Cortex; Auditory Perception; Auditory Perceptual Disorders; Cognition; Cognitive Dysfunction; Entorhinal Cortex; Hearing; Hippocampus; Interneurons; Neurons; Nicotine; Nicotinic Agonists; Nootropic Agents; Pharmaceutical Preparations; Physiology; Receptors, Nicotinic; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Mooney, Kailen</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Adaptation, Physiological; Alleles; Ants; Artemisia; Arthropods; Biodiversity; Biological Evolution; Biological Phenomena; Biomass; Biota; Birds; Brassicaceae; Climate; Climate Change; Colorado; Conservation of Natural Resources; Curriculum; Drought Resistance; Droughts; Ecology; Ecosystem; Ecotype; Ficus; Food Chain; Genetic Variation; Herbivory; Home Environment; Host-Parasite Interactions; Insecta; Larva; Lepidoptera; Moths; Natural Resources; Phenotype; Plant Development; Plant Leaves; Plants; Predatory Behavior; Quantitative Trait Loci; Schools; Selection, Genetic; Snow; Songbirds; Trees; Wasps; Water</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Morehouse, Benjamin</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2',5'-oligoadenylate; Allergy and Immunology; Amino Acids; Anti-Infective Agents; Antiviral Agents; Archaea; Autoimmune Diseases; Bacteria; Bacteriophages; Biochemistry; Biological Evolution; CRISPR-Cas Systems; Cell Death; Chromatography, High Pressure Liquid; Cryoelectron Microscopy; Crystallography, X-Ray; Cyclic AMP; Cyclic GMP; Cyclization; Cytosol; Defense Mechanisms; Delivery of Health Care; Drug Resistance, Microbial; Eukaryota; Evolution, Molecular; Genome, Human; Host Microbial Interactions; Immune System; Immunity, Innate; Incidence; Interferons; Ion Channels; Lipopolysaccharides; Membrane Proteins; Microbiology; Microbiota; Molecular Structure; Mutagenesis; NAD; Neoplasms; Nucleic Acids; Nucleotides; Nucleotides, Cyclic; Nucleotidyltransferases; Oligonucleotides; Pandemics; Phage Therapy; Phylogeny; Planets; Postdoctoral Training; Prokaryotic Cells; Proteins; Pyrimidines; Ribonucleotides; Second Messenger Systems; Signal Transduction; Toll-Like Receptor 4; Uridine Monophosphate; Virus Activation; Virus Diseases; Virus Replication; cyclic 3',5'-uridine monophosphate; cyclic guanosine monophosphate-adenosine monophosphate</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Morrissette, Naomi</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Amino Acid Substitution; Amino Acids; Antiparasitic Agents; Apicoplasts; Binding Sites; Biolistics; Cell Shape; Cells, Cultured; Chemistry, Pharmaceutical; Chlamydomonas; Clemastine; Colchicine; Communicable Diseases; Cryptosporidiosis; Cryptosporidium; Cryptosporidium parvum; Cytokinesis; Cytoskeleton; Drug Resistance; Embryophyta; Eukaryota; Fibroblasts; Genes, Essential; Germ Cells; Haploidy; Helminths; Herbicides; Histamine Antagonists; Household Work; Ligands; Macronucleus; Malaria; Meiosis; Micronucleus, Germline; Microtubules; Mitosis; Morbidity; Mutation; Mutation, Missense; Neoplasms; Paclitaxel; Parasites; Paromomycin; Pharmaceutical Preparations; Plasmids; Protozoan Proteins; Recombination, Genetic; Solubility; Tetrahymena; Toxoplasma; Transfection; Treatment Outcome; Tropism; Tubulin; Vertebrates; nan; oryzalin; pendimethalin; pironetin; pronamide</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Mortazavi, Ali</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>5-Methylcytosine; 6-methyladenine; ATP-Binding Cassette Transporters; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Antineoplastic Combined Chemotherapy Protocols; Astrocytes; Brain; Carcinoma, Transitional Cell; Cell Differentiation; Cerebellum; Chromatin; DNA Methylation; Gene Expression Profiling; Gene Regulatory Networks; Genetic Variation; Genomics; Hair; Hair Follicle; High-Throughput Nucleotide Sequencing; Hippocampus; Homeodomain Proteins; Hyaluronan Receptors; In Situ Hybridization, Fluorescence; Machine Learning; Melanocytes; Microglia; Molecular Sequence Annotation; Muscle Fibers, Skeletal; Muscular Dystrophy, Facioscapulohumeral; Myoblasts; Neoplasm Metastasis; Neuroglia; Neurons; Nevus; Nivolumab; Nucleotides; Osteopontin; Phagocytosis; Plaque, Amyloid; Pseudouridine; RNA Editing; RNA, Long Noncoding; RNA-Seq; Receptor, Anaphylatoxin C5a; Resilience, Psychological; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Stem Cells; Transcriptome; Urinary Bladder Neoplasms; Urologic Neoplasms</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Nicholas, Dequina</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Adaptive Immunity; Adipose Tissue; Adiposity; Aged; Aging; Allergy and Immunology; Anabolic Androgenic Steroids; Androgens; Anti-Inflammatory Agents; Antibodies; Antibodies, Neutralizing; Antibody Formation; Antigen Presentation; Antigens, CD1; Autoantibodies; Autoantigens; Autoimmune Diseases; B-Lymphocyte Subsets; Bacteriophages; Biocompatible Materials; Blood Glucose; Brain; CD8-Positive T-Lymphocytes; COVID-19; Cardiac Output; Cardiovascular Diseases; Carrier Proteins; Cell Differentiation; Cell Fractionation; Cell Line; Cell Line, Tumor; Cell Membrane; Cell Plasticity; Cell Proliferation; Cell Survival; Cellular Senescence; Coculture Techniques; Computer Simulation; Cross-Sectional Studies; Culture Media, Conditioned; Cytokines; Diabetes Mellitus; Diabetes Mellitus, Type 2; Diet; Diet, High-Fat; Disease Progression; Drug Evaluation, Preclinical; Endocrinology; Escherichia coli; Ethnic and Racial Minorities; Fertility; Flow Cytometry; Follicle Stimulating Hormone; Gastrointestinal Microbiome; Gene Expression Profiling; Gene Expression Regulation, Neoplastic; Glucose; Glucose Transporter Type 1; Glycated Hemoglobin; Glycolysis; Gonadal Steroid Hormones; Gonadotropins; Gonadotropins, Pituitary; H3B-8800; Homeostasis; Immunophenotyping; Immunotherapy; Industrial Development; Infertility; Inflammation; Inflammation Mediators; Influenza Vaccines; Insulin; Insulin Resistance; Interleukin-17; Laboratories; Lipid Metabolism; Lipids; Lipopolysaccharides; Losartan; Luteinizing Hormone; Lymphocytic Choriomeningitis; Lymphocytic choriomeningitis virus; Lymphoid Tissue; Memory B Cells; Metabolic Networks and Pathways; Metabolism; Methanol; Mexican Americans; Mice, Obese; Neoplastic Stem Cells; Obesity; Organoids; Ovarian Neoplasms; Palatine Tonsil; Pandemics; Persistent Infection; Phenotype; Pituitary Diseases; Pituitary Gland; Polycystic Ovary Syndrome; Preceptorship; Prevalence; Printing, Three-Dimensional; Professional Competence; Proprotein Convertase 9; Protein Array Analysis; Protein Transport; Proteins; Proto-Oncogene Proteins c-akt; Quality of Life; RNA, Long Noncoding; Reproduction; Research Personnel; Risk Factors; Sedentary Behavior; Sequence Analysis, RNA; Signal Transduction; Single-Cell Gene Expression Analysis; Solvents; T-Lymphocytes; Technology; Testosterone; Th17 Cells; Transcriptome; Up-Regulation; Virion; Weight Loss; Workflow; Zebrafish; lobeglitazone; nan; polyvinylidene fluoride</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Nie, Qing</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Adenosine; Adipocytes; Adjuvants, Immunologic; Algorithms; Alpha-Ketoglutarate-Dependent Dioxygenase FTO; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Antibodies, Neutralizing; Antibodies, Viral; Benchmarking; Big Data; Biocompatible Materials; Biological Phenomena; Biomechanical Phenomena; CD8-Positive T-Lymphocytes; COVID-19; Cardiomyopathy, Dilated; Cartilage; Cell Body; Cell Communication; Cell Cycle Checkpoints; Cell Differentiation; Cell Line, Tumor; Cell Lineage; Cellular Senescence; Chemokines; Choroid Plexus; Cicatrix; Clinical Relevance; Cluster Analysis; Computational Biology; Computer Simulation; Connectome; Cross-Linking Reagents; Cues; Cytokines; Data Analysis; Deep Learning; Developmental Biology; Down-Regulation; Drug Repositioning; Embryo, Mammalian; Embryonic Development; Endocrine System Diseases; Endopeptidases; Epithelial Cells; Extracellular Fluid; Extracellular Matrix; Extracellular Space; Feedback, Physiological; Fibroblasts; Gelatin; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genomics; Haploinsufficiency; Hemagglutinin Glycoproteins, Influenza Virus; Homeostasis; Hydrogels; Immune Checkpoint Inhibitors; Immunotherapy; Induced Pluripotent Stem Cells; Inducible T-Cell Co-Stimulator Protein; Inflammation; Influenza A Virus, H5N1 Subtype; Influenza Vaccines; Interleukin-2; Islets of Langerhans; Keratinocytes; Kidney Diseases; Lamin Type A; Ligands; Lipid A; Lipid Droplets; Lipid Metabolism; Lipogenesis; Lymphocytes; Machine Learning; Macrophages; Melanoma; Melanoma, Experimental; Methylation; Methyltransferases; Mice, Inbred BALB C; Motor Neurons; Multiomics; Mutation; Myocytes, Cardiac; Nervous System Diseases; Neural Networks, Computer; Neurons; Neurotransmitter Agents; Obesity; Oligodeoxyribonucleotides; Organoids; Orthomyxoviridae Infections; Peptide Hydrolases; Pericardium; Pluripotent Stem Cells; Polysorbates; Programmed Cell Death 1 Receptor; Proteins; RANK Ligand; RNA; RNA-Seq; Rosacea; SARS-CoV-2; Saponins; Schwann Cells; Secretome; Senescence-Associated Secretory Phenotype; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Skin; Software; Squalene; Systems Biology; T-Lymphocytes; T-Lymphocytes, Regulatory; Transcriptome; Vacuoles; Wound Healing; Young Adult</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Parsons, Michael</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Academic Performance; Acinar Cells; Adenocarcinoma; Alleles; Animals, Genetically Modified; Animals, Laboratory; Antigen Presentation; BRCA1 Protein; BRCA2 Protein; Bayes Theorem; Bicarbonates; Breast Neoplasms; Carcinogens; Carcinoma, Ovarian Epithelial; Case-Control Studies; Cell Differentiation; Child; Demography; Developed Countries; Developmental Biology; Diabetes Mellitus; Diabetes Mellitus, Type 1; Diabetes Mellitus, Type 2; Disease Progression; Endocrine Cells; Epithelium; Financial Support; Gastrointestinal Microbiome; Gene Knockout Techniques; Genetic Phenomena; Genetic Predisposition to Disease; Genetic Testing; Genetic Variation; Growth and Development; Hispanic or Latino; Homeostasis; Homozygote; Hyperglycemia; Incidence; Indigenous Peoples; Inflammation; Insulin-Secreting Cells; Insulins; Integrases; Islets of Langerhans; Language; Larva; Leadership; Likelihood Functions; Liver; Metaplasia; Metronidazole; Neoplasms; Nitroreductases; Optimism; Ovarian Neoplasms; Pancreas; Pancreas, Exocrine; Pancreatic Neoplasms; Pancreatitis; Penetrance; Polymorphism, Single Nucleotide; Prospective Studies; Regeneration; Risk Factors; Sequence Analysis, RNA; Signal Transduction; Stem Cells; Stroke; Technology; Thinking; Transcriptome; Volunteers; Water; Workforce; Zebrafish; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Pizzagalli, Diego</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Plikus, Maksim</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Adaptor Proteins, Signal Transducing; Adipocytes; Aged; Aging; Ambystoma mexicanum; Amputation, Surgical; Anti-Infective Agents; Autopsy; Biocompatible Materials; Biological Evolution; Biomechanical Phenomena; Birds; Black or African American; Body Patterning; Brazil; Cadaver; Calcitonin Gene-Related Peptide; Cartilage; Casein Kinase 1 epsilon; Cell Communication; Cell Line, Tumor; Cell Proliferation; Cellular Senescence; China; Chromatin; Cicatrix; Circadian Clocks; Circadian Rhythm; Collagen; Colorectal Neoplasms; Computational Biology; Computer Simulation; Cross-Linking Reagents; Culicidae; Cytokines; Cytosol; DNA, Ancient; DNA-Binding Proteins; Dengue; Dermis; Disease Progression; Disease Susceptibility; Elephants; Embryonic Development; Epidermis; Epigenesis, Genetic; Epigenomics; Epithelial Cells; Ethnicity; Evidence Gaps; Evolution, Molecular; Extracellular Matrix; Eyebrows; Eyelids; Fibroblasts; Fibrosis; Flavivirus; Fossils; Gelatin; Gene Expression; Gene Expression Profiling; Gene Expression Regulation, Developmental; Gene Expression Regulation, Neoplastic; Gene Ontology; Gene Regulatory Networks; Genome; Genome, Human; Genomics; Glycolysis; HCT116 Cells; Hair; Hair Follicle; Heterografts; Hispanic or Latino; Homeodomain Proteins; Homeostasis; Hydrogels; Inflammation; Inflammatory Bowel Diseases; Internship and Residency; Intestinal Mucosa; Keloid; Keratinocytes; Latin America; Lipid Droplets; Lipid Metabolism; Lipogenesis; Locomotion; Macrophages; Mammoths; Marsupialia; Mechanistic Target of Rapamycin Complex 2; Melanocytes; Mesenchymal Stem Cells; Mitochondria; Mitochondrial Proteins; Mosquito Vectors; Multifactorial Inheritance; Multiomics; Myofibroblasts; NAD; Necroptosis; Neoplasms; Nevus; Nociceptors; Obesity; Organoids; Osteopontin; Ovosiston; Pain; Pandemic Preparedness; Pandemics; Phenotype; Phosphofructokinase-2; Phosphoprotein Phosphatases; Phosphorylation; Phylogeny; Pigmentation Disorders; Protein Serine-Threonine Kinases; Proto-Oncogene Proteins c-akt; Pruritus; Public Health; Quality Control; R-Loop Structures; RANK Ligand; RNA; RNA, Small Interfering; RNA-Seq; Reactive Oxygen Species; Referral and Consultation; Regeneration; Regulatory Sequences, Nucleic Acid; Reptiles; Saliva; Scalp; Schools; Secretome; Senescence-Associated Secretory Phenotype; Senotherapeutics; Sequence Analysis, RNA; Serine-Threonine Kinase 3; Signal Transduction; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Sirolimus; Skin; Skin Aging; Skin Diseases; Skin Physiological Phenomena; Skin Pigmentation; Software; Stem Cells; TOR Serine-Threonine Kinases; TRPV Cation Channels; Transcription Factors; Transcriptome; Tumor Suppressor Proteins; Urodela; Vaccines; Vaccinology; Vacuoles; West Nile virus; Wnt Signaling Pathway; World Health Organization; Wound Healing; X Chromosome; YAP-Signaling Proteins; Yellow Fever; Young Adult; Zebrafish; Zika Virus; Zika Virus Infection; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Ranz, Jose</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Axonemal Dyneins; Biological Evolution; Biomass; Butterflies; Cell Differentiation; Chromosomes; Diptera; Drosophila Proteins; Drosophila melanogaster; Ecological and Environmental Phenomena; Evolution, Molecular; Gene Expression; Gene Expression Profiling; Genetic Fitness; Genetic Speciation; Genetics; Genome; Genomics; Heterozygote; Hybridization, Genetic; INDEL Mutation; Insecta; Larva; Lepidoptera; Multigene Family; Phylogeny; RNA; RNA, Long Noncoding; Random Allocation; Research; Semen; Sequence Analysis; Sex Characteristics; Spain; Spermatogenesis; Spermatozoa; Spiroplasma; Testis; Transcriptome; Tsetse Flies; X Chromosome</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Razorenova, Olga</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Adenosine Triphosphate; Apoptosis; Basic Helix-Loop-Helix Transcription Factors; Binding Sites; Biomarkers; Breast Neoplasms; CRISPR-Cas Systems; Cancer Survivors; Carcinogens; Carcinoma, Renal Cell; Cell Line, Tumor; Cell Lineage; Cell Movement; Cell Plasticity; Cell Transformation, Neoplastic; Cyclic N-Oxides; Cyclin-Dependent Kinase 9; Cyclin-Dependent Kinase Inhibitor Proteins; Cyclin-Dependent Kinases; Dimerization; Down-Regulation; Drug Resistance, Neoplasm; Electron Transport; Epithelial Cell Adhesion Molecule; ErbB Receptors; Fatty Acids; Gene Expression Regulation, Neoplastic; Genes, Suppressor; Heterografts; Hypoxia; Immune Checkpoint Inhibitors; Immunogenic Cell Death; Indolizines; Integrin alpha6; Integrins; Kidney Neoplasms; Lipid Droplets; Lipid Metabolism; Lipids; Metabolism; Microscopy; Mitochondria; Motivation; Myeloid Cell Leukemia Sequence 1 Protein; Neoplasm Metastasis; Neoplasms; Neoplastic Processes; Neoplastic Stem Cells; Ovarian Neoplasms; Oxidative Phosphorylation; Oxygen; Pedigree; Peptides; Phenotype; Phosphoproteins; Protein Kinase Inhibitors; Pyridinium Compounds; RNA Polymerase II; RNA, Long Noncoding; Signal Transduction; Survival Rate; Synthetic Lethal Mutations; Tetracyclines; Transcriptome; Triple Negative Breast Neoplasms; Tumor Microenvironment; Tyrosine; Tyrosine Kinase Inhibitors; Up-Regulation; Von Hippel-Lindau Tumor Suppressor Protein; belzutifan; dinaciclib; endothelial PAS domain-containing protein 1; nan; saracatinib; src-Family Kinases; von Hippel-Lindau Disease</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Rebolleda-Gomez, Maria</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Agave; Agriculture; Algorithms; Ammonia; Arabidopsis; Awards and Prizes; Bacteria; Biological Evolution; Bioprinting; Carbon; Cell Survival; Communicable Diseases; Crops, Agricultural; Denitrification; Droughts; Drug Resistance, Microbial; Ecological and Environmental Phenomena; Ecosystem; Edible Grain; Evolution, Molecular; Farmers; Feedback
- DNA, Single-Stranded
- Learning
- Ecology
- Empirical Research; Gases; Genetics, Population; Metabolism; Mexico; Microbiota; Natural Science Disciplines; Nitrogen; Nitrogen Cycle; Pandemics; Plants; Plasmids; Printing, Three-Dimensional; Soil; Sorghum; Switzerland; Synthetic Biology; Technology; United Kingdom; Water; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Ribbe, Markus</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Adenosine Triphosphate; Aldehyde Oxidoreductases; Ammonia; Azotobacter vinelandii; Bacterial Proteins; Biocatalysis; Biofuels; Biosynthetic Pathways; Biotechnology; Carbon Dioxide; Carbon Monoxide; Catalysis; Chemistry, Bioinorganic; Electrons; Escherichia coli; Evolution, Molecular; Formate Dehydrogenases; Gene Expression; Hydrocarbons; Hydrogenase; Iron-Sulfur Proteins; Metalloproteins; Methyltransferases; Models, Molecular; Molybdenum; Molybdoferredoxin; Multienzyme Complexes; Nitrogen; Nitrogen Fixation; Nitrogenase; Organic Chemicals; Oxidation-Reduction; Oxidoreductases; Phylogeny; Protons; Recombinant Proteins; Reducing Agents; S-Adenosylmethionine; Sulfur</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Rodriguez Verdugo, Alejandra</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Acclimatization; Acinetobacter; Actinobacteria; Adaptation, Physiological; Anti-Bacterial Agents; Anti-Infective Agents; Anti-Infective Agents, Local; Bacteria; Bacteroidetes; Biodiversity; Biofilms; Biological Evolution; Chemotaxis; Climate Change; Coculture Techniques; Computer Simulation; DNA-Directed RNA Polymerases; Drug Resistance, Bacterial; Drug Resistance, Microbial; Ecological and Environmental Phenomena; Ecosystem; Epistasis, Genetic; Escherichia coli; Escherichia coli Proteins; Evolution, Molecular; Fecal Microbiota Transplantation; Ficus; Flagella; Genetic Background; Genetic Fitness; Genotype; Hot Temperature; Internship and Residency; Microbial Consortia; Microbial Interactions; Microbiota; Mutation; Nutrients; One Health; Phenotype; Plant Leaves; Poaceae; Proteobacteria; Pseudomonas putida; Rho Factor; Rifampin; Selection, Genetic; Species Specificity; Stress, Physiological; Symbiosis; Synthetic Biology; Whole Genome Sequencing; Xylans; Xylose</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Schechtman-Drayman, Eitan</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Academia; Algorithms; Arousal; Bacteriophage T7; Bacteriophages; Behavior Control; Brain; Cognition; Cognitive Dysfunction; Cognitive Neuroscience; Computational Biology; Consciousness; Cues; DNA; DNA-Directed RNA Polymerases; Data Collection; Decision Making; Depression; Diffusion; Electroencephalography; Electrophysiology; Healthy Volunteers; Latent Infection; Leadership; Learning; Machine Learning; Magnetic Resonance Imaging; Memory; Memory Consolidation; Memory, Episodic; Mental Health; Molecular Dynamics Simulation; Mood Disorders; Neurobiology; Neuroimaging; Odorants; Pilot Projects; Probability; Promoter Regions, Genetic; RNA, Viral; Research Personnel; Rodentia; Sexual and Gender Minorities; Sleep; Spatial Memory; Spatial Navigation; Stress Disorders, Post-Traumatic; Transcription Factors; Transcription, Genetic; Vacuum; Wakefulness</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Schilling, Thomas</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Adipocytes; Animals, Genetically Modified; Aquaporins; Biological Evolution; Biomechanical Phenomena; Bone and Bones; Branchial Region; Calcium; Cartilage; Cell Adhesion; Cell Cycle Proteins; Cell Lineage; Cell Movement; Cell Polarity; Cell Proliferation; Chondrocytes; Chromosomal Proteins, Non-Histone; Cichlids; Clinical Relevance; Cohesins; Computer Simulation; Congenital Abnormalities; Craniofacial Abnormalities; Embryo, Nonmammalian; Embryology; Embryonic Development; Embryonic Induction; Extracellular Matrix; Eye Proteins; Fibroblasts; Gene Dosage; Gene Expression; Gene Expression Profiling; Gene Expression Regulation, Developmental; Germ Cells; Gonads; Growth Plate; Hand-Foot Syndrome; Jaw; Laboratories; Lakes; Larva; Lens, Crystalline; Ligaments; Lipid Droplets; Lipid Metabolism; Lipogenesis; Malawi; Mechanotransduction, Cellular; Mesoderm; Morphogenesis; Muscle Contraction; Mutation; Neural Crest; Obesity; Permeability; Phenotype; Quantitative Trait Loci; Receptor Tyrosine Kinase-like Orphan Receptors; Receptors, Retinoic Acid; Receptors, Wnt; Regulatory Sequences, Nucleic Acid; Sex Determination Processes; Signal Transduction; Skeleton; Skull; Species Specificity; Systems Biology; Tendons; Tenocytes; Transcription Factors; Transcriptome; Tretinoin; Vacuoles; Van Maldergem Wetzburger Verloes syndrome; Vertebrates; Water; Wnt Proteins; Wnt Signaling Pathway; Zebrafish; Zebrafish Proteins; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Shi, Xiaoyu</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Academia; Acyltransferases; Adaptor Proteins, Signal Transducing; Aging; Alzheimer Disease; Amyloid beta-Peptides; Amyloidogenic Proteins; Astrocytes; Axons; Benchmarking; Bioengineering; Biomarkers; Biophysics; Biotechnology; Brain; Brain Injuries; Capacity Building; Carcinogenesis; Cell Biology; Cell Line, Tumor; Cell Nucleus; Cell Proliferation; Cell Transformation, Neoplastic; Chromatin; Chromosomes, Plant; Colorectal Neoplasms; Crops, Agricultural; Cytosol; Dendrites; Diploidy; Disease Progression; Early Diagnosis; Endocytosis; Epigenesis, Genetic; Epigenomics; Estrogens; Fibrinolytic Agents; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Plant; Genes, Plant; Genetic Variation; Genetics, Population; Genome, Plant; Genomics; HCT116 Cells; HEK293 Cells; HeLa Cells; Heterochromatin; Heterozygote; High-Throughput Nucleotide Sequencing; Hippocampus; Homozygote; Human Body; Hydrogels; Intrinsically Disordered Proteins; Lamins; Latin America; Long-Term Potentiation; Mass Spectrometry; Memory; Memory Disorders; Microscopy; Microscopy, Fluorescence; Mitochondria; Mitochondrial Proteins; Molecular Structure; Multiomics; Nerve Degeneration; Neurodegenerative Diseases; Neurons; Nuclear Lamina; Nucleic Acids; Organelles; Outsourced Services; Peptides; Phenotype; Phosphoprotein Phosphatases; Phosphorylation; Pinocytosis; Plague; Plant Breeding; Plaque, Amyloid; Pollination; Prefrontal Cortex; Protein Binding; Protein Biosynthesis; Protein Interaction Mapping; Protein Kinase C; Protein Processing, Post-Translational; Protein Serine-Threonine Kinases; Proteins; Proteome; Proteomics; RNA 3' End Processing; RNA Polymerase II; RNA Precursors; RNA Processing, Post-Transcriptional; RNA Splicing; RNA, Messenger; RNA-Binding Proteins; Reactive Oxygen Species; Receptors, AMPA; Receptors, Progesterone; Reproduction; Ribosomes; Sequence Analysis, RNA; Serine-Threonine Kinase 3; Sex Factors; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Staining and Labeling; Synapses; Tissues; Transcription Factors; Transcriptome; Triple Negative Breast Neoplasms; Tumor Suppressor Proteins; Vitis; YAP-Signaling Proteins; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Sorte, Cascade</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Alaska; Anthropogenic Effects; Biodiversity; Carbon Dioxide; Climate Change; Conservation of Natural Resources; Ecological and Environmental Phenomena; Ecosystem; Europe; Gastropoda; Geography; Human Activities; Hydrogen-Ion Concentration; Introduced Species; Nitrogen; Oceans and Seas; Oxygen; Plants; Predatory Behavior; Species Specificity; Temperature</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Stark, Craig</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid beta-Peptides; Atlases as Topic; Atrophy; Behavior, Animal; Benchmarking; Biomarkers; Brain; Brain Mapping; Calcineurin; Calcineurin Inhibitors; Cerebral Cortex; Cognition; Cognitive Dysfunction; Disease Progression; Dogs; Entorhinal Cortex; Foot; Foot Deformities; Hallux Valgus; Hippocampus; Image Processing, Computer-Assisted; Learning; Magnetic Resonance Imaging; Memory; Mental Status and Dementia Tests; NFATC Transcription Factors; Neuroimaging; Neuropsychological Tests; Oxygen; Pattern Recognition, Physiological; Pattern Recognition, Visual; Positron-Emission Tomography; Quality Control; Radiography; Reading; Repression, Psychology; Reproducibility of Results; Spatial Learning; Tacrolimus; Temporal Lobe; Verbal Learning; Young Adult; nan; tau Proteins</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Striedter, Georg</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Biological Evolution; Physiology, Comparative</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Suetterlin, Christine</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>AMP-Activated Protein Kinases; Asymptomatic Infections; Bacteria; Bacterial Proteins; Causality; Cell Biology; Cell Culture Techniques; Cell Cycle; Centers for Disease Control and Prevention, U.S.; Centrosome; Chlamydia; Chlamydia Infections; Chlamydia trachomatis; Cilia; Epithelial Cells; Epithelium; Escherichia coli; Fallopian Tubes; Gene Expression Regulation, Bacterial; Gene Knockdown Techniques; Golgi Apparatus; HeLa Cells; Infertility; Lipids; Membrane Proteins; Membranes; Microbiology; Microbiota; Microscopy; Oocytes; Organelles; Ovary; Pregnancy; Pregnancy, Ectopic; Proto-Oncogene Proteins c-akt; RNA; RNA, Messenger; RNA, Small Untranslated; Reverse Genetics; Sorting Nexins; Staining and Labeling; Stem Cells; Vacuoles; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Sumikawa, Katumi</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Acetylation; Adolescent; Allosteric Regulation; Alzheimer Disease; Animals, Genetically Modified; Behavior Rating Scale; Brain; CA1 Region, Hippocampal; Cause of Death; Chemokines; Child; Cholinergic Neurons; Cognition; Cognitive Dysfunction; Cytokines; Down-Regulation; Electrophysiology; Epigenesis, Genetic; Fluorescent Antibody Technique; Hippocampus; Histone Deacetylase Inhibitors; Histone Deacetylases; Histones; Homeostasis; Interneurons; Ligands; Long-Term Potentiation; Longevity; Memory Disorders; Microglia; Mortality, Premature; Mutation; N-Methylaspartate; Neocortex; Neuregulin-1; Nicotiana; Nicotine; Nicotinic Agonists; Phosphorylation; Plaque, Amyloid; Prefrontal Cortex; Pregnancy; Pyramidal Cells; Quinolines; RNA, Messenger; Rats, Sprague-Dawley; Receptor, Muscarinic M1; Receptors, N-Methyl-D-Aspartate; Receptors, Nicotinic; Reward; Schizophrenia; Signal Transduction; Smoking; Smoking Cessation; Somatostatin; Substance-Related Disorders; Tobacco Smoking; Tobacco Use; Tobacco Use Disorder; Transcription, Genetic; Tyrosine; Up-Regulation; src-Family Kinases</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Sun, Sha</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Aged; Algorithms; Biological Evolution; Biomarkers; Biomarkers, Tumor; Brain; Breast Neoplasms; Carcinogenesis; Carcinoma, Hepatocellular; Carcinoma, Non-Small-Cell Lung; Cell Differentiation; Cell Line, Tumor; Cell Plasticity; Cell Proliferation; Cell Survival; Chromosomes, Human, X; Circulating Tumor DNA; Clustered Regularly Interspaced Short Palindromic Repeats; Colonic Neoplasms; Computational Biology; Diagnosis, Differential; Down-Regulation; Drug Resistance, Neoplasm; Educational Measurement; Embryonic Development; Epigenesis, Genetic; Epigenomics; ErbB Receptors; Eutheria; Evolution, Molecular; Exons; Fetal Stem Cells; Gene Editing; Gene Expression Profiling; Gene Expression Regulation, Neoplastic; Genes, X-Linked; Genetics; Genital Neoplasms, Female; Glutamine; Health; Incidence; Large Language Models; Life Style; Liver Neoplasms; Lung Neoplasms; Marsupialia; Metabolic Reprogramming; Microscopy, Fluorescence; Molecular Biology; Multigene Family; Mutagenesis, Insertional; Mutation; Neoplastic Processes; Neoplastic Stem Cells; Optical Imaging; Organoids; Ovarian Neoplasms; Oxidative Phosphorylation; Precision Medicine; Prognosis; Protein Kinase Inhibitors; RNA; RNA, Guide, CRISPR-Cas Systems; RNA, Long Noncoding; RNA, Untranslated; Radiology; Reproducibility of Results; Retrospective Studies; Sex Characteristics; Sex Chromosomes; Specialty Boards; Stem Cells; Stress, Physiological; Trans-Activators; Tumor Microenvironment; X Chromosome; X Chromosome Inactivation; Y Chromosome; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Swarup, Vivek</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid beta-Peptides; Apolipoproteins E; Astrocytes; Brain; CD8-Positive T-Lymphocytes; Cell Communication; Cell Line; Cell Nucleus; Cell Proliferation; Cellular Reprogramming; Central Nervous System; Chromatin Immunoprecipitation Sequencing; Cocaine; Cognition; Critical Pathways; Demyelinating Diseases; Disease Progression; Down Syndrome; Encephalitis Virus, Japanese; Encephalitis, Japanese; Epigenesis, Genetic; Epigenomics; Fatty Acids, Volatile; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genes; Genetic Variation; Genetics; Genomics; Habenula; Healthy Aging; Immunity, Innate; Inflammation; Integrases; Killer Cells, Natural; Longevity; Memory; MicroRNAs; Microglia; Multiomics; Multiple Sclerosis; Myelin Sheath; Myeloid Cells; NF-KappaB Inhibitor alpha; NF-kappa B; Natural Killer T-Cells; Nervous System Malformations; Neurodegenerative Diseases; Neuroglia; Neuroinflammatory Diseases; Neurons; Occipital Lobe; Oligodendrocyte Precursor Cells; Oligodendroglia; Parkinson Disease; Parkinsonian Disorders; Plaque, Amyloid; Postmortem Changes; Prefrontal Cortex; Proteomics; Pseudogenes; Quality Control; RNA; RNA, Small Nuclear; RNA-Seq; Recurrence; Regulator; Remyelination; Reproducibility of Results; Resilience, Psychological; Risk Factors; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Spatial Memory; Spinal Cord; Spinal Cord Injuries; Sterol Regulatory Element Binding Protein 1; Stroke; Substance-Related Disorders; Systems Biology; Tauopathies; Time Factors; Transcription Factors; Transcriptome; White Matter; Wound Healing; nan; tau Proteins</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Symons, Celia</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Additional Terms; Antelopes; Anthropogenic Effects; Bacteria; Biodiversity; Biological Specimen Banks; Biomass; Biota; Capacity Building; Carbon Dioxide; Climate Change; Conservation of Natural Resources; Data Science; Diet; Dissolved Organic Matter; Ecological and Environmental Phenomena; Ecology; Ecosystem; Environmental Indicators; Environmental Monitoring; Europe; Feeding Behavior; Fires; Food Chain; Forests; Fresh Water; Freshwater Biology; Guidelines as Topic; Hunting; Hydrobiology; Interdisciplinary Research; Introduced Species; Lakes; Literacy; Mobile Applications; North America; Organic Chemicals; Phytoplankton; Planets; Plankton; Ponds; Population Dynamics; Remote Sensing; Remote Sensing Technology; Resilience, Psychological; Salinity; Seasons; Smoke; Technology; Temperature; Time Factors; Vertebrates; Water Quality; Wildfires; Workforce; Zooplankton</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Tenner, Andrea</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>ATP-Binding Cassette Transporters; Aged; Allergy and Immunology; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Apolipoproteins E; Astrocytes; Biological Phenomena; Brain; Calcium; Cognition; Cognitive Dysfunction; Complement Activation; Complement C1q; Complement C5a; Complement System Proteins; Cuprizone; Demyelinating Diseases; Disease Progression; Gastrointestinal Microbiome; Gene Expression; Gene Knock-In Techniques; Genetic Variation; Genotype; Hippocampus; Immune System; Immunity, Innate; Immunologic Factors; Incidence; Inflammation; Long-Term Potentiation; Lysosomes; Membrane Glycoproteins; Memory Disorders; Metabolomics; Microbiota; Microglia; Microscopy; Mutation; Neurodegenerative Diseases; Neuroglia; Neuroinflammatory Diseases; Neuronal Plasticity; Neurons; Neuroprotection; Phagocytosis; Plaque, Amyloid; RNA Splicing; RNA-Seq; Receptor, Anaphylatoxin C5a; Receptors, Complement; Receptors, Immunologic; Resilience, Psychological; Sex Characteristics; Signal Transduction; Synapses; Tauopathies; Therapeutics; hydrocinnamate-cyclo(ornithyl-prolyl-cyclohexylalanyl-tryptophyl-arginyl); tau Proteins</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Thompson-Peer, Katherine</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Actin Cytoskeleton; Actins; Adenosine Triphosphate; Alleles; Axons; Blood-Brain Barrier; Calcium; Cell Death; Cytoskeleton; Dendrites; Drosophila melanogaster; Endothelial Cells; Energy Metabolism; Extracellular Matrix; Gene Expression Profiling; Glutamine; Huntington Disease; Integrins; Microtubules; Mitochondria; Mitochondrial Dynamics; Nerve Regeneration; Neurites; Neurodegenerative Diseases; Neurogenesis; Neuroglia; Neurons; Neuroprotection; Neuroprotective Agents; Peptides; Peripheral Nervous System; Potassium Channels, Inwardly Rectifying; Proteolysis; Regeneration; Sensory Receptor Cells; Signal Transduction; Spinocerebellar Ataxias; Time-Lapse Imaging; Transgenes; nan; polyglutamine</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Thompson, Leslie</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>6-methyladenine; Academia; Adenosine; Aged; Algorithms; Alternative Splicing; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Animals, Genetically Modified; Artificial Intelligence; Astrocytes; Ataxin-1; Atrophy; Autophagy; Biological Phenomena; Biomarkers; Biomedical Research; Biotin; Brain; Brain-Derived Neurotrophic Factor; C9orf72 Protein; Calcium Signaling; Caregivers; Case-Control Studies; Cell Death; Cell Differentiation; Cell Line; Cell- and Tissue-Based Therapy; Cells, Cultured; Cerebellum; Cerebral Cortex; Child; Child, Preschool; Chorea; Chromatin; Chromatin Immunoprecipitation Sequencing; Chromatography, Liquid; Clinical Trials, Phase I as Topic; Clustered Regularly Interspaced Short Palindromic Repeats; Cognition; Cognitive Dysfunction; Colon; Communication; Corpus Striatum; DNA Breaks, Double-Stranded; DNA Damage; DNA Repair; DNA-Binding Proteins; Deep Learning; Delayed Diagnosis; Dementia; Demography; Depression; Dihydroxyphenylalanine; Disease Progression; Dopaminergic Neurons; Drug Development; Dystonia 3, Torsion, X-Linked; Edema; Electrophysiology; Embryonic Stem Cells; Epigenesis, Genetic; Epigenomics; Epilepsies, Partial; Exons; Feasibility Studies; Fibroblasts; Frontotemporal Dementia; Frontotemporal Lobar Degeneration; Gene Editing; Gene Expression Profiling; Gene Expression Regulation; Gene Knockout Techniques; Genetic Diseases, X-Linked; Genetic Therapy; Genetic Variation; Graft Rejection; HeLa Cells; Hematopoietic Stem Cell Transplantation; Histones; Hospital Mortality; Hospitalization; Huntingtin Protein; Huntington Disease; Immunosuppression Therapy; Induced Pluripotent Stem Cells; Inflammation; Inosine; Intermediate Filaments; Intranuclear Inclusion Bodies; Isomerism; Length of Stay; Lewy Bodies; Ligases; Liquid Chromatography-Mass Spectrometry; Lysosomes; Medium Spiny Neurons; Methylation; Methyltransferases; Microglia; Microscopy; Microscopy, Electron; Mitochondria; Mitochondrial Proteins; Motor Neurons; Multiomics; Muscle, Skeletal; Mutation; Negotiating; Nervous System Diseases; Neural Stem Cells; Neurites; Neurobiology; Neurodegenerative Diseases; Neurons; Neurons, Efferent; Oligonucleotides, Antisense; Optogenetics; Organelles; Outcome Assessment, Health Care; Parkinson Disease; Peptides; Pharmaceutical Preparations; Phenotype; Poly Adenosine Diphosphate Ribose; Prevalence; Primates; Prisoners; Promoter Regions, Genetic; Prospective Studies; Protein Binding; Protein Biosynthesis; Protein Isoforms; Proteomics; Proteostasis; Quantitative Trait Loci; RNA; RNA Methylation; RNA Splicing; RNA Stability; RNA, Messenger; RNA, Small Interfering; RNA-Binding Proteins; Receptors, Antigen, T-Cell; Receptors, Metabotropic Glutamate; Rectum; Regenerative Medicine; Registries; Research Report; Retroelements; Robotic Surgical Procedures; SUMO-1 Protein; Salts; Seizures; Seizures, Febrile; Sequence Analysis, RNA; Signal Transduction; Sodium Chloride; Spinocerebellar Ataxias; Stem Cell Transplantation; Stem Cells; Sumoylation; Superoxide Dismutase-1; Surgical Wound Infection; Synapses; Synapsins; Synaptosomes; Synucleins; Systems Biology; Tandem Mass Spectrometry; Tandem Repeat Sequences; Terminology as Topic; Tissue Distribution; Transcription, Genetic; Transcriptome; Translational Science, Biomedical; Treatment Outcome; Trinucleotide Repeat Expansion; Ubiquitin; Ubiquitin-Protein Ligases; Whole Genome Sequencing; Wound Closure Techniques; gamma-Aminobutyric Acid; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Thornton, Kevin</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Algorithms; Alleles; Computer Simulation; Demography; Ecological and Environmental Phenomena; Genetics, Population; Mutation; Phylogeny; Software; Uncertainty</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Tinoco, Roberto</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>ADP-ribosyl Cyclase; AMP-Activated Protein Kinases; Adaptive Immunity; Aged; Aging; Allergy and Immunology; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Antibodies, Blocking; Antigens; Antiviral Agents; Arm; Autoimmunity; B7-H1 Antigen; Brain; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Calcium Signaling; Caregivers; Cell Differentiation; Cell Line, Tumor; Cell Movement; Cell Proliferation; Cell Survival; Chromatin; Chronic Disease; Cognition; Cognitive Dysfunction; Coloring Agents; Delivery of Health Care; Dendritic Cells; Dengue; Diet; Disease-Free Survival; Epigenesis, Genetic; Feasibility Studies; Ficus; Financing, Organized; Flow Cytometry; Gene Expression Profiling; Genetic Predisposition to Disease; HIV Infections; HMGB2 Protein; Hemorrhagic Fever, Ebola; Hepatitis A Virus Cellular Receptor 2; Hepatitis B; Hepatitis C; Homeostasis; Immune Checkpoint Inhibitors; Immune Checkpoint Proteins; Immune System; Immunity; Immunoglobulin G; Immunologic Memory; Immunologic Techniques; Immunosuppression Therapy; Immunotherapy; Incidence; Influenza A Virus, H1N1 Subtype; Influenza A Virus, H7N9 Subtype; Intravital Microscopy; Ligands; Longevity; Lymph Nodes; Lymphocyte Activation; Lymphocytic Choriomeningitis; Lymphocytic choriomeningitis virus; Macrophages; Melanoma; Membrane Glycoproteins; Memory T Cells; Metabolic Networks and Pathways; Microbiota; Microscopy; Military Personnel; Molecular Biology; Morbidity; Mutation; Myeloid Cells; Natural Killer T-Cells; Neoadjuvant Therapy; Neoplasms; Neoplasms, Second Primary; P-Selectin; P-selectin ligand protein; Persistent Infection; Phosphoprotein Phosphatases; PrPC Proteins; Prion Proteins; Programmed Cell Death 1 Receptor; Receptors, Antigen, T-Cell; Research; Risk Factors; SARS-CoV-2; Sequence Analysis, RNA; Signal Transduction; Skin Neoplasms; Spleen; Survival Rate; T-Cell Exhaustion; T-Lymphocytes; Transcription Factors; Treatment Outcome; Tumor Microenvironment; Up-Regulation; Vaccines; Virus Diseases; nan; protein phosphatase 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Treseder, Kathleen</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Actinomycetales; Alaska; Alternaria; Anti-Bacterial Agents; Ants; Arthropods; Bacteria; Biomass; Canada; Carbon; Carbon Dioxide; Climate Change; Climate Models; Cold Temperature; Computers; Crop Production; Dermabrasion; Droughts; Drug Resistance, Bacterial; Ecological and Environmental Phenomena; Ecology; Ecosystem; Extracellular Polymeric Substance Matrix; Farmers; Forests; Fungi; Gene Expression Profiling; Genes, Bacterial; Genome, Bacterial; Genotype; Global Warming; Grassland; Hawaii; Hot Temperature; Incidence; Information Dissemination; Lepidoptera; Life History Traits; Longevity; Metagenome; Metagenomics; Microbiota; Mycorrhizae; Neon; Nitrogen; Plant Development; Plants; Poaceae; Policy; Resilience, Psychological; Seedlings; Seeds; Soil; Soil Microbiology; Songbirds; Survivorship; Technology; Temperature; Thermotolerance; Transcription, Genetic; Transcriptome; Uncertainty; Water; West Nile Fever; West Nile virus; Wildfires</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Tsai, Shiou-Chuan</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Aged; Aged, 80 and over; Algorithms; Analgesics, Opioid; Androgens; Antineoplastic Agents; Atrial Fibrillation; Big Data; Biological Products; Bipolar Disorder; Black or African American; Brain; COVID-19; COVID-19 Drug Treatment; COVID-19 Serotherapy; Catalytic Domain; Cell Differentiation; Child; Chromosome Mapping; Cohort Studies; Comorbidity; Cross-Sectional Studies; Crystallography; Daunorubicin; Drug Design; Electrocardiography, Ambulatory; Epithelial Cells; Europe; Genetic Predisposition to Disease; Genome-Wide Association Study; Genomics; Gray Matter; HIV Infections; Hair Follicle; Heart; Hippocampus; Hispanic or Latino; Hospitalization; Hypertension; Immunization, Passive; Machine Learning; Magnetic Resonance Imaging; Medical Oncology; Mutagenesis; Neoplasms; Neuroimaging; North America; Oncology Nursing; Opioid-Related Disorders; Oxygen; Patient Safety; Pediatrics; Phenotype; Polyketide Synthases; Polyketides; Post-Acute COVID-19 Syndrome; Reproducibility of Results; SARS-CoV-2; Schizophrenia; Sebaceous Glands; Single-Cell Analysis; Skin; Societies, Nursing; Treatment Outcome; White; White People</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Walsh, Craig</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Adjuvants, Immunologic; Alcoholism; Allergy and Immunology; Alzheimer Disease; Anti-HIV Agents; Antibodies, Monoclonal, Humanized; Antibody Formation; Assessment of Medication Adherence; Astrocytes; Autoimmunity; Bioengineering; Bioprinting; Biotechnology; Bone Marrow; CD4 Antigens; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Cell Adhesion Molecules; Cell Death; Clinical Trials, Phase II as Topic; Clustered Regularly Interspaced Short Palindromic Repeats; Coronavirus Infections; Demyelinating Diseases; Embryonic Stem Cells; Encephalomyelitis, Autoimmune, Experimental; Epitopes; Epstein-Barr Virus Infections; Esophageal Neoplasms; Flow Cytometry; Fluticasone; Forkhead Transcription Factors; Fucose; Fucosyltransferases; Gene Expression Profiling; Graft vs Host Disease; HIV Infections; Hematologic Neoplasms; Hematopoietic Stem Cell Transplantation; Hematopoietic Stem Cells; Herpesvirus 4, Human; Image Cytometry; Immune Tolerance; Immunity, Cellular; Immunity, Innate; Immunization; Immunosuppressive Agents; Immunotherapy; Incubators; Induced Pluripotent Stem Cells; Inflammation; Ischemia; Killer Cells, Natural; Laboratories; Lymphocyte Activation; Macrophages; Magnetic Phenomena; Medication Adherence; Meningitis, Aseptic; Microglia; Microscopy; Motivational Interviewing; Multiomics; Multiple Sclerosis; Multiple Sclerosis, Relapsing-Remitting; Murine hepatitis virus; Neural Stem Cells; Neuroinflammatory Diseases; Organoids; Persistent Infection; Receptors, Antigen, T-Cell; Regenerative Medicine; Remyelination; S Phase; Single-Cell Gene Expression Analysis; Smartphone; Stem Cell Research; Stem Cells; T-Lymphocytes; T-Lymphocytes, Regulatory; Transplantation, Homologous; Treatment Outcome; Tumor Escape; Vaccination; Vaccine Efficacy; Vaccines; White Matter; aducanumab; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Wang, Wenqi</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>AMP-Activated Protein Kinases; Adaptor Proteins, Signal Transducing; Adenocarcinoma of Lung; Adolescent; Air Pollutants; Air Pollution; Animals, Domestic; Antineoplastic Agents; Apoptosis; Benzothiazoles; Biological Phenomena; Body Patterning; Brain; Carcinogenesis; Catalysis; Cell Line, Tumor; Cell Proliferation; Cell Survival; Cell Transformation, Neoplastic; Child; China; Cities; Cues; DNA-Binding Proteins; Drug Resistance, Neoplasm; Environmental Exposure; Environmental Monitoring; Ependymoma; Fertilization; Florida; Fluorescence; Gene Expression; Gene Expression Regulation, Neoplastic; Genes, Neurofibromatosis 2; Genetic Background; Genomics; Genotype; Glucose; Head and Neck Neoplasms; High-Throughput Screening Assays; Hippo Signaling Pathway; Homeostasis; Hydroxyl Radical; Intercellular Signaling Peptides and Proteins; Interdisciplinary Research; Kinetics; Lipids; Loss of Function Mutation; Lung Neoplasms; MAP Kinase Signaling System; Meningeal Neoplasms; Meningioma; Metabolic Networks and Pathways; Metals, Heavy; Models, Chemical; Morbidity; Mortality; Mutation; Mutation, Missense; Neoplasms; Neurilemmoma; Neurofibromatosis 2; Neurofibromin 2; Organ Size; Ovarian Neoplasms; Oxidation-Reduction; Oxygen; Particulate Matter; Phenotype; Phosphorylation; Physiological Phenomena; Plasmodium falciparum; Platinum; Polyamines; Protein Interaction Maps; Protein Serine-Threonine Kinases; Publishing; Putrescine; Regeneration; Saccharomyces cerevisiae; Saccharomyces cerevisiae Proteins; Sequence Deletion; Signal Transduction; Spermidine; Stem Cells; TEA Domain Transcription Factors; Transcription Factors; Transcriptome; Writing; Xenograft Model Antitumor Assays; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Warrior, Rahul</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Cadmium; Cell Line, Tumor; DNA-Binding Proteins; Developmental Biology; Gene Expression Regulation; Genetics; HEK293 Cells; HeLa Cells; Hippo Signaling Pathway; Homeostasis; Inactivation, Metabolic; Phosphorylation; Protein Biosynthesis; Protein Serine-Threonine Kinases; Proteoglycans; Stress, Physiological; Transcription Factor MTF-1; Transcription Factors; Transcription, Genetic; Tumor Suppressor Proteins; Zinc</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Whiteson, Katrine</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Adjuvants, Immunologic; Adjuvants, Pharmaceutic; Aged; Aging; Alzheimer Disease; Ampicillin; Amyloid beta-Peptides; Angiotensin Receptor Antagonists; Angiotensin-Converting Enzyme Inhibitors; Anti-Bacterial Agents; Anti-Infective Agents; Antineoplastic Agents, Hormonal; Antioxidants; Appendectomy; Appendicitis; Autistic Disorder; Autoimmune Diseases; Bacteremia; Bacteria; Bacteria, Anaerobic; Bacterial Infections; Bacterial Physiological Phenomena; Bacteriophages; Benchmarking; Biodiversity; Biofilms; Biological Evolution; Biomarkers; Brain; Brain-Gut Axis; Breast Neoplasms; Bronchoalveolar Lavage Fluid; COVID-19; Caregivers; Case-Control Studies; Child; Chromatography, Gas; Clostridioides difficile; Clostridium Infections; Cohort Studies; Coliphages; Colon; Colonic Neoplasms; Colonoscopy; Communicable Diseases; Compassionate Use Trials; Complement C1q; Computational Biology; Critical Illness; Cross Infection; Cryopreservation; Culture Media; Cystic Fibrosis; DNA; Data Management; Dementia; Demography; Dendritic Cells; Diabetes Mellitus, Type 1; Diabetes Mellitus, Type 2; Diagnosis; Diet; Diet Therapy; Diet, Mediterranean; Dietary Fiber; Digestion; Drug Resistance, Bacterial; Drug Resistance, Microbial; Drug Resistance, Multiple, Bacterial; Dysbiosis; Ecology; Ecosystem; Ecuador; Endometriosis; Enterococcus; Enterococcus faecalis; Enterococcus faecium; Epithelium; Escherichia coli; Estonia; Ethics Committees, Research; Fatty Acids, Volatile; Feasibility Studies; Fecal Microbiota Transplantation; Fellowships and Scholarships; Fermentation; Freezing; Gas Chromatography-Mass Spectrometry; Gastroenterology; Gastrointestinal Microbiome; Gene Expression Profiling; Gene Knock-In Techniques; Genome Size; Genomics; Genotype; Germ-Free Life; Global Health; Glycoside Hydrolases; Gram-Negative Bacteria; Gram-Negative Bacterial Infections; Gram-Positive Bacterial Infections; Health; Healthy Volunteers; High-Throughput Nucleotide Sequencing; Hospitalization; Host Microbial Interactions; Host Specificity; Human Body; Hunting; Hydrogen-Ion Concentration; Hypersensitivity; Immunity; Immunocompromised Host; Immunosenescence; Immunotherapy; Incidence; Individuality; Inflammation; Inflammatory Bowel Diseases; Informed Consent; Inpatients; Interdisciplinary Research; Internship and Residency; Intestine, Small; Kinetics; Laboratories; Leadership; Life Cycle Stages; Linezolid; Longitudinal Studies; Lung; Macrophages; Mass Spectrometry; Melanoma; Metabolome; Metabolomics; Metagenome; Metagenomics; Methicillin-Resistant Staphylococcus aureus; Microbial Sensitivity Tests; Microbiology; Microbiota; Microscopy; Microscopy, Fluorescence; Molecular Biology; Molecular Sequence Annotation; Morocco; Mutation; Myeloproliferative Disorders; Neoplasms; Neurodegenerative Diseases; Neuroinflammatory Diseases; Nutrients; Obesity; Optical Imaging; Outcome Assessment, Health Care; Pandemics; Patient Discharge; Phage Therapy; Pilot Projects; Planets; Pneumonia; Precision Medicine; Premature Birth; Prevalence; Probiotics; Pseudomonas; Pseudomonas aeruginosa; Public Health; Pyocyanine; RNA; RNA, Ribosomal, 16S; Random Forest; Receptors, Complement; Recommended Dietary Allowances; Reproducibility of Results; Research Personnel; Resilience, Psychological; Respiration; Respiration Disorders; Respiratory Mucosa; Respiratory System; Respiratory Tract Infections; Sequence Analysis, DNA; Sequence Analysis, RNA; Sewage; Sex Characteristics; Societies, Scientific; Sputum; Staphylococcal Infections; Staphylococcus; Staphylococcus aureus; Stenotrophomonas; Stenotrophomonas maltophilia; Stomach; Streptococcus; Surface-Active Agents; Tamoxifen; Tetracycline; Tobacco Smoke Pollution; Transcriptome; Translational Research, Biomedical; Translational Science, Biomedical; Vaccine Efficacy; Vancomycin; Virome; Viruses; Volatile Organic Compounds; Volunteers; Wastewater; Wastewater-Based Epidemiological Monitoring; Western World; Young Adult; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Wiles, Travis</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Animals, Genetically Modified; Animals, Wild; Anti-Bacterial Agents; Anti-Inflammatory Agents; Antioxidants; Bacteria; Bacterial Physiological Phenomena; Bacterial Proteins; Bacteriophages; Biological Evolution; Brain; Chromosomes; Climate Change; DNA Damage; Diabetes Mellitus; Disease Transmission, Infectious; Drug Resistance, Microbial; Ecology; Ecosystem; Escherichia coli; Evolution, Molecular; Feasibility Studies; Food Supply; Gastrointestinal Microbiome; Gastrointestinal Motility; Gene Flow; Gene Transfer, Horizontal; Genetic Engineering; Genetics; Homeostasis; Host Microbial Interactions; Hyperglycemia; Imaging, Three-Dimensional; Immune System; Inflammation; Intestines; Macrophages; Metronidazole; Microbial Consortia; Microbiology; Microbiota; Motivation; Nitroreductases; Oxidation-Reduction; Peptides; Planets; Predatory Behavior; Public Health; Reactive Oxygen Species; SOS Response, Genetics; Soil; Symbiosis; Synthetic Biology; Systems Biology; Type VI Secretion Systems; Vibrio cholerae; Virion; Zebrafish; nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Wood, Marcelo</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Abortion, Induced; Acetyl Coenzyme A; Acetylation; Activin Receptors, Type I; Adverse Childhood Experiences; Aged; Aging; Alzheimer Disease; Amyloid beta-Peptides; Antibodies; Anxiety; Autism Spectrum Disorder; Blotting, Western; Brain; Brain-Derived Neurotrophic Factor; Calcium; Cannabinoids; Cannabis; Cardiovascular System; Censuses; Chin; Cholinergic Agents; Cholinergic Neurons; Chromatin; Chromatin Immunoprecipitation; Cocaine; Cocaine-Related Disorders; Cognition; Color Vision Defects; Conditioning, Operant; Cues; Cuprizone; DNA; DNA Methylation; DNA-Binding Proteins; Delivery of Health Care; Demyelinating Diseases; Depression; Dopamine Uptake Inhibitors; Dopaminergic Neurons; Drug-Seeking Behavior; Epigenesis, Genetic; Epigenetic Memory; Epigenomics; Gastrin-Secreting Cells; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genes, X-Linked; Genetic Variation; Genetics; Genomics; Habenula; High-Throughput Nucleotide Sequencing; Hippocampus; Histone Code; Histone Deacetylases; Histones; Immunohistochemistry; Intellectual Disability; Interneurons; Jumonji Domain-Containing Histone Demethylases; Leucine Zippers; Life Change Events; Long-Term Potentiation; Longevity; Mass Spectrometry; Maternal Health; Medium Spiny Neurons; Membrane Glycoproteins; Memory; Memory Consolidation; Memory, Long-Term; Mental Health; Microglia; Multivariate Analysis; Mutation; N-nitrosoiminodiacetic acid; Neoplasms; Neurodegenerative Diseases; Neurogenesis; Neuroglia; Neuroinflammatory Diseases; Neuronal Plasticity; Neurons; Neurosciences; Nicotine; Nucleosomes; Nucleus Accumbens; Occupations; Pharmaceutical Preparations; Physical Conditioning, Animal; Plaque, Amyloid; Point Mutation; Polyadenylation; Polymerase Chain Reaction; Pregnancy; Promoter Regions, Genetic; Proteomics; Psychiatry; Public Health; RNA Splicing; RNA, Catalytic; RNA, Messenger; RNA-Binding Proteins; Radiation Dose Hypofractionation; Radiotherapy Dosage; Receptors, Immunologic; Recurrence; Reproducibility of Results; Resilience, Psychological; Reward; Schools; Self Administration; Self Report; Sequence Analysis, RNA; Spatial Memory; Speech; Substance-Related Disorders; Synapses; Synaptic Transmission; Trans-Activators; Transcription Factors; Transcriptome; Wood; X Chromosome; histone deacetylase 3; hydrogen sulfite</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Xue, Katherine</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Bacteria; Coculture Techniques; Ecosystem; Gastrointestinal Microbiome; Microbiota; Phylogeny; Population Density; Ruminants</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Yassa, Michael</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Adolescent; Adverse Childhood Experiences; Age Factors; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amygdala; Amyloid; Amyloid beta-Peptides; Anhedonia; Aniline Compounds; Anniversaries and Special Events; Anxiety; Artificial Intelligence; Biological Specimen Banks; Biomarkers; Brain; Cerebral Small Vessel Diseases; Cerebrovascular Disorders; Child; Clinical Trials as Topic; Cognition; Cognitive Dysfunction; Cohort Studies; Community-Institutional Relations; Compulsive Behavior; Computational Biology; Computer Simulation; Consensus; Data Aggregation; Data Collection; Data Management; Data Science; Dementia; Depression; Discrimination, Psychological; Documentation; Down Syndrome; Drug Discovery; Ecosystem; Electrophysiological Phenomena; Emotions; Entorhinal Cortex; Exercise; Financial Management; Frontal Lobe; Gamma Rhythm; Head; Hippocampus; Hypoxia; Infant, Newborn; Interdisciplinary Research; Interneurons; Learning; Longitudinal Studies; Machine Learning; Magnetic Resonance Imaging; Memory; Memory Consolidation; Memory Disorders; Memory, Episodic; Mental Disorders; Mental Recall; Metadata; Midline Thalamic Nuclei; Motivation; Neocortex; Nervous System Diseases; Neural Pathways; Neuroimaging; Neurophysiology; Neuropsychological Tests; Neuropsychology; Nucleus Accumbens; Oceans and Seas; Pattern Recognition, Physiological; Peptide Fragments; Phenotype; Physicians; Policy; Polyethylene Terephthalates; Polysomnography; Positron-Emission Tomography; Prefrontal Cortex; Premature Birth; Primates; Prospective Studies; Proteostasis Deficiencies; Psychiatry; Publishing; Quality of Life; Reward; Risk Factors; Saliva; Sleep; Sleep Apnea, Obstructive; Software; Spectrum Analysis; Stress Disorders, Post-Traumatic; Surveys and Questionnaires; Temporal Lobe; Theta Rhythm; UK Biobank; Wakefulness; White Matter; Writing; Young Adult; tau Proteins</t>
+          <t>Aged; Aging; Amyloidogenic Proteins; Body Patterning; Brain; Cell Differentiation; Cell Lineage; Cerebellum; Cerebral Hemorrhage; Cholesterol; Choroid Plexus; Corpus Striatum; DNA Methylation; Embryonic Development; Epigenome; Epithelial Cells; Glycosylation; Homeostasis; Huntingtin Protein; Huntington Disease; Hydrocephalus; Ion Channels; Lewy Bodies; Lewy Body Disease; Mechanotransduction, Cellular; Membrane Proteins; Neural Stem Cells; Neurogenesis; Neurons; Organoids; Phenotype; Plaque, Amyloid; Pluripotent Stem Cells; Records; Staining and Labeling; Transcriptome; Virion</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002B87155CDAEBE54E8A991CDFF09FE870" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07d22f826efb92a1b7f7a52cdc9ab0c0">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ccd2e96c-ba06-41a4-9d14-ee5d4767a409" xmlns:ns3="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f50f4dd1661db9c8120150ec829b0b2" ns2:_="" ns3:_="">
+    <xsd:import namespace="ccd2e96c-ba06-41a4-9d14-ee5d4767a409"/>
+    <xsd:import namespace="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:ProjectRole" minOccurs="0"/>
+                <xsd:element ref="ns3:Notes" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ccd2e96c-ba06-41a4-9d14-ee5d4767a409" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{5edd41bb-06d5-49d8-8697-11a388b6c936}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="ccd2e96c-ba06-41a4-9d14-ee5d4767a409">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="733ad1a4-bcb6-4664-8873-2816a39d1396" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="ProjectRole" ma:index="26" nillable="true" ma:displayName="Project Role" ma:format="Dropdown" ma:internalName="ProjectRole">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="Senior/Key Person"/>
+          <xsd:enumeration value="Other Personnel"/>
+          <xsd:enumeration value="Advisory Board"/>
+          <xsd:enumeration value="Evaluator"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Notes" ma:index="27" nillable="true" ma:displayName="Notes" ma:format="Dropdown" ma:internalName="Notes">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ccd2e96c-ba06-41a4-9d14-ee5d4767a409" xsi:nil="true"/>
+    <ProjectRole xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" xsi:nil="true"/>
+    <Notes xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39AEEB43-C0C1-467E-8FAE-78CD224749EF}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186FE51F-7F5A-45A8-A4EF-7F2A48EF295E}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8ABD69C6-4EB8-4E7E-8E48-832888BF6EC4}"/>
 </file>
--- a/faculty_unique_mesh_terms.xlsx
+++ b/faculty_unique_mesh_terms.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,1092 +443,1360 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Acharya, Munjal Mahendra</t>
+          <t>Allison, Steven</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adolescent; Aged; Aged, 80 and over; Alzheimer Disease; Amyloid beta-Peptides; Antineoplastic Agents; Behavior, Animal; Brain; Brain Neoplasms; Brain-Derived Neurotrophic Factor; Breast Neoplasms; CA1 Region, Hippocampal; Cell Communication; Cognition; Cognitive Dysfunction; Cranial Irradiation; Cytokines; Dendrites; Dose-Response Relationship, Radiation; Doxorubicin; Dynamin I; Dynamins; Ethnicity; Extinction, Psychological; Extracellular Vesicles; Fear; GABAergic Neurons; Glial Cell Line-Derived Neurotrophic Factor; Glioblastoma; Glutamic Acid; Hippocampus; Immune Checkpoint Inhibitors; Incidence; Inflammation; Interleukin-21; Interleukins; Long-Term Potentiation; Longitudinal Studies; Microglia; Neoplasms; Neurodegenerative Diseases; Neurogenesis; Neuroinflammatory Diseases; Neuronal Plasticity; Neurons; Neuroprotective Agents; Neurosciences; Patient Reported Outcome Measures; Plaque, Amyloid; Prefrontal Cortex; Prospective Studies; Pyramidal Cells; Quality of Life; RNA, Long Noncoding; Radiation Exposure; Receptors, Interleukin-21; Riluzole; Risk Factors; Self Report; Synapses; Translational Research, Biomedical; Tumor Microenvironment; Young Adult</t>
+          <t>Adaptation, Physiological; Australia; Authorship; Bacteria; Biodegradation, Environmental; Biodiversity; Biological Evolution; Biomass; California; Carbon; Carbon Cycle; Climate; Climate Change; Communication; Conservation of Natural Resources; Coral Reefs; Curriculum; Drought Resistance; Droughts; Earth, Planet; Ecological and Environmental Phenomena; Ecosystem; Education, Graduate; Environmental Justice; Environmental Microbiology; Environmental Science; Enzymes; Extreme Weather; Feasibility Studies; Financial Management; Forests; Genomics; Global Warming; Government; Government Agencies; Grassland; Greenhouse Gases; Hot Temperature; Humanities; Interdisciplinary Communication; Interdisciplinary Research; Introduced Species; Isoptera; Life History Traits; Loma; Metagenome; Metagenomics; Methane; Microbial Interactions; Microbiota; Mutation; Needs Assessment; Nitrification; Nitrogen; Phylogeny; Plant Leaves; Plants; Policy; Policy Making; Private Sector; Program Evaluation; Resilience, Psychological; Risk Assessment; Skin Pigmentation; Social Planning; Social Sciences; Soil; Soil Microbiology; Sphingomonas; Stress, Physiological; Temperature; Trees; Tropical Climate; Uncertainty; Water; Wildfires; Wood; Workforce; Writing; nan</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Calof, Anne L</t>
+          <t>Arora, Kavita</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Animals, Genetically Modified; Brain; CHO Cells; Cell Cycle Proteins; Cricetulus; Databases, Factual; De Lange Syndrome; Gastrulation; Gene Expression; Green Fluorescent Proteins; HEK293 Cells; Heterozygote; Metronidazole; Mutation; Nitroreductases; Phenotype; Pregnancy; Prodrugs; Protein Engineering; Proteins; Recombinant Proteins; Retina; Transcriptome; Vibrio; X-Ray Microtomography; Zebrafish</t>
+          <t>Binding Sites; CDC2 Protein Kinase; Cadmium; Caenorhabditis elegans; Caenorhabditis elegans Proteins; Cdc20 Proteins; Cell Line, Tumor; Cells, Cultured; Computational Biology; Conserved Sequence; Cyclin B; Cyclin B1; Cyclin B2; DNA-Binding Proteins; Developmental Biology; Embryo, Nonmammalian; Gene Expression Regulation; Genetics; HEK293 Cells; HeLa Cells; Hedgehog Proteins; Hippo Signaling Pathway; Homeostasis; Inactivation, Metabolic; MAP Kinase Signaling System; Metabolism; Mitogen-Activated Protein Kinase 1; Mitosis; Mutation; Neoplasms; Phosphorylation; Protein Binding; Protein Serine-Threonine Kinases; Repressor Proteins; Signal Transduction; Stress, Physiological; Transcription Factor MTF-1; Transcription Factors; Transcription, Genetic; Transforming Growth Factor beta; Tumor Suppressor Proteins; Zinc; Zinc Finger Protein GLI1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chen, Lulu Y</t>
+          <t>Atwood, Scott</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Adipocytes; Basolateral Nuclear Complex; Behavior, Animal; Boron Compounds; Cell Adhesion Molecules, Neuronal; Central Nervous System Stimulants; Conditioning, Operant; Corticotropin-Releasing Hormone; Dopaminergic Neurons; Fat Necrosis; Gene Deletion; Hippocampus; Homeodomain Proteins; Homing Behavior; Lipolysis; Maze Learning; Nerve Net; Nerve Tissue Proteins; Neural Cell Adhesion Molecules; Nucleus Accumbens; Pilot Projects; Presynaptic Terminals; Reversal Learning; Reward; Seizures; Sex Characteristics; Swine; Synaptic Transmission; Transcription Factors; gamma-Aminobutyric Acid</t>
+          <t>Algorithms; Allografts; Binding Sites; Bioprinting; Brain; CRISPR-Cas Systems; Carcinogenesis; Carcinoma, Basal Cell; Carcinoma, Basosquamous; Cell Communication; Cell Differentiation; Cell Line, Tumor; Cell Proliferation; Cells, Cultured; Chromatography, Liquid; Clone Cells; Clustered Regularly Interspaced Short Palindromic Repeats; Computer Simulation; Conserved Sequence; Dermis; Drug Resistance; Ecosystem; Epidermal Cells; Epidermis; Epithelial Cells; Extrude; Gene Expression Profiling; Gene Regulatory Networks; Genes, Suppressor; Genetic Techniques; Hair Follicle; Hedgehog Proteins; Hedgehogs; HhAntag691; Immune System; Immunity; Immunotherapy; Intercellular Signaling Peptides and Proteins; Keratinocytes; Lung Neoplasms; Lymphocytes; MAP Kinase Signaling System; Macrophage Activation; Membrane Proteins; Microphysiological Systems; Mitogen-Activated Protein Kinase 1; Molecular Biology; Multiomics; Mutation; Neoplasms; Neutrophil Activation; Neutrophils; Nucleosides; Organoids; Phosphorylation; Phosphotransferases; Pluripotent Stem Cells; Prostate; Protein Binding; Protein Kinase C; RNA; Repressor Proteins; Sebaceous Glands; Secretome; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Skin; Skin Neoplasms; Small Cell Lung Carcinoma; Stem Cells; T-Lymphocytes; Tandem Mass Spectrometry; Tissue Engineering; Transcription Factors; Transcriptome; Tumor Microenvironment; Wnt Signaling Pathway; Zinc Finger Protein GLI1; cemiplimab</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Diaz Alonso, Javier</t>
+          <t>Azizi, Emanuel</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Disks Large Homolog 4 Protein; Long-Term Potentiation; Nuclear Proteins; Receptors, AMPA; Synapses; Synaptic Transmission</t>
+          <t>Achilles Tendon; Aging; Alligators and Crocodiles; Anura; Biocompatible Materials; Biomechanical Phenomena; Biomimetic Materials; Bufo marinus; Connective Tissue; Conservation of Energy Resources; Elasticity; Elastomers; Electromyography; Environment; Exercise; Extremities; Forelimb; Gait; Galliformes; Hindlimb; Isometric Contraction; Locomotion; Lower Extremity; Motor Activity; Movement; Muscle Contraction; Muscle Fibers, Skeletal; Muscle Spindles; Muscle, Skeletal; Nonlinear Dynamics; Physics; Poaceae; Robotic Surgical Procedures; Robotics; Running; Sand; Stress, Mechanical; Swimming; Temperature; Tendons; Torque; Trees; Virtual Reality; Viscosity; Walking</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ewell, Laura Ann</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Acetamides; Action Potentials; Brain Injuries; Cerebellum; Dendrites; Dentate Gyrus; Dystonia; Epilepsy; GTP-Binding Proteins; Hippocampus; Neurons; Purkinje Cells; Pyramidal Cells; Reproducibility of Results; Seizures; Software; User-Computer Interface</t>
-        </is>
-      </c>
+          <t>Baker, Nicholas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gall, Christine M</t>
+          <t>Bardwell, Lee</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Arachidonic Acids; CA1 Region, Hippocampal; CA3 Region, Hippocampal; Calcium; Dentate Gyrus; Dizocilpine Maleate; Electric Stimulation; Endocannabinoids; Entorhinal Cortex; Estrogen Receptor alpha; Excitatory Postsynaptic Potentials; Glycerides; Hippocampus; Long-Term Potentiation; Memory; Memory, Episodic; Microglia; Nerve Net; Neural Pathways; Neuronal Plasticity; Perforant Pathway; Phenols; Piperidines; Rats, Sprague-Dawley; Receptors, N-Methyl-D-Aspartate; Rodentia; Sex Characteristics; Sex Factors; Signal Transduction; Spatial Memory; Synapses; Theta Rhythm; gamma-Aminobutyric Acid</t>
+          <t>Alleles; Binding Sites; CDC2 Protein Kinase; Cadmium; Caenorhabditis elegans; Caenorhabditis elegans Proteins; Cdc20 Proteins; Cell Line, Tumor; Cells, Cultured; Child; Clinical Relevance; Comprehension; Congenital Hypothyroidism; Conserved Sequence; Cyclin B; Cyclin B1; Cyclin B2; DNA; DNA-Binding Proteins; Developmental Disabilities; Diabetes Mellitus; Embryo, Nonmammalian; Evidence Gaps; Extracellular Signal-Regulated MAP Kinases; Gene Expression Regulation; Greig cephalopolysyndactyly syndrome; HEK293 Cells; HeLa Cells; Hedgehog Proteins; Hippo Signaling Pathway; Homeostasis; Inactivation, Metabolic; Infant, Newborn; Ligands; MAP Kinase Signaling System; Mitogen-Activated Protein Kinase 1; Mitogen-Activated Protein Kinases; Mitosis; Mutation; Neoplasms; Nuclear Matrix-Associated Proteins; Phosphatidylinositol 3-Kinases; Phosphorylation; Protein Binding; Protein Kinases; Protein Serine-Threonine Kinases; Repressor Proteins; Saccharomyces cerevisiae; Schizophrenia; Signal Transduction; Stress, Physiological; Transcription Factor MTF-1; Transcription Factors; Transcription, Genetic; Transcriptional Activation; Tumor Suppressor Proteins; Zinc; Zinc Finger Protein GLI1; ras GTPase-Activating Proteins</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hunt, Robert Francis</t>
+          <t>Blumberg, Bruce</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Acyltransferases; Brain; Brain Injuries; Brain Injuries, Traumatic; Brain Mapping; Endocytosis; Glycosylation; Hippocampus; Homing Behavior; Interneurons; Long-Term Potentiation; Membrane Proteins; Memory; Memory Disorders; Nerve Net; Neurogenesis; Neurons; Peptides; Pinocytosis; Protein Kinase C; Receptors, AMPA; Seizures; Sex Characteristics; Synapses; Synaptic Transmission</t>
+          <t>3T3-L1 Cells; Adipocytes; Adipogenesis; Adipose Tissue; Adolescent; Autism Spectrum Disorder; Autistic Disorder; Benzamides; Caenorhabditis elegans; Cannabidiol; Cell Differentiation; Cell Line, Transformed; Child; Child, Preschool; Chromatin; Consensus; DNA; DNA Methylation; Diabetes Mellitus; Diabetes Mellitus, Type 2; Diet, Fat-Restricted; Diet, High-Fat; Diet, Western; Dietary Fats; Drinking Water; Endocrine Disruptors; Energy Metabolism; Environmental Exposure; Epidemiologic Studies; Epigenesis, Genetic; Epigenomics; Fasting; Flutamide; Genetic Predisposition to Disease; Genetics; Germ Cells; Histones; Inheritance Patterns; Insulin Resistance; Insulysin; Leptin; Lipids; Lipogenesis; Lipolysis; Liver; Mesenchymal Stem Cells; Metabolic Diseases; Methylation; MicroRNAs; Multiomics; Mutation; Noncommunicable Diseases; Obesity; Oxazoles; PPAR gamma; Pandemics; Pesticides; Phenotype; Pregnancy; Pregnane X Receptor; Prenatal Exposure Delayed Effects; Pyridines; Receptors, Cytoplasmic and Nuclear; Receptors, Steroid; Retinoid X Receptors; Rosiglitazone; Spermatozoa; Trialkyltin Compounds; Weight Gain; Xenobiotics; Zebrafish; vinclozolin</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Igarashi, Kei</t>
+          <t>Blurton-Jones, Mathew</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alzheimer Disease; Brain; Cognition; Entorhinal Cortex; Hippocampus; Learning; Memory; Neurofibrillary Tangles; Neurons; Olfactory Bulb; Olfactory Cortex; Olfactory Pathways; Olfactory Perception; Optogenetics; Prefrontal Cortex; Punishment; Reward; Smell</t>
+          <t>Acetylation; Administration, Inhalation; Aged; Aging; Alleles; Alzheimer Disease; Amino Acid Sequence; Amyloid beta-Peptides; Amyloidogenic Proteins; Amyloidosis; Antibodies; Antibodies, Monoclonal; Apolipoprotein E3; Apolipoprotein E4; Apolipoproteins E; Astrocytes; Autoimmune Diseases; Biomarkers; Blood-Brain Barrier; Brain; Brain Neoplasms; Breast Neoplasms; C9orf72 Protein; Calcinosis; Calcium; Calcium Signaling; Caregivers; Cell Death; Cell Movement; Cell- and Tissue-Based Therapy; Cells, Cultured; Central Nervous System; Chemokines; Chemotaxis; Chimera; Cholesterol; Chromatin; Chromatin Immunoprecipitation Sequencing; Coculture Techniques; Cognition; Cognitive Dysfunction; Complement C1q; Cyclic AMP; Cytokines; Dementia; Diabetes Mellitus; Diet; Disease Progression; Drug Development; Endoplasmic Reticulum; Endosomal Sorting Complexes Required for Transport; Endothelial Cells; Epigenesis, Genetic; Ferroptosis; Frontal Lobe; Frontotemporal Dementia; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genome-Wide Association Study; Genomics; Gliosis; Grassland; Hepatitis A Virus Cellular Receptor 2; Hippocampus; Histones; Homeostasis; Housing Quality; Immunohistochemistry; Immunotherapy; Induced Pluripotent Stem Cells; Infant; Infant, Newborn; Inflammation; Inflammation Mediators; Injections, Intraperitoneal; Interferon-gamma; Interferons; Interleukin-17; Interleukin-1beta; Intermediate Filaments; Intracranial Hemorrhages; Isothiocyanates; Leukoencephalopathies; Lipid Metabolism; Lipid Peroxidation; Lipopolysaccharides; Liver Diseases; Lysosomes; Macrophage Colony-Stimulating Factor; Macrophages; Microglia; Microscopy; Microtubules; Mitochondria; Monocytes; Multiple Sclerosis; Mutation; Mycoses; Myelin Basic Protein; Myelin Sheath; Myeloid Cells; NF-E2-Related Factor 2; Neprilysin; Nervous System Diseases; Nervous System Malformations; Neurites; Neurodegenerative Diseases; Neurofibrillary Tangles; Neuroinflammatory Diseases; Neurons; Neutrophils; Nucleotide Motifs; Obesity; Organelles; Organic Chemicals; Organoids; Outcome Assessment, Health Care; Oxidative Stress; Parkinson Disease; Patient Advocacy; Phagocytosis; Phenotype; Phosphorylation; Physicians; Pick Disease of the Brain; Plaque, Amyloid; Pluripotent Stem Cells; Presenilin-1; Prosencephalon; Protein Isoforms; Proteomics; Quantitative Trait Loci; RNA; Rare Diseases; Receptor, Macrophage Colony-Stimulating Factor; Receptor, Transforming Growth Factor-beta Type II; Receptors, Chimeric Antigen; Receptors, Granulocyte-Macrophage Colony-Stimulating Factor; Research Report; Resilience, Psychological; Risk Factors; Schizophrenia; Sequence Analysis, RNA; Sex Factors; Signal Transduction; Single-Cell Gene Expression Analysis; Smad2 Protein; Social Cohesion; Stem Cell Research; Stem Cells; Sulfoxides; Synaptophysin; Tauopathies; Thalamus; Tissue Distribution; Toll-Like Receptor 4; Transcription Factors; Transcriptional Activation; Transcriptome; Transforming Growth Factor beta; Transplantation, Heterologous; Treatment Outcome; Twins, Monozygotic; Weaning; White Matter; Whole Genome Sequencing; Xenon; anti-synaptophysin; heparin proteoglycan; peptide A; tau Proteins</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lyon, David Christian</t>
+          <t>Bracken, Matthew</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aging; Brain; Brain Injuries, Traumatic; Brain Mapping; CRISPR-Cas Systems; Cell-Penetrating Peptides; Ceramidases; Chromatin; DNA; DNA Mutational Analysis; Electrophysiological Phenomena; Evoked Potentials, Visual; Eye Proteins; Gene Editing; Glaucoma; HEK293 Cells; Interneurons; Intraocular Pressure; Leber Congenital Amaurosis; Lipids; Liposomes; Mice, Mutant Strains; Mutation; Nanoparticles; Neurons; Receptors, Adiponectin; Retinal Cone Photoreceptor Cells; Retinal Degeneration; Retinal Diseases; Retinal Ganglion Cells; Retinitis Pigmentosa; Rhodopsin; Ribonucleoproteins; cis-trans-Isomerases</t>
+          <t>Alaska; Ammonium Compounds; Biodiversity; Biomass; California; Carbon Dioxide; Climate Change; Conservation of Natural Resources; Curriculum; Ecological and Environmental Phenomena; Ecosystem; Extinction, Biological; Food Chain; Hydrogen-Ion Concentration; Kelp; Macrocystis; Marine Biology; Mollusca; Nitrates; Nitrogen; Oceans and Seas; Oxygen; Physiological Phenomena; Portugal; Seawater; Seaweed; Urea</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Piomelli, Daniele</t>
+          <t>Briscoe, Adriana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Abdominal Pain; Adipocytes; Adiposity; Administration, Inhalation; Adolescent; Age Factors; Aged; Amides; Amidohydrolases; Analgesics; Anemia, Sickle Cell; Anti-Inflammatory Agents; Anxiety; Arachidonic Acids; Avoidance Learning; Azetidines; Behavior, Animal; Benzamides; Biomarkers; Brain; Cannabidiol; Cannabinoid Receptor Agonists; Cannabinoids; Cannabis; Carbamates; Carrier Proteins; Case-Control Studies; Child; Corticosterone; Dentate Gyrus; Dose-Response Relationship, Drug; Dronabinol; Endocannabinoids; Energy Intake; Enzyme Inhibitors; Ethanolamines; Extracellular Vesicles; Fatty Liver; Fructose; Ganglia, Spinal; Gelatin; Glycerides; Hallucinogens; Hippocampus; Homeostasis; Hyperalgesia; Hypothermia; Inflammation; Ligands; Lipids; Lipogenesis; Liver; Long-Term Potentiation; Memory, Episodic; Microglia; Monoacylglycerol Lipases; Monocytes; Monoglycerides; Neurons; Neuroprotective Agents; Non-alcoholic Fatty Liver Disease; Obesity; Oleic Acids; PPAR alpha; Pain; Palmitic Acids; Pancreatitis; Pancreatitis, Chronic; Perforant Pathway; Persian Gulf Syndrome; Polyunsaturated Alkamides; Prefrontal Cortex; Prospective Studies; Proteomics; Rats, Sprague-Dawley; Receptor, Cannabinoid, CB1; Receptors, Cannabinoid; Reflex, Startle; Signal Transduction; Social Behavior; Social Defeat; Stress, Psychological; Synaptic Transmission; Virus Diseases; Zika Virus; Zika Virus Infection; p38 Mitogen-Activated Protein Kinases</t>
+          <t>American Indian or Alaska Native; Antibody Specificity; Bees; Binding Sites; Biological Mimicry; Blotting, Western; Butterflies; Carrier Proteins; Central Nervous System; Chromosomes; Clustered Regularly Interspaced Short Palindromic Repeats; Colombia; Color; Color Vision; Communication; Costa Rica; Crystallization; Drosophila melanogaster; Ecology; Ecosystem; Electrophysiology; Evolution, Molecular; Eye; Farms; Forests; Gardening; Gene Duplication; Gene Editing; Gene Expression Profiling; Genomics; Guyana; Heating; Heredity; Immunohistochemistry; In Situ Hybridization; Insecta; Iridescence; Mating Preference, Animal; Mexican Americans; Microscopy, Confocal; Opsins; Perception; Photoreceptor Cells; Phylogeny; Pigmentation; Pupa; RNA, Messenger; RNA-Seq; Reproduction; Retina; Retinal Pigments; Rhodopsin; Rod Opsins; Sex Characteristics; Sexual Behavior, Animal; Sexual Selection; Technology; Transcriptome; Translocation, Genetic; Trees; Ultraviolet Rays; Wings, Animal; Writing; long-wavelength opsin; ommochrome; short-wavelength opsin</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Reinkensmeyer, David J</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Aged; Algorithms; Arm; Biomechanical Phenomena; Brain-Computer Interfaces; Chronic Disease; Cross-Over Studies; Delivery of Health Care; Electric Stimulation Therapy; Entropy; Feasibility Studies; Forearm; Gait; Gait Disorders, Neurologic; Hand; Information Dissemination; Learning; Movement; Muscle Spasticity; Persons with Disabilities; Posture; Proprioception; Recovery of Function; Rehabilitation Research; Robotics; Shoulder; Single-Blind Method; Spinal Cord Injuries; Stroke; Stroke Rehabilitation; Translational Research, Biomedical; Treatment Outcome; Upper Extremity; Wearable Electronic Devices; Wheelchairs; Wrist</t>
-        </is>
-      </c>
+          <t>Burley, Nancy</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Steward, Oswald</t>
+          <t>Busciglio, Jorge</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Axons; Biopsy; Cell Body; Cervical Cord; Dendrites; Dentate Gyrus; Electroencephalography; Epilepsy; Exercise; Forelimb; Gene Deletion; Genetic Therapy; Genetic Vectors; Hippocampus; Luciferases; Luminescent Measurements; Mossy Fibers, Hippocampal; Motor Endplate; Motor Neurons; Muscles; Nerve Regeneration; Nerve Transfer; Neural Pathways; Neurons; PTEN Phosphohydrolase; Pyramidal Tracts; RNA; RNA, Small Interfering; Rats, Sprague-Dawley; Recovery of Function; Sex Characteristics; Shoulder; Spinal Cord; Spinal Cord Injuries</t>
+          <t>Aged; Aging; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Aneuploidy; Anhedonia; Antiviral Agents; Anxiety; Apathy; Atrophy; Basal Forebrain; Biomarkers; Biomedical Research; Blood-Brain Barrier; Body Fluids; Brain; COVID-19; Cells, Cultured; Cellular Senescence; Cerebral Cortex; Checklist; Child; Cholinergic Agents; Chromosomes, Human, Pair 21; Cognition; Cognitive Dysfunction; Defense Mechanisms; Delusions; Depression; Diagnostic Errors; Down Syndrome; Extracellular Vesicles; Fetus; Gene Expression Profiling; Guanosine Triphosphate; Hallucinations; Human Genetics; Incidence; Inflammation; Interferons; Leadership; Live Birth; Longitudinal Studies; Membrane Proteins; Memory Disorders; Microglia; Mitochondria; Models, Genetic; Molecular Biology; Mutation; Nerve Degeneration; Nerve Growth Factor; Nervous System Diseases; Neurodegenerative Diseases; Neurofibrillary Tangles; Neuroinflammatory Diseases; Neurons; New York; Oxidative Stress; Peptides; Pharmaceutical Preparations; Plaque, Amyloid; Precision Medicine; Pregnancy; Probability; Protein Precursors; Proteomics; Psychiatrists; Quality of Life; RNA, Viral; SARS-CoV-2; Schizophrenia; Serine Endopeptidases; Spain; Spinal Puncture; Tetraspanin 28; Trisomy; United States Food and Drug Administration; Vulnerable Populations; tau Proteins</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Watanabe Kuwata, Momoko</t>
+          <t>Cahill, Larry</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Administration, Oral; Anticoagulants; Atrial Fibrillation; Austria; COVID-19; Cell Communication; Choroid Plexus; Cross-Sectional Studies; Embryonic Development; Gene Expression Profiling; Islets of Langerhans; Migraine Disorders; Multiple Sclerosis; Neuromyelitis Optica; Registries; Retrospective Studies; Risk Factors; SARS-CoV-2; Sequence Analysis, RNA; Single-Cell Analysis; Stroke; Switzerland; Transcriptome</t>
+          <t>Administration, Intranasal; Double-Blind Method; Emotions; Estradiol; Magnetic Resonance Imaging; Memory, Episodic; Oxytocin; Sex Characteristics</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Xu, Xiangmin</t>
+          <t>Cho, Ken</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Adenosine; Aged; Aged, 80 and over; Algorithms; Alzheimer Disease; Blood-Brain Barrier; Brain; Brain Mapping; Capsid; Carbon; Chromosomes, Plant; Cognitive Dysfunction; Cohort Studies; Crops, Agricultural; Deep Learning; Dependovirus; Diploidy; Disease Progression; Electrical Equipment and Supplies; Endothelial Cells; Enhancer Elements, Genetic; Epigenesis, Genetic; Epigenomics; Feasibility Studies; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Plant; Genes, Plant; Genetic Variation; Genetic Vectors; Genetics, Population; Genome, Plant; Genomics; Geologic Sediments; Groundwater; Heterozygote; Hippocampus; Homozygote; Image Processing, Computer-Assisted; Imaging, Three-Dimensional; Induced Pluripotent Stem Cells; Longitudinal Studies; Magnetic Resonance Imaging; Microbiota; Microglia; Monte Carlo Method; Neural Networks, Computer; Neuroimaging; Neurons; Neuropsychological Tests; Plant Breeding; Pollination; Primary Visual Cortex; Prognosis; Promoter Regions, Genetic; Prosencephalon; RNA, Antisense; RNA, Messenger; Radiation Dosage; Radiotherapy Dosage; Radiotherapy Planning, Computer-Assisted; Reproduction; Transcriptome; Transduction, Genetic; Vision, Ocular; Visual Cortex; Vitis; Water Microbiology; tau Proteins</t>
+          <t>Acetylation; Adolescent; Aged; Aged, 80 and over; Biological Phenomena; Blastocyst; Blastula; CRISPR-Cas Systems; Caenorhabditis elegans; Caregivers; Case-Control Studies; Cell Differentiation; Cell Lineage; Central Nervous System; Chromatin; Computational Biology; Congenital Abnormalities; Cryoelectron Microscopy; Curriculum; Depression; Developmental Biology; Ectoderm; Educational Measurement; Embryo, Nonmammalian; Embryonic Development; Embryonic Structures; Endoderm; Endodermal Sinus Tumor; Epidermis; Epigenesis, Genetic; Epigenome; Epigenomics; Fertilization; Fetus; Forkhead Transcription Factors; Gastrula; Gastrulation; Gene Expression; Gene Expression Profiling; Gene Expression Regulation, Developmental; Gene Regulatory Networks; Genes, Developmental; Genome; Genomics; Germ Layers; Health Services Accessibility; Healthcare Disparities; Heart Failure; Histone Deacetylase 1; Histone Deacetylase 2; Histone Deacetylases; Histones; Insurance Coverage; International Cooperation; Kidney Failure, Chronic; Kidney Transplantation; Laboratories; Learning; Logistic Models; Lysine; Medicaid; Mesoderm; Molecular Biology; Multiomics; Mutation; N-Myc Proto-Oncogene Protein; Nervous System; Neural Tube; Neurulation; Nutrients; Ovarian Neoplasms; Phenotype; Pregnancy Complications; Preimplantation Diagnosis; Prodromal Symptoms; Prospective Studies; Proteomics; Psychotic Disorders; RNA; Regenerative Medicine; Risk Assessment; Risk Factors; SOXB1 Transcription Factors; Schizophrenia; Self Care; Sequence Analysis, RNA; Signal Transduction; Socioeconomic Disparities in Health; Socioeconomic Factors; Stem Cell Research; Stem Cells; Thinking; Transcription Factors; Transcription, Genetic; Uterus; Xenopus; Xenopus Proteins; Xenopus laevis; Young Adult; Zygote; animal cap</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Buisson, Remi</t>
+          <t>Chrastil, Elizabeth</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2',5'-Oligoadenylate Synthetase; Adenosine Deaminase; Antineoplastic Agents; Ataxia Telangiectasia Mutated Proteins; CD8-Positive T-Lymphocytes; CRISPR-Cas Systems; Carcinoma, Squamous Cell; Cell Differentiation; Cell Line, Tumor; Cell Nucleus; Cell Proliferation; Chromatin; Cyclin D1; Cytidine Deaminase; Cytoplasmic Granules; Cytosine; DNA; DNA Breaks, Double-Stranded; DNA Damage; DNA Helicases; DNA Replication; DNA, Single-Stranded; DNA-(Apurinic or Apyrimidinic Site) Lyase; DNA-Binding Proteins; Deamination; Desmoplastic Small Round Cell Tumor; Drug Resistance, Neoplasm; Endoribonucleases; Enzyme Activation; Enzyme Assays; Gene Editing; Gene Expression Regulation; Gene Expression Regulation, Neoplastic; Gene Knockout Techniques; Gene Regulatory Networks; Genomic Instability; HEK293 Cells; HMGB2 Protein; HeLa Cells; High-Throughput Nucleotide Sequencing; Immunity, Innate; Interferon Regulatory Factor-2; Interleukin-1 Receptor-Associated Kinases; Intrinsically Disordered Proteins; Keratinocytes; Lung Neoplasms; Minor Histocompatibility Antigens; Molecular Targeted Therapy; Mutation; NF-kappa B; Neoplasms; Nucleotide Motifs; Oncogene Proteins, Fusion; Persistent Infection; Piperazines; Poly (ADP-Ribose) Polymerase-1; Poly-ADP-Ribose Binding Proteins; Protein Binding; Protein Isoforms; Protein Kinases; Proteins; Pyridines; Pyrimidines; RNA 3' End Processing; RNA Helicases; RNA Polymerase II; RNA Precursors; RNA Processing, Post-Transcriptional; RNA Recognition Motif Proteins; RNA Splicing; RNA Stability; RNA, Double-Stranded; RNA, Messenger; RNA, Mitochondrial; RNA, Viral; RNA-Binding Protein EWS; RNA-Binding Proteins; STAT2 Transcription Factor; Sequence Analysis, DNA; Signal Transduction; Stress Granules; Transcription Factors; Tumor Suppressor Protein p53; Virus Diseases; Virus Replication; WT1 Proteins; Xenograft Model Antitumor Assays; eIF-2 Kinase</t>
+          <t>Adolescent; Alzheimer Disease; Artificial Intelligence; Brain; Cerebral Cortex; Cognition; Cognitive Neuroscience; Cognitive Science; Computer Simulation; Confusion; Depression; Diffusion Magnetic Resonance Imaging; Exploratory Behavior; Figural Aftereffect; Functional Neuroimaging; Gray Matter; Gyrus Cinguli; Head; Hippocampus; Individuality; Interpersonal Relations; Judgment; Learning; Magnetic Resonance Imaging; Maze Learning; Memory; Memory, Episodic; Menopause; Motion; Motion Perception; Neuroimaging; Neurons; Organ Size; Parietal Lobe; Pregnancy; Sex Factors; Spatial Learning; Spatial Memory; Spatial Navigation; Temporal Lobe; Theta Rhythm; Virtual Reality; White Matter; Young Adult</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dai, Xing</t>
+          <t>Cinquin, Olivier</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3T3 Cells; Age Distribution; Aged; Aged, 80 and over; Amphiregulin; Antibodies, Monoclonal, Humanized; Axin Protein; Basic Helix-Loop-Helix Transcription Factors; Biomarkers; Blindness; Brain; Breast; CD8-Positive T-Lymphocytes; Cardiovascular Diseases; Cataract; Cell Communication; Cell Differentiation; Cell Lineage; Cell Proliferation; Chromatin; Cognition; Cognitive Dysfunction; Cognitive Training; DNA-Binding Proteins; Dermatitis, Atopic; Endothelial Cells; Environmental Exposure; Epidermal Cells; Epidermis; Epithelial Cells; Epithelial-Mesenchymal Transition; Fatty Liver; Fibroblasts; Fibrosis; Fructose; Gene Expression Regulation; Global Burden of Disease; Global Health; HEK293 Cells; HaCaT Cells; Homeostasis; Imiquimod; Immunotherapy; Inflammation; Interleukin-17; Intracellular Signaling Peptides and Proteins; Keratinocytes; Lipogenesis; Liver; Macrophages; Macular Degeneration; Mammary Glands, Animal; Myocardial Ischemia; Non-alcoholic Fatty Liver Disease; Occupations; Persons with Visual Disabilities; Pharmaceutical Preparations; Prevalence; Prostatic Neoplasms; Psoriasis; Quality-Adjusted Life Years; RNA; Receptors, Aryl Hydrocarbon; Risk Assessment; Risk Factors; Sex Distribution; Signal Transduction; Single-Cell Analysis; Skin; Smoking; Stem Cells; T-Lymphocytes, Cytotoxic; Transcription Factors; Tumor Microenvironment; Universal Health Insurance; Vision, Low; Visual Acuity; White Matter; Wnt Signaling Pathway; Workforce; Wound Healing; Zinc Finger E-box-Binding Homeobox 1</t>
+          <t>Aging; Artificial Intelligence; Cell Line; Chromatin Immunoprecipitation; Computational Biology; Consensus; DNA Damage; Databases, Factual; Generative Artificial Intelligence; Genomics; Language; Large Language Models; Liquid Biopsy; Medicine; Mutation; Neoplasms; Noninvasive Prenatal Testing; Peer Review; Programming Languages; Software; Systems Biology</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Donovan, Peter J</t>
+          <t>Cocco, Melanie</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cell Line; Chromatin; Human Embryonic Stem Cells; Protein Binding; Transcription Factor 7-Like 1 Protein; Wnt Signaling Pathway</t>
+          <t>Amino Acids; Amino Sugars; Anemia, Sickle Cell; Arabidopsis; Bacteria; Basic Helix-Loop-Helix Transcription Factors; Biological Products; Biological Science Disciplines; Brain; Cannabidiol; Cannabinoids; Cannabis; Carcinogens; Cell Adhesion; Cell Membrane; Cellular Senescence; Cerebral Hemorrhage; Chromatography, High Pressure Liquid; DNA, Satellite; Dronabinol; Drug Development; Drug Resistance, Microbial; Employment; Epigenesis, Genetic; Erythrocytes; Ethanol; Fertilizers; Flavonoids; Furunculosis; Gas Chromatography-Mass Spectrometry; Genomics; Genotype; Heinz Bodies; Helium; Hemoglobinopathies; Hemoglobins; Herbicides; Hispanic or Latino; Hydrogen; Hydrogen-Ion Concentration; Information Sources; Isotopes; Kinetics; Ligands; Lipids; Magnetic Resonance Imaging; Magnetic Resonance Spectroscopy; Magnets; Marijuana Use; Medical Marijuana; Membrane Proteins; Metabolome; Microbiota; Molecular Dynamics Simulation; Molecular Structure; Mutation; Myoglobin; Natural Science Disciplines; Neoplasms; Oryza; Oxides; Oxygen; Pesticides; Plant Extracts; Protein Binding; Protein Interaction Maps; Proteins; Recombinant Proteins; Seasons; Seeds; Sugars; Temperature; Terpenes; Water; beta-myrcene; caryophyllene oxide; nan; voxelotor</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jang, Cholsoon</t>
+          <t>Cohen-Cory, Susana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ADP-ribosyl Cyclase 1; ATP Citrate (pro-S)-Lyase; Acetate-CoA Ligase; Acetates; Acetic Acid; Acetylation; Adenosine; Adipocytes; Adipose Tissue, Brown; Adolescent; Aging; Allosteric Regulation; Alternative Splicing; Amino Acids, Branched-Chain; Anti-Bacterial Agents; Antigens, CD; Antineoplastic Agents, Hormonal; Bacteria; Biomarkers; Biomedical Research; Body Mass Index; Body Weight; Brain; Brain Stem; Breast Neoplasms; CD8-Positive T-Lymphocytes; Cadherins; Calcium; Calcium Channels; Calcium Signaling; Cardiovascular Diseases; Carrier Proteins; Cell Differentiation; Cell Line, Tumor; Cell Movement; Cell Proliferation; Cellular Senescence; Child; Citric Acid; Citric Acid Cycle; DNA-Binding Proteins; Disease Progression; Down-Regulation; Eating; Elasticity Imaging Techniques; Energy Metabolism; Epigenesis, Genetic; Epithelial-Mesenchymal Transition; Exercise; Fatty Acids; Fatty Liver; Fructokinases; Fructose; Gastrointestinal Microbiome; Gene Knockdown Techniques; Germ-Free Life; Glucose; Glycolysis; Hematopoietic Stem Cells; Hepatocytes; Hispanic or Latino; Histone Acetyltransferases; Histone Code; Histones; Homeostasis; Huntingtin Protein; Huntington Disease; Hydrolases; Hydrolysis; Insulin; Kidney; Kynurenine; Lactic Acid; Lipidomics; Lipogenesis; Lipolysis; Liver; Liver Cirrhosis; Membrane Glycoproteins; Metabolomics; Methyltransferases; Mice, Nude; Mitochondria; NAD; Neoplasm Metastasis; Non-alcoholic Fatty Liver Disease; Nutrients; Obesity; Oxidation-Reduction; Oxidative Stress; Pediatric Obesity; Phosphoglycerate Dehydrogenase; Predictive Value of Tests; Protein Kinases; Proteomics; RNA Methylation; RNA Splicing; RNA, Ribosomal, 16S; RNA, Small Interfering; Receptors, G-Protein-Coupled; Secondary Metabolism; Serine; Signal Transduction; Stress, Physiological; Tamoxifen; Taurine; Thermogenesis; Tryptophan; Weight Loss</t>
+          <t>Amphibians; Axons; Cell Adhesion Molecules; Cell Tracking; Dendrites; Neurogenesis; Retina; Superior Colliculi; Synapses; Visual Pathways; Xenopus Proteins; Xenopus laevis</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kaiser, Peter</t>
+          <t>Connor, Kwasi</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Adaptor Proteins, Signal Transducing; Alternative Splicing; Antineoplastic Agents; Autoantigens; Autophagy; Bevacizumab; Biosimilar Pharmaceuticals; CRISPR-Cas Systems; Cadmium; Cell Cycle Proteins; Cell Line; Cell Line, Tumor; Cell Proliferation; Centromere; Centromere Protein A; Chromatin; Chromosomal Instability; Chromosomal Proteins, Non-Histone; Circadian Clocks; Circadian Rhythm; Consensus; Cullin Proteins; DNA; DNA Damage; DNA Modification Methylases; DNA Repair; DNA Repair Enzymes; DNA-Binding Proteins; Europe; F-Box Proteins; Geographic Atrophy; Glycogen Synthase Kinase 3; Histones; Homocysteine; Huntingtin Protein; Huntington Disease; Ligands; Liver; Lysosomes; Methionine; Methylation; Mitochondria; Mitochondrial Proteins; Mutation; Neoplasms; Nucleocytoplasmic Transport Proteins; Nutrients; Optometrists; Peptides; Phosphorylation; Precision Medicine; Protein Binding; Protein Domains; Protein-Arginine N-Methyltransferases; Proteolysis; Proto-Oncogene Proteins c-mdm2; Pyrimidines; RNA Splicing; RNA-Binding Proteins; Retina; Retinal Diseases; S-Phase Kinase-Associated Proteins; SKP Cullin F-Box Protein Ligases; Saccharomyces cerevisiae; Saccharomyces cerevisiae Proteins; Stress, Physiological; Sumoylation; Suprachiasmatic Nucleus; Surveys and Questionnaires; Tryptophan; Tumor Suppressor Protein p53; Tumor Suppressor Proteins; Ubiquitin; Ubiquitin-Protein Ligase Complexes; Ubiquitin-Protein Ligases; Ubiquitination; Valosin Containing Protein; Vesicular Transport Proteins; beta-Transducin Repeat-Containing Proteins</t>
+          <t>Academies and Institutes; Acclimatization; Amylases; Anaerobiosis; Cellulase; Cold Temperature; Diet; Ecosystem; Gene Expression; Heat-Shock Response; Homeostasis; Hot Temperature; Metabolome; Metabolomics; Mytilus; Oxygen; Respiration; Temperature</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kessenbrock, Kai</t>
+          <t>Cramer, Karina</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3T3 Cells; Aging; Axin Protein; B7-H1 Antigen; BRCA1 Protein; BRCA2 Protein; Breast; Breast Neoplasms; CD4 Antigens; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Carcinogenesis; Cell Communication; Cell Differentiation; Cell Line, Tumor; Cell Lineage; Cell Proliferation; Cell Transformation, Neoplastic; Cellular Reprogramming; Choroid Plexus; Chromatin; Circadian Clocks; Circadian Rhythm; Colorectal Neoplasms; Cryptochromes; Cytokines; Endogenous Retroviruses; Endothelial Cells; Epigenesis, Genetic; Epigenomics; Epithelial Cells; Epithelial-Mesenchymal Transition; Fibroblasts; Fibrosis; Forkhead Transcription Factors; Galectin 3; Gene Expression; Gene Expression Profiling; Genome-Wide Association Study; Genomics; Germ-Line Mutation; HEK293 Cells; Heterochromatin; Immune Checkpoint Inhibitors; Immune Tolerance; Immunity; Immunosuppression Therapy; Lymphocyte Activation; Macrophages; Mammary Glands, Human; Multiple Sclerosis; Muscle, Skeletal; Mutation; Myeloid-Derived Suppressor Cells; Neural Stem Cells; Organoids; Paclitaxel; Pluripotent Stem Cells; RNA, Nuclear; Signal Transduction; Single-Cell Analysis; Skin; Stem Cells; Stromal Cells; Supervised Machine Learning; T-Lymphocytes, Regulatory; Transcription Factors; Transcriptome; Triple Negative Breast Neoplasms; Tumor Microenvironment; Wnt Signaling Pathway; Wound Healing; Zinc Finger E-box-Binding Homeobox 1</t>
+          <t>Acoustics; Apoptosis; Astrocytes; Auditory Pathways; Axon Guidance; Axons; Biological Evolution; Brain; Brain Stem; Caspase 3; Caspases; Cell Death; Cochlear Nerve; Cysteine; Deafness; Dendrites; Embryonic Development; Endopeptidases; Evoked Potentials, Auditory, Brain Stem; Exosomes; Gene Expression Regulation; Gene Ontology; Hearing; Microglia; Myelin Sheath; Nervous System; Neurodevelopmental Disorders; Neuroglia; Neuronal Plasticity; Neurons; Oligodendroglia; Peptide Hydrolases; Phylogeny; Presynaptic Terminals; Proteomics; RNA, Long Noncoding; Synapses; Synaptic Transmission; Tandem Mass Spectrometry; Transcriptome; Trapezoid Body</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Li, Wei</t>
+          <t>Daley, Monica</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3' Untranslated Regions; Acute-Phase Proteins; Adolescent; Age of Onset; Aged; Aged, 80 and over; Algorithms; Alternative Splicing; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Anilides; Animals, Domestic; Bacteria; Bayes Theorem; Biomarkers, Tumor; Black or African American; Body Mass Index; Brain; Brain Neoplasms; C9orf72 Protein; Carbon; Carbon Cycle; Carcinoma, Non-Small-Cell Lung; Carrier Proteins; Cell Nucleus; Cell-Free Nucleic Acids; Child; Child, Preschool; Cohort Studies; Colorectal Neoplasms; Computational Biology; CpG Islands; DEAD-box RNA Helicases; DNA Copy Number Variations; DNA Methylation; DNA Repeat Expansion; DNA-Binding Proteins; Databases, Genetic; Disease; Ecosystem; Epigenesis, Genetic; Exome; Exome Sequencing; Exosome Multienzyme Ribonuclease Complex; False Positive Reactions; Frontotemporal Dementia; Gene Conversion; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Neoplastic; Genetic Predisposition to Disease; Genetic Testing; Genetic Variation; Genome, Human; Genome-Wide Association Study; Genomic Structural Variation; Genomics; Genotype; Germ Cells; Germ-Line Mutation; HEK293 Cells; Haplotypes; HeLa Cells; Hispanic or Latino; Imidazoles; Inflammation; Introns; Liver; Liver Cirrhosis; Lung Neoplasms; Membrane Glycoproteins; Multiomics; MutS Homolog 2 Protein; Neoplasms; Organ Specificity; Phenotype; Poly A; Polyadenylation; Polymorphism, Single Nucleotide; Progression-Free Survival; Protein Kinase Inhibitors; Protein-Tyrosine Kinases; Proto-Oncogene Proteins; Pyrazoles; Pyridazines; Quantitative Trait Loci; Quinolines; RNA Splice Sites; RNA Stability; RNA, Messenger; RNA, Nuclear; RNA-Seq; Ribonucleoprotein, U1 Small Nuclear; Segmental Duplications, Genomic; Sequence Analysis, DNA; Sequence Analysis, RNA; Soil; Soil Microbiology; Tandem Repeat Sequences; Transcriptome; Whole Genome Sequencing; tau Proteins</t>
+          <t>Air; Aircraft; Algorithms; Artificial Limbs; Avatar; Awards and Prizes; Basal Metabolism; Behavior, Animal; Bioengineering; Biomechanical Phenomena; Biomimetics; Biophysics; Biotechnology; Birds; Cognition; Communication; Computer Simulation; Connective Tissue; Conservation of Energy Resources; Dancing; Elasticity; Elastomers; Electromyography; Energy Metabolism; Environment; Exoskeleton Device; Extremities; Fellowships and Scholarships; Financial Management; Flight, Animal; Gait; Galliformes; Genomics; History, 20th Century; History, 21st Century; Information Dissemination; Interdisciplinary Research; Invertebrates; Isometric Contraction; Leadership; Leg; Locomotion; Mole Rats; Motion; Motor Activity; Movement; Muscle Contraction; Muscle Proteins; Muscle, Skeletal; Muscles; Neuromuscular Diseases; Prostheses and Implants; Rats, Sprague-Dawley; Resilience, Psychological; Robotic Surgical Procedures; Robotics; Running; Schools; Self-Help Devices; Social Cohesion; Social Media; Spinal Cord; Sports; Stress, Mechanical; Tendons; Vertebrates; Viscosity; Walking; Wearable Electronic Devices; Wings, Animal; X-Ray Diffraction</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Liu, Haoping</t>
+          <t>Donovan, Peter</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aedes; Agammaglobulinaemia Tyrosine Kinase; Aged; Aged, 80 and over; Amino Acids, Diamino; Aminopyridines; Angiotensin II; Angiotensin II Type 1 Receptor Blockers; Animals, Domestic; Antibodies, Viral; Apoptosis; Atrial Fibrillation; Australasia; Bed Occupancy; Benzimidazoles; Benzoates; Breast; Breast Neoplasms; CARD Signaling Adaptor Proteins; COVID-19; Calcium-Binding Proteins; Candida albicans; Cartilage, Articular; Caspase 8; Cell Line; Cerebral Hemorrhage; Chondrocytes; Claudin-5; Clinical Competence; Cohort Studies; Colitis; Conjunctiva; Critical Care; Diffusion Magnetic Resonance Imaging; Dry Eye Syndromes; Enzyme-Linked Immunosorbent Assay; Epithelium, Corneal; Fas-Associated Death Domain Protein; Fungal Proteins; Gene Expression Regulation; Genomics; Genotype; Goblet Cells; Health Personnel; Hypertension; Hypertrophy; Inflammasomes; Insect Proteins; Intensive Care Units; Interferon-gamma; Interleukin-1; Interleukin-13; Interleukin-1beta; Jurkat Cells; Lectins, C-Type; Leukemia, Lymphocytic, Chronic, B-Cell; Lymphoma, Large B-Cell, Diffuse; Macrophages; Magnetic Resonance Imaging; Mannose Receptor; Mannose-Binding Lectins; Membrane Potential, Mitochondrial; Microfilament Proteins; Microglia; Mosquito Vectors; Mucins; Myocytes, Cardiac; Observer Variation; Osteoarthritis; Osteoarthritis, Knee; Oviposition; Personal Protective Equipment; Phenotype; Pneumonia; Postoperative Care; Postoperative Complications; Protein Kinase Inhibitors; Proteomics; Pyrimidines; Pyrroles; RNA, Messenger; Real-Time Polymerase Chain Reaction; Receptors, Cell Surface; Receptors, Odorant; Receptors, Somatotropin; Respiration, Artificial; Respiratory Distress Syndrome; Retrospective Studies; Risk Factors; SARS-CoV-2; Sensitivity and Specificity; Seroepidemiologic Studies; Signal Transduction; Surveys and Questionnaires; Tears; Telmisartan; Tight Junctions; Transcriptome; Treatment Outcome; United Kingdom; Vision, Ocular; X-Ray Microtomography; Young Adult</t>
+          <t>Academia; Cell Line; Chromatin; Communication; DNA Transposable Elements; Developmental Biology; Dystonia; Embryology; Human Embryonic Stem Cells; Leadership; Mutation; Neurobiology; Neurodegenerative Diseases; Neurons; Parkinsonian Disorders; Personnel Selection; Protein Binding; Retroelements; Stem Cells; Transcription Factor 7-Like 1 Protein; Wnt Signaling Pathway</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marazzi, Ivan</t>
+          <t>Drayman, Nir</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adiposity; Alternative Splicing; Amyotrophic Lateral Sclerosis; Antineoplastic Agents; Antiviral Agents; Arginine; Ataxia Telangiectasia Mutated Proteins; B7-H1 Antigen; Blastocyst; CD8-Positive T-Lymphocytes; Carcinoma, Hepatocellular; Carrier Proteins; Cell Line; Cell Line, Tumor; Circadian Clocks; Circadian Rhythm; Clone Cells; Colorectal Neoplasms; Cytokines; DNA Damage; DNA Helicases; DNA Replication; DNA-Binding Proteins; Embryonic Development; Endogenous Retroviruses; Epigenesis, Genetic; Gene Expression; Gene Expression Profiling; Gene Knock-In Techniques; Heterochromatin; Homeostasis; Immune Checkpoint Inhibitors; Immune Tolerance; Immunity, Innate; Immunosuppression Therapy; Interleukin-1 Receptor-Associated Kinases; Ligands; Liver Neoplasms; Motor Neurons; Multifunctional Enzymes; Mutation; Myeloid-Derived Suppressor Cells; NF-kappa B; Proprotein Convertase 9; Protein Isoforms; Protein Kinase Inhibitors; Protein-Arginine N-Methyltransferases; Proteolysis; RNA Helicases; RNA Precursors; RNA Processing, Post-Transcriptional; RNA, Messenger; RNA, Nuclear; RNA, Viral; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Stress, Physiological; Transcription Factors; Transcriptome; Tumor Microenvironment; Ubiquitin-Protein Ligases; Viral Proteins; Viruses; Zygote; beta Catenin</t>
+          <t>Acyclovir; Alzheimer Disease; Antiviral Agents; Blister; COVID-19; CRISPR-Cas Systems; Cell Culture Techniques; Cell Line; Cell Nucleus; Chlorocebus aethiops; Cidofovir; Clustered Regularly Interspaced Short Palindromic Repeats; Clustered Regularly Interspaced Short Paradromic Repeats; Cytomegalovirus; DNA Replication; DNA, Viral; DNA-Directed DNA Polymerase; Decitabine; Drug Repositioning; Drug Resistance, Viral; Drug Synergism; Encephalitis, Herpes Simplex; Epidermis; Epithelial Cells; Eukaryotic Cells; Fibroblasts; Ficus; Foscarnet; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Viral; Genes, Tumor Suppressor; Genome, Viral; HEK293 Cells; Hepatitis C, Chronic; Herpes Labialis; Herpes Simplex; Herpesviridae; Herpesviridae Infections; Herpesvirus 1, Equid; Herpesvirus 1, Human; Homeodomain Proteins; Host Microbial Interactions; Host-Pathogen Interactions; Immunity, Innate; Immunocompromised Host; Infant, Newborn; Interferons; Kaposi Varicelliform Eruption; Keratinocytes; Keratitis, Herpetic; Life Cycle Stages; Machine Learning; Meningitis; Methylation; Microfluidics; Morbidity; Mutation; Myelodysplastic Syndromes; National Institute of Allergy and Infectious Diseases (U.S.); Open Reading Frames; Organoids; Orthomyxoviridae; Pandemics; Phenotype; Plasmids; Prevalence; Protein Interaction Mapping; RNA; SARS-CoV-2; Sequence Analysis, RNA; Serial Passage; Simplexvirus; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Skin Diseases, Viral; Surgery, Plastic; Systems Biology; Thymidine Kinase; Transcription, Genetic; Transferases; Ulcer; Vero Cells; Viral Proteins; Virology; Virus Diseases; Virus Replication; Viruses; Zygote</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Masri, Selma</t>
+          <t>Edinger, Aimee</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AICDA (Activation-Induced Cytidine Deaminase); ARNTL Transcription Factors; Adipocytes; Adipose Tissue; Adiposity; Ataxia Telangiectasia Mutated Proteins; B-Lymphocytes; B7-H1 Antigen; Biodiversity; CD8-Positive T-Lymphocytes; California; Cell Line, Tumor; Child; Chromatin; Circadian Clocks; Circadian Rhythm; Colorectal Neoplasms; Cross-Sectional Studies; Crowdsourcing; Cytidine Deaminase; Cytokines; DNA Breaks, Double-Stranded; DNA Damage; DNA Repair; DNA-Binding Proteins; Dopamine; Dysbiosis; Epidermal Cells; Epidermis; Fatty Acids, Nonesterified; Gastrointestinal Microbiome; Gene Expression Regulation; Genetic Loci; Glucose; Health Status Disparities; Hispanic or Latino; Homeostasis; Immune Checkpoint Inhibitors; Immune Tolerance; Immunity, Innate; Immunosuppression Therapy; Interleukin-1 Receptor-Associated Kinases; Intestinal Mucosa; Latin America; Levodopa; Lipidomics; Lipolysis; Liver; Motor Activity; Movement Disorders; Muscle, Skeletal; Mutation; Myeloid-Derived Suppressor Cells; NF-kappa B; Neoplasms; Oligopeptides; Perception; Permeability; Plants; Polycomb Repressive Complex 2; Precursor Cell Lymphoblastic Leukemia-Lymphoma; Proprotein Convertase 9; RNA Polymerase II; Receptors, Calcium-Sensing; Receptors, Cytokine; Signal Transduction; Single-Cell Analysis; Skin; Smoke; Socioeconomic Disparities in Health; Spatial Analysis; Tracheophyta; Transcription Factors; Transcription, Genetic; Translocation, Genetic; Triglycerides; Tumor Microenvironment; Wildfires</t>
+          <t>Alleles; Allergy and Immunology; Amiloride; Aminopyridines; Angiogenesis; Asialoglycoprotein Receptor; Autophagy; Base Pairing; Biological Transport; Bone Marrow; Breast Neoplasms; COVID-19; COVID-19 Vaccines; CRISPR-Cas Systems; Cell Death; Cell Line, Tumor; Cell Membrane; Cell Proliferation; Ceramides; Class III Phosphatidylinositol 3-Kinases; Codon, Nonsense; Codon, Terminator; Cultural Diversity; Cytoplasm; Cytosol; DNA Damage; DNA Repair; Diet, High-Fat; Drug Repositioning; Drug Resistance; Drug Resistance, Neoplasm; Endocytosis; Endosomes; ErbB Receptors; Feasibility Studies; Ficus; Fingolimod Hydrochloride; Genomics; HeLa Cells; Heart Rate; Hepatocytes; Heterocyclic Compounds, 3-Ring; Hot Temperature; Immune Checkpoint Inhibitors; Immunity; Immunosuppressive Agents; Intercellular Signaling Peptides and Proteins; Karyopherins; Kidney; Kidney Glomerulus; Ligands; Lipid Nanoparticles; Liver; Lung; Lung Neoplasms; Lysosomes; Metabolism; Minority Groups; Mitochondria; Morpholines; Motor Activity; Multiple Organ Failure; Mutation; Neoplasms; Nucleotides; Nutrients; Obesity; Oligonucleotides; Oligonucleotides, Antisense; Oncogenes; PTEN Phosphohydrolase; Phosphatidylinositol 3-Kinases; Phosphatidylinositols; Pinocytosis; Plague; Podocytes; Polypharmacology; Proof of Concept Study; Prostatic Neoplasms; Prostatic Neoplasms, Castration-Resistant; Protein Phosphatase 2; Proto-Oncogene Proteins B-raf; Proto-Oncogene Proteins c-akt; Proto-Oncogene Proteins p21(ras); Quality of Life; RNA, Small Interfering; Ribosomes; Saccharomyces cerevisiae; Schools; Sodium-Hydrogen Exchangers; Solubility; Sphingolipids; Sphingosine; Sphingosine-1-Phosphate Receptors; Transcription Factors; Tumor Microenvironment; Tumor Suppressor Protein p53; Vacuolar Proton-Translocating ATPases; Vacuoles; capivasertib; patisiran; sphingosine 1-phosphate</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ng, Stanley Wai Kwong</t>
+          <t>Emerson, J.J.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Acyltransferases; Bone Marrow Cells; Hepatic Stellate Cells; Hepatitis, Alcoholic; Leukemia, Myeloid, Acute; Ligands; Liver; Liver Cirrhosis; Recurrence</t>
+          <t>Alleles; Butterflies; Chromatin; Chromatin Assembly and Disassembly; Color Vision; Cost-Benefit Analysis; Drosophila Proteins; Drosophila melanogaster; Enhancer Elements, Genetic; Evolution, Molecular; Eye; Gene Duplication; Gene Frequency; Gene Regulatory Networks; Genes, Duplicate; Genome; Genome, Insect; Genome-Wide Association Study; Genomics; Genotype; Heterochromatin; High-Throughput Nucleotide Sequencing; Molecular Conformation; Mutation; Opsins; Pesticides; Phenotype; Plants; Repetitive Sequences, Nucleic Acid; Reverse Genetics; Rhodopsin; Selection, Genetic; Software; Telomere; Uncertainty; Whole Genome Sequencing</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Qiao, Feng</t>
+          <t>Eom, Dae Seok</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cell Cycle Proteins; Cell Line; Cell Line, Tumor; Chromatin; DNA; DNA Polymerase I; DNA Replication; Epigenesis, Genetic; Heterochromatin; Histone Chaperones; Histones; Mutation; Neoplasms; Protein Binding; Protein Domains; RNA Precursors; RNA Processing, Post-Transcriptional; RNA, Messenger; Schizosaccharomyces; Schizosaccharomyces pombe Proteins; Tumor Suppressor Protein p53</t>
+          <t>Cell Communication; Cell Surface Extensions; Circadian Rhythm; Connexins; Diffusion; Drosophila Proteins; Endoderm; Epidermis; Extracellular Vesicles; Homeostasis; Keratinocytes; Macrophages; Matrix Metalloproteinase 9; Muscles; Neoplasms; Paracrine Communication; Pigments, Biological; Pseudopodia; Signal Transduction; Zebrafish</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sandmeyer, Suzanne B</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>Faiola, Celia</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Acer; Acyclic Monoterpenes; Aerosols; Air Pollutants; Air Pollution; Alabama; Artemisia; Atmosphere; Bicyclic Monoterpenes; Carbon; Carbon Dioxide; Cities; Citizen Science; Climate Change; Colorado; Computer Simulation; Crops, Agricultural; Curriculum; Dehydration; Demography; Drought Resistance; Droughts; Ecological and Environmental Phenomena; Ecosystem; Endophytes; Environmental Justice; Environmental Monitoring; Environmental Pollutants; Forests; Fossil Fuels; Greenhouse Gases; Hot Temperature; Humans; Internship and Residency; Isomerism; Liquidambar; Literacy; Los Angeles; Metabolomics; Models, Chemical; Monoterpenes; Mortality, Premature; Mycorrhizae; Oxidation-Reduction; Oxygen; Ozone; Pacific Ocean; Photochemical Processes; Photosynthesis; Pilot Projects; Plant Leaves; Plant Physiological Phenomena; Plants; Poaceae; Prognosis; Quercus; Radiation Injuries; Remote Sensing Technology; Resilience, Psychological; Rhizosphere; Schools; Seasons; Sesquiterpenes; Social Conditions; Soil; Temperature; Terpenes; Trees; Volatile Organic Compounds; Wettability</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Seldin, Marcus Michael</t>
+          <t>Fortin, Norbert</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3T3-L1 Cells; Adaptation, Physiological; Adipocytes; Adipogenesis; Adipokines; Adiponectin; Adipose Tissue; Adipose Tissue, White; Adiposity; Aged; Aged, 80 and over; Aging; Antibodies, Neutralizing; Antibodies, Viral; Biomarkers; Biomedical Research; Biopsy; Blood Glucose; Blood Proteins; CRISPR-Cas Systems; Cardiovascular Diseases; Cell Differentiation; Circadian Clocks; Colorectal Neoplasms; DNA; DNA, Mitochondrial; Diabetes Mellitus, Type 2; Diet, High-Fat; Dimethylallyltranstransferase; Dysbiosis; Estrogen Receptor alpha; Exercise; Gastrointestinal Microbiome; Gene Editing; Gene Expression Regulation; Glucose; Heart Failure; High-Throughput Nucleotide Sequencing; Homeostasis; Immunoinformatics; Influenza Vaccines; Influenza, Human; Insulin; Insulin Resistance; Insulin Secretion; Intestinal Mucosa; Islets of Langerhans; Leptin; Lipid Metabolism; Liver; Macrophages; Magnetic Resonance Imaging; Metabolomics; Mitochondria; Mitochondria, Muscle; Muscle, Skeletal; Myocardium; Nucleotide Motifs; Obesity; Organoids; Overweight; Pancreas; Paracrine Communication; Permeability; Physical Conditioning, Animal; Promoter Regions, Genetic; Proteomics; RNA-Seq; Sequence Analysis, DNA; Sequence Analysis, RNA; Serpin E2; Sex Factors; Signal Transduction; Stroke Volume; Subcutaneous Fat; Subcutaneous Fat, Abdominal; Systems Biology; Th1 Cells; Transcription Factors; Transcription, Genetic; Vaccination; Vasodilation; Weight Loss</t>
+          <t>Academia; Acoustic Stimulation; Algorithms; Auditory Perception; Behavior; Brain; CA1 Region, Hippocampal; Cognition; Computers; Decision Making; Electrodes, Implanted; Electrophysiology; Government; Hippocampus; Leadership; Machine Learning; Memory; Memory, Episodic; Nerve Net; Odorants; Olfactory Perception; Planning Techniques; Prefrontal Cortex; Stereotaxic Techniques; Substance-Related Disorders; Technology; Theta Rhythm; Time; Time Factors</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Steele, Robert E</t>
+          <t>Fowler, Christie</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Animals, Genetically Modified; Biological Evolution; Biological Transport; Body Patterning; Cell Differentiation; Cell Lineage; Cnidaria; Ectoderm; Epithelial Cells; Genes, Homeobox; Hippo Signaling Pathway; Hydra; Morphogenesis; Nerve Net; Neurites; Neurons; Nutrients; Sea Anemones; Transcription, Genetic; Transcriptional Activation; Vitellogenesis; YAP-Signaling Proteins</t>
+          <t>Adenosine Triphosphate; Administration, Inhalation; Adolescent; Aerosols; Alcohol Drinking; Alcoholism; Analgesics, Opioid; Antineoplastic Agents; Apoptosis; Behavior; Biomedical Research; Brain; Brain-Derived Neurotrophic Factor; Cannabidiol; Cannabis; Cell Line, Tumor; Cell Movement; Cell Proliferation; Cerebellar Neoplasms; Child; Cholinergic Neurons; Chromatin; Clustered Regularly Interspaced Short Palindromic Repeats; Cocaine; Cognition; Consummatory Behavior; Craving; Dopamine; Dopaminergic Neurons; Dronabinol; E-Cigarette Vapor; Eating; Electronic Nicotine Delivery Systems; Electrophysiology; Epigenesis, Genetic; Ethanol; Extracellular Vesicles; Eye Diseases; Genomics; Habenula; Learning; Lynx; Marketing; Mass Spectrometry; Medulloblastoma; Memory; Menthol; Mice; Microscopy; National Eye Institute (U.S.); Nicotine; Nicotinic Agonists; Nucleus Accumbens; Pregnancy; Prenatal Exposure Delayed Effects; Proteomics; Quality of Life; Rats, Sprague-Dawley; Receptor, Cannabinoid, CB1; Receptors, Nicotinic; Receptors, Purinergic P2; Recurrence; Rodentia; Self Administration; Sex Characteristics; Signal Transduction; Smoking; Smoking Cessation; Social Behavior; Social Environment; Substance Withdrawal Syndrome; Substance-Related Disorders; Synaptic Transmission; Therapeutics; Tobacco Products; Tobacco Use; Tobacco Use Cessation Devices; Tobacco Use Disorder; Ventral Tegmental Area; Vision, Ocular; Xenograft Model Antitumor Assays; nan</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Yokomori, Kyoko</t>
+          <t>Frank, Steven</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Adolescent; Cell Differentiation; Gene Expression Profiling; Homeodomain Proteins; In Situ Hybridization, Fluorescence; Muscle Fibers, Skeletal; Muscle, Skeletal; Muscular Atrophy; Muscular Dystrophy, Facioscapulohumeral; Myoblasts; Single-Cell Analysis; Transcriptome</t>
+          <t>Access to Information; Artificial Intelligence; Bacteria; Biological Evolution; Cell Biology; Communicable Diseases; Computational Biology; Computer Simulation; Disease; Ecological and Environmental Phenomena; Epigenesis, Genetic; Ergonomics; Evolution, Molecular; Gene Expression; Genetic Drift; Genetics; Genetics, Population; Genotype; Host-Parasite Interactions; Inheritance Patterns; Life History Traits; Logic; Microbiota; Models, Genetic; Molecular Epidemiology; Mutation; Neoplasms; Neurobiology; Phenotype; Public Health; Selection, Genetic; Social Evolution; Software; Systems Biology</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Baker, Nicholas Edward</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>Frostig, Ron</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Action Potentials; Anesthetics; Astrocytes; Behavior, Animal; Biosensing Techniques; Brain; Brain Diseases, Metabolic; Brain Ischemia; Cerebral Cortex; Cerebrovascular Circulation; Diagnostic Imaging; Electric Stimulation; Electrophysiology; Glutamic Acid; Head; Histology; Infarction, Middle Cerebral Artery; Ischemic Attack, Transient; Ischemic Stroke; Lactic Acid; Lidocaine; Magnetic Resonance Imaging; Metabolism; Microelectrodes; Middle Cerebral Artery; Neural Conduction; Neuroimaging; Neuronal Plasticity; Neurons; Neuroprotection; Neurotransmitter Agents; Pharmacology; Rats, Sprague-Dawley; Rodentia; Sense Organs; Social Isolation; Stroke; Wakefulness; gamma-Aminobutyric Acid</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Barbour, Alan G</t>
+          <t>Fruman, David</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Arthritis; Autoimmunity; Borrelia burgdorferi; Breeding; Deer; Endotoxins; Epitopes, T-Lymphocyte; Extracellular Matrix Proteins; Genome-Wide Association Study; HLA-DRB1 Chains; Interferon Type I; Interferon-gamma; Lipopolysaccharides; Lyme Disease; Multifactorial Inheritance; Peptides; Peromyscus; Phenotype; Polymorphism, Single Nucleotide; Zoonoses</t>
+          <t>AMP-Activated Protein Kinases; Adolescent; Antineoplastic Agents; Apoptosis; Apoptosis Regulatory Proteins; Biological Transport; Biomarkers; Biosynthetic Pathways; Catalysis; Cell Cycle Checkpoints; Cell Death; Cell Line; Cell Line, Tumor; Cell Membrane; Cell Proliferation; Cell Survival; Child; Cholesterol; Clustered Regularly Interspaced Short Palindromic Repeats; Cobalt; Cytokines; DNA Adducts; Dasatinib; Diet; Doxorubicin; Drug Delivery Systems; Drug Repositioning; Drug Synergism; Endocytosis; Endosomes; Fasting; Fusion Proteins, bcr-abl; GTP Phosphohydrolases; Gene Expression; Guanosine Triphosphate; Health Inequities; Heart Diseases; Hematologic Neoplasms; Heterografts; Hispanic or Latino; Hydroxymethylglutaryl-CoA Reductase Inhibitors; Immunosuppressive Agents; Janus Kinases; Leukemia; Leukemia, Lymphocytic, Chronic, B-Cell; Leukemia, Myeloid, Acute; Lipids; Lymphocytes; Lymphoma; MTOR Inhibitors; Mechanistic Target of Rapamycin Complex 1; Mechanistic Target of Rapamycin Complex 2; Mevalonic Acid; Mitochondria; Molecular Targeted Therapy; Multiple Myeloma; Multiprotein Complexes; Myeloid Cell Leukemia Sequence 1 Protein; Neoplasms; Neoplastic Processes; Nutrients; Oligonucleotides; Oligonucleotides, Antisense; Organelles; Philadelphia Chromosome; Phosphatidylinositol 3-Kinases; Phosphoinositide-3 Kinase Inhibitors; Phosphorylation; Precursor Cell Lymphoblastic Leukemia-Lymphoma; Prognosis; Prospective Studies; Proteasome Endopeptidase Complex; Protein Isoforms; Protein Prenylation; Protein-Tyrosine Kinases; Proteolysis; Proto-Oncogene Proteins c-akt; Proto-Oncogene Proteins c-bcl-2; Quinolines; RNA, Small Interfering; Receptors, Cytokine; Recurrence; Reperfusion Injury; Retrospective Studies; Signal Transduction; Sirolimus; Standard of Care; Sterol Regulatory Element Binding Protein 2; Sterols; Survival Rate; TOR Serine-Threonine Kinases; Terpenes; Therapeutic Index; Transcription Factors; Transcriptome; Triple Negative Breast Neoplasms; Tumor Suppressor Protein p53; Tyrosine Kinase Inhibitors; Ubiquitin; Ubiquitin-Protein Ligases; Up-Regulation; Xenograft Model Antitumor Assays; Young Adult; pitavastatin; ruxolitinib; venetoclax</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Borrelli, Emilia</t>
+          <t>Gaut, Brandon</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aged; Aged, 80 and over; Angiogenesis Inhibitors; Atrophy; Bruch Membrane; Circadian Clocks; Cocaine; Corpus Striatum; Cross-Sectional Studies; Diabetic Retinopathy; Dopamine; Fluorescein Angiography; Fovea Centralis; Fundus Oculi; Liver; Macula Lutea; Metabolomics; Neurons; Reading; Receptors, Dopamine D1; Receptors, Dopamine D2; Reproducibility of Results; Retinal Neovascularization; Retinal Pigment Epithelium; Retrospective Studies; Tomography, Optical Coherence; Vascular Endothelial Growth Factor A; Visual Acuity; Wet Macular Degeneration</t>
+          <t>Adaptation, Physiological; Agriculture; Alleles; Altitude; Arabidopsis; Archaeology; Base Sequence; Biological Evolution; Biological Variation, Population; California; China; Chromatin; Chromosome Mapping; Chromosomes, Plant; Clergy; Climate; Climate Change; Climate Models; Crops, Agricultural; DNA; DNA Methylation; DNA Transposable Elements; DNA-Directed RNA Polymerases; Demography; Diploidy; Disease Vectors; Domestication; Drought Resistance; Droughts; Ecological and Environmental Phenomena; Ecology; Ecosystem; Epigenesis, Genetic; Epigenome; Epigenomics; Epistasis, Genetic; Escherichia coli; Escherichia coli Proteins; Europe; Evolution, Molecular; Extreme Weather; Fruit; Gene Expression; Gene Expression Regulation, Plant; Gene Flow; Gene Frequency; Genes, Plant; Genetic Drift; Genetic Fitness; Genetic Load; Genetic Variation; Genetics; Genetics, Population; Genome Size; Genome, Plant; Genome-Wide Association Study; Genomic Instability; Genomics; Genotype; Grassland; Heterozygote; Hispanic or Latino; History, Ancient; Homozygote; Honduras; Hot Temperature; Hyperspectral Imaging; Metagenomics; MicroRNAs; Microbiota; Microscopy, Electron, Scanning Transmission; Molecular Biology; Mutation; North America; Nucleic Acid Conformation; Oryza; Parasites; Periodicals as Topic; Persea; Phenomics; Phenotype; Phylogeny; Plant Breeding; Plant Physiological Phenomena; Plants; Pollination; Polymorphism, Single Nucleotide; Protoplasts; Quantitative Trait Loci; RNA, Plant; RNA, Small Interfering; Reproduction; Rho Factor; Salt Tolerance; Seeds; Selection, Genetic; Sequence Analysis, DNA; Setaria Plant; Social Mobility; Software; Soil Microbiology; Sorghum; Species Specificity; Sphingomonas; Stress, Physiological; Temperature; Tibet; Vitis; Zea mays</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Burke, Thomas P</t>
+          <t>German, Donovan</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Amino Acid Transport Systems; Cytosol; Phospholipases; Rickettsia; Rickettsia Infections; Symporters</t>
+          <t>Acclimatization; Adaptation, Physiological; Alkaline Phosphatase; Alzheimer Disease; Aminopeptidases; Amylases; Animal Husbandry; Bays; Biological Evolution; Biomarkers; Biota; Body Size; California; Carbohydrates; Carboxylesterase; Carnivory; Cellulases; Chromosomes; Cold Temperature; Conservation of Natural Resources; DNA Copy Number Variations; Diet; Diet, Food, and Nutrition; Dietary Fiber; Digestion; Digestive System Physiological Phenomena; Disease Progression; Down Syndrome; Ecological and Environmental Phenomena; Ecosystem; Employment; Endangered Species; Enzymes; Esters; Fatty Acids, Essential; Fermentation; Financial Management; Fires; Fisheries; Fishes; Gametogenesis; Gastrointestinal Microbiome; Gastrointestinal Tract; Gastropoda; Gene Dosage; Gene Expression Profiling; Genetics; Genome; Genomics; Heat-Shock Response; Herbivory; Hydrogen-Ion Concentration; Hydrolysis; Immunohistochemistry; Laboratories; Leucine; Life Cycle Stages; Lipase; Lipids; Lizards; Macrocystis; Marine Biology; Mexico; Microalgae; Microbiota; Mytilus; Pancreatic alpha-Amylases; Parents; Perciformes; Phylogeny; Physiology; Protein Isoforms; Proteomics; RNA, Ribosomal, 16S; Reproducibility of Results; Reproduction; Schools; Stomach; Temperature; Transcriptome; Trypsin; Zebrafish; alpha-Glucosidases; tau Proteins</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Byun, Minji</t>
+          <t>Gershon, Paul</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Amyotrophic Lateral Sclerosis; CD8-Positive T-Lymphocytes; Clone Cells; DNA Helicases; Endogenous Retroviruses; Epigenesis, Genetic; Gene Expression; Gene Knock-In Techniques; Heterochromatin; Motor Neurons; Multifunctional Enzymes; Mutation; RNA Helicases; RNA, Nuclear</t>
+          <t>Adipogenesis; Adipose Tissue; Aged; Allografts; Antineoplastic Combined Chemotherapy Protocols; Antiviral Agents; Artificial Intelligence; Biomarkers, Tumor; Cell Differentiation; Cell Line; Cell Nucleus; Chromatin; Cytochrome P-450 CYP1B1; DNA; DNA Damage; DNA-Binding Proteins; Deep Learning; Diabetes Mellitus, Experimental; Disease Outbreaks; Drug Labeling; Drug Resistance, Neoplasm; Escherichia coli; Family; Fascia; Glucose; Human Embryonic Stem Cells; Immunity, Innate; Immunoglobulins; Insulin Secretion; Insulin-Secreting Cells; Ion Channels; Islets of Langerhans; Mass Spectrometry; Membrane Proteins; Morphogenesis; Mpox (monkeypox); Neoadjuvant Therapy; Nuclear Proteins; Obesity; Organoids; Phosphoric Monoester Hydrolases; Pluripotent Stem Cells; Poxviridae; Protein Binding; Protein C; Proteome; Proteomics; Proto-Oncogene Mas; Recreation; Retrospective Studies; Rodentia; Signal Transduction; Smallpox; Systems Biology; Technology; Tecovirimat; Transcription Factor 7-Like 1 Protein; Transcription Factors; Transcriptome; Triple Negative Breast Neoplasms; Tumor Microenvironment; Vaccination; Vaccines; Vaccinia; Vaccinia virus; Variola virus; Viral Replication Compartments; Virion; Virology; Wnt Signaling Pathway; brincidofovir; src-Family Kinases</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Goldin, Alan L</t>
+          <t>Glabe, Charles</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Action Potentials; Arrhythmias, Cardiac; Heart Conduction System; Myocytes, Cardiac; NAV1.5 Voltage-Gated Sodium Channel; Sodium Channel Blockers; Voltage-Gated Sodium Channel Blockers</t>
+          <t>Adaptive Immunity; Aging; Algorithms; Allergy and Immunology; Alzheimer Disease; Amino Acid Sequence; Amino Acids; Amyloid; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Amyloidogenic Proteins; Antibodies; Antibodies, Monoclonal; Antibody Specificity; Antigen-Antibody Reactions; Autoantibodies; Autoantigens; Bacteriophages; Brain; Brain-Derived Neurotrophic Factor; CA1 Region, Hippocampal; Calcium; Cognition; Communicable Diseases; Congo Red; Desmoglein 1; Desmoglein 3; Energy Metabolism; Epitope Mapping; Epitopes; Glutathione; High-Throughput Nucleotide Sequencing; Hypertension; Immunity; Immunity, Innate; Immunoglobulin G; Immunotherapy; Indicators and Reagents; Infant; Keratinocytes; Microglia; Neurodegenerative Diseases; Neurofibrillary Tangles; Pemphigus; Peptides; Phosphatidylinositol-3,4,5-Trisphosphate 5-Phosphatases; Plaque, Amyloid; Pre-Eclampsia; Pregnancy; Protein Conformation, alpha-Helical; Protein Conformation, beta-Strand; Proteinuria; Receptor, Muscarinic M3; Serum Amyloid A Protein; Single-Domain Antibodies; Statistics, Nonparametric; Supranuclear Palsy, Progressive; Synucleins; Vaccines; Virulence; nan; tau Proteins</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Hertel, Klemens J</t>
+          <t>Gonen, Shane</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Alternative Splicing; Cell Line, Tumor; Cell Proliferation; Exons; Homocysteine; Introns; Methionine; Methylation; Nutrients; Protein-Arginine N-Methyltransferases; RNA Splice Sites; RNA Splicing; RNA-Binding Proteins</t>
+          <t>Action Potentials; Algorithms; Anti-Bacterial Agents; Bacteriophages; Biochemistry; Brain; Carrier Proteins; Conotoxins; Conus Snail; Cryoelectron Microscopy; Deep Learning; Drug Design; Escherichia coli; Eye; Gastrointestinal Microbiome; Genomics; Gram-Negative Bacterial Infections; Heart; Image Processing, Computer-Assisted; Ion Channel Gating; Kinetics; Membrane Proteins; Membrane Transport Proteins; Membranes; Microscopy; Models, Molecular; Molecular Structure; Multiprotein Complexes; NAV1.8 Voltage-Gated Sodium Channel; Nanostructures; Neoplasms; Peptides; Phage Therapy; Protein Conformation; Protein Folding; Proteins; Receptors, G-Protein-Coupled; Spider Venoms; Stenotrophomonas maltophilia; Virion; Voltage-Gated Sodium Channel Blockers; Wastewater; Zebrafish; nan</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>James, Anthony A</t>
+          <t>Goulding, Celia</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Adaptive Clinical Trials as Topic; Aedes; Animals, Genetically Modified; Anopheles; Betalains; Bombyx; CRISPR-Cas Systems; Cell Death; Circadian Rhythm; Color; Culex; Culicidae; DNA Transposable Elements; Dengue; Dengue Virus; Disease Vectors; Family; Filariasis; Gene Drive Technology; Gene Expression; Gene Expression Regulation, Enzymologic; Gene Transfer Techniques; Genetic Engineering; Genetic Introgression; Hedgehog Proteins; Insect Proteins; Insecticides; Introduced Species; Malaria; Malaria, Falciparum; MicroRNAs; Mosquito Control; Mosquito Vectors; Mutagenesis, Insertional; Oviposition; Peptide Hydrolases; Pigments, Biological; Plasmodium; Plasmodium falciparum; Promoter Regions, Genetic; Protein Isoforms; RNA; RNA, Guide, CRISPR-Cas Systems; Rabbits; Receptors, Odorant; Reproduction; Sex Differentiation; Sporozoites; Transcriptional Activation; Transgenes; Tubulin; Vector Borne Diseases; Vision, Ocular; Zika Virus; Zika Virus Infection</t>
+          <t>Alanine Dehydrogenase; Anti-Bacterial Agents; Arginine; Bacteria; Bacterial Proteins; Biliverdine; Biochemistry; Bordetella pertussis; Carrier Proteins; Communicable Diseases; Cryoelectron Microscopy; Disulfides; Drug Discovery; Electrons; Enterobacter cloacae; Enzyme Inhibitors; Escherichia coli; Escherichia coli Proteins; Eukaryotic Cells; Glycation End Products, Advanced; Hemagglutinins; Heme; Heme Oxygenase (Decyclizing); Hemoglobins; Histidine Kinase; Infant; Infant, Newborn; Iron; Latent Tuberculosis; Ligands; Lysine; Mass Spectrometry; Membrane Proteins; Molecular Biology; Molecular Structure; Mycobacteriaceae; Mycobacterium tuberculosis; Nucleosides; Nutrients; Pandemics; Pertussis Vaccine; Protein Interaction Mapping; Protein Processing, Post-Translational; Protein Sorting Signals; Proteins; Proteolysis; Pyruvaldehyde; Siderophores; Tomography, X-Ray Computed; Toxins, Biological; Tuberculosis; Vaccination; Virulence; Virulence Factors; Whooping Cough</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Koyuncu, Orkide</t>
+          <t>Green, Kim</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Alphaherpesvirinae; Alzheimer Disease; Axons; Brain; Brain Mapping; Cells, Cultured; Connectome; Dependovirus; Gene Silencing; Genetic Vectors; Green Fluorescent Proteins; Herpes Simplex; Herpes Simplex Virus Protein Vmw65; Herpesvirus 1, Human; Herpesvirus 1, Suid; Microscopy, Fluorescence; Nerve Net; Neurons; Pseudorabies; Rabies; Rabies virus; Viral Proteins; Virus Activation; Virus Latency; Virus Replication</t>
+          <t>ATP-Binding Cassette Transporters; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Apolipoproteins E; Astrocytes; Biomarkers; Bone Marrow; Brain; Brain Neoplasms; Brain-Derived Neurotrophic Factor; Breast Neoplasms; Cell Communication; Cell Nucleus; Cell Proliferation; Central Nervous System Diseases; Clusterin; Cognition; Complement C3; Coronavirus Infections; Cystatins; Demyelinating Diseases; Dendrimers; Disease Progression; Double-Blind Method; Down Syndrome; Gastrointestinal Microbiome; Gene Expression; Gene Expression Profiling; Gene Knock-In Techniques; Gene Regulatory Networks; Genes, fms; Genetic Variation; Genotype; Homeostasis; Immunotherapy; Integrases; Macrophage Colony-Stimulating Factor; Macrophages; Membrane Glycoproteins; Metabolomics; Microbiota; Microglia; Monocytes; Murine hepatitis virus; Mutation; Mutation, Missense; Myeloid Cells; NF-kappa B; NLR Family, Pyrin Domain-Containing 3 Protein; Nerve Degeneration; Nerve Regeneration; Neurites; Neuroglia; Neuroinflammatory Diseases; Neurons; Niacinamide; Phagocytosis; Phosphorylation; Plaque, Amyloid; Proof of Concept Study; Receptor, trkB; Receptors, Granulocyte-Macrophage Colony-Stimulating Factor; Receptors, Immunologic; Resilience, Psychological; Sex Characteristics; Single-Cell Analysis; Synapses; Tauopathies; Transcriptome; Treatment Outcome; Trimethoprim; Vitamin B Complex; tau Proteins</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marsden, Matthew D</t>
+          <t>Green, Michael</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Anti-HIV Agents; Anti-Retroviral Agents; Bone Marrow; Bryostatins; CD4-Positive T-Lymphocytes; Coculture Techniques; Cytokines; HIV Infections; HIV-1; Host-Pathogen Interactions; Immunotherapy, Adoptive; Jurkat Cells; Killer Cells, Natural; Leukocytes, Mononuclear; NF-kappa B; Protein Kinase C; Protein Kinase Inhibitors; Receptors, Chimeric Antigen; Sex Characteristics; Sirolimus; Spleen; Viral Load; Viremia; Virus Activation; Virus Latency; Virus Replication</t>
+          <t>Administration, Intravenous; Adolescent; Algorithms; Anisotropy; Antifungal Agents; Bias; Bipolar Disorder; Black or African American; Brain; Candidiasis, Invasive; Catalysis; Catalytic Domain; Chemistry, Bioinorganic; Child; Child, Preschool; Chromosome Mapping; Climate Change; Cohort Studies; Cross-Sectional Studies; Crystallography, X-Ray; Cytochrome P-450 Enzyme System; Cytochromes; Diffusion Tensor Imaging; Ecosystem; Electron Transport; Electrons; Europe; Genetic Predisposition to Disease; Genetic Variation; Genome-Wide Association Study; Genomics; Gray Matter; Head; Hemeproteins; Hippocampus; Hispanic or Latino; Infant; Iron; Ligands; Machine Learning; Magnetic Resonance Imaging; Metalloproteins; Metals; Models, Molecular; Multifactorial Inheritance; Neoplasms; Neuroimaging; Nitrogen; North America; Organ Size; Oxidation-Reduction; Oxygen; Phenotype; Plant Development; Plant Leaves; Plant Physiological Phenomena; Plants; Polymorphism, Single Nucleotide; Quantitative Trait Loci; Reproducibility of Results; Schizophrenia; Schizophrenic Psychology; Signal Transduction; Snow; Spectrum Analysis, Raman; Thermodynamics; Thinking; Treatment Outcome; Triazoles; White; White Matter; White People; X-Ray Absorption Spectroscopy</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mcclelland, Michael</t>
+          <t>Grill, Joshua</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Amino Acids; Anaerobiosis; Anti-Bacterial Agents; Bacteria; Bacterial Proteins; Caco-2 Cells; Cardiolipins; Cattle; Cecum; Colitis; Dietary Proteins; Endodeoxyribonucleases; Enterobacteriaceae Infections; Formates; Gastrointestinal Microbiome; Gene Deletion; HT29 Cells; Host-Pathogen Interactions; Hydrogen Peroxide; Inflammasomes; Inflammation; Lipopolysaccharides; Lyases; Macrophages; Methionine; Mucus; NADPH Oxidases; Operon; Oxidative Stress; Peptide Hydrolases; Phagocytes; Phylogeny; Prophages; Providencia; Pyruvates; RNA; RNA, Transfer; Reactive Oxygen Species; Respiration; SOS Response, Genetics; Salmonella; Salmonella Infections; Salmonella Infections, Animal; Salmonella Phages; Salmonella enterica; Salmonella typhimurium; Serogroup; Tetracycline; Toll-Like Receptor 4; Transcription Factors; Type III Secretion Systems; Viral Proteins; Virulence Factors</t>
+          <t>Adenosine Triphosphate; Administration, Oral; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloidogenic Proteins; Anhedonia; Antibodies, Monoclonal; Antibodies, Monoclonal, Humanized; Anxiety; Apathy; Apolipoprotein E4; Asian; Asian American Native Hawaiian and Pacific Islander; Autopsy; Biomarkers; Biomedical Research; Brain; California; Caregivers; Checklist; Clinical Trials Data Monitoring Committees; Clinical Trials as Topic; Clinical Trials, Phase II as Topic; Cognition; Cognitive Dysfunction; Cohort Studies; Control Groups; Delusions; Dementia; Depression; Diagnostic Errors; Disclosure; Disease Management; Disease Progression; Double-Blind Method; Feasibility Studies; Hallucinations; Hispanic or Latino; Intermediate Filaments; Leadership; Life Style; Longitudinal Studies; Magnetic Resonance Imaging; Memory Disorders; Mental Status and Dementia Tests; Motivation; Native Hawaiian or Pacific Islander; Neurodegenerative Diseases; Niacinamide; Patient Selection; Philippines; Phosphorylation; Positron-Emission Tomography; Prognosis; Proof of Concept Study; Psychiatrists; Randomized Controlled Trials as Topic; Registries; Republic of Korea; Research Subjects; Schizophrenia; Severity of Illness Index; Spinal Puncture; Suicidal Ideation; Suicide; Surveys and Questionnaires; Treatment Outcome; Vitamin B Complex; tau Proteins</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Semler, Bert L</t>
+          <t>Gross, Steven</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2',5'-Oligoadenylate Synthetase; Adenosine Deaminase; Alzheimer Disease; Antigens, Viral; Brain; Brain Mapping; COVID-19 Nucleic Acid Testing; CRISPR-Cas Systems; Cardiomyopathy, Dilated; Connectome; Coxsackievirus Infections; Cytidine Deaminase; Cytoplasmic Granules; DNA Helicases; Endoribonucleases; Enterovirus B, Human; Enzyme Activation; Gene Knockout Techniques; Genetic Vectors; Genomics; Green Fluorescent Proteins; HEK293 Cells; Interferon Regulatory Factor-2; Microscopy, Fluorescence; Minor Histocompatibility Antigens; Molecular Diagnostic Techniques; Myocytes, Cardiac; Nerve Net; Neurons; Nucleic Acid Amplification Techniques; Peptide Hydrolases; Persistent Infection; Poly-ADP-Ribose Binding Proteins; Protein Kinases; RNA Helicases; RNA Recognition Motif Proteins; RNA Stability; RNA, Double-Stranded; RNA, Viral; RNA-Binding Proteins; Rabies; Rabies virus; Real-Time Polymerase Chain Reaction; SARS-CoV-2; STAT2 Transcription Factor; Saliva; Specimen Handling; Stress Granules; Viral Proteins; Virus Diseases; Virus Replication; eIF-2 Kinase</t>
+          <t>Adenosine Diphosphate; Adjuvants, Immunologic; Adjuvants, Pharmaceutic; Anti-Bacterial Agents; Anti-Infective Agents; Antimicrobial Cationic Peptides; Antimicrobial Peptides; Biological Transport; Biophysics; Brain; Cell Communication; Cell Membrane; Clostridioides; Clostridioides difficile; Computational Biology; Computer Simulation; Cytoskeleton; DNA; Diffusion; Dynactin Complex; Dyneins; Escherichia coli; Glycogen Synthase Kinase 3 beta; Histones; Immunity, Innate; Kinesins; Kinetics; Lipid Droplets; Lipopolysaccharides; Metronidazole; Microbiota; Microtubule-Associated Proteins; Microtubules; Molecular Motor Proteins; Motor Neuron Disease; Muscular Atrophy, Spinal; Mutation; Neurodegenerative Diseases; Neurons; Optical Tweezers; Organelles; Parkinson Disease; Polymyxin B; Protein Binding; Protein Conformation; Protein Processing, Post-Translational; Proteins; Saccharomyces cerevisiae; Tubulin; Vancomycin</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Shi, Yongsheng</t>
+          <t>Halbrook, Christopher</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3' Untranslated Regions; Adenine; Adenosine; Agammaglobulinaemia Tyrosine Kinase; Aged; Aged, 80 and over; Air Pollutants; Air Pollution; Alternative Splicing; Alzheimer Disease; American Indian or Alaska Native; Amyloid beta-Peptides; Asian; Astrocytes; Ataxin-7; Basic Helix-Loop-Helix Transcription Factors; Blindness; Blood Pressure; Brain; Carcinoma, Pancreatic Ductal; Cell Differentiation; Cell Line, Tumor; Cell Nucleus; Cell Survival; Coculture Techniques; Comorbidity; Cross-Sectional Studies; DNA-Binding Proteins; Dementia; Dermatitis, Atopic; Diaphragm; Disease Progression; Disorders of Excessive Somnolence; Drug Resistance, Neoplasm; Emigrants and Immigrants; Endoplasmic Reticulum; Environmental Exposure; Epidermis; Exosome Multienzyme Ribonuclease Complex; Ferroptosis; Gene Expression Regulation; Gene Expression Regulation, Neoplastic; Genes, Reporter; HEK293 Cells; HeLa Cells; High-Throughput Nucleotide Sequencing; Homeostasis; Hypertension; Hypoglossal Nerve; Immunoglobulin M; Induced Pluripotent Stem Cells; Inflammation; Interferon Regulatory Factors; Intrinsically Disordered Proteins; Keratinocytes; Leukemia, Lymphocytic, Chronic, B-Cell; Lipid Peroxidation; Machine Learning; Magnetic Resonance Imaging; Medulla Oblongata; Microglia; Multimorbidity; Mutation; Neuromuscular Junction; Neurons; Nitrogen Dioxide; Organoids; Pancreatic Neoplasms; Particulate Matter; Peptides; Phagocytosis; Phrenic Nerve; Piperidines; Plasma Cells; Poly A; Polyadenylation; Polymorphism, Single Nucleotide; Polysomnography; Positive Regulatory Domain I-Binding Factor 1; Presenilin-1; Promoter Regions, Genetic; Protein Binding; Protein Kinase Inhibitors; Pyrazoles; Pyrimidines; RNA 3' End Processing; RNA Polymerase II; RNA Precursors; RNA Processing, Post-Transcriptional; RNA Splice Sites; RNA Splicing; RNA Stability; RNA, Antisense; RNA, Messenger; RNA, Nuclear; RNA, Small Nuclear; RNA-Binding Proteins; Receptors, Aryl Hydrocarbon; Retrospective Studies; Ribonucleoprotein, U1 Small Nuclear; Ribonucleoproteins, Small Nuclear; Signal Transduction; Sleep Apnea Syndromes; Sleep Apnea, Obstructive; Snoring; Spinal Cord; Spinocerebellar Ataxias; Spliceosomes; Tongue; Transcription Factors; Transcriptome; Visual Cortex; Visual Prosthesis; tau Proteins</t>
+          <t>3-hydroxy-3-methylglutaryl-coenzyme A; Acute Disease; Adenocarcinoma; Allografts; Amiloride; Anti-Inflammatory Agents; Arginase; Arginine; Asparagine; Autophagy; CD8-Positive T-Lymphocytes; CRISPR-Cas Systems; Cancer-Associated Fibroblasts; Carcinogenesis; Carcinoma, Pancreatic Ductal; Catalytic Domain; Cell Line, Tumor; Cell Lineage; Cell Proliferation; Cell Transformation, Neoplastic; Chromatography, Liquid; Clone Cells; Communication; Critical Pathways; Cues; Cytotoxins; Deoxycytidine; Drug Resistance, Neoplasm; Early Diagnosis; Energy Metabolism; Epigenesis, Genetic; Epithelial Cells; Fibroblasts; Fibrosis; Flow Cytometry; Gemcitabine; Gene Expression Profiling; Glutathione; Granulocyte-Macrophage Colony-Stimulating Factor; Hepatocyte Growth Factor; Histones; Hospitalization; Immunotherapy; Indicators and Reagents; Liver Neoplasms; Macrophages; Metabolic Networks and Pathways; Metabolic Reprogramming; Metabolomics; Methylation; Mevalonic Acid; Myeloid Cells; Neoplasms; Organoids; Oxidation-Reduction; Oxidoreductases; Pain Management; Pancreas; Pancreatic Diseases; Pancreatic Hormones; Pancreatic Neoplasms; Pancreatitis; Pancreatitis, Chronic; Pinocytosis; Prognosis; Proteomics; Pyrimidines; RNA; Regeneration; Sequence Analysis, RNA; Signal Transduction; Sodium-Hydrogen Exchangers; Staining and Labeling; Standard of Care; Stromal Cells; Survival Rate; Symbiosis; Tandem Mass Spectrometry; Transcription Factors; Transcriptome; Tumor Microenvironment; Tumor-Associated Macrophages; Uracil; geranylgeranyl pyrophosphate</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tan, Ming</t>
+          <t>Hammer, Tobin</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Acrylamides; Aftercare; Aged; Aged, 80 and over; Anilides; Aniline Compounds; Antineoplastic Combined Chemotherapy Protocols; Asia, Southeastern; Bacterial Proteins; Cambodia; Carbazoles; Carcinoma, Non-Small-Cell Lung; Chlamydia Infections; Chlamydia trachomatis; Cilia; DNA; Delirium; Disease Susceptibility; Drosophila Proteins; Enhancer Elements, Genetic; Epithelial Cells; ErbB Receptors; Exons; Fever; Gene Expression Regulation; Gene Expression Regulation, Bacterial; Gene Knockdown Techniques; HeLa Cells; Health Resources; High-Throughput Nucleotide Sequencing; Incidence; Indoles; Intensive Care Units; Length of Stay; Lung Neoplasms; Membrane Proteins; Metagenome; Metagenomics; Mutagenesis, Insertional; Mutation; Patient Discharge; Pilot Projects; Prognosis; Promoter Regions, Genetic; Prospective Studies; Protein Kinase Inhibitors; Public Health Surveillance; Pyrimidines; Quinolines; Retrospective Studies; Seroepidemiologic Studies; Sorting Nexins; Transcription Factors; Treatment Outcome</t>
+          <t>Agriculture; Anthropogenic Effects; Bacteria; Bees; Biodiversity; Biological Evolution; Coral Bleaching; Crithidia; Crops, Agricultural; DNA Contamination; Data Analysis; Diet; Disease Resistance; Dysbiosis; Ecological and Environmental Phenomena; Ecology; Ecosystem; Gastrointestinal Microbiome; Genetics; Health; Host Microbial Interactions; Human Activities; Insecta; Longevity; Magnolia; Metagenomics; Microbiota; Motivation; Parasites; Pollination; Quality Indicators, Health Care; RNA, Ribosomal, 16S; Reproduction; Schools; Seasons; Serratia marcescens; Social Behavior; Social Interaction; Symbiosis</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Abbott, Geoffrey Winston</t>
+          <t>Hu, Yilin</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Alkaloids; Analgesics; Anti-Arrhythmia Agents; Anti-Inflammatory Agents; Arrhythmias, Cardiac; Ataxia; Behavior, Animal; Benzhydryl Compounds; Calcitonin Gene-Related Peptide; Canagliflozin; Cardiomyopathies; Cardiopulmonary Resuscitation; Cocaine; Coriandrum; Death, Sudden, Cardiac; Diabetes Mellitus, Type 2; Diterpenes; Dopamine; Dopamine Uptake Inhibitors; Dopaminergic Neurons; Globus Pallidus; Glucosides; Guanidines; HEK293 Cells; Heart Arrest; Indigenous Canadians; Ion Channel Gating; Ischemic Postconditioning; KCNQ Potassium Channels; KCNQ2 Potassium Channel; KCNQ3 Potassium Channel; Kv1.1 Potassium Channel; Levodopa; Ligands; Medicine, Traditional; Memantine; Mesenteric Arteries; Molecular Docking Simulation; Molecular Dynamics Simulation; Motor Activity; Movement Disorders; Muscle, Smooth, Vascular; Mutation; Myocardial Reperfusion Injury; Myocytes, Cardiac; Myokymia; Neuronal Plasticity; Oligopeptides; Parvalbumins; Piperidines; Plant Extracts; Plants, Medicinal; Potassium Channel Blockers; Protein Isoforms; Rats, Sprague-Dawley; Rats, Wistar; Receptors, Calcium-Sensing; Receptors, N-Methyl-D-Aspartate; Renal Artery; Reperfusion Injury; Rosmarinus; Sensory Receptor Cells; Sodium-Glucose Transporter 1; Sodium-Glucose Transporter 2; Sodium-Glucose Transporter 2 Inhibitors; Sodium-Hydrogen Exchanger 1; Spermatic Cord Torsion; Stroke Volume; Sulfones; TRPV Cation Channels; Tannins; Testis; Vasodilation; Vasodilator Agents; Ventral Tegmental Area; Ventricular Function, Left</t>
+          <t>Adenosine Triphosphate; Aged; Aged, 80 and over; Ammonia; Anaerobiosis; Animals, Genetically Modified; Azotobacter vinelandii; Bacterial Proteins; Biocatalysis; Biomarkers, Tumor; Bioreactors; Biosynthetic Pathways; Breast Neoplasms; Carbon Dioxide; Carbon Monoxide; Carcinoma, Non-Small-Cell Lung; Catalysis; Cell Line, Tumor; Chemistry, Bioinorganic; Chromosomes, Human, Pair 17; Circulating Tumor DNA; Drosophila Proteins; Drosophila melanogaster; Drug Carriers; Drug Delivery Systems; Drug Liberation; Drug Resistance, Neoplasm; Ecosystem; Electrons; Enzymes; ErbB Receptors; Escherichia coli; Evolution, Molecular; Exons; Gene Expression; Gold; Hydrocarbons; Hydrogen; Hydrogen Peroxide; Immunohistochemistry; In Situ Hybridization; Iron-Sulfur Proteins; Lactic Acid; Lung Neoplasms; Metal Nanoparticles; Metalloproteins; Mixed Function Oxygenases; Models, Molecular; Molybdenum; Molybdoferredoxin; Mutagenesis, Insertional; Nanoparticles; Neoplasms; Nitrogen; Nitrogen Cycle; Nitrogen Fixation; Nitrogenase; Oxidoreductases; Oxygen; Phylogeny; Prognosis; Protein Kinase Inhibitors; Receptor, ErbB-2; Retrospective Studies; Rotation; Silicon Dioxide; Sulfur; Technology; Transcription Factors; Warburg Effect, Oncologic</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Beier, Kevin T</t>
+          <t>Hughes, Christopher</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Acyltransferases; Amygdala; Analgesics, Opioid; Anxiety; Behavior, Animal; Brain; Brain Injuries; Cocaine; Cocaine-Related Disorders; Dopamine; Dopamine Uptake Inhibitors; Dopaminergic Neurons; Dronabinol; Endocytosis; Globus Pallidus; Hippocampus; Hypothalamic Area, Lateral; Hypothalamus; KCNQ Potassium Channels; KCNQ3 Potassium Channel; Logic; Long-Term Potentiation; Memory; Memory Disorders; Morphine; Neural Pathways; Neuronal Plasticity; Neurons; Nicotine; Parvalbumins; Peptides; Pinocytosis; Prefrontal Cortex; Preoptic Area; Protein Kinase C; Receptors, AMPA; Receptors, Nicotinic; Receptors, Opioid, mu; Sleep; Sleep Deprivation; Sleep, REM; Social Behavior; Substance Withdrawal Syndrome; Substantia Nigra; Synapses; Tegmentum Mesencephali; Ventral Tegmental Area; Wakefulness; alpha7 Nicotinic Acetylcholine Receptor; gamma-Aminobutyric Acid</t>
+          <t>Adipogenesis; Adipose Tissue; Alkylating Agents; Allografts; Alzheimer Disease; Anemia; Angiogenesis; Anxiety; Apolipoprotein E2; Apolipoprotein E4; Arteries; Arteriovenous Malformations; Astrocytes; Basement Membrane; Bayes Theorem; Biomarkers, Tumor; Biomimetics; Blood Substitutes; Blood Vessels; Blood-Borne Pathogens; Blood-Brain Barrier; Brain; Brain Neoplasms; Breast; Capillaries; Cell Cycle; Cell Cycle Checkpoints; Cell Line; Cell Line, Tumor; Cell Proliferation; Cellular Senescence; Central Nervous System Diseases; Clustered Regularly Interspaced Short Palindromic Repeats; Coculture Techniques; Colonic Neoplasms; Colorectal Neoplasms; Cytoreduction Surgical Procedures; Diabetes Mellitus; Drug Development; Drug Evaluation; Drug Interactions; Drug Repositioning; Endoglin; Endothelial Cells; Endothelium, Vascular; Epistaxis; Exosomes; Extracellular Matrix; Fascia; Fibroblasts; Fluorouracil; Galactosidases; Gene Expression; Glioblastoma; Glucose; Heart Failure; Huntington Disease; Hyperthermia, Induced; Hyperthermic Intraperitoneal Chemotherapy; Incidence; Induced Pluripotent Stem Cells; Infant; Insulin; Islets of Langerhans; Islets of Langerhans Transplantation; Lab-On-A-Chip Devices; Leucovorin; Liver; Lung; Microfluidics; Microglia; Microphysiological Systems; Microvessels; Mutation; Myocytes, Smooth Muscle; Neoadjuvant Therapy; Neoplasm Recurrence, Local; Neoplasms; Neoplastic Processes; Neovascularization, Pathologic; Neurons; Obesity; Oxaliplatin; Paclitaxel; Pancreas; Pancreatic Neoplasms; Patient Advocacy; Pazopanib; Peptides; Pericytes; Peritoneal Cavity; Peritoneal Neoplasms; Peritoneum; Phenotype; Port-Wine Stain; Prognosis; Prospective Studies; RNA; Rare Diseases; Rodentia; Senescence-Associated Secretory Phenotype; Senotherapeutics; Signal Transduction; Single-Cell Gene Expression Analysis; Sitting Position; Snail Family Transcription Factors; Splenic Neoplasms; Standard of Care; Stomach Neoplasms; Stroke; Stromal Cells; Sturge-Weber Syndrome; Survival Rate; Technology; Telangiectasia, Hereditary Hemorrhagic; Temozolomide; Thrombosis; Tight Junctions; Tissue Engineering; Transcription Factors; Transcriptome; Transcytosis; Triple Negative Breast Neoplasms; Tumor Microenvironment; Vascular Malformations; peptide I</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cahalan, Michael</t>
+          <t>Huxman, Travis</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Adenosine Diphosphate; Alzheimer Disease; Amyloid beta-Peptides; Analgesics; Anti-Inflammatory Agents; Antigen Presentation; CD8-Positive T-Lymphocytes; Calcium; Calcium Signaling; Chemokines; Coriandrum; Corticotropin-Releasing Hormone; Fluorescent Dyes; Heart Rate; Induced Pluripotent Stem Cells; Ion Channels; Ionophores; Lighting; Membrane Glycoproteins; Membrane Potentials; Microglia; Molecular Docking Simulation; Neural Stem Cells; Neurons; Plant Extracts; Plants, Medicinal; Potassium Channel Blockers; Receptors, Immunologic; Receptors, Purinergic; Signal Transduction; Synapses; T-Lymphocytes; Tannins</t>
+          <t>Biodiversity; Biomass; California; Carbon; Climate Change; Desert Climate; Ecological and Environmental Phenomena; Ecology; Ecosystem; Fertilizers; Grassland; Groundwater; Health Surveys; Humidity; Hydrology; Introduced Species; Museums; Nitrogen; Nutrients; Phosphorus; Physiology, Comparative; Plants; Rain; Remote Sensing Technology; Soil; Temperature; Volunteers; Water; Water Resources; Water Supply; Wind</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Davies, David Huw</t>
+          <t>Inlay, Matthew</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Adjuvants, Immunologic; Adjuvants, Pharmaceutic; Adjuvants, Vaccine; Adolescent; Aerosols; Antibodies, Neutralizing; Antibodies, Viral; Antibody Formation; Antigens; Antigens, Bacterial; B-Lymphocytes; Bacterial Vaccines; CD4-Positive T-Lymphocytes; Child; Child, Preschool; Coxiella burnetii; Cytokines; Delayed-Action Preparations; Down-Regulation; Ebola Vaccines; Ebolavirus; Flagellin; Glycoproteins; Green Fluorescent Proteins; Guinea Pigs; Hemagglutinin Glycoproteins, Influenza Virus; Hemagglutinins; Hemorrhagic Fever, Ebola; Homeostasis; Hydrogels; Immunization; Immunogenicity, Vaccine; Immunoglobulin Class Switching; Immunoglobulin G; Immunoglobulin Isotypes; Immunoinformatics; Immunologic Memory; Influenza A Virus, H5N1 Subtype; Influenza Vaccines; Influenza, Human; Ligands; Lipid A; Lipopolysaccharides; Lymphocytes; Malaria; Malaria Vaccines; Malaria, Falciparum; Malaria, Vivax; Memory B Cells; Mice, Inbred BALB C; Nanoparticles; Oligodeoxyribonucleotides; Organ Specificity; Organoids; Orthomyxoviridae Infections; Palatine Tonsil; Particle Size; Phylogeny; Plasmodium falciparum; Plasmodium vivax; Polylactic Acid-Polyglycolic Acid Copolymer; Polymers; Polysorbates; Q Fever; Saponins; Sex Characteristics; Sex Factors; Sporozoites; Squalene; Streptavidin; Sudan; T-Lymphocytes; Th1 Cells; Toll-Like Receptor 4; Toll-Like Receptor Agonists; Toll-Like Receptors; Vaccination; Vaccines; Vaccines, Combined; Vaccines, Synthetic; Young Adult</t>
+          <t>Allografts; Anemia, Aplastic; Apoptosis; Blood Component Removal; Bone Marrow; Bone Marrow Transplantation; Brain; CD4-Positive T-Lymphocytes; COVID-19 Nucleic Acid Testing; Coronavirus Infections; Cyclophosphamide; Cytokines; Drug Combinations; Fetal Blood; Flow Cytometry; Fluticasone; Glucocorticoids; Graft vs Host Disease; HLA Antigens; Hematologic Neoplasms; Hematopoietic Stem Cell Transplantation; Hematopoietic Stem Cells; Heterografts; Immunity; Immunophenotyping; Immunosuppression Therapy; Immunosuppressive Agents; Incidence; Infertility; Interleukin-2; Leptospiraceae; Leukocytes, Mononuclear; Macrophages; Magnetic Phenomena; Major Histocompatibility Complex; Microglia; Molecular Diagnostic Techniques; Neoplasms; Nucleic Acid Amplification Techniques; Parents; Patient Care; Pharmaceutical Preparations; Prednisolone; Proto-Oncogene Proteins c-bcl-2; Real-Time Polymerase Chain Reaction; Regenerative Medicine; SARS-CoV-2; Saliva; Siblings; Specimen Handling; Stem Cells; Survival Rate; Systemic Inflammatory Response Syndrome; T-Lymphocytes; T-Lymphocytes, Regulatory; Tissue Donors; Transplantation Conditioning; Transplantation, Haploidentical; Transplantation, Heterologous; Transplantation, Homologous; venetoclax</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Eguchi, Asuka</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>James, Anthony</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Adaptive Clinical Trials as Topic; Aedes; Animals, Genetically Modified; Anopheles; Betalains; Blood Vessels; Bombyx; Brain; CRISPR-Cas Systems; Case-Control Studies; Cell Death; Cerebral Cortex; Circadian Rhythm; Color; Culex; Culicidae; DNA Transposable Elements; Dengue; Dengue Virus; Disease Vectors; Family; Filariasis; Functional Laterality; Gene Drive Technology; Gene Expression; Gene Expression Regulation, Enzymologic; Gene Transfer Techniques; Genetic Engineering; Genetic Introgression; Genetics; Global Health; Hedgehog Proteins; Insect Proteins; Insecticides; Magnetic Resonance Imaging; Malaria; Malaria, Falciparum; MicroRNAs; Mosquito Control; Mosquito Vectors; Mutagenesis, Insertional; Oviposition; Peptide Hydrolases; Pigments, Biological; Plasmodium; Plasmodium falciparum; Promoter Regions, Genetic; RNA; RNA, Guide, CRISPR-Cas Systems; Rabbits; Receptors, Odorant; Reproduction; Schizophrenia; Sex Differentiation; Sporozoites; Transcriptional Activation; Transgenes; Tubulin; Vector Borne Diseases; Vision, Ocular; Zika Virus; Zika Virus Infection</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Felgner, Philip</t>
+          <t>Kawas, Claudia</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Adjuvants, Immunologic; Adjuvants, Vaccine; Aerosols; Aged; Antibodies, Neutralizing; Antibodies, Protozoan; Antibodies, Viral; Antibody Formation; Antigens; Antigens, Bacterial; Antigens, Protozoan; Bacterial Vaccines; COVID-19; COVID-19 Serotherapy; COVID-19 Vaccines; CRISPR-Cas Systems; Case-Control Studies; Cell-Penetrating Peptides; Child; Child, Preschool; Clone Cells; Computational Biology; Coxiella burnetii; Cross Reactions; Cross-Sectional Studies; Delayed-Action Preparations; Endothelial Protein C Receptor; Epitopes; Flavivirus; Furocoumarins; Gene Editing; Gene Transfer Techniques; Genetic Therapy; Guinea Pigs; HEK293 Cells; HIV Infections; Health Personnel; Hydrogels; Immunity, Humoral; Immunization; Immunization, Passive; Immunoglobulin G; Immunoglobulin M; Lipids; Lipopolysaccharides; Liposomes; Machine Learning; Malaria; Malaria Vaccines; Malaria, Falciparum; Malaria, Vivax; Mice, Inbred BALB C; Nanoparticles; Nucleic Acids; Pandemics; Peptides; Plasmodium falciparum; Plasmodium vivax; Polylactic Acid-Polyglycolic Acid Copolymer; Protozoan Proteins; Q Fever; RNA, Small Interfering; RNA, Viral; Ribonucleoproteins; SARS-CoV-2; Seroepidemiologic Studies; Sporozoites; Support Vector Machine; Tanzania; Th1 Cells; Vaccination; Vaccine Efficacy; Vaccines, Combined; mRNA Vaccines</t>
+          <t>Adrenergic beta-Antagonists; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloidosis; Amyotrophic Lateral Sclerosis; Angiotensin-Converting Enzyme Inhibitors; Aniline Compounds; Apolipoproteins E; Atrophy; Autopsy; Biomarkers; Brain; Case-Control Studies; Cataract; Cell Separation; Centenarians; Cerebral Cortex; Cerebrovascular Circulation; Cerebrovascular Disorders; Clinical Trials as Topic; Cognition; Cognitive Dysfunction; Cohort Studies; Cryopreservation; DNA-Binding Proteins; Databases, Factual; Dementia; Dementia, Vascular; Diagnosis, Differential; Disease Progression; Educational Status; Epidemiology; Ethnicity; Ethylene Glycols; Executive Function; Extracellular Vesicles; Frailty; Frontotemporal Lobar Degeneration; Geriatric Assessment; Hand Strength; Hippocampus; Incidence; Inclusion Bodies; Lewy Bodies; Lewy Body Disease; Life Style; Limbic System; Longitudinal Studies; Magnetic Resonance Imaging; Medical History Taking; Nervous System Diseases; Neurofibrillary Tangles; Neuroglia; Neuroimaging; Neurons; Neuropsychological Tests; Nonagenarians; Organ Size; Physical Functional Performance; Plaque, Amyloid; Positron-Emission Tomography; Public Health; RNA-Seq; Racial Groups; Reference Values; Resilience, Psychological; Retrospective Studies; Risk Factors; Self Report; Self-Help Devices; Sex Factors; Sleep; Sleep Duration; Syncope; TDP-43 Proteinopathies; Tauopathies; Walking Speed; White Matter</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hicks, Michael Ryan</t>
+          <t>Kim, Seungsoo</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cell Differentiation; Dystrophin; Homeodomain Proteins; Mice, Inbred mdx; Muscle Development; Muscle, Skeletal; PAX3 Transcription Factor; PAX7 Transcription Factor; Pluripotent Stem Cells; Regeneration; Satellite Cells, Skeletal Muscle; Stem Cell Niche; Tissue Distribution</t>
+          <t>Academies and Institutes; Aged; Antibodies, Monoclonal, Humanized; Antineoplastic Combined Chemotherapy Protocols; Asia, Eastern; Bevacizumab; Blepharoptosis; California; Carboplatin; Cisplatin; East Asian People; Ecological Momentary Assessment; Emotions; Environmental Monitoring; Fluorocarbons; Love; Machine Learning; Neoplasm Recurrence, Local; Ophthalmic Solutions; Ophthalmology; Paclitaxel; Phenylephrine; Progression-Free Survival; Uterine Cervical Neoplasms; Waste Disposal, Fluid; Wastewater; Water Pollutants, Chemical; Young Adult</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Holmes, Todd C</t>
+          <t>Kong, Mei</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alzheimer Disease; Amyloid beta-Peptides; Animals, Genetically Modified; Arthropod Antennae; Autism Spectrum Disorder; Blood-Brain Barrier; Brain; Brain Diseases; Brain Mapping; CA1 Region, Hippocampal; Calcium; Capsid; Cell Differentiation; Cells, Cultured; Cerebral Hemorrhage; Cholecystokinin; Cognition; Cognition Disorders; Congresses as Topic; Connectome; Connexins; Dependovirus; Drosophila Proteins; Drosophila melanogaster; Endothelial Cells; Endothelium; Enhancer Elements, Genetic; Entorhinal Cortex; Erythrocytes; GABAergic Neurons; Gap Junctions; Gene Expression; Gene Expression Profiling; Genetic Vectors; Green Fluorescent Proteins; Hippocampus; Homeodomain Proteins; Immunohistochemistry; In Situ Hybridization, Fluorescence; Interneurons; Ketamine; Learning; Macaca fascicularis; Microglia; Microscopy, Fluorescence; Muscle Fibers, Skeletal; Muscular Dystrophy, Facioscapulohumeral; Myoblasts; Nerve Net; Neural Pathways; Neuroimaging; Neuronal Plasticity; Neurons; Olfactory Bulb; Olfactory Pathways; Oxidative Phosphorylation; Parvalbumins; Prosencephalon; Pyramidal Cells; Rabies; Rabies virus; Schizophrenia; Single-Cell Analysis; Smell; Transcriptome; Transduction, Genetic</t>
+          <t>AMP-Activated Protein Kinases; Abdominal Cavity; Adenocarcinoma; Adenocarcinoma, Mucinous; Adenomatous Polyposis Coli; Adolescent; Aged; Allografts; Antineoplastic Agents; Appendectomy; Appendiceal Neoplasms; Ascitic Fluid; Autoimmune Diseases; Biological Products; Cachexia; California; Carcinogenesis; Carcinoma; Catalytic Domain; Cell Cycle; Cell Differentiation; Cell Line; Cell Line, Tumor; Cell Plasticity; Cell Proliferation; Chemistry, Pharmaceutical; Chromatin; Chromatography, Liquid; Clinical Relevance; Colonic Neoplasms; Colorectal Neoplasms; Communication Barriers; Cost of Illness; Cytokines; Cytoreduction Surgical Procedures; DNA; Diabetes Mellitus; Diabetes Mellitus, Type 2; Diet, High-Fat; Diet, Ketogenic; Dietary Supplements; Dioxygenases; Drug Resistance, Neoplasm; Early Detection of Cancer; Epigenesis, Genetic; Epigenomics; Ficus; Gastrointestinal Neoplasms; Gene Expression; Gene Expression Regulation, Neoplastic; Genes, Tumor Suppressor; Genes, p16; Genetics; Glucose; Glutamine; Heterografts; High-Throughput Screening Assays; Histone Code; Histone Demethylases; Histone Methyltransferases; Histones; Homeostasis; Hospitalization; Hyperthermic Intraperitoneal Chemotherapy; Immunity; Immunoglobulin G; Immunoglobulin G4-Related Disease; Immunotherapy; Incidence; Intestinal Mucosa; Isotopes; Ketoglutaric Acids; Ketone Bodies; Ketones; Lactic Acid; Language; Lipid Metabolism; Lipids; Lipogenesis; Liquid Chromatography-Mass Spectrometry; Liver Neoplasms; Lubricants; Melanoma; Metabolic Diseases; Metabolic Networks and Pathways; Metabolism; Metformin; Micronutrients; Microscopy; Military Personnel; Monocarboxylic Acid Transporters; Morbidity; Muscles; Mutation; National Center for Advancing Translational Sciences (U.S.); Neoplasms; Neoplasms, Second Primary; Neoplastic Processes; Neoplastic Stem Cells; Nutrients; Obesity; Organoids; Ovarian Neoplasms; Oxidative Phosphorylation; PPAR gamma; Pancreas; Patient Preference; Peptide Hydrolases; Peritoneal Cavity; Peritoneal Neoplasms; Peritoneum; Peroxisome Proliferator-Activated Receptors; Phenotype; Phosphoprotein Phosphatases; Phosphoric Monoester Hydrolases; Phosphorylation; Pilot Projects; Pioglitazone; Positron Emission Tomography Computed Tomography; Prevalence; Prostatic Neoplasms; Protein Phosphatase 2; Protein Serine-Threonine Kinases; Proteolysis; Pseudomyxoma Peritonei; Pyruvic Acid; Qualitative Research; Quality of Life; RNA; RNA, Long Noncoding; Rectal Neoplasms; Risk Factors; Sequence Analysis, RNA; Sex Characteristics; Sex Chromosomes; Signal Transduction; Standard of Care; Stem Cells; Substrate Specificity; T-Lymphocytes; TWEAK Receptor; Tandem Mass Spectrometry; Thiazolidinediones; Transcription Factors; Tumor Microenvironment; Videoconferencing; Vitamin A; Vitamin B 6; Vitamins; Weight Loss; Wnt Signaling Pathway</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Huang, Lan</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Air Pollutants; Air Pollution; Autophagy; Breast Neoplasms; Cadmium; Catalysis; Catalytic Domain; Cell Cycle Proteins; Cell Nucleus; Child Development; China; Congresses as Topic; Endopeptidases; Endoplasmic Reticulum; Endoplasmic Reticulum-Associated Degradation; Environmental Monitoring; F-Box Proteins; Gene Expression Regulation; Golgi Apparatus; HEK293 Cells; HeLa Cells; Huntingtin Protein; Huntington Disease; Immunotherapy, Adoptive; Infant; Infant, Extremely Premature; Infant, Newborn; Integrins; Intrinsically Disordered Proteins; Leukemia, Myeloid, Acute; Lipidomics; Lipids; Lysosomes; Mass Spectrometry; Membrane Proteins; Mental Health; Mice, Nude; Microscopy; Mitochondria; Mitochondrial Proteins; Models, Molecular; Multicenter Studies as Topic; Neurodevelopmental Disorders; Ozone; Parents; Peptides; Pharmaceutical Preparations; Proteasome Endopeptidase Complex; Protein Binding; Protein Biosynthesis; Protein Domains; Protein Interaction Mapping; Protein Interaction Maps; Protein Transport; Proteins; Proteolysis; Proteome; Proteomics; Proteostasis; Quality of Life; RNA 3' End Processing; RNA Polymerase II; RNA Precursors; RNA Processing, Post-Transcriptional; RNA Splicing; RNA, Messenger; RNA-Binding Proteins; Randomized Controlled Trials as Topic; Receptors, Chimeric Antigen; Ribosomes; S-Phase Kinase-Associated Proteins; SKP Cullin F-Box Protein Ligases; Saccharomyces cerevisiae; Saccharomyces cerevisiae Proteins; Seasons; Staining and Labeling; Stress, Physiological; T-Lymphocytes; Telemedicine; Ubiquitin; Ubiquitination; Valosin Containing Protein; Victoria; Volatile Organic Compounds; alpha-Synuclein</t>
-        </is>
-      </c>
+          <t>Konieczny, Piotr</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jin, Rongsheng</t>
+          <t>Kvon, Evgeny</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Administration, Oral; Amino Acids; Bacterial Proteins; Bacterial Toxins; Biological Transport; Botulinum Toxins; Botulinum Toxins, Type A; Breast Neoplasms; CRISPR-Associated Protein 9; CRISPR-Cas Systems; Calcitonin Gene-Related Peptide; Cattle; Cecum; Cisplatin; Clostridioides difficile; Clostridium Infections; Clostridium botulinum; Clustered Regularly Interspaced Short Palindromic Repeats; Cryoelectron Microscopy; Dogs; Endothelial Cells; Enterotoxins; Epitopes; Gene Editing; Genetic Code; Genotype; Glucosyltransferases; Inflammation Mediators; Mammary Neoplasms, Animal; Membrane Glycoproteins; Molecular Conformation; Monomeric GTP-Binding Proteins; Multigene Family; Neoplasms; Neovascularization, Pathologic; Nerve Tissue Proteins; Neurogenic Inflammation; Neurons, Afferent; Neurotoxins; Peptide Hydrolases; Pericytes; Phenotype; Point Mutation; Protease Inhibitors; Protein Binding; Protein Domains; Proteins; Proteolysis; Receptors, Neurokinin-1; Recombination, Genetic; Saccharomyces cerevisiae; Signal Transduction; Single-Domain Antibodies; Structure-Activity Relationship; Substance P; Synaptic Vesicles; Tumor Microenvironment; Wnt Signaling Pathway; cdc42 GTP-Binding Protein; rho GTP-Binding Proteins; rhoA GTP-Binding Protein</t>
+          <t>Africa; Alleles; Animal Fins; Australia; Autism Spectrum Disorder; Autistic Disorder; Base Sequence; Binding Sites; Brain; Brain Neoplasms; CCCTC-Binding Factor; CRISPR-Cas Systems; Cell Culture Techniques; Cell Cycle Proteins; Chromatin; Chromosomal Proteins, Non-Histone; Chromosomes; Chromosomes, Human, Pair 8; Clinical Relevance; Cohesins; Congenital Abnormalities; Craniofacial Abnormalities; DNA; DNA Transposable Elements; DNA, Intergenic; Ectopic Gene Expression; Enhancer Elements, Genetic; Epigenome; Epigenomics; Evolution, Molecular; Extinction, Biological; Extremities; Fetal Heart; Fishes; Gain of Function Mutation; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Developmental; Gene Rearrangement; Genes, Reporter; Genetic Code; Genetic Variation; Genome; Genome Size; Genomics; Glioma; Heart Diseases; Hedgehog Proteins; Homeodomain Proteins; Intellectual Disability; Introns; Isocitrate Dehydrogenase; Karyotype; Limb Buds; Locomotion; Marsupialia; MicroRNAs; Mutation; Nucleotide Motifs; Organoids; Otx Transcription Factors; Phenotype; Phylogeny; Piwi-Interacting RNA; Polydactyly; Polymorphism, Single Nucleotide; Promoter Regions, Genetic; Protein Binding; RNA, Long Noncoding; Regulatory Sequences, Nucleic Acid; SELEX Aptamer Technique; Single-Cell Analysis; South America; Time Factors; Transcription Factors; Transcriptional Activation; Virulence; Zinc Fingers</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jusiak, Barbara</t>
+          <t>LaFerla, Frank</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Animals, Genetically Modified; Drosophila Proteins; Drosophila melanogaster; Gene Expression; Transcription Factors</t>
+          <t>5' Untranslated Regions; ATP-Binding Cassette Transporters; Aged; Aged, 80 and over; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Apolipoproteins E; Asian; Astrocytes; Biomarkers; Brain; CRISPR-Associated Proteins; CRISPR-Cas Systems; Case-Control Studies; Cathepsin D; Chromatin Immunoprecipitation Sequencing; Chromosomes, Human, X; Clustered Regularly Interspaced Short Palindromic Repeats; Cognition; Cuprizone; Data Management; Demyelinating Diseases; Disease Progression; Down Syndrome; Down-Regulation; Doxycycline; Endoribonucleases; Fibroblasts; Gastrointestinal Microbiome; Gene Editing; Gene Expression Profiling; Gene Expression Regulation; Gene Knock-In Techniques; Genetic Predisposition to Disease; Genetic Variation; Genome-Wide Association Study; Genotype; Glial Fibrillary Acidic Protein; HEK293 Cells; Hispanic or Latino; Induced Pluripotent Stem Cells; Laboratories; Leadership; Lipidomics; Longevity; Membrane Glycoproteins; Metabolome; Metabolomics; Microbiota; Microglia; Mobile Applications; Mutation; Myeloid Differentiation Factor 88; NF-kappa B; Neurodegenerative Diseases; Neuroglia; Neuroimaging; Neurons; Phagocytosis; Phenotype; Plaque, Amyloid; Polymorphism, Single Nucleotide; Proteomics; RNA Splicing; RNA, Messenger; RNA-Seq; Receptors, Immunologic; Registries; Resilience, Psychological; Response Elements; Rodentia; Sex Characteristics; Signal Transduction; Single-Cell Gene Expression Analysis; Tauopathies; Tetracycline; Transcriptome; Translational Research, Biomedical; X Chromosome Inactivation; tau Proteins</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kiser, Philip</t>
+          <t>Lamb, Joleah</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ambystoma; Amphibian Proteins; Arrestin; Arrestins; Biocatalysis; Bromocriptine; CRISPR-Cas Systems; Calcium; Camelids, New World; Carotenoids; Carrier Proteins; Catalysis; Catalytic Domain; Cattle; Cell-Penetrating Peptides; Ceramides; Cone Opsins; Crystallography, X-Ray; Cyclic AMP; Cyclic Nucleotide Phosphodiesterases, Type 6; Diabetic Retinopathy; Dioxygenases; Dogs; Drug Repositioning; Drug Therapy, Combination; Ear Auricle; Ependymoglial Cells; Evolution, Molecular; Eye Proteins; Fatty Acids, Unsaturated; Fungal Proteins; Gene Editing; Gene Library; HEK293 Cells; Hydrolysis; Iron; Isomerases; Isomerism; Leber Congenital Amaurosis; Lipids; Liposomes; Macular Degeneration; Models, Molecular; Mutation; NADP; Nanoparticles; Neuroglia; Nitric Oxide; Opsins; Oxygen; Oxygenases; Phenyl Ethers; Phosphorylation; Photoreceptor Cells, Vertebrate; Propanolamines; Protein Conformation; Protein Multimerization; Receptors, Adiponectin; Receptors, G-Protein-Coupled; Retina; Retinal Cone Photoreceptor Cells; Retinal Degeneration; Retinal Pigment Epithelium; Retinal Pigments; Retinal Rod Photoreceptor Cells; Retinaldehyde; Retinitis Pigmentosa; Retinoids; Rhodopsin; Ribonucleoproteins; Single-Domain Antibodies; Vision, Ocular; Vitamin A; Xenopus Proteins; Xenopus laevis; cis-trans-Isomerases</t>
+          <t>Acclimatization; Aquaculture; Behavioral Sciences; Biodiversity; Cities; Conservation of Natural Resources; Disease Outbreaks; Ecological and Environmental Phenomena; Ecosystem; Environmental Microbiology; Environmental Science; Germ Cells, Plant; Hot Temperature; Housing; Indonesia; Kelp; Macrocystis; Marine Biology; Microbiota; Motivation; Mutation; Oceans and Seas; One Health; Policy; Refugees; Remote Sensing Technology; Reproduction; Seaweed; Temperature; Water</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Lawson, Devon A</t>
+          <t>Lander, Arthur</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>B7-H1 Antigen; Blood-Brain Barrier; Brain; Brain Neoplasms; Breast; Breast Neoplasms; CD8-Positive T-Lymphocytes; Cell Line, Tumor; Cholesterol; Circadian Clocks; Circadian Rhythm; Colorectal Neoplasms; Cytokines; Endothelial Cells; Epithelial Cells; Gene Expression Profiling; Genomics; Hair; Hair Follicle; Hyaluronan Receptors; Immune Checkpoint Inhibitors; Immune Tolerance; Immunity; Immunosuppression Therapy; Melanocytes; Microglia; Myeloid-Derived Suppressor Cells; Nevus; Organic Chemicals; Osteopontin; Receptors, Granulocyte-Macrophage Colony-Stimulating Factor; Signal Transduction; Single-Cell Analysis; Stem Cells; Treatment Outcome; Tumor Microenvironment</t>
+          <t>Aging; Algorithms; Animals, Genetically Modified; Body Patterning; Brain; CHO Cells; Carcinogenesis; Cartilage; Cell Competition; Cell Cycle Proteins; Cell Differentiation; Cell Lineage; Cell Plasticity; Cell Proliferation; Chondrocytes; Chromatin; Chromosomal Proteins, Non-Histone; Cluster Analysis; Cohesins; Communication; Computational Biology; Congenital Abnormalities; Cricetulus; Data Analysis; Databases, Factual; De Lange Syndrome; Drosophila Proteins; Drosophila melanogaster; Drug Resistance, Neoplasm; Embryo, Mammalian; Embryonic Development; Entropy; Epithelial Cells; Face; Fracture Healing; Fusion Proteins, bcr-abl; Gastrulation; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Developmental; Gene Expression Regulation, Neoplastic; Gene Regulatory Networks; Green Fluorescent Proteins; Growth and Development; HEK293 Cells; Hedgehog Proteins; Heterozygote; Homeostasis; Imaging, Three-Dimensional; Immunity, Innate; Leukemia, Myelogenous, Chronic, BCR-ABL Positive; Machine Learning; Mass Behavior; Melanoma; Metronidazole; Morphogenesis; Mutation; Myelopoiesis; Neoplasms; Nitroreductases; Organoids; Osteoblasts; Osteogenesis; PTEN Phosphohydrolase; Periosteum; Phenotype; Pregnancy; Prodrugs; Promoter Regions, Genetic; Protein Engineering; Protein Kinase Inhibitors; Proteins; Proto-Oncogene Proteins B-raf; RNA; Recombinant Proteins; Retina; Saccharomyces cerevisiae; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Skin Neoplasms; Stem Cells; Systems Biology; TOR Serine-Threonine Kinases; Transcriptome; Tyrosine Kinase Inhibitors; Vibrio; Wings, Animal; X-Ray Microtomography; Zebrafish</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Marangoni, Francesco</t>
+          <t>Lane, Thomas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B7-H1 Antigen; CD8-Positive T-Lymphocytes; Cell Line, Tumor; Circadian Clocks; Circadian Rhythm; Colorectal Neoplasms; Cyclodextrins; Cytokines; Immune Checkpoint Inhibitors; Immune Tolerance; Immunosuppression Therapy; Immunotherapy; Inducible T-Cell Co-Stimulator Protein; Interleukin-2; Intravital Microscopy; Lymphocyte Activation; Melanoma; Melanoma, Experimental; Metal-Organic Frameworks; Metals; Myeloid-Derived Suppressor Cells; Neoplasms; Programmed Cell Death 1 Receptor; Proteins; Signal Transduction; Single-Cell Analysis; Solubility; T-Lymphocytes; T-Lymphocytes, Regulatory; Tumor Microenvironment</t>
+          <t>Activin Receptors; Adiposity; Aged; Aging; Allergy and Immunology; Alzheimer Disease; Amino Acid Sequence; Amino Acids; Amyloid beta-Peptides; Aneuploidy; Angiotensin-Converting Enzyme 2; Animals, Genetically Modified; Anosmia; Apolipoprotein E4; Astrocytes; Axons; B-Lymphocytes; Bacterial Infections; Bone Marrow Transplantation; Brain; CD4 Antigens; CD4-Positive T-Lymphocytes; COVID-19; Catalytic Domain; Cells, Cultured; Central Nervous System; Cerebral Cortex; Chemokine CXCL1; Cognition; Cognitive Dysfunction; Coronavirus; Coronavirus 3C Proteases; Coronavirus Infections; Crystallography, X-Ray; Cystatins; Cysteine; Cytokine Release Syndrome; Dementia; Demyelinating Diseases; Disease Progression; Disulfides; Down Syndrome; Dysgeusia; Encephalitis; Encephalitis, Viral; Encephalomyelitis, Autoimmune, Experimental; Forkhead Transcription Factors; Gene Expression; Gene Expression Profiling; Hashimoto's encephalitis; Headache; Human Embryonic Stem Cells; Immune System; Immunity; Immunity, Innate; Induced Pluripotent Stem Cells; Infant; Inflammation; Inflammation Mediators; Integrases; Ischemia; Lung; Lymphocyte Activation; Lysosomal Membrane Proteins; Macrophages; Matrix Metalloproteinase 9; Memory Consolidation; Meningitis; Mental Fatigue; Microglia; Mitochondrial Diseases; Models, Molecular; Monocytes; Monomeric GTP-Binding Proteins; Multiple Sclerosis; Murine hepatitis virus; Muscle, Skeletal; Mutation; Myelin Sheath; Neural Stem Cells; Neurodegenerative Diseases; Neuroglia; Neuroinflammatory Diseases; Neurons; Neutrophils; Oxidation-Reduction; Pandemics; Parkinson Disease; Plaque, Amyloid; Protein Multimerization; RNA, Messenger; RNA, Viral; Receptor Protein-Tyrosine Kinases; Remyelination; Risk Factors; Rodentia; SARS-CoV-2; Secretome; Sequence Analysis, RNA; Serine Endopeptidases; Signal Transduction; Single Molecule Imaging; Spinal Cord; Stem Cells; Stroke; Sweden; Synaptic Transmission; T-Lymphocytes; T-Lymphocytes, Regulatory; Tetracyclines; Virus Diseases; Virus Replication; White Matter</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Othy, Shivashankar</t>
+          <t>Lara-Gonzalez, Pablo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Adenosine Diphosphate; Adjuvants, Immunologic; Aged; Aged, 80 and over; Alzheimer Disease; Analgesics; Anti-Inflammatory Agents; Antibodies, Neutralizing; Antibodies, Viral; CD8-Positive T-Lymphocytes; Calcium; Calcium Signaling; Cell Line, Tumor; Cognitive Dysfunction; Coriandrum; Corticotropin-Releasing Hormone; Down-Regulation; Ethnicity; Fibrosis; Galectin 3; Hemagglutinin Glycoproteins, Influenza Virus; Homeostasis; Immune Checkpoint Inhibitors; Immunotherapy; Incidence; Induced Pluripotent Stem Cells; Inducible T-Cell Co-Stimulator Protein; Influenza A Virus, H5N1 Subtype; Influenza Vaccines; Interleukin-2; Intravital Microscopy; Lipid A; Longitudinal Studies; Lymphocyte Activation; Lymphocytes; Macrophages; Melanoma; Melanoma, Experimental; Membrane Glycoproteins; Mice, Inbred BALB C; Microglia; Molecular Docking Simulation; Muscle, Skeletal; Neoplasms; Neural Stem Cells; Neurons; Oligodeoxyribonucleotides; Orthomyxoviridae Infections; Patient Reported Outcome Measures; Plant Extracts; Plants, Medicinal; Polysorbates; Potassium Channel Blockers; Programmed Cell Death 1 Receptor; Prospective Studies; Receptors, Immunologic; Receptors, Purinergic; Risk Factors; Saponins; Self Report; Signal Transduction; Squalene; Synapses; T-Lymphocytes; T-Lymphocytes, Regulatory; Tannins; Transcriptome</t>
+          <t>Aging; Anaphase-Promoting Complex-Cyclosome; Antineoplastic Agents; CDC2 Protein Kinase; Caenorhabditis elegans; Caenorhabditis elegans Proteins; Cdc20 Proteins; Cell Cycle; Cell Cycle Checkpoints; Cell Cycle Proteins; Cell Differentiation; Cell Proliferation; Centers for Disease Control and Prevention, U.S.; Chromosome Segregation; Clustered Regularly Interspaced Short Palindromic Repeats; Cues; Cyclin B; Cyclin B1; Cyclin B2; Cyclins; Embryo, Nonmammalian; Embryonic Development; Ependymoglial Cells; Genomics; Germ Cells; Kinetochores; M Phase Cell Cycle Checkpoints; Microscopy; Microtubule-Associated Proteins; Mitosis; Neocortex; Neoplasms; Phosphorylation; Protein Serine-Threonine Kinases; Repressor Proteins; Spindle Apparatus; Tetratricopeptide Repeat</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pathak, Medha</t>
+          <t>Lee, Grace</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Brain; Calcium; Cell Membrane; Cell Movement; Cholesterol; Cytokinesis; Ion Channels; Keratinocytes; Mechanotransduction, Cellular; Neural Stem Cells; Pseudopodia</t>
+          <t>5'-Nucleotidase; Absorptiometry, Photon; Adenosine; Adipocytes; Aged; Aging; Alternative Splicing; Anti-Bacterial Agents; Antigens, CD; Base Sequence; Bile Acids and Salts; Biological Evolution; Biomarkers; Bone Density; Bone Diseases, Metabolic; Brain; Breast Neoplasms; COVID-19; COVID-19 Drug Treatment; Cadherins; Caenorhabditis elegans; Caenorhabditis elegans Proteins; Cell Death; Cell Line, Tumor; Cell Movement; Cell Proliferation; Chromatin; Chromosomes; Colonic Neoplasms; Cricetinae; DNA; DNA Transposable Elements; DNA-Binding Proteins; Diet; Disease Progression; Drug-Related Side Effects and Adverse Reactions; Dysbiosis; Early Detection of Cancer; Eating; Ecological and Environmental Phenomena; Epigenesis, Genetic; Epigenome; Epigenomics; Epithelial-Mesenchymal Transition; Eukaryotic Cells; Evolution, Molecular; Eye Neoplasms; Fabry Disease; Fatty Acid-Binding Proteins; Fatty Liver; Fellowships and Scholarships; Femur Neck; Fertility; Fructose; Gastrointestinal Microbiome; Gene Expression Profiling; Genetics; Genetics, Population; Genome; Genome, Human; Genomic Instability; Genomics; HEK293 Cells; Health; Heterochromatin; Homeostasis; Huntingtin Protein; Huntington Disease; Individuality; Kidney; Lipogenesis; Lipopolysaccharides; Liver; Longevity; Lung; Mechanistic Target of Rapamycin Complex 1; Metagenomics; Methyltransferases; Mevalonic Acid; Mice, Nude; Moles; Multiomics; Multiprotein Complexes; Mutation; NAD; Necroptosis; Neoplasm Metastasis; Neoplasms; Niacinamide; Nicotinamide-Nucleotide Adenylyltransferase; Non-alcoholic Fatty Liver Disease; Nuclear Proteins; Nutrients; Ophthalmologic Surgical Procedures; Orbital Implants; Osteoporosis; Oxidative Stress; Parasites; Pharmaceutical Preparations; Phosphoglycerate Dehydrogenase; Phosphorylation; Phosphotransferases (Alcohol Group Acceptor); Proteasome Endopeptidase Complex; Protein Binding; Protein Stability; Proteolysis; Pyridinium Compounds; RNA; RNA Methylation; RNA Splicing; RNA, Messenger; Receptor-Interacting Protein Serine-Threonine Kinases; Recombination, Genetic; Repressor Proteins; Retroelements; Ribosomal Protein S6 Kinases, 70-kDa; SARS-CoV-2; Sequence Homology; Serine; Signal Transduction; Social Responsibility; Species Specificity; TOR Serine-Threonine Kinases; Tetraodontiformes; Transcription, Genetic; Transcriptome; Ubiquitin; Ubiquitin-Protein Ligases; Ubiquitination; Urodela; Virus Replication</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Skowronska-Krawczyk, Dorota</t>
+          <t>Lodoen, Melissa</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Aged; Aging; Axonal Transport; Cell Differentiation; Cell Membrane; Cellular Senescence; Ceramides; Chromatin; Cyclic Nucleotide Phosphodiesterases, Type 6; Cytoskeletal Proteins; DNA Damage; DNA-Binding Proteins; Docosahexaenoic Acids; Endonucleases; Eye Proteins; Fatty Acids, Unsaturated; Glaucoma; Glaucoma, Open-Angle; Glycoproteins; Glycosylation; Integrases; Intraocular Pressure; Leber Congenital Amaurosis; Lipid Metabolism; Lipids; Macular Degeneration; Membrane Proteins; Microscopy; Nonlinear Optical Microscopy; Organoids; Pluripotent Stem Cells; Progeria; Proteins; Proteome; Proteomics; Receptors, Adiponectin; Retina; Retinal Degeneration; Retinal Ganglion Cells; Retinal Pigment Epithelium; Retinitis Pigmentosa; Spectrum Analysis, Raman; Trabecular Meshwork; cis-trans-Isomerases</t>
+          <t>AIDS Dementia Complex; Acquired Immunodeficiency Syndrome; Adaptive Immunity; Adaptor Proteins, Signal Transducing; Allergy and Immunology; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Anti-Infective Agents; Antigen Presentation; Astrocytes; Blood Coagulation; Blood-Brain Barrier; Brain; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Capparis; Caspase 1; Caspase 8; Caspases; Cell Death; Cell Membrane; Cell Proliferation; Central Nervous System; Central Nervous System Infections; Cerebrovascular Circulation; Chemokine CCL2; Chemokines; Clustered Regularly Interspaced Short Palindromic Repeats; Coculture Techniques; Cognition; Coinfection; Communicable Disease Control; Cytokines; Dendritic Cells; Encephalitis; Endothelial Cells; Fibrin; Gasdermins; Gene Regulatory Networks; HIV Infections; Heart Transplantation; Hemodynamics; Hippo Signaling Pathway; Host-Parasite Interactions; Host-Pathogen Interactions; Immunity; Immunity, Innate; Induced Pluripotent Stem Cells; Infections; Inflammasomes; Inflammation; Inflammation Mediators; Intercellular Adhesion Molecule-1; Interleukin-1beta; Ion Channels; Lipoproteins; Liver; Macrophages; Mechanotransduction, Cellular; Memory T Cells; Metabolic Diseases; Microglia; Microscopy; Microvessels; Monocytes; Myeloid Cells; NF-kappa B; NLR Family, Pyrin Domain-Containing 3 Protein; Necroptosis; Neoplasm Recurrence, Local; Neurodegenerative Diseases; Neuroimaging; Neuroinflammatory Diseases; Neuroprotection; Neuroprotective Agents; Parasites; Peptides; Perfusion; Persistent Infection; Phagocytosis; Phenotype; Plaque, Amyloid; Platelet Aggregation; Protozoan Proteins; Receptor-Interacting Protein Serine-Threonine Kinases; Receptors, CCR2; Receptors, Scavenger; Signal Transduction; Syk Kinase; T-Lymphocytes; T-Lymphocytes, Regulatory; THP-1 Cells; Thromboinflammation; Toxoplasma; Toxoplasmosis; Toxoplasmosis, Animal; Toxoplasmosis, Cerebral; Transcription Factor RelA; Virulence; Virulence Factors; nan; tdTomato</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tombola, Francesco</t>
+          <t>Long, Anthony</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Biosensing Techniques; Electronic Nose; Ion Channels; Ligands; Lipid Bilayers; Magnoliopsida; Nanowires; Protons; Receptors, Odorant; Tracheophyta</t>
+          <t>Adaptation, Biological; Aging; Alleles; Antibody Formation; Biological Evolution; Borrelia burgdorferi; Breeding; CRISPR-Cas Systems; Chromatin; Chromatin Immunoprecipitation Sequencing; Chromosome Mapping; Computers; Confidence Intervals; CpG Islands; DNA; DNA Methylation; Data Analysis; Deer; Diptera; Drosophila melanogaster; Ecological and Environmental Phenomena; Gene Frequency; Gene Knockout Techniques; Genes, MHC Class II; Genetic Variation; Genetics; Genetics, Population; Genome, Fungal; Genome-Wide Association Study; Genomics; Genotype; Haplotypes; High-Throughput Nucleotide Sequencing; Immunization; Immunoglobulin G; Incubators; Insecticide Resistance; Insecticides; Kansas; Lyme Disease; Macrophages; Malathion; Models, Genetic; Multifactorial Inheritance; Nitric Oxide; OspA protein; Parents; Peromyscus; Persistent Infection; Phagocytes; Phenotype; Photoperiod; Polymorphism, Single Nucleotide; Quantitative Trait Loci; Reactive Nitrogen Species; Recombination, Genetic; Reproduction; Reproduction, Asexual; Reverse Genetics; Saccharomyces cerevisiae; Seasons; Selection, Genetic; Translational Research, Biomedical</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Villalta, Sergio Armando</t>
+          <t>Luo, Ray</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Amidohydrolases; Brain; Brain Neoplasms; Breast Neoplasms; CD8-Positive T-Lymphocytes; Cross-Sectional Studies; DNA-Binding Proteins; Disease Progression; Endogenous Retroviruses; Enzyme Inhibitors; Epigenesis, Genetic; Fibrosis; Galectin 3; Gene Expression; Hand Strength; Heterochromatin; Heterografts; Hyperalgesia; Immunologic Memory; Immunophenotyping; Killer Cells, Natural; Leukocytes, Mononuclear; Lipids; Macrophages; Mice, Inbred mdx; Microglia; Monocytes; Muscle, Skeletal; Muscular Dystrophy, Duchenne; Myositis; Myositis, Inclusion Body; Outcome Assessment, Health Care; PPAR alpha; Pain; RNA, Nuclear; Severity of Illness Index; Transcriptome; Treatment Outcome; Vacuoles</t>
+          <t>Adaptor Proteins, Signal Transducing; Adenosine Triphosphate; Allosteric Regulation; Allosteric Site; Amines; Amino Acids; Antineoplastic Agents; Artificial Cells; Binding Sites; Biocatalysis; Biomarkers; Bioreactors; Budgets; Carcinoma, Hepatocellular; Cats; Cell Line, Tumor; Computational Biology; Dendritic Cells; Dimerization; Drug Delivery Systems; Early Detection of Cancer; Entropy; Escherichia coli; Gas Chromatography-Mass Spectrometry; Glucose 1-Dehydrogenase; Green Fluorescent Proteins; Head and Neck Neoplasms; Hippo Signaling Pathway; Hydrogels; Immunity, Cellular; Intrinsically Disordered Proteins; Liver Cirrhosis; Liver Neoplasms; Loss of Function Mutation; Lung Neoplasms; Models, Molecular; Molecular Dynamics Simulation; Mutation; Mutation, Missense; NAD; NADP; Neoplasms; Neurofibromin 2; Nicotinamide Mononucleotide; Normal Distribution; Oxidation-Reduction; Oxidoreductases; Peptides; Phase Separation; Polymers; Protein Binding; Protein Biosynthesis; Protein Conformation; Protein Serine-Threonine Kinases; Protein Tyrosine Phosphatase, Non-Receptor Type 11; Proteins; RNA, Messenger; Signal Transduction; Solutions; Solvents; Static Electricity; T-Lymphocytes; Viral Vaccines; Volatile Organic Compounds; mRNA Vaccines</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Wagar, Lisa</t>
+          <t>Lur, Gyorgy</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Adaptive Immunity; Adjuvants, Immunologic; Adolescent; Antibodies, Neutralizing; Antibodies, Viral; Antibody Formation; Antigens; Antigens, Viral; B-Lymphocytes; Bangladesh; CD4-Positive T-Lymphocytes; CD40 Ligand; COVID-19; Cell Culture Techniques; Cells, Cultured; Child; Child, Preschool; Environmental Exposure; Hemagglutinin Glycoproteins, Influenza Virus; Immunity; Immunoinformatics; Immunologic Memory; Infant; Influenza A Virus, H1N1 Subtype; Influenza A virus; Influenza Vaccines; Influenza, Human; Lymphoma, Follicular; Memory B Cells; Nanoparticles; Organ Specificity; Organoids; Palatine Tonsil; Receptors, Antigen, T-Cell; SARS-CoV-2; Sex Characteristics; Sex Factors; T Follicular Helper Cells; T-Lymphocytes; T-Lymphocytes, Helper-Inducer; Th1 Cells; Toll-Like Receptor 7; Tumor Microenvironment; Vaccination; Vaccines; Vaccines, Subunit; Young Adult</t>
+          <t>Action Potentials; Adenosine Triphosphate; Adolescent; Adverse Childhood Experiences; Aging; Amblyopia; Animal Care Committees; Anticonvulsants; Basolateral Nuclear Complex; Brain; Calcium; Calcium Channels; Central Nervous System; Cholinergic Neurons; Cognition; Computer Simulation; Decision Making; Electroencephalography; Electronic Nicotine Delivery Systems; Electrophysiology; Epilepsy; Epilepsy, Temporal Lobe; Genetics; Habenula; Hippocampus; Magnetic Fields; Memory; Memory Consolidation; Memory, Short-Term; Mental Disorders; Movement; Nanoparticles; Neural Pathways; Neurons; Neurosciences; Nicotine; Nicotinic Agonists; Optogenetics; Parietal Lobe; Patch-Clamp Techniques; Postsynaptic Potential Summation; Primary Visual Cortex; Psychomotor Performance; Pyramidal Cells; Quality of Life; Receptors, Purinergic P2; Rejuvenation; Reward; Seizures; Software; Stress, Psychological; Synapses; Synaptic Transmission; Visual Acuity; Wakefulness</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Yu, Alvin</t>
+          <t>Lutterschmidt, Deborah</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3' Untranslated Regions; Acoustics; Acrylic Resins; Aged; Alanine; Antiviral Agents; Asian People; Ataxia; Blepharoplasty; Bone Density; Bone and Bones; Brain; British Columbia; Butadienes; COVID-19; COVID-19 Vaccines; California; Canada; Cell Line; Cell Nucleus; Cohort Studies; DNA Breaks, Double-Stranded; DNA Repair; Diterpenes; Dose-Response Relationship, Radiation; Electrons; Exosome Multienzyme Ribonuclease Complex; Eyelids; Feasibility Studies; HEK293 Cells; Hand Disinfection; HeLa Cells; Health Knowledge, Attitudes, Practice; Hepatitis C; Hippocampus; Incidence; Infection Control; Interrupted Time Series Analysis; Kv1.1 Potassium Channel; Ligands; Long-Term Potentiation; Lung; Masks; Molecular Conformation; Molecular Dynamics Simulation; Myokymia; Neoplasms; Neurogenesis; Osteoporosis; Pandemics; Parents; Particle Accelerators; Patient Acceptance of Health Care; Phantoms, Imaging; Phosphorylation; Physical Distancing; Pilot Projects; Plant Extracts; Poly A; Polyadenylation; Polyesters; Polymorphism, Single Nucleotide; Polystyrenes; Printing, Three-Dimensional; Protein Conformation; RNA Precursors; RNA Processing, Post-Transcriptional; RNA Splice Sites; RNA Stability; RNA, Messenger; RNA, Nuclear; Radiometry; Radiotherapy Dosage; Radiotherapy Planning, Computer-Assisted; Reproducibility of Results; Retrospective Studies; Ribonucleoprotein, U1 Small Nuclear; SARS-CoV-2; Substance Abuse, Intravenous; Suture Techniques; Telemedicine; Tomography, X-Ray Computed; Transcriptome; Translocation, Genetic; Treatment Outcome; Ubiquitin; Ubiquitin-Protein Ligases; Vaccination; Vaccination Hesitancy; Vaccines; Wastewater; Wastewater-Based Epidemiological Monitoring; Water; X-Ray Microtomography; Young Adult</t>
+          <t>Behavior, Animal; Body Temperature Regulation; Brain; Ecological and Environmental Phenomena; Hibernation; Hormones; Life History Traits; Neurobiology; Periodicity; Physiology, Comparative; Seasons; Stress, Physiological; Temperature; nan</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Monuki, Edwin</t>
+          <t>MacGregor, Grant</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Aged; Aging; Amyloidogenic Proteins; Body Patterning; Brain; Cell Differentiation; Cell Lineage; Cerebellum; Cerebral Hemorrhage; Cholesterol; Choroid Plexus; Corpus Striatum; DNA Methylation; Embryonic Development; Epigenome; Epithelial Cells; Glycosylation; Homeostasis; Huntingtin Protein; Huntington Disease; Hydrocephalus; Ion Channels; Lewy Bodies; Lewy Body Disease; Mechanotransduction, Cellular; Membrane Proteins; Neural Stem Cells; Neurogenesis; Neurons; Organoids; Phenotype; Plaque, Amyloid; Pluripotent Stem Cells; Records; Staining and Labeling; Transcriptome; Virion</t>
+          <t>ATP-Binding Cassette Transporters; Adenosine Triphosphate; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Apolipoproteins E; Astrocytes; Brain; Brain-Derived Neurotrophic Factor; Coronavirus Infections; Cuprizone; Cystatins; DNA, Mitochondrial; Demyelinating Diseases; Diabetes Mellitus; Diabetic Cardiomyopathies; Disease Progression; Energy Metabolism; Gastrointestinal Microbiome; Gene Expression Profiling; Gene Knock-In Techniques; Genetic Variation; Genotype; Heart Transplantation; Insulin; Integrases; Membrane Glycoproteins; Metabolomics; Microbiota; Microglia; Mitochondria; Mitochondria, Heart; Murine hepatitis virus; Mutation; Mutation, Missense; Myocardium; Neuroglia; Neuroinflammatory Diseases; Neurons; Oxidative Phosphorylation; Phagocytosis; Phosphatidylinositol 3-Kinases; Plaque, Amyloid; Proto-Oncogene Proteins c-akt; RNA Splicing; Reactive Oxygen Species; Receptor, trkB; Receptors, Immunologic; Resilience, Psychological; Sex Characteristics; Signal Transduction; Single-Cell Analysis; T-Lymphocytes, Regulatory; Tauopathies; Transcriptome; tau Proteins</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Mahler, Stephen</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Adolescent; Adolescent Development; Adverse Childhood Experiences; Aerosols; Amphetamine; Analgesics, Opioid; Anhedonia; Arachidonic Acids; Basal Forebrain; Basolateral Nuclear Complex; Brain; Cannabidiol; Cannabis; Chromatography, High Pressure Liquid; Clozapine; Cognition; Conditioning, Operant; Corticotropin-Releasing Hormone; Designer Drugs; Dopamine; Dopaminergic Neurons; Dose-Response Relationship, Drug; Dronabinol; Endocannabinoids; Genetics; Growth and Development; Learning; Mass Spectrometry; Microglia; Microsomes; Morphine; Motivation; Neural Pathways; Neurobiology; Neuronal Plasticity; Nucleus Accumbens; Ovarian Follicle; Ovarian Reserve; Polyunsaturated Alkamides; Prefrontal Cortex; Rats, Long-Evans; Rats, Sprague-Dawley; Reward; Substance-Related Disorders; Tandem Mass Spectrometry; Vaping; Ventral Tegmental Area; gamma-Aminobutyric Acid</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Martinez, Christopher</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Aquatic Organisms; Biological Evolution; Biomechanical Phenomena; Carbon; Characidae; Coral Reefs; Ecological and Environmental Phenomena; Ecosystem; Evolution, Molecular; Extinction, Biological; Feeding Behavior; Fishes; Genetic Speciation; Information Services; Jaw; Mandible; Motion; Movement; Natural History; Perciformes; Phylogeny; Predatory Behavior; Schools; Social Behavior; Social Factors; Somatotypes; Swimming; Water</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Martiny, Adam</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Anti-Bacterial Agents; Bacteria; Bayes Theorem; Biodiversity; Biomass; California; Carbon; Carbon Cycle; Climate Change; Drug Resistance, Bacterial; Drug Resistance, Multiple, Bacterial; Earth, Planet; Ecological and Environmental Phenomena; Ecosystem; Ecotype; El Nino-Southern Oscillation; Escherichia coli; Escherichia coli Infections; Food Chain; Genetic Variation; Genetics; Genomics; Indian Ocean; Life History Traits; Metagenome; Metagenomics; Microbial Sensitivity Tests; Microbiology; Microbiota; Nitrates; Nitrogen; Nitrogen Fixation; Nutrients; Oceanography; Oceans and Seas; Phosphates; Phylogeny; Phylogeography; Phytoplankton; Plankton; Prochlorococcus; Proteome; Seasons; Seawater; Soil; Soil Microbiology; Synechococcus; Temperature; Uncertainty</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Martiny, Jennifer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Actinomycetales; Ambulatory Care Facilities; American Indian or Alaska Native; Anti-Bacterial Agents; Bacteria; Bays; Bifidobacterium; Biodiversity; Biological Evolution; Biotechnology; Carbohydrates; Carbon; Carbon Sequestration; Cardiovascular Diseases; Climate Change; Computational Biology; Curriculum; Cyanobacteria; DNA Damage; DNA Methylation; DNA Repair; Desert Climate; Desiccation; Diabetes Mellitus; Diet; Dietary Fiber; Drought Resistance; Droughts; Earth, Planet; Ecological and Environmental Phenomena; Ecology; Ecosystem; Electrons; Feces; Fermentation; Gastrointestinal Microbiome; Gene Transfer, Horizontal; Genetic Engineering; Genetic Variation; Genomics; Greenhouse Gases; Human Body; Internship and Residency; Interspersed Repetitive Sequences; Leadership; Life History Traits; Masks; Metadata; Metagenome; Metagenomics; Microbiology; Microbiota; Mutation; Mycobiome; Neoplasms; New Mexico; Nitrogen; Nitrogen Fixation; Noncommunicable Diseases; Ohio; Oregon; Pacific Island People; Phylogeny; Plant Leaves; Plasmids; Prebiotics; Probiotics; RNA, Ribosomal, 16S; Reproducibility of Results; Resilience, Psychological; Schools; Soil; Soil Microbiology; Stress, Physiological; Time Factors; Uncertainty; Water Purification; Wildfires; Workflow</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>McHenry, Matthew</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Acclimatization; Animal Communication; Animals, Wild; Behavior, Animal; Biomechanical Phenomena; Climate Change; Communication; Cues; Cypriniformes; Ecological and Environmental Phenomena; Ecosystem; Environment; Escape Reaction; Fisheries; Fishes; Food Chain; Fresh Water; Gait; Genomics; Group Dynamics; Hydrodynamics; Hydrogen-Ion Concentration; Larva; Lateral Line System; Light; Locomotion; Longevity; Mass Behavior; Movement; Ocean Acidification; Oligochaeta; Organizations; Perciformes; Phototaxis; Predatory Behavior; Resilience, Psychological; Robotics; Schools; Scyphozoa; Seawater; Sensation; Sense Organs; Skeleton; Smegmamorpha; Social Behavior; Starfish; Swimming; Technology; Virtual Reality; Water Movements; Zebrafish</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>McNaughton, Bruce</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Action Potentials; Adverse Childhood Experiences; Auditory Cortex; Autistic Disorder; Behavior Therapy; Brain; Brain Diseases; Brain Stem; Cognition; Cognitive Reserve; Computer Simulation; Control Groups; Cues; Deep Learning; Default Mode Network; ET protocol; Electroencephalography; Electronic Mail; Electrophysiological Phenomena; Electrophysiology; Feasibility Studies; GABAergic Neurons; Grid Cells; Gyrus Cinguli; Hallucinogens; Hippocampal Sclerosis; Hippocampus; History, 20th Century; History, 21st Century; Imaging, Three-Dimensional; Ketanserin; Learning; Maze Learning; Memory; Memory Consolidation; Memory Disorders; Memory, Episodic; Memory, Short-Term; Models, Neurological; Neocortex; Nesting Behavior; Neural Networks, Computer; Neuroanatomy; Neuronal Plasticity; Neurons; Neurosciences; Optogenetics; Pilot Projects; Place Cells; Psilocybin; Reward; Schizophrenia; Serotonin 5-HT2 Receptor Antagonists; Silicon; Sleep; Sleep Deprivation; Sleep, REM; Sleep, Slow-Wave; Software; Space Perception; Spatial Navigation; Stroke; Synapses; Systems Theory; Wakefulness</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>McNulty, Reginald</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Allergy and Immunology; Alzheimer Disease; Amino Acids; Anti-Inflammatory Agents; Apoptosis; Bacteria; Bacterial Infections; Bacteriophage P22; Binding Sites; Biological Phenomena; Biomedical Research; Biosimilar Pharmaceuticals; COVID-19; COVID-19 Drug Treatment; CRISPR-Cas Systems; Capsid; Carcinoma, Hepatocellular; Caspase 1; Cell Culture Techniques; Cell Survival; Clostridium acetobutylicum; Clustered Regularly Interspaced Short Palindromic Repeats; Communicable Diseases; Cryoelectron Microscopy; Cryopyrin-Associated Periodic Syndromes; Cytokines; DNA; DNA Damage; DNA Glycosylases; DNA, Mitochondrial; DNA, Viral; Diabetes Mellitus, Type 2; Drug Discovery; Endodeoxyribonucleases; Epithelium; Fluorocarbons; Galium; Gasdermins; Gene Editing; HIV Infections; Heat-Shock Response; Host Microbial Interactions; Imaging, Three-Dimensional; Immune System; Immunity, Innate; Inflammasomes; Inflammation; Inflammation Mediators; Interleukin-1; Interleukin-18; Interleukin-1beta; Ligands; Liver Neoplasms; Macromolecular Substances; Macrophages; Malaria; Mass Spectrometry; Membrane Fluidity; Microscopy, Electron, Transmission; Mitochondria; Mitochondrial Diseases; Molecular Structure; Morbidity; Mutagenesis; Mutation; NLR Family, Pyrin Domain-Containing 3 Protein; National Institute of General Medical Sciences (U.S.); Neoplasms; Non-alcoholic Fatty Liver Disease; Nucleic Acids; Oxidative Stress; Oxides; Pathogen-Associated Molecular Pattern Molecules; Protein Binding; Protein Processing, Post-Translational; Protein Subunits; Proteins; Pyrin; Pyrin Domain; RNA; Signal Transduction; Signal-To-Noise Ratio; Virus Assembly</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Metherate, Raju</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Acetylcholine; Acoustic Stimulation; Alzheimer Disease; Auditory Cortex; Auditory Perception; Auditory Perceptual Disorders; Cognition; Cognitive Dysfunction; Entorhinal Cortex; Hearing; Hippocampus; Interneurons; Neurons; Nicotine; Nicotinic Agonists; Nootropic Agents; Pharmaceutical Preparations; Physiology; Receptors, Nicotinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Mooney, Kailen</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Adaptation, Physiological; Alleles; Ants; Artemisia; Arthropods; Biodiversity; Biological Evolution; Biological Phenomena; Biomass; Biota; Birds; Brassicaceae; Climate; Climate Change; Colorado; Conservation of Natural Resources; Curriculum; Drought Resistance; Droughts; Ecology; Ecosystem; Ecotype; Ficus; Food Chain; Genetic Variation; Herbivory; Home Environment; Host-Parasite Interactions; Insecta; Larva; Lepidoptera; Moths; Natural Resources; Phenotype; Pinus; Plant Development; Plant Leaves; Plants; Predatory Behavior; Quantitative Trait Loci; Schools; Selection, Genetic; Snow; Songbirds; Symbiosis; Trees; Wasps; Water</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Morehouse, Benjamin</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2',5'-oligoadenylate; Allergy and Immunology; Amino Acids; Anti-Infective Agents; Antiviral Agents; Archaea; Autoimmune Diseases; Bacteria; Bacteriophages; Biochemistry; Biological Evolution; CRISPR-Cas Systems; Cell Death; Chromatography, High Pressure Liquid; Cryoelectron Microscopy; Crystallography, X-Ray; Cyclic AMP; Cyclic GMP; Cyclization; Cytosol; Defense Mechanisms; Delivery of Health Care; Drug Resistance, Microbial; Eukaryota; Evolution, Molecular; Genome, Human; Host Microbial Interactions; Immune System; Immunity, Innate; Incidence; Interferons; Ion Channels; Lipopolysaccharides; Membrane Proteins; Microbiology; Microbiota; Molecular Structure; Mutagenesis; NAD; Neoplasms; Nucleic Acids; Nucleotides; Nucleotides, Cyclic; Nucleotidyltransferases; Oligonucleotides; Pandemics; Phage Therapy; Phylogeny; Planets; Postdoctoral Training; Prokaryotic Cells; Proteins; Pyrimidines; Ribonucleotides; Second Messenger Systems; Signal Transduction; Toll-Like Receptor 4; Uridine Monophosphate; Virus Activation; Virus Diseases; Virus Replication; cyclic 3',5'-uridine monophosphate; cyclic guanosine monophosphate-adenosine monophosphate</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Morrissette, Naomi</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Amino Acid Substitution; Amino Acids; Antiparasitic Agents; Apicoplasts; Binding Sites; Biolistics; Cell Shape; Cells, Cultured; Chemistry, Pharmaceutical; Chlamydomonas; Clemastine; Colchicine; Communicable Diseases; Cryptosporidiosis; Cryptosporidium; Cryptosporidium parvum; Cytokinesis; Cytoskeleton; Drug Resistance; Embryophyta; Eukaryota; Fibroblasts; Genes, Essential; Germ Cells; Haploidy; Helminths; Herbicides; Histamine Antagonists; Household Work; Ligands; Macronucleus; Malaria; Meiosis; Micronucleus, Germline; Microtubules; Mitosis; Morbidity; Mutation; Mutation, Missense; Neoplasms; Paclitaxel; Parasites; Paromomycin; Pharmaceutical Preparations; Plasmids; Protozoan Proteins; Recombination, Genetic; Solubility; Tetrahymena; Toxoplasma; Transfection; Treatment Outcome; Tropism; Tubulin; Vertebrates; oryzalin; pendimethalin; pironetin; pronamide</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Mortazavi, Ali</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5-Methylcytosine; 6-methyladenine; ATP-Binding Cassette Transporters; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Antineoplastic Combined Chemotherapy Protocols; Astrocytes; Brain; Carcinoma, Transitional Cell; Cell Differentiation; Cerebellum; Chromatin; DNA Methylation; Gene Expression Profiling; Gene Regulatory Networks; Genetic Variation; Genomics; High-Throughput Nucleotide Sequencing; Hippocampus; Homeodomain Proteins; In Situ Hybridization, Fluorescence; Machine Learning; Microglia; Molecular Sequence Annotation; Muscle Fibers, Skeletal; Muscular Dystrophy, Facioscapulohumeral; Myoblasts; Neoplasm Metastasis; Neuroglia; Neurons; Nivolumab; Nucleotides; Phagocytosis; Plaque, Amyloid; Pseudouridine; RNA Editing; RNA, Long Noncoding; RNA-Seq; Receptor, Anaphylatoxin C5a; Resilience, Psychological; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Transcriptome; Urinary Bladder Neoplasms; Urologic Neoplasms</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Nicholas, Dequina</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5'-Nucleotidase; Adaptive Immunity; Adipose Tissue; Adiposity; Aged; Aging; Allergy and Immunology; Anabolic Androgenic Steroids; Androgens; Anti-Inflammatory Agents; Antibodies; Antibodies, Neutralizing; Antibody Formation; Antigen Presentation; Antigens; Antigens, CD1; Autoantibodies; Autoantigens; Autoimmune Diseases; B-Lymphocyte Subsets; Bacteriophages; Biocompatible Materials; Blood Glucose; Brain; CD8-Positive T-Lymphocytes; COVID-19; Cardiac Output; Cardiovascular Diseases; Carrier Proteins; Cell Differentiation; Cell Fractionation; Cell Line; Cell Line, Tumor; Cell Membrane; Cell Plasticity; Cell Proliferation; Cell Survival; Cellular Senescence; Coculture Techniques; Communicable Diseases; Computer Simulation; Cross-Sectional Studies; Culture Media, Conditioned; Cytokines; Diabetes Mellitus; Diabetes Mellitus, Type 2; Diet; Diet, High-Fat; Disease Progression; Drug Evaluation, Preclinical; Endocrinology; Escherichia coli; Ethnic and Racial Minorities; Fertility; Flow Cytometry; Follicle Stimulating Hormone; Gastrointestinal Microbiome; Gene Expression Profiling; Gene Expression Regulation, Neoplastic; Glucose; Glucose Transporter Type 1; Glycated Hemoglobin; Glycolysis; Gonadal Steroid Hormones; Gonadotropins; Gonadotropins, Pituitary; H3B-8800; Homeostasis; Immunophenotyping; Immunotherapy; Industrial Development; Infertility; Inflammation; Inflammation Mediators; Influenza Vaccines; Insulin; Insulin Resistance; Interleukin-17; Kidney; Laboratories; Lipid Metabolism; Lipids; Lipopolysaccharides; Liver; Losartan; Luteinizing Hormone; Lymphocytic Choriomeningitis; Lymphocytic choriomeningitis virus; Lymphoid Tissue; Memory B Cells; Metabolic Networks and Pathways; Metabolism; Methanol; Mexican Americans; Mice, Obese; NAD; Neoplastic Stem Cells; Niacinamide; Nicotinamide-Nucleotide Adenylyltransferase; Noncommunicable Diseases; Obesity; Organoids; Ovarian Neoplasms; Palatine Tonsil; Pandemics; Persistent Infection; Phenotype; Phosphotransferases (Alcohol Group Acceptor); Pituitary Diseases; Pituitary Gland; Polycystic Ovary Syndrome; Preceptorship; Prevalence; Printing, Three-Dimensional; Professional Competence; Proprotein Convertase 9; Protein Array Analysis; Protein Transport; Proteins; Proto-Oncogene Proteins c-akt; Pyridinium Compounds; Quality of Life; RNA, Long Noncoding; Reproduction; Research Personnel; Risk Factors; Sedentary Behavior; Sequence Analysis, RNA; Signal Transduction; Single-Cell Gene Expression Analysis; Solubility; Solvents; Streptavidin; T-Lymphocytes; Technology; Testosterone; Th17 Cells; Transcriptome; Up-Regulation; Virion; Weight Loss; Workflow; Zebrafish; lobeglitazone; polyvinylidene fluoride</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Nie, Qing</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Adenosine; Adipocytes; Adjuvants, Immunologic; Algorithms; Alpha-Ketoglutarate-Dependent Dioxygenase FTO; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Antibodies, Neutralizing; Antibodies, Viral; Benchmarking; Big Data; Biocompatible Materials; Biological Phenomena; Biomechanical Phenomena; COVID-19; Carcinogenesis; Carcinoma, Basal Cell; Cardiomyopathy, Dilated; Cartilage; Cell Body; Cell Communication; Cell Cycle Checkpoints; Cell Differentiation; Cell Lineage; Cellular Senescence; Chemokines; Choroid Plexus; Clinical Relevance; Clone Cells; Cluster Analysis; Computational Biology; Computer Simulation; Connectome; Cross-Linking Reagents; Cues; Cytokines; Data Analysis; Deep Learning; Developmental Biology; Down-Regulation; Drug Repositioning; Embryo, Mammalian; Embryonic Development; Endocrine System Diseases; Endopeptidases; Epithelial Cells; Extracellular Fluid; Extracellular Matrix; Extracellular Space; Feedback, Physiological; Fibroblasts; Gelatin; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Neoplastic; Gene Regulatory Networks; Genomics; Haploinsufficiency; Hemagglutinin Glycoproteins, Influenza Virus; Homeostasis; Hydrogels; Immune System; Immunity; Induced Pluripotent Stem Cells; Inflammation; Influenza A Virus, H5N1 Subtype; Influenza Vaccines; Islets of Langerhans; Keratinocytes; Kidney Diseases; Lamin Type A; Ligands; Lipid A; Lipid Droplets; Lipid Metabolism; Lipogenesis; Lymphocytes; Machine Learning; Macrophage Activation; Macrophages; Melanoma; Methylation; Methyltransferases; Mice, Inbred BALB C; Molecular Biology; Motor Neurons; Multiomics; Mutation; Myocytes, Cardiac; Nervous System Diseases; Neural Networks, Computer; Neurons; Neurotransmitter Agents; Obesity; Oligodeoxyribonucleotides; Organoids; Orthomyxoviridae Infections; PTEN Phosphohydrolase; Peptide Hydrolases; Pericardium; Pluripotent Stem Cells; Polysorbates; Proteins; Proto-Oncogene Proteins B-raf; RANK Ligand; RNA; RNA-Seq; Rosacea; SARS-CoV-2; Saponins; Schwann Cells; Secretome; Senescence-Associated Secretory Phenotype; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Skin; Skin Neoplasms; Software; Squalene; Systems Biology; T-Lymphocytes; Transcription Factors; Transcriptome; Vacuoles; Wound Healing; Young Adult</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Parsons, Michael</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Academic Performance; Acinar Cells; Adenocarcinoma; Alleles; Animals, Genetically Modified; Animals, Laboratory; Antigen Presentation; Autoimmunity; BRCA1 Protein; BRCA2 Protein; Bayes Theorem; Bicarbonates; Breast Neoplasms; Carcinogens; Carcinoma, Ovarian Epithelial; Case-Control Studies; Cell Differentiation; Child; Demography; Developed Countries; Developmental Biology; Diabetes Mellitus; Diabetes Mellitus, Type 1; Diabetes Mellitus, Type 2; Disease Progression; Endocrine Cells; Epithelium; Financial Support; Gastrointestinal Microbiome; Gene Knockout Techniques; Genetic Phenomena; Genetic Predisposition to Disease; Genetic Testing; Genetic Variation; Growth and Development; Hispanic or Latino; Homeostasis; Homozygote; Hyperglycemia; Immunity, Innate; Incidence; Indigenous Peoples; Inflammation; Insulin-Secreting Cells; Insulins; Integrases; Islets of Langerhans; Language; Larva; Leadership; Likelihood Functions; Liver; Metaplasia; Metronidazole; Mice, Inbred NOD; Microbiota; Neoplasms; Nitroreductases; Optimism; Ovarian Neoplasms; Pancreas; Pancreas, Exocrine; Pancreatic Neoplasms; Pancreatitis; Penetrance; Polymorphism, Single Nucleotide; Prevalence; Prospective Studies; Regeneration; Risk Factors; Sequence Analysis, RNA; Signal Transduction; Stem Cells; Stroke; T-Lymphocytes; Technology; Thinking; Transcriptome; Volunteers; Water; Workforce; Zebrafish</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Pizzagalli, Diego</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Plikus, Maksim</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Adaptor Proteins, Signal Transducing; Adipocytes; Aged; Aging; Ambystoma mexicanum; Amputation, Surgical; Anti-Infective Agents; Autopsy; Biocompatible Materials; Biological Evolution; Biomechanical Phenomena; Birds; Black or African American; Body Patterning; Brazil; Cadaver; Calcitonin Gene-Related Peptide; Cartilage; Casein Kinase 1 epsilon; Cell Communication; Cell Cycle Proteins; Cell Line, Tumor; Cell Proliferation; Cellular Senescence; China; Chromatin; Cicatrix; Circadian Clocks; Circadian Rhythm; Collagen; Colorectal Neoplasms; Computational Biology; Computer Simulation; Cross-Linking Reagents; Culicidae; Cytokines; Cytosol; DNA, Ancient; DNA-Binding Proteins; Dengue; Dermis; Disease Progression; Disease Susceptibility; Elephants; Embryonic Development; Epidermis; Epigenesis, Genetic; Epigenomics; Epithelial Cells; Ethnicity; Evidence Gaps; Evolution, Molecular; Extracellular Matrix; Eyebrows; Eyelids; Fibroblasts; Fibrosis; Flavivirus; Fossils; Gelatin; Gene Expression; Gene Expression Profiling; Gene Expression Regulation, Developmental; Gene Expression Regulation, Neoplastic; Gene Ontology; Gene Regulatory Networks; Genome; Genome, Human; Genomics; Glycolysis; HCT116 Cells; Hair; Hair Follicle; Heterografts; Hispanic or Latino; Homeodomain Proteins; Homeostasis; Hydrogels; Inflammation; Inflammatory Bowel Diseases; Internship and Residency; Intestinal Mucosa; Intestines; Keloid; Keratinocytes; Latin America; Lipid Droplets; Lipid Metabolism; Lipogenesis; Locomotion; Macrophages; Mammoths; Marsupialia; Mechanistic Target of Rapamycin Complex 2; Melanocytes; Membrane Proteins; Mesenchymal Stem Cells; Mesoderm; Mitochondria; Mitochondrial Proteins; Morphogenesis; Mosquito Vectors; Multifactorial Inheritance; Multiomics; Myofibroblasts; NAD; Necroptosis; Neoplasms; Nevus; Nociceptors; Obesity; Organoids; Osteopontin; Ovosiston; Pain; Pandemic Preparedness; Pandemics; Peer Review; Phenotype; Phosphofructokinase-2; Phosphoprotein Phosphatases; Phosphorylation; Phylogeny; Pigmentation Disorders; Protein Serine-Threonine Kinases; Proto-Oncogene Proteins c-akt; Pruritus; Public Health; Quality Control; R-Loop Structures; RANK Ligand; RNA; RNA, Small Interfering; RNA-Seq; Reactive Oxygen Species; Referral and Consultation; Regeneration; Regulatory Sequences, Nucleic Acid; Reptiles; Saliva; Scalp; Schools; Secretome; Senescence-Associated Secretory Phenotype; Senotherapeutics; Sequence Analysis, RNA; Serine-Threonine Kinase 3; Signal Transduction; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Sirolimus; Skin; Skin Aging; Skin Diseases; Skin Physiological Phenomena; Skin Pigmentation; Software; Stem Cells; Sugars; TOR Serine-Threonine Kinases; TRPV Cation Channels; Transcription Factors; Transcriptome; Tumor Suppressor Proteins; Urodela; Vaccines; Vaccinology; Vacuoles; West Nile virus; Wnt Signaling Pathway; World Health Organization; Wound Healing; Writing; X Chromosome; YAP-Signaling Proteins; Yellow Fever; Young Adult; Zebrafish; Zika Virus; Zika Virus Infection</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Ranz, Jose</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Axonemal Dyneins; Biological Evolution; Biomass; Butterflies; Cell Differentiation; Chromosomes; Diptera; Drosophila Proteins; Drosophila melanogaster; Ecological and Environmental Phenomena; Evolution, Molecular; Gene Expression; Gene Expression Profiling; Genetic Fitness; Genetic Speciation; Genetics; Genome; Genomics; Heterozygote; Hybridization, Genetic; INDEL Mutation; Insecta; Larva; Lepidoptera; Multigene Family; Phylogeny; RNA; RNA, Long Noncoding; Random Allocation; Research; Semen; Sequence Analysis; Sex Characteristics; Spain; Spermatogenesis; Spermatozoa; Spiroplasma; Testis; Transcriptome; Tsetse Flies; X Chromosome</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Razorenova, Olga</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Adenosine Triphosphate; Apoptosis; Basic Helix-Loop-Helix Transcription Factors; Binding Sites; Biomarkers; Breast Neoplasms; CRISPR-Cas Systems; Cancer Survivors; Carcinogens; Carcinoma, Renal Cell; Cell Line, Tumor; Cell Lineage; Cell Movement; Cell Plasticity; Cell Transformation, Neoplastic; Cyclic N-Oxides; Cyclin-Dependent Kinase 9; Cyclin-Dependent Kinase Inhibitor Proteins; Cyclin-Dependent Kinases; Dimerization; Down-Regulation; Drug Resistance, Neoplasm; Electron Transport; Epithelial Cell Adhesion Molecule; ErbB Receptors; Fatty Acids; Gene Expression Regulation, Neoplastic; Genes, Suppressor; Heterografts; Hypoxia; Immune Checkpoint Inhibitors; Immunogenic Cell Death; Indolizines; Integrin alpha6; Integrins; Kidney Neoplasms; Lipid Droplets; Lipid Metabolism; Lipids; Metabolism; Microscopy; Mitochondria; Motivation; Myeloid Cell Leukemia Sequence 1 Protein; Neoplasm Metastasis; Neoplasms; Neoplastic Processes; Neoplastic Stem Cells; Ovarian Neoplasms; Oxidative Phosphorylation; Oxygen; Pedigree; Peptides; Phenotype; Phosphoproteins; Protein Kinase Inhibitors; Pyridinium Compounds; RNA Polymerase II; RNA, Long Noncoding; Signal Transduction; Survival Rate; Synthetic Lethal Mutations; Tetracyclines; Transcriptome; Triple Negative Breast Neoplasms; Tumor Microenvironment; Tyrosine; Tyrosine Kinase Inhibitors; Up-Regulation; Von Hippel-Lindau Tumor Suppressor Protein; belzutifan; dinaciclib; endothelial PAS domain-containing protein 1; saracatinib; src-Family Kinases; von Hippel-Lindau Disease</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Rebolleda-Gomez, Maria</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Agave; Agriculture; Algorithms; Ammonia; Arabidopsis; Awards and Prizes; Bacteria; Biological Evolution; Bioprinting; Carbon; Cell Survival; Communicable Diseases; Crops, Agricultural; Denitrification; Droughts; Drug Resistance, Microbial; Ecological and Environmental Phenomena; Ecosystem; Edible Grain; Evolution, Molecular; Farmers; Feedback
+ DNA, Single-Stranded
+ Learning
+ Ecology
+ Empirical Research; Gases; Genetics, Population; Metabolism; Mexico; Microbiota; Natural Science Disciplines; Nitrogen; Nitrogen Cycle; Pandemics; Plants; Plasmids; Printing, Three-Dimensional; Soil; Sorghum; Switzerland; Synthetic Biology; Technology; United Kingdom; Water</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Ribbe, Markus</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Adenosine Triphosphate; Aldehyde Oxidoreductases; Ammonia; Azotobacter vinelandii; Bacterial Proteins; Biocatalysis; Biofuels; Biosynthetic Pathways; Biotechnology; Carbon Dioxide; Carbon Monoxide; Catalysis; Chemistry, Bioinorganic; Electrons; Escherichia coli; Evolution, Molecular; Formate Dehydrogenases; Gene Expression; Hydrocarbons; Hydrogenase; Iron-Sulfur Proteins; Metalloproteins; Methyltransferases; Models, Molecular; Molybdenum; Molybdoferredoxin; Multienzyme Complexes; Nitrogen; Nitrogen Fixation; Nitrogenase; Organic Chemicals; Oxidation-Reduction; Oxidoreductases; Phylogeny; Protons; Recombinant Proteins; Reducing Agents; S-Adenosylmethionine; Sulfur</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Rodriguez Verdugo, Alejandra</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Acclimatization; Acinetobacter; Actinobacteria; Adaptation, Physiological; Anti-Bacterial Agents; Anti-Infective Agents; Anti-Infective Agents, Local; Bacteria; Bacteroidetes; Biodiversity; Biofilms; Biological Evolution; Chemotaxis; Climate Change; Coculture Techniques; Computer Simulation; DNA-Directed RNA Polymerases; Drug Resistance, Bacterial; Drug Resistance, Microbial; Ecological and Environmental Phenomena; Ecosystem; Epistasis, Genetic; Escherichia coli; Escherichia coli Proteins; Evolution, Molecular; Fecal Microbiota Transplantation; Ficus; Flagella; Genetic Background; Genetic Fitness; Genotype; Hot Temperature; Internship and Residency; Microbial Consortia; Microbial Interactions; Microbiota; Mutation; Nutrients; One Health; Phenotype; Plant Leaves; Poaceae; Proteobacteria; Pseudomonas putida; Rho Factor; Rifampin; Selection, Genetic; Species Specificity; Stress, Physiological; Symbiosis; Synthetic Biology; Whole Genome Sequencing; Xylans; Xylose</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Schechtman-Drayman, Eitan</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Academia; Algorithms; Arousal; Bacteriophage T7; Bacteriophages; Behavior Control; Brain; Cognition; Cognitive Dysfunction; Cognitive Neuroscience; Computational Biology; Consciousness; Cues; DNA; DNA-Directed RNA Polymerases; Data Collection; Decision Making; Depression; Diffusion; Electroencephalography; Electrophysiology; Healthy Volunteers; Latent Infection; Leadership; Learning; Machine Learning; Magnetic Resonance Imaging; Memory; Memory Consolidation; Memory, Episodic; Mental Health; Molecular Dynamics Simulation; Mood Disorders; Neurobiology; Neuroimaging; Odorants; Pilot Projects; Probability; Promoter Regions, Genetic; RNA, Viral; Research Personnel; Rodentia; Sexual and Gender Minorities; Sleep; Spatial Memory; Spatial Navigation; Stress Disorders, Post-Traumatic; Transcription Factors; Transcription, Genetic; Vacuum; Wakefulness</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Schilling, Thomas</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Adipocytes; Animals, Genetically Modified; Aquaporins; Biological Evolution; Biomechanical Phenomena; Bone and Bones; Branchial Region; Calcium; Cartilage; Cell Adhesion; Cell Cycle Proteins; Cell Lineage; Cell Movement; Cell Polarity; Cell Proliferation; Chondrocytes; Chromosomal Proteins, Non-Histone; Cichlids; Clinical Protocols; Clinical Relevance; Cohesins; Computer Simulation; Congenital Abnormalities; Craniofacial Abnormalities; Embryo, Nonmammalian; Embryology; Embryonic Development; Embryonic Induction; Extracellular Matrix; Extracellular Matrix Proteins; Eye Proteins; Fibroblasts; Gene Dosage; Gene Expression; Gene Expression Profiling; Gene Expression Regulation, Developmental; Germ Cells; Gonads; Growth Plate; Hand-Foot Syndrome; Integrins; Jaw; Laboratories; Lakes; Larva; Lens, Crystalline; Ligaments; Lipid Droplets; Lipid Metabolism; Lipogenesis; Malawi; Mechanotransduction, Cellular; Mesoderm; Morphogenesis; Muscle Contraction; Muscles; Musculoskeletal System; Mutation; Neural Crest; Obesity; Permeability; Phenotype; Quantitative Trait Loci; Receptor Tyrosine Kinase-like Orphan Receptors; Receptors, Retinoic Acid; Receptors, Wnt; Regeneration; Regulatory Sequences, Nucleic Acid; Sex Determination Processes; Signal Transduction; Skeleton; Skull; Species Specificity; Systems Biology; Tendon Injuries; Tendons; Tenocytes; Thrombospondins; Transcription Factors; Transcriptome; Tretinoin; Vacuoles; Van Maldergem Wetzburger Verloes syndrome; Vertebrates; Water; Wnt Proteins; Wnt Signaling Pathway; Zebrafish; Zebrafish Proteins; thrombospondin 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Shi, Xiaoyu</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Academia; Acyltransferases; Adaptor Proteins, Signal Transducing; Adrenergic Agents; Aging; Alzheimer Disease; Amyloid beta-Peptides; Amyloidogenic Proteins; Arrhythmias, Cardiac; Astrocytes; Axons; Benchmarking; Bioengineering; Biomarkers; Biophysics; Biotechnology; Brain; Brain Injuries; Capacity Building; Carcinogenesis; Caveolae; Cell Biology; Cell Line, Tumor; Cell Membrane; Cell Nucleus; Cell Proliferation; Cell Transformation, Neoplastic; Chromatin; Chromosomes, Plant; Clathrin; Colorectal Neoplasms; Crops, Agricultural; Cytosol; Dementia; Dendrites; Diploidy; Disease Progression; Early Diagnosis; Endocytosis; Epigenesis, Genetic; Epigenomics; Estrogens; Excitation Contraction Coupling; Fibrinolytic Agents; Gene Expression Profiling; Gene Expression Regulation; Gene Expression Regulation, Plant; Genes, Plant; Genetic Variation; Genetics, Population; Genome, Plant; Genomics; HCT116 Cells; HEK293 Cells; HeLa Cells; Heterochromatin; Heterozygote; High-Throughput Nucleotide Sequencing; Hippocampus; Homozygote; Human Body; Hydrogels; Hypertrophy; Intrinsically Disordered Proteins; Ion Channels; Lamins; Latin America; Long-Term Potentiation; Mass Spectrometry; Memory; Memory Disorders; Microscopy; Microscopy, Fluorescence; Mitochondria; Mitochondrial Proteins; Molecular Structure; Multiomics; Myocytes, Cardiac; Nanostructures; Nerve Degeneration; Neurodegenerative Diseases; Neurons; Nuclear Lamina; Nucleic Acids; Organelles; Outsourced Services; Peptides; Phenotype; Phosphoprotein Phosphatases; Phosphorylation; Pinocytosis; Plague; Plant Breeding; Plaque, Amyloid; Pollination; Prefrontal Cortex; Protein Binding; Protein Biosynthesis; Protein Interaction Mapping; Protein Kinase C; Protein Processing, Post-Translational; Protein Serine-Threonine Kinases; Proteins; Proteome; Proteomics; RNA 3' End Processing; RNA Polymerase II; RNA Precursors; RNA Processing, Post-Transcriptional; RNA Splicing; RNA, Messenger; RNA-Binding Proteins; Reactive Oxygen Species; Receptors, AMPA; Receptors, Progesterone; Reproduction; Ribosomes; Sequence Analysis, RNA; Serine-Threonine Kinase 3; Sex Factors; Single-Cell Analysis; Single-Cell Gene Expression Analysis; Staining and Labeling; Synapses; Tissues; Transcription Factors; Transcriptome; Triple Negative Breast Neoplasms; Tumor Suppressor Proteins; Vitis; YAP-Signaling Proteins</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Sorte, Cascade</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Alaska; Anthropogenic Effects; Biodiversity; Carbon Dioxide; Climate Change; Conservation of Natural Resources; Ecological and Environmental Phenomena; Ecosystem; Europe; Gastropoda; Geography; Human Activities; Hydrogen-Ion Concentration; Introduced Species; Nitrogen; Oceans and Seas; Oxygen; Plants; Predatory Behavior; Species Specificity; Temperature</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Stark, Craig</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid beta-Peptides; Apolipoprotein E4; Apolipoproteins E; Atlases as Topic; Atrophy; Behavior, Animal; Benchmarking; Biomarkers; Brain; Brain Mapping; Breast Neoplasms; Calcineurin; Calcineurin Inhibitors; Cerebral Cortex; Cognition; Cognitive Dysfunction; Cranial Irradiation; Diffusion Magnetic Resonance Imaging; Disease Progression; Dogs; Early Diagnosis; Entorhinal Cortex; Estradiol; Genotype; Health Surveys; Heterozygote; Hippocampus; Image Processing, Computer-Assisted; Learning; Longevity; Magnetic Resonance Imaging; Memory; Memory, Episodic; Menopause; Mental Status and Dementia Tests; NFATC Transcription Factors; Neurites; Neuroimaging; Neuropsychological Tests; Oxygen; Pattern Recognition, Physiological; Pattern Recognition, Visual; Phosphorylation; Positron-Emission Tomography; Proteomics; Quality Control; Radiotherapy Dosage; Reading; Repression, Psychology; Reproducibility of Results; Risk Factors; Spatial Learning; Surveys and Questionnaires; Tacrolimus; Temporal Lobe; Verbal Learning; Young Adult; nan; tau Proteins</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Striedter, Georg</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Biological Evolution; Physiology, Comparative</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Suetterlin, Christine</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>AMP-Activated Protein Kinases; Asymptomatic Infections; Bacteria; Bacterial Proteins; Binding Sites; Causality; Cell Biology; Cell Culture Techniques; Cell Cycle; Centers for Disease Control and Prevention, U.S.; Centrosome; Chlamydia; Chlamydia Infections; Chlamydia trachomatis; Cilia; Coinfection; Cytoplasm; Epithelial Cells; Epithelium; Escherichia coli; Fallopian Tubes; Gene Expression Regulation, Bacterial; Gene Knockdown Techniques; Golgi Apparatus; HeLa Cells; Infertility; Lipids; Membrane Proteins; Membranes; Microbiology; Microbiota; Microscopy; Oocytes; Organelles; Ovary; Pregnancy; Pregnancy, Ectopic; Protein Sorting Signals; Proto-Oncogene Proteins c-akt; RNA; RNA, Messenger; RNA, Small Untranslated; Reverse Genetics; Sorting Nexins; Staining and Labeling; Stem Cells; Type III Secretion Systems; Vacuoles; Virulence</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Sumikawa, Katumi</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Acetylation; Adolescent; Allosteric Regulation; Alzheimer Disease; Animals, Genetically Modified; Behavior Rating Scale; Brain; CA1 Region, Hippocampal; Cause of Death; Chemokines; Child; Cholinergic Neurons; Cognition; Cognitive Dysfunction; Cytokines; Down-Regulation; Electrophysiology; Epigenesis, Genetic; Fluorescent Antibody Technique; Hippocampus; Histone Deacetylase Inhibitors; Histone Deacetylases; Histones; Homeostasis; Interneurons; Ligands; Long-Term Potentiation; Longevity; Memory Disorders; Microglia; Mortality, Premature; Mutation; N-Methylaspartate; Neocortex; Neuregulin-1; Nicotiana; Nicotine; Nicotinic Agonists; Phosphorylation; Plaque, Amyloid; Prefrontal Cortex; Pregnancy; Pyramidal Cells; Quinolines; RNA, Messenger; Rats, Sprague-Dawley; Receptor, Muscarinic M1; Receptors, N-Methyl-D-Aspartate; Receptors, Nicotinic; Reward; Schizophrenia; Signal Transduction; Smoking; Smoking Cessation; Somatostatin; Substance-Related Disorders; Tobacco Smoking; Tobacco Use; Tobacco Use Disorder; Transcription, Genetic; Tyrosine; Up-Regulation; src-Family Kinases</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Sun, Sha</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Aged; Algorithms; Base Sequence; Biological Evolution; Biomarkers; Biomarkers, Tumor; Brain; Breast Neoplasms; Carcinogenesis; Carcinoma, Hepatocellular; Carcinoma, Non-Small-Cell Lung; Cell Differentiation; Cell Line, Tumor; Cell Plasticity; Cell Proliferation; Cell Survival; Chromosomes, Human, X; Circulating Tumor DNA; Clustered Regularly Interspaced Short Palindromic Repeats; Colonic Neoplasms; Computational Biology; Diagnosis, Differential; Down-Regulation; Drug Resistance, Neoplasm; Educational Measurement; Embryonic Development; Epigenesis, Genetic; Epigenomics; ErbB Receptors; Eutheria; Evolution, Molecular; Exons; Fetal Stem Cells; Gene Editing; Gene Expression Profiling; Gene Expression Regulation, Neoplastic; Genes, X-Linked; Genetics; Genital Neoplasms, Female; Genomics; Genotype; Glutamine; Health; Incidence; Large Language Models; Life Style; Liver Neoplasms; Lung Neoplasms; Marsupialia; Metabolic Reprogramming; Microscopy, Fluorescence; Molecular Biology; Multigene Family; Mutagenesis, Insertional; Mutation; Neoplastic Processes; Neoplastic Stem Cells; Optical Imaging; Organoids; Ovarian Neoplasms; Oxidative Phosphorylation; Phenotype; Precision Medicine; Prognosis; Protein Kinase Inhibitors; RNA; RNA, Guide, CRISPR-Cas Systems; RNA, Long Noncoding; RNA, Untranslated; Radiology; Reproducibility of Results; Retrospective Studies; Rodentia; Sex Characteristics; Sex Chromosomes; Specialty Boards; Species Specificity; Stem Cells; Stress, Physiological; Trans-Activators; Tumor Microenvironment; X Chromosome; X Chromosome Inactivation; Y Chromosome</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Swarup, Vivek</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amyloid beta-Peptides; Apolipoproteins E; Astrocytes; Brain; CD8-Positive T-Lymphocytes; Cell Communication; Cell Line; Cell Nucleus; Cell Proliferation; Cellular Reprogramming; Central Nervous System; Chromatin Immunoprecipitation Sequencing; Cocaine; Cognition; Critical Pathways; Demyelinating Diseases; Disease Progression; Down Syndrome; Encephalitis Virus, Japanese; Encephalitis, Japanese; Epigenesis, Genetic; Epigenomics; Fatty Acids, Volatile; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genes; Genetic Variation; Genetics; Genomics; Habenula; Healthy Aging; Immunity, Innate; Inflammation; Integrases; Killer Cells, Natural; Longevity; Memory; MicroRNAs; Microglia; Multiomics; Multiple Sclerosis; Myelin Sheath; Myeloid Cells; NF-KappaB Inhibitor alpha; NF-kappa B; Natural Killer T-Cells; Nervous System Malformations; Neurodegenerative Diseases; Neuroglia; Neuroinflammatory Diseases; Neurons; Occipital Lobe; Oligodendrocyte Precursor Cells; Oligodendroglia; Parkinson Disease; Parkinsonian Disorders; Plaque, Amyloid; Postmortem Changes; Prefrontal Cortex; Proteomics; Pseudogenes; Quality Control; RNA; RNA, Small Nuclear; RNA-Seq; Recurrence; Regulator; Remyelination; Reproducibility of Results; Resilience, Psychological; Risk Factors; Sequence Analysis, RNA; Signal Transduction; Single-Cell Analysis; Spatial Memory; Spinal Cord; Spinal Cord Injuries; Sterol Regulatory Element Binding Protein 1; Stroke; Substance-Related Disorders; Systems Biology; Tauopathies; Time Factors; Transcription Factors; Transcriptome; White Matter; Wound Healing; nan; tau Proteins</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Symons, Celia</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Additional Terms; Antelopes; Anthropogenic Effects; Bacteria; Biodiversity; Biological Specimen Banks; Biomass; Biota; Capacity Building; Carbon Dioxide; Climate Change; Conservation of Natural Resources; Data Science; Diet; Dissolved Organic Matter; Ecological and Environmental Phenomena; Ecology; Ecosystem; Environmental Indicators; Environmental Monitoring; Europe; Feeding Behavior; Fires; Food Chain; Forests; Fresh Water; Freshwater Biology; Guidelines as Topic; Hunting; Hydrobiology; Interdisciplinary Research; Introduced Species; Lakes; Literacy; Mobile Applications; North America; Organic Chemicals; Phytoplankton; Planets; Plankton; Ponds; Population Dynamics; Remote Sensing; Remote Sensing Technology; Resilience, Psychological; Salinity; Seasons; Smoke; Technology; Temperature; Time Factors; Vertebrates; Water Quality; Wildfires; Workforce; Zooplankton</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Tenner, Andrea</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ATP-Binding Cassette Transporters; Aged; Allergy and Immunology; Alzheimer Disease; Amyloid; Amyloid beta-Peptides; Amyloid beta-Protein Precursor; Apolipoproteins E; Astrocytes; Biological Phenomena; Brain; Calcium; Cognition; Cognitive Dysfunction; Complement Activation; Complement C1q; Complement C5a; Complement System Proteins; Cuprizone; Demyelinating Diseases; Disease Progression; Gastrointestinal Microbiome; Gene Expression; Gene Knock-In Techniques; Genetic Variation; Genotype; Hippocampus; Immune System; Immunity, Innate; Immunologic Factors; Incidence; Inflammation; Long-Term Potentiation; Lysosomes; Membrane Glycoproteins; Memory Disorders; Metabolomics; Microbiota; Microglia; Microscopy; Mutation; Neurodegenerative Diseases; Neuroglia; Neuroinflammatory Diseases; Neuronal Plasticity; Neurons; Neuroprotection; Phagocytosis; Plaque, Amyloid; RNA Splicing; RNA-Seq; Receptor, Anaphylatoxin C5a; Receptors, Complement; Receptors, Immunologic; Resilience, Psychological; Sex Characteristics; Signal Transduction; Synapses; Tauopathies; Therapeutics; hydrocinnamate-cyclo(ornithyl-prolyl-cyclohexylalanyl-tryptophyl-arginyl); tau Proteins</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Thompson-Peer, Katherine</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Actin Cytoskeleton; Actins; Adenosine Triphosphate; Alleles; Axons; Blood-Brain Barrier; Calcium; Cell Death; Cytoskeleton; Dendrites; Drosophila melanogaster; Endothelial Cells; Energy Metabolism; Extracellular Matrix; Gene Expression Profiling; Glutamine; Huntington Disease; Integrins; Microtubules; Mitochondria; Mitochondrial Dynamics; Nerve Regeneration; Neurites; Neurodegenerative Diseases; Neurogenesis; Neuroglia; Neurons; Neuroprotection; Neuroprotective Agents; Peptides; Peripheral Nervous System; Potassium Channels, Inwardly Rectifying; Proteolysis; Regeneration; Sensory Receptor Cells; Signal Transduction; Spinocerebellar Ataxias; Time-Lapse Imaging; Transgenes; polyglutamine</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Thompson, Leslie</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>6-methyladenine; Academia; Adenosine; Aged; Algorithms; Alternative Splicing; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Animals, Genetically Modified; Artificial Intelligence; Astrocytes; Ataxin-1; Atrophy; Autophagy; Biological Phenomena; Biomarkers; Biomedical Research; Biotin; Brain; Brain-Derived Neurotrophic Factor; C9orf72 Protein; Calcium Signaling; Caregivers; Case-Control Studies; Cell Death; Cell Differentiation; Cell Line; Cell- and Tissue-Based Therapy; Cells, Cultured; Cerebellum; Cerebral Cortex; Child; Child, Preschool; Chorea; Chromatin; Chromatin Immunoprecipitation Sequencing; Chromatography, Liquid; Clinical Trials, Phase I as Topic; Clustered Regularly Interspaced Short Palindromic Repeats; Cognition; Cognitive Dysfunction; Colon; Communication; Corpus Striatum; DNA Breaks, Double-Stranded; DNA Damage; DNA Repair; DNA-Binding Proteins; Deep Learning; Delayed Diagnosis; Dementia; Demography; Depression; Dihydroxyphenylalanine; Disease Progression; Dopaminergic Neurons; Drug Development; Dystonia 3, Torsion, X-Linked; Edema; Electrophysiology; Embryonic Stem Cells; Epigenesis, Genetic; Epigenomics; Epilepsies, Partial; Exons; Feasibility Studies; Fibroblasts; Frontotemporal Dementia; Frontotemporal Lobar Degeneration; Gene Editing; Gene Expression Profiling; Gene Expression Regulation; Gene Knockout Techniques; Genetic Diseases, X-Linked; Genetic Therapy; Genetic Variation; Graft Rejection; HeLa Cells; Hematopoietic Stem Cell Transplantation; Histones; Hospital Mortality; Hospitalization; Huntingtin Protein; Huntington Disease; Immunosuppression Therapy; Induced Pluripotent Stem Cells; Inflammation; Inosine; Intermediate Filaments; Intranuclear Inclusion Bodies; Isomerism; Length of Stay; Lewy Bodies; Ligases; Liquid Chromatography-Mass Spectrometry; Lysosomes; Medium Spiny Neurons; Methylation; Methyltransferases; Microglia; Microscopy; Microscopy, Electron; Mitochondria; Mitochondrial Proteins; Motor Neurons; Multiomics; Muscle, Skeletal; Mutation; Negotiating; Nervous System Diseases; Neural Stem Cells; Neurites; Neurobiology; Neurodegenerative Diseases; Neurons; Neurons, Efferent; Oligonucleotides, Antisense; Optogenetics; Organelles; Outcome Assessment, Health Care; Parkinson Disease; Peptides; Pharmaceutical Preparations; Phenotype; Poly Adenosine Diphosphate Ribose; Prevalence; Primates; Prisoners; Promoter Regions, Genetic; Prospective Studies; Protein Binding; Protein Biosynthesis; Protein Isoforms; Proteomics; Proteostasis; Quantitative Trait Loci; RNA; RNA Methylation; RNA Splicing; RNA Stability; RNA, Messenger; RNA, Small Interfering; RNA-Binding Proteins; Receptors, Antigen, T-Cell; Receptors, Metabotropic Glutamate; Rectum; Regenerative Medicine; Registries; Research Report; Retroelements; Robotic Surgical Procedures; SUMO-1 Protein; Salts; Seizures; Seizures, Febrile; Sequence Analysis, RNA; Signal Transduction; Sodium Chloride; Spinocerebellar Ataxias; Stem Cell Transplantation; Stem Cells; Sumoylation; Superoxide Dismutase-1; Surgical Wound Infection; Synapses; Synapsins; Synaptosomes; Synucleins; Systems Biology; Tandem Mass Spectrometry; Tandem Repeat Sequences; Terminology as Topic; Tissue Distribution; Transcription, Genetic; Transcriptome; Translational Science, Biomedical; Treatment Outcome; Trinucleotide Repeat Expansion; Ubiquitin; Ubiquitin-Protein Ligases; Whole Genome Sequencing; Wound Closure Techniques; gamma-Aminobutyric Acid</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Thornton, Kevin</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Algorithms; Alleles; Computer Simulation; Demography; Ecological and Environmental Phenomena; Genetics, Population; Mutation; Phylogeny; Software; Uncertainty</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Tinoco, Roberto</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ADP-ribosyl Cyclase; AMP-Activated Protein Kinases; Adaptive Immunity; Aged; Aging; Allergy and Immunology; Alzheimer Disease; Amyotrophic Lateral Sclerosis; Antibodies, Blocking; Antigens; Antiviral Agents; Arm; Autoimmunity; B7-H1 Antigen; Brain; Breast Neoplasms; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Calcium Signaling; Caregivers; Cell Death; Cell Differentiation; Cell Line, Tumor; Cell Movement; Cell Proliferation; Cell Survival; Chromatin; Chronic Disease; Cognition; Cognitive Dysfunction; Coloring Agents; DNA Damage; DNA Repair; Delivery of Health Care; Dendritic Cells; Dengue; Diet; Disease-Free Survival; Epigenesis, Genetic; Feasibility Studies; Ficus; Financing, Organized; Flow Cytometry; Gene Expression Profiling; Genetic Predisposition to Disease; HIV Infections; HMGB2 Protein; Hemorrhagic Fever, Ebola; Hepatitis A Virus Cellular Receptor 2; Hepatitis B; Hepatitis C; Homeostasis; Immune Checkpoint Inhibitors; Immune Checkpoint Proteins; Immune System; Immunity; Immunoglobulin G; Immunologic Memory; Immunologic Techniques; Immunosuppression Therapy; Immunotherapy; Incidence; Influenza A Virus, H1N1 Subtype; Influenza A Virus, H7N9 Subtype; Intravital Microscopy; Ligands; Longevity; Lymph Nodes; Lymphocyte Activation; Lymphocytic Choriomeningitis; Lymphocytic choriomeningitis virus; Macrophages; Melanoma; Membrane Glycoproteins; Memory T Cells; Metabolic Networks and Pathways; Microbiota; Microscopy; Military Personnel; Molecular Biology; Morbidity; Mutation; Myeloid Cells; Natural Killer T-Cells; Neoadjuvant Therapy; Neoplasms; Neoplasms, Second Primary; P-Selectin; P-selectin ligand protein; Persistent Infection; Phosphatidylinositol 3-Kinases; Phosphoprotein Phosphatases; PrPC Proteins; Prion Proteins; Programmed Cell Death 1 Receptor; Proto-Oncogene Proteins c-akt; Quality of Life; Receptors, Antigen, T-Cell; Research; Risk Factors; SARS-CoV-2; Sequence Analysis, RNA; Signal Transduction; Skin Neoplasms; Spleen; Survival Rate; T-Cell Exhaustion; T-Lymphocytes; Transcription Factors; Treatment Outcome; Tumor Microenvironment; Up-Regulation; Vaccines; Virus Diseases; capivasertib; protein phosphatase 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Treseder, Kathleen</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Actinomycetales; Alaska; Alternaria; Anti-Bacterial Agents; Ants; Arthropods; Bacteria; Biomass; Canada; Carbon; Carbon Dioxide; Climate Change; Climate Models; Cold Temperature; Computers; Crop Production; Dermabrasion; Droughts; Drug Resistance, Bacterial; Ecological and Environmental Phenomena; Ecology; Ecosystem; Extracellular Polymeric Substance Matrix; Farmers; Forests; Fungi; Gene Expression Profiling; Genes, Bacterial; Genome, Bacterial; Genotype; Global Warming; Grassland; Hawaii; Hot Temperature; Incidence; Information Dissemination; Lepidoptera; Life History Traits; Longevity; Metagenome; Metagenomics; Microbiota; Mycorrhizae; Neon; Nitrogen; Plant Development; Plants; Poaceae; Policy; Resilience, Psychological; Seedlings; Seeds; Soil; Soil Microbiology; Songbirds; Survivorship; Technology; Temperature; Thermotolerance; Transcription, Genetic; Transcriptome; Uncertainty; Water; West Nile Fever; West Nile virus; Wildfires</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Tsai, Shiou-Chuan</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Aged; Aged, 80 and over; Algorithms; Analgesics, Opioid; Androgens; Antineoplastic Agents; Atrial Fibrillation; Big Data; Biological Products; Bipolar Disorder; Black or African American; Brain; COVID-19; COVID-19 Drug Treatment; COVID-19 Serotherapy; Catalytic Domain; Cell Differentiation; Child; Chromosome Mapping; Cohort Studies; Comorbidity; Cross-Sectional Studies; Crystallography; Daunorubicin; Drug Design; Electrocardiography, Ambulatory; Epithelial Cells; Europe; Genetic Predisposition to Disease; Genome-Wide Association Study; Genomics; Gray Matter; HIV Infections; Hair Follicle; Heart; Hippocampus; Hispanic or Latino; Hospitalization; Hypertension; Immunization, Passive; Machine Learning; Magnetic Resonance Imaging; Medical Oncology; Mutagenesis; Neoplasms; Neuroimaging; North America; Oncology Nursing; Opioid-Related Disorders; Oxygen; Patient Safety; Pediatrics; Phenotype; Polyketide Synthases; Polyketides; Post-Acute COVID-19 Syndrome; Reproducibility of Results; SARS-CoV-2; Schizophrenia; Sebaceous Glands; Single-Cell Analysis; Skin; Societies, Nursing; Treatment Outcome; White; White People</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Walsh, Craig</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Adjuvants, Immunologic; Alcoholism; Allergy and Immunology; Alzheimer Disease; Anti-HIV Agents; Antibodies, Monoclonal, Humanized; Antibody Formation; Assessment of Medication Adherence; Astrocytes; Autoimmunity; Bioengineering; Bioprinting; Biotechnology; Bone Marrow; CD4 Antigens; CD4-Positive T-Lymphocytes; CD8-Positive T-Lymphocytes; Cell Adhesion Molecules; Cell Death; Clinical Trials, Phase II as Topic; Clustered Regularly Interspaced Short Palindromic Repeats; Coronavirus Infections; Demyelinating Diseases; Embryonic Stem Cells; Encephalomyelitis, Autoimmune, Experimental; Epitopes; Epstein-Barr Virus Infections; Esophageal Neoplasms; Flow Cytometry; Fluticasone; Forkhead Transcription Factors; Fucose; Fucosyltransferases; Gene Expression Profiling; Graft vs Host Disease; HIV Infections; Hematologic Neoplasms; Hematopoietic Stem Cell Transplantation; Hematopoietic Stem Cells; Herpesvirus 4, Human; Image Cytometry; Immune Tolerance; Immunity, Cellular; Immunity, Innate; Immunization; Immunosuppressive Agents; Immunotherapy; Incubators; Induced Pluripotent Stem Cells; Inflammation; Ischemia; Killer Cells, Natural; Laboratories; Lymphocyte Activation; Macrophages; Magnetic Phenomena; Medication Adherence; Meningitis, Aseptic; Microglia; Microscopy; Motivational Interviewing; Multiomics; Multiple Sclerosis; Multiple Sclerosis, Relapsing-Remitting; Murine hepatitis virus; Neural Stem Cells; Neuroinflammatory Diseases; Organoids; Persistent Infection; Receptors, Antigen, T-Cell; Regenerative Medicine; Remyelination; S Phase; Single-Cell Gene Expression Analysis; Smartphone; Stem Cell Research; Stem Cells; T-Lymphocytes; T-Lymphocytes, Regulatory; Transplantation, Homologous; Treatment Outcome; Tumor Escape; Vaccination; Vaccine Efficacy; Vaccines; White Matter; aducanumab; nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Wang, Wenqi</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>AMP-Activated Protein Kinases; Adaptor Proteins, Signal Transducing; Adenocarcinoma of Lung; Adolescent; Air Pollutants; Air Pollution; Animals, Domestic; Antineoplastic Agents; Apoptosis; Benzothiazoles; Biological Phenomena; Body Patterning; Brain; Carcinogenesis; Catalysis; Cell Line, Tumor; Cell Proliferation; Cell Survival; Cell Transformation, Neoplastic; Child; China; Cities; Cues; DNA-Binding Proteins; Drug Resistance, Neoplasm; Environmental Exposure; Environmental Monitoring; Ependymoma; Fertilization; Florida; Fluorescence; Gene Expression; Gene Expression Regulation, Neoplastic; Genes, Neurofibromatosis 2; Genetic Background; Genomics; Genotype; Glucose; Head and Neck Neoplasms; High-Throughput Screening Assays; Hippo Signaling Pathway; Homeostasis; Hydroxyl Radical; Intercellular Signaling Peptides and Proteins; Interdisciplinary Research; Kinetics; Lipids; Loss of Function Mutation; Lung Neoplasms; MAP Kinase Signaling System; Meningeal Neoplasms; Meningioma; Metabolic Networks and Pathways; Metals, Heavy; Models, Chemical; Morbidity; Mortality; Mutation; Mutation, Missense; Neoplasms; Neurilemmoma; Neurofibromatosis 2; Neurofibromin 2; Organ Size; Ovarian Neoplasms; Oxidation-Reduction; Oxygen; Particulate Matter; Phenotype; Phosphorylation; Physiological Phenomena; Plasmodium falciparum; Platinum; Polyamines; Protein Interaction Maps; Protein Serine-Threonine Kinases; Publishing; Putrescine; Regeneration; Saccharomyces cerevisiae; Saccharomyces cerevisiae Proteins; Sequence Deletion; Signal Transduction; Spermidine; Stem Cells; TEA Domain Transcription Factors; Transcription Factors; Transcriptome; Writing; Xenograft Model Antitumor Assays</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Warrior, Rahul</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Cadmium; Cell Line, Tumor; DNA-Binding Proteins; Developmental Biology; Gene Expression Regulation; Genetics; HEK293 Cells; HeLa Cells; Hippo Signaling Pathway; Homeostasis; Inactivation, Metabolic; Phosphorylation; Protein Biosynthesis; Protein Serine-Threonine Kinases; Proteoglycans; Stress, Physiological; Transcription Factor MTF-1; Transcription Factors; Transcription, Genetic; Tumor Suppressor Proteins; Zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Whiteson, Katrine</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Adjuvants, Immunologic; Adjuvants, Pharmaceutic; Aged; Aging; Alzheimer Disease; Ampicillin; Amyloid beta-Peptides; Angiotensin Receptor Antagonists; Angiotensin-Converting Enzyme Inhibitors; Anti-Bacterial Agents; Anti-Infective Agents; Antineoplastic Agents, Hormonal; Appendectomy; Appendicitis; Autistic Disorder; Autoimmune Diseases; Bacteremia; Bacteria; Bacteria, Anaerobic; Bacterial Infections; Bacterial Physiological Phenomena; Bacteriophages; Benchmarking; Biodiversity; Biofilms; Biological Evolution; Biomarkers; Brain; Brain-Gut Axis; Breast Neoplasms; Bronchoalveolar Lavage Fluid; COVID-19; Case-Control Studies; Child; Chromatography, Gas; Clostridioides difficile; Clostridium Infections; Cohort Studies; Coliphages; Colon; Colonic Neoplasms; Colonoscopy; Communicable Diseases; Compassionate Use Trials; Computational Biology; Critical Illness; Cross Infection; Cryopreservation; Culture Media; Cystic Fibrosis; DNA; Data Management; Dementia; Demography; Dendritic Cells; Diabetes Mellitus, Type 1; Diabetes Mellitus, Type 2; Diagnosis; Diet; Diet Therapy; Diet, Mediterranean; Dietary Fiber; Digestion; Drug Resistance, Bacterial; Drug Resistance, Microbial; Drug Resistance, Multiple, Bacterial; Dysbiosis; Ecology; Ecosystem; Ecuador; Endometriosis; Enterococcus; Enterococcus faecalis; Enterococcus faecium; Epithelium; Escherichia coli; Estonia; Ethics Committees, Research; Fatty Acids, Volatile; Feasibility Studies; Fecal Microbiota Transplantation; Fellowships and Scholarships; Fermentation; Freezing; Gas Chromatography-Mass Spectrometry; Gastroenterology; Gastrointestinal Microbiome; Gene Expression Profiling; Gene Knock-In Techniques; Genome Size; Genomics; Genotype; Germ-Free Life; Global Health; Glycoside Hydrolases; Gram-Negative Bacteria; Gram-Negative Bacterial Infections; Gram-Positive Bacterial Infections; Health; Healthy Volunteers; High-Throughput Nucleotide Sequencing; Hospitalization; Host Microbial Interactions; Host Specificity; Human Body; Hunting; Hydrogen-Ion Concentration; Hypersensitivity; Immunity; Immunocompromised Host; Immunosenescence; Immunotherapy; Incidence; Individuality; Inflammation; Inflammatory Bowel Diseases; Informed Consent; Inpatients; Interdisciplinary Research; Internship and Residency; Intestine, Small; Kinetics; Laboratories; Leadership; Life Cycle Stages; Linezolid; Longitudinal Studies; Lung; Macrophages; Mass Spectrometry; Melanoma; Metabolome; Metabolomics; Metagenome; Metagenomics; Methicillin-Resistant Staphylococcus aureus; Microbial Sensitivity Tests; Microbiology; Microbiota; Microscopy; Microscopy, Fluorescence; Molecular Biology; Molecular Sequence Annotation; Morocco; Mutation; Myeloproliferative Disorders; Neoplasms; Nutrients; Obesity; Optical Imaging; Outcome Assessment, Health Care; Pandemics; Patient Discharge; Phage Therapy; Pilot Projects; Planets; Pneumonia; Precision Medicine; Premature Birth; Prevalence; Probiotics; Pseudomonas; Pseudomonas aeruginosa; Public Health; Pyocyanine; RNA; RNA, Ribosomal, 16S; Random Forest; Recommended Dietary Allowances; Reproducibility of Results; Research Personnel; Resilience, Psychological; Respiration; Respiration Disorders; Respiratory Mucosa; Respiratory System; Respiratory Tract Infections; Sequence Analysis, DNA; Sequence Analysis, RNA; Sewage; Sex Characteristics; Societies, Scientific; Sputum; Staphylococcal Infections; Staphylococcus; Staphylococcus aureus; Stenotrophomonas; Stenotrophomonas maltophilia; Stomach; Surface-Active Agents; Tamoxifen; Tetracycline; Transcriptome; Translational Research, Biomedical; Translational Science, Biomedical; Vaccine Efficacy; Vancomycin; Virome; Viruses; Volatile Organic Compounds; Volunteers; Wastewater; Wastewater-Based Epidemiological Monitoring; Western World; Young Adult; nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Wiles, Travis</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Animals, Genetically Modified; Animals, Wild; Anti-Bacterial Agents; Anti-Inflammatory Agents; Antioxidants; Bacteria; Bacterial Physiological Phenomena; Bacterial Proteins; Bacteriophages; Biological Evolution; Brain; Chromosomes; Climate Change; Computers; Curriculum; DNA Damage; Diabetes Mellitus; Disease Transmission, Infectious; Drug Resistance, Microbial; Ecology; Ecosystem; Environmental Pollutants; Escherichia coli; Evolution, Molecular; Feasibility Studies; Food Supply; Gastrointestinal Microbiome; Gastrointestinal Motility; Gene Flow; Gene Transfer, Horizontal; Genetic Engineering; Genetics; Germ-Free Life; Homeostasis; Host Microbial Interactions; Hyperglycemia; Imaging, Three-Dimensional; Immune System; Inflammation; Intestines; Macrophages; Metronidazole; Microbial Consortia; Microbiology; Microbiota; Montana; Motivation; Nitroreductases; Oxidation-Reduction; Peptides; Planets; Predatory Behavior; Public Health; Reactive Oxygen Species; SOS Response, Genetics; Soil; Symbiosis; Synthetic Biology; Systems Biology; Temperature; Ticks; Tissue Distribution; Type VI Secretion Systems; Vibrio cholerae; Virion; Zebrafish</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Wood, Marcelo</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Abortion, Induced; Acetyl Coenzyme A; Acetylation; Activin Receptors, Type I; Adverse Childhood Experiences; Aged; Aging; Alzheimer Disease; Amyloid beta-Peptides; Antibodies; Anxiety; Autism Spectrum Disorder; Blotting, Western; Brain; Brain-Derived Neurotrophic Factor; Calcium; Cannabinoids; Cannabis; Cardiovascular System; Censuses; Chin; Cholinergic Agents; Cholinergic Neurons; Chromatin; Chromatin Immunoprecipitation; Cocaine; Cocaine-Related Disorders; Cognition; Color Vision Defects; Conditioning, Operant; Cues; DNA; DNA Methylation; DNA-Binding Proteins; Delivery of Health Care; Depression; Dopamine Uptake Inhibitors; Dopaminergic Neurons; Drug-Seeking Behavior; Epigenesis, Genetic; Epigenetic Memory; Epigenomics; Gastrin-Secreting Cells; Gene Expression; Gene Expression Profiling; Gene Expression Regulation; Gene Regulatory Networks; Genes, X-Linked; Genetic Variation; Genetics; Genomics; Habenula; High-Throughput Nucleotide Sequencing; Hippocampus; Histone Code; Histone Deacetylases; Histones; Immunohistochemistry; Intellectual Disability; Interneurons; Jumonji Domain-Containing Histone Demethylases; Leucine Zippers; Life Change Events; Long-Term Potentiation; Longevity; Mass Spectrometry; Maternal Health; Medium Spiny Neurons; Memory; Memory Consolidation; Memory, Long-Term; Mental Health; Microglia; Multivariate Analysis; N-nitrosoiminodiacetic acid; Neoplasms; Neurodegenerative Diseases; Neurogenesis; Neuroglia; Neuroinflammatory Diseases; Neuronal Plasticity; Neurons; Neurosciences; Nicotine; Nucleosomes; Nucleus Accumbens; Occupations; Pharmaceutical Preparations; Physical Conditioning, Animal; Plaque, Amyloid; Point Mutation; Polyadenylation; Polymerase Chain Reaction; Pregnancy; Promoter Regions, Genetic; Proteomics; Psychiatry; Public Health; RNA, Catalytic; RNA, Messenger; RNA-Binding Proteins; Radiation Dose Hypofractionation; Radiotherapy Dosage; Recurrence; Reproducibility of Results; Resilience, Psychological; Reward; Schools; Self Administration; Self Report; Sequence Analysis, RNA; Spatial Memory; Speech; Substance-Related Disorders; Synapses; Synaptic Transmission; Trans-Activators; Transcription Factors; Transcriptome; Wood; X Chromosome; histone deacetylase 3; hydrogen sulfite; nan</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Xue, Katherine</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Bacteria; Coculture Techniques; Ecosystem; Gastrointestinal Microbiome; Microbiota; Phylogeny; Population Density; Ruminants</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Yassa, Michael</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Adolescent; Adverse Childhood Experiences; Age Factors; Aged; Aged, 80 and over; Aging; Alzheimer Disease; Amygdala; Amyloid; Amyloid beta-Peptides; Anhedonia; Aniline Compounds; Anniversaries and Special Events; Anxiety; Artificial Intelligence; Biological Specimen Banks; Biomarkers; Brain; Cerebral Small Vessel Diseases; Cerebrovascular Disorders; Child; Clinical Trials as Topic; Cognition; Cognitive Dysfunction; Cohort Studies; Community-Institutional Relations; Compulsive Behavior; Computational Biology; Computer Simulation; Consensus; Data Aggregation; Data Collection; Data Management; Data Science; Dementia; Depression; Discrimination, Psychological; Documentation; Down Syndrome; Drug Discovery; Ecosystem; Electrophysiological Phenomena; Emotions; Entorhinal Cortex; Exercise; Financial Management; Frontal Lobe; Gamma Rhythm; Head; Hippocampus; Hypoxia; Infant, Newborn; Interdisciplinary Research; Interneurons; Learning; Longitudinal Studies; Machine Learning; Magnetic Resonance Imaging; Memory; Memory Consolidation; Memory Disorders; Memory, Episodic; Mental Disorders; Mental Recall; Metadata; Midline Thalamic Nuclei; Motivation; Neocortex; Nervous System Diseases; Neural Pathways; Neuroimaging; Neurophysiology; Neuropsychological Tests; Neuropsychology; Nucleus Accumbens; Oceans and Seas; Pattern Recognition, Physiological; Peptide Fragments; Phenotype; Physicians; Policy; Polyethylene Terephthalates; Polysomnography; Positron-Emission Tomography; Prefrontal Cortex; Premature Birth; Primates; Prospective Studies; Proteostasis Deficiencies; Psychiatry; Publishing; Quality of Life; Reward; Risk Factors; Saliva; Sleep; Sleep Apnea, Obstructive; Software; Spectrum Analysis; Stress Disorders, Post-Traumatic; Surveys and Questionnaires; Temporal Lobe; Theta Rhythm; UK Biobank; Wakefulness; White Matter; Writing; Young Adult; tau Proteins</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002B87155CDAEBE54E8A991CDFF09FE870" ma:contentTypeVersion="21" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07d22f826efb92a1b7f7a52cdc9ab0c0">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ccd2e96c-ba06-41a4-9d14-ee5d4767a409" xmlns:ns3="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8f50f4dd1661db9c8120150ec829b0b2" ns2:_="" ns3:_="">
-    <xsd:import namespace="ccd2e96c-ba06-41a4-9d14-ee5d4767a409"/>
-    <xsd:import namespace="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns3:ProjectRole" minOccurs="0"/>
-                <xsd:element ref="ns3:Notes" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ccd2e96c-ba06-41a4-9d14-ee5d4767a409" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{5edd41bb-06d5-49d8-8697-11a388b6c936}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="ccd2e96c-ba06-41a4-9d14-ee5d4767a409">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="733ad1a4-bcb6-4664-8873-2816a39d1396" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="ProjectRole" ma:index="26" nillable="true" ma:displayName="Project Role" ma:format="Dropdown" ma:internalName="ProjectRole">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Choice">
-          <xsd:enumeration value="Senior/Key Person"/>
-          <xsd:enumeration value="Other Personnel"/>
-          <xsd:enumeration value="Advisory Board"/>
-          <xsd:enumeration value="Evaluator"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Notes" ma:index="27" nillable="true" ma:displayName="Notes" ma:format="Dropdown" ma:internalName="Notes">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ccd2e96c-ba06-41a4-9d14-ee5d4767a409" xsi:nil="true"/>
-    <ProjectRole xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" xsi:nil="true"/>
-    <Notes xmlns="b238fc39-fcbb-4f8c-bfd3-e3a789f7784e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39AEEB43-C0C1-467E-8FAE-78CD224749EF}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{186FE51F-7F5A-45A8-A4EF-7F2A48EF295E}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8ABD69C6-4EB8-4E7E-8E48-832888BF6EC4}"/>
 </file>